--- a/小语种考试营销雷达_数据模板_V2.xlsx
+++ b/小语种考试营销雷达_数据模板_V2.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12880"/>
+    <workbookView windowWidth="28800" windowHeight="12880" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="考试基础信息" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="421" uniqueCount="206">
   <si>
     <t>考试iD</t>
   </si>
@@ -80,7 +80,7 @@
     <t>日语</t>
   </si>
   <si>
-    <t>JLPT考试</t>
+    <t>JLPT</t>
   </si>
   <si>
     <t>每年2次</t>
@@ -120,7 +120,7 @@
     <t>韩语</t>
   </si>
   <si>
-    <t>TOPIK考试</t>
+    <t>TOPIK</t>
   </si>
   <si>
     <t>大陆地区一年2次，韩国地区</t>
@@ -148,7 +148,7 @@
     <t>德语</t>
   </si>
   <si>
-    <t>Goethe-Zertifikat歌德考试</t>
+    <t>歌德</t>
   </si>
   <si>
     <t>基本每月都有</t>
@@ -172,7 +172,7 @@
     <t>DE-德福</t>
   </si>
   <si>
-    <t>德福考试</t>
+    <t>德福</t>
   </si>
   <si>
     <t>大陆地区一年3次</t>
@@ -190,6 +190,39 @@
     <t>https://testdaf.neea.edu.cn/</t>
   </si>
   <si>
+    <t>JP-JLCT</t>
+  </si>
+  <si>
+    <t>JLCT</t>
+  </si>
+  <si>
+    <t>每年12次</t>
+  </si>
+  <si>
+    <t>每月都有</t>
+  </si>
+  <si>
+    <t>考后3天</t>
+  </si>
+  <si>
+    <t>新通是考点</t>
+  </si>
+  <si>
+    <t>FR-TCF/TEF</t>
+  </si>
+  <si>
+    <t>法语</t>
+  </si>
+  <si>
+    <t>TCF/TEF</t>
+  </si>
+  <si>
+    <t>考后立马</t>
+  </si>
+  <si>
+    <t>算了</t>
+  </si>
+  <si>
     <t>记录ID</t>
   </si>
   <si>
@@ -247,9 +280,6 @@
     <t>JP-JLPT-2026-07</t>
   </si>
   <si>
-    <t>JLPT</t>
-  </si>
-  <si>
     <t>2026年7月场</t>
   </si>
   <si>
@@ -274,30 +304,33 @@
     <t>KR-TOPIK</t>
   </si>
   <si>
-    <t>TOPIK</t>
-  </si>
-  <si>
     <t>2026年10月场</t>
   </si>
   <si>
     <t>DE-德福-2026-11</t>
   </si>
   <si>
-    <t>德福</t>
-  </si>
-  <si>
     <t>2026年11月场</t>
   </si>
   <si>
     <t>DE-歌德-2026-8</t>
   </si>
   <si>
-    <t>歌德</t>
-  </si>
-  <si>
     <t>2026年8月北京场</t>
   </si>
   <si>
+    <t>JP-JLCT-2026-8</t>
+  </si>
+  <si>
+    <t>2026年8月场</t>
+  </si>
+  <si>
+    <t>FR-TCF/TEF-2026-9</t>
+  </si>
+  <si>
+    <t>2026年9月场</t>
+  </si>
+  <si>
     <t>规则ID</t>
   </si>
   <si>
@@ -340,7 +373,7 @@
     <t>🔴</t>
   </si>
   <si>
-    <t>排查目标学员；提醒提前准备注册资料；朋友圈预告</t>
+    <t>盘点系统目标学员；提醒提前准备注册资料；朋友圈预告</t>
   </si>
   <si>
     <t>R02</t>
@@ -358,7 +391,7 @@
     <t>R03</t>
   </si>
   <si>
-    <t>营销期</t>
+    <t>重点跟进</t>
   </si>
   <si>
     <t>🟡</t>
@@ -370,7 +403,7 @@
     <t>R04</t>
   </si>
   <si>
-    <t>强营销期</t>
+    <t>强跟进期</t>
   </si>
   <si>
     <t>重点客户私聊；群内提醒；朋友圈倒计时</t>
@@ -406,7 +439,7 @@
     <t>🔵</t>
   </si>
   <si>
-    <t>考前关怀；备考资料；铺垫考后升阶规划</t>
+    <t>考前关怀；备考资料；铺垫考后规划</t>
   </si>
   <si>
     <t>R09</t>
@@ -418,7 +451,7 @@
     <t>R10</t>
   </si>
   <si>
-    <t>考后承接期</t>
+    <t>考后复盘</t>
   </si>
   <si>
     <t>🟣</t>
@@ -514,24 +547,13 @@
     <t>⏰ {考试名称}今天开放报名</t>
   </si>
   <si>
-    <t>准备参加{考试场次}{考试名称}的同学注意啦～
-今天进入正式报名节点。
-建议提前确认考试级别、考点和报名信息。报名只是第一步，更重要的是根据距离考试的时间，把接下来的学习节奏安排清楚。
-具体安排请以官方最新通知为准。</t>
-  </si>
-  <si>
     <t>PYQ-PLAN-01</t>
   </si>
   <si>
     <t>专业规划型</t>
   </si>
   <si>
-    <t>{考试名称}报名后，学习计划怎么倒推？</t>
-  </si>
-  <si>
-    <t>考试时间一旦确定，学习规划就可以真正倒推：
-当前基础 → 目标等级 → 剩余时间 → 每周投入 → 阶段任务。
-相比“先学着看看”，有明确考试节点以后，学习节奏通常会清楚很多。</t>
+    <t>{考试名称}报名后，学习计划怎么准备？</t>
   </si>
   <si>
     <t>PYQ-LIGHT-01</t>
@@ -543,22 +565,15 @@
     <t>又到{考试名称}报名节点啦</t>
   </si>
   <si>
-    <t>最近也开始集中帮一些同学重新梳理{考试名称}学习计划。
-不同基础、不同目标、不同考试时间，学习节奏其实完全不一样。
-如果今年有考试计划，建议早点把自己的时间线确定下来～</t>
-  </si>
-  <si>
     <t>PYQ-SCORE-01</t>
   </si>
   <si>
+    <t>品宣型</t>
+  </si>
+  <si>
     <t>📣 {考试名称}出分日</t>
   </si>
   <si>
-    <t>{考试名称}迎来出分节点啦～
-无论这次成绩是否达到目标，都建议尽快复盘：哪些模块稳定、哪些需要补强、下一阶段目标是什么。
-成绩不是终点，更适合作为下一阶段学习规划的起点。</t>
-  </si>
-  <si>
     <t>配置类型</t>
   </si>
   <si>
@@ -578,9 +593,6 @@
   </si>
   <si>
     <t>俄语</t>
-  </si>
-  <si>
-    <t>法语</t>
   </si>
   <si>
     <t>其他</t>
@@ -1166,7 +1178,7 @@
     </border>
   </borders>
   <cellStyleXfs count="50">
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1315,7 +1327,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1330,6 +1342,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1819,6 +1834,7 @@
   <dimension ref="A1:M20"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
+    <col min="1" max="1" width="12.3676470588235" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
@@ -1902,7 +1918,7 @@
       <c r="J2" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="K2" s="9" t="s">
+      <c r="K2" s="10" t="s">
         <v>23</v>
       </c>
       <c r="L2" s="4" t="s">
@@ -1943,7 +1959,7 @@
       <c r="J3" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="K3" s="9" t="s">
+      <c r="K3" s="10" t="s">
         <v>34</v>
       </c>
       <c r="L3" s="4" t="s">
@@ -1994,7 +2010,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" ht="34" spans="1:13">
+    <row r="5" ht="17" spans="1:13">
       <c r="A5" s="4" t="s">
         <v>44</v>
       </c>
@@ -2025,41 +2041,89 @@
       <c r="J5" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="K5" s="9" t="s">
+      <c r="K5" s="10" t="s">
         <v>50</v>
       </c>
       <c r="L5" s="4"/>
-      <c r="M5" s="4"/>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="B6" s="4"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4"/>
-      <c r="I6" s="4"/>
-      <c r="J6" s="4"/>
+      <c r="M5" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" ht="17" spans="1:13">
+      <c r="A6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="G6" s="4">
+        <v>600</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>56</v>
+      </c>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
-      <c r="M6" s="4"/>
+      <c r="M6" s="4" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="7" ht="17" spans="1:13">
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4"/>
-      <c r="I7" s="4"/>
-      <c r="J7" s="4"/>
+      <c r="A7" t="s">
+        <v>57</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G7" s="4">
+        <v>1850</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>61</v>
+      </c>
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
-      <c r="M7" s="4"/>
-    </row>
-    <row r="8" ht="17" spans="1:13">
+      <c r="M7" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
       <c r="D8" s="4"/>
@@ -2073,7 +2137,7 @@
       <c r="L8" s="4"/>
       <c r="M8" s="4"/>
     </row>
-    <row r="9" ht="17" spans="1:13">
+    <row r="9" spans="1:13">
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>
@@ -2087,7 +2151,7 @@
       <c r="L9" s="4"/>
       <c r="M9" s="4"/>
     </row>
-    <row r="10" ht="17" spans="1:13">
+    <row r="10" spans="1:13">
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
@@ -2101,7 +2165,7 @@
       <c r="L10" s="4"/>
       <c r="M10" s="4"/>
     </row>
-    <row r="11" ht="17" spans="1:13">
+    <row r="11" spans="1:13">
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
@@ -2115,7 +2179,7 @@
       <c r="L11" s="4"/>
       <c r="M11" s="4"/>
     </row>
-    <row r="12" ht="17" spans="1:13">
+    <row r="12" spans="1:13">
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
       <c r="D12" s="4"/>
@@ -2129,7 +2193,7 @@
       <c r="L12" s="4"/>
       <c r="M12" s="4"/>
     </row>
-    <row r="13" ht="17" spans="1:13">
+    <row r="13" spans="1:13">
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
@@ -2143,7 +2207,7 @@
       <c r="L13" s="4"/>
       <c r="M13" s="4"/>
     </row>
-    <row r="14" ht="17" spans="1:13">
+    <row r="14" spans="1:13">
       <c r="B14" s="4"/>
       <c r="C14" s="4"/>
       <c r="D14" s="4"/>
@@ -2157,7 +2221,7 @@
       <c r="L14" s="4"/>
       <c r="M14" s="4"/>
     </row>
-    <row r="15" ht="17" spans="1:13">
+    <row r="15" spans="1:13">
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
@@ -2171,7 +2235,7 @@
       <c r="L15" s="4"/>
       <c r="M15" s="4"/>
     </row>
-    <row r="16" ht="17" spans="1:13">
+    <row r="16" spans="1:13">
       <c r="B16" s="4"/>
       <c r="C16" s="4"/>
       <c r="D16" s="4"/>
@@ -2185,7 +2249,7 @@
       <c r="L16" s="4"/>
       <c r="M16" s="4"/>
     </row>
-    <row r="17" ht="17" spans="2:13">
+    <row r="17" spans="2:13">
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
       <c r="D17" s="4"/>
@@ -2199,7 +2263,7 @@
       <c r="L17" s="4"/>
       <c r="M17" s="4"/>
     </row>
-    <row r="18" ht="17" spans="2:13">
+    <row r="18" spans="2:13">
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
       <c r="D18" s="4"/>
@@ -2213,7 +2277,7 @@
       <c r="L18" s="4"/>
       <c r="M18" s="4"/>
     </row>
-    <row r="19" ht="17" spans="2:13">
+    <row r="19" spans="2:13">
       <c r="B19" s="4"/>
       <c r="C19" s="4"/>
       <c r="D19" s="4"/>
@@ -2227,7 +2291,7 @@
       <c r="L19" s="4"/>
       <c r="M19" s="4"/>
     </row>
-    <row r="20" ht="17" spans="2:13">
+    <row r="20" spans="2:13">
       <c r="B20" s="4"/>
       <c r="C20" s="4"/>
       <c r="D20" s="4"/>
@@ -2243,7 +2307,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" sqref="M2:M500">
+    <dataValidation type="list" sqref="M2:M5 M6:M7 M8:M500">
       <formula1>"是,否"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2284,13 +2348,13 @@
   <sheetData>
     <row r="1" ht="17" spans="1:21">
       <c r="A1" s="2" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>1</v>
@@ -2299,57 +2363,57 @@
         <v>2</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="N1" s="2" t="s">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="O1" s="2" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="P1" s="2" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="Q1" s="2" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="R1" s="2" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="S1" s="2" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="T1" s="2" t="s">
         <v>12</v>
       </c>
       <c r="U1" s="2" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
     </row>
     <row r="2" ht="51" spans="1:21">
       <c r="A2" s="4" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="B2" s="4">
         <v>2026</v>
@@ -2361,56 +2425,56 @@
         <v>14</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>70</v>
+        <v>15</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="G2" s="4">
         <v>7</v>
       </c>
-      <c r="H2" s="6">
+      <c r="H2" s="7">
         <v>46153</v>
       </c>
-      <c r="I2" s="6">
+      <c r="I2" s="7">
         <v>46159</v>
       </c>
-      <c r="J2" s="6">
+      <c r="J2" s="7">
         <v>46164</v>
       </c>
-      <c r="K2" s="6">
+      <c r="K2" s="7">
         <v>46215</v>
       </c>
-      <c r="L2" s="6">
+      <c r="L2" s="7">
         <v>46247</v>
       </c>
-      <c r="M2" s="7">
+      <c r="M2" s="8">
         <v>46245</v>
       </c>
       <c r="N2" s="4" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="O2" s="4"/>
-      <c r="P2" s="8" t="s">
+      <c r="P2" s="9" t="s">
         <v>23</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="R2" s="4"/>
       <c r="S2" s="4" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="T2" s="4" t="s">
         <v>25</v>
       </c>
       <c r="U2" s="4" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
     </row>
     <row r="3" ht="51" spans="1:21">
       <c r="A3" s="4" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="B3" s="4">
         <v>2026</v>
@@ -2422,51 +2486,51 @@
         <v>14</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>70</v>
+        <v>15</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="G3" s="4">
         <v>12</v>
       </c>
-      <c r="H3" s="6">
+      <c r="H3" s="7">
         <v>46307</v>
       </c>
-      <c r="I3" s="6">
+      <c r="I3" s="7">
         <v>46313</v>
       </c>
-      <c r="J3" s="6">
+      <c r="J3" s="7">
         <v>46321</v>
       </c>
-      <c r="K3" s="6">
+      <c r="K3" s="7">
         <v>46366</v>
       </c>
-      <c r="L3" s="6">
+      <c r="L3" s="7">
         <v>46387</v>
       </c>
-      <c r="M3" s="7">
-        <v>46246</v>
+      <c r="M3" s="8">
+        <v>46245</v>
       </c>
       <c r="N3" s="4" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="O3" s="4"/>
-      <c r="P3" s="8" t="s">
+      <c r="P3" s="9" t="s">
         <v>23</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="R3" s="4"/>
       <c r="S3" s="4" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="T3" s="4" t="s">
         <v>25</v>
       </c>
       <c r="U3" s="4" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
     </row>
     <row r="4" ht="51" spans="1:21">
@@ -2477,62 +2541,62 @@
         <v>2026</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>27</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>79</v>
+        <v>28</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G4" s="4">
         <v>10</v>
       </c>
-      <c r="H4" s="6">
+      <c r="H4" s="7">
         <v>46216</v>
       </c>
-      <c r="I4" s="6">
+      <c r="I4" s="7">
         <v>46223</v>
       </c>
-      <c r="J4" s="6">
+      <c r="J4" s="7">
         <v>46231</v>
       </c>
-      <c r="K4" s="6">
+      <c r="K4" s="7">
         <v>46304</v>
       </c>
-      <c r="L4" s="6">
+      <c r="L4" s="7">
         <v>46307</v>
       </c>
-      <c r="M4" s="7">
-        <v>46247</v>
+      <c r="M4" s="8">
+        <v>46245</v>
       </c>
       <c r="N4" s="4" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="O4" s="4"/>
-      <c r="P4" s="8" t="s">
+      <c r="P4" s="9" t="s">
         <v>23</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="R4" s="4"/>
       <c r="S4" s="4" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="T4" s="4" t="s">
         <v>25</v>
       </c>
       <c r="U4" s="4" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
     </row>
     <row r="5" ht="17" spans="1:21">
       <c r="A5" s="4" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="B5" s="4">
         <v>2026</v>
@@ -2544,56 +2608,56 @@
         <v>36</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>82</v>
+        <v>45</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="G5" s="4">
         <v>11</v>
       </c>
-      <c r="H5" s="6">
+      <c r="H5" s="7">
         <v>46248</v>
       </c>
-      <c r="I5" s="6">
+      <c r="I5" s="7">
         <v>46254</v>
       </c>
-      <c r="J5" s="6">
+      <c r="J5" s="7">
         <v>46264</v>
       </c>
-      <c r="K5" s="6">
+      <c r="K5" s="7">
         <v>46333</v>
       </c>
-      <c r="L5" s="6">
+      <c r="L5" s="7">
         <v>46376</v>
       </c>
-      <c r="M5" s="7">
-        <v>46248</v>
+      <c r="M5" s="8">
+        <v>46245</v>
       </c>
       <c r="N5" s="4" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="O5" s="4"/>
       <c r="P5" s="4" t="s">
         <v>43</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="R5" s="4"/>
       <c r="S5" s="4" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="T5" s="4" t="s">
         <v>25</v>
       </c>
       <c r="U5" s="4" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
     </row>
     <row r="6" ht="17" spans="1:21">
       <c r="A6" s="4" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="B6" s="4">
         <v>2026</v>
@@ -2605,100 +2669,174 @@
         <v>36</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>85</v>
+        <v>37</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="G6" s="4">
         <v>8</v>
       </c>
-      <c r="H6" s="6">
+      <c r="H6" s="7">
         <v>46218</v>
       </c>
-      <c r="I6" s="6">
+      <c r="I6" s="7">
         <v>46223</v>
       </c>
-      <c r="J6" s="6">
+      <c r="J6" s="7">
         <v>46233</v>
       </c>
-      <c r="K6" s="6">
+      <c r="K6" s="7">
         <v>46241</v>
       </c>
-      <c r="L6" s="6">
+      <c r="L6" s="7">
         <v>46275</v>
       </c>
-      <c r="M6" s="7">
-        <v>46249</v>
+      <c r="M6" s="8">
+        <v>46245</v>
       </c>
       <c r="N6" s="4" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="O6" s="4"/>
-      <c r="P6" s="9" t="s">
+      <c r="P6" s="10" t="s">
         <v>50</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="R6" s="4"/>
       <c r="S6" s="4" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="T6" s="4" t="s">
         <v>25</v>
       </c>
       <c r="U6" s="4" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
     </row>
     <row r="7" ht="17" spans="1:21">
-      <c r="A7" s="4"/>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="6"/>
-      <c r="I7" s="6"/>
-      <c r="J7" s="6"/>
-      <c r="K7" s="6"/>
-      <c r="L7" s="6"/>
-      <c r="M7" s="6"/>
-      <c r="N7" s="4"/>
+      <c r="A7" t="s">
+        <v>94</v>
+      </c>
+      <c r="B7" s="4">
+        <v>2026</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="G7" s="4">
+        <v>8</v>
+      </c>
+      <c r="H7" s="7">
+        <v>46237</v>
+      </c>
+      <c r="I7" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="J7" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="K7" s="7">
+        <v>46259</v>
+      </c>
+      <c r="L7" s="7">
+        <v>46262</v>
+      </c>
+      <c r="M7" s="8">
+        <v>46245</v>
+      </c>
+      <c r="N7" s="4" t="s">
+        <v>82</v>
+      </c>
       <c r="O7" s="4"/>
-      <c r="P7" s="4"/>
-      <c r="Q7" s="4"/>
+      <c r="P7" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q7" s="4" t="s">
+        <v>83</v>
+      </c>
       <c r="R7" s="4"/>
-      <c r="S7" s="4"/>
-      <c r="T7" s="4"/>
-      <c r="U7" s="4"/>
+      <c r="S7" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="T7" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="U7" s="4" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="8" ht="17" spans="1:21">
-      <c r="A8" s="4"/>
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="6"/>
-      <c r="I8" s="6"/>
-      <c r="J8" s="6"/>
-      <c r="K8" s="6"/>
-      <c r="L8" s="6"/>
-      <c r="M8" s="6"/>
-      <c r="N8" s="4"/>
+      <c r="A8" t="s">
+        <v>96</v>
+      </c>
+      <c r="B8" s="4">
+        <v>2027</v>
+      </c>
+      <c r="C8" t="s">
+        <v>57</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="G8" s="4">
+        <v>9</v>
+      </c>
+      <c r="H8" s="7">
+        <v>46238</v>
+      </c>
+      <c r="I8" s="7">
+        <v>46239</v>
+      </c>
+      <c r="J8" s="7">
+        <v>46244</v>
+      </c>
+      <c r="K8" s="7">
+        <v>46285</v>
+      </c>
+      <c r="L8" s="7">
+        <v>46315</v>
+      </c>
+      <c r="M8" s="7">
+        <v>46246</v>
+      </c>
+      <c r="N8" s="4" t="s">
+        <v>82</v>
+      </c>
       <c r="O8" s="4"/>
       <c r="P8" s="4"/>
-      <c r="Q8" s="4"/>
+      <c r="Q8" s="4" t="s">
+        <v>83</v>
+      </c>
       <c r="R8" s="4"/>
-      <c r="S8" s="4"/>
-      <c r="T8" s="4"/>
-      <c r="U8" s="4"/>
-    </row>
-    <row r="9" ht="17" spans="1:21">
+      <c r="S8" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="T8" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="U8" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21">
       <c r="A9" s="4"/>
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
@@ -2706,14 +2844,14 @@
       <c r="E9" s="4"/>
       <c r="F9" s="4"/>
       <c r="G9" s="4"/>
-      <c r="H9" s="6"/>
-      <c r="I9" s="6"/>
-      <c r="J9" s="6"/>
-      <c r="K9" s="6"/>
-      <c r="L9" s="6"/>
-      <c r="M9" s="6"/>
+      <c r="H9" s="7"/>
+      <c r="I9" s="7"/>
+      <c r="J9" s="7"/>
+      <c r="K9" s="7"/>
+      <c r="L9" s="7"/>
+      <c r="M9" s="7"/>
       <c r="N9" s="4"/>
-      <c r="O9" s="8"/>
+      <c r="O9" s="9"/>
       <c r="P9" s="4"/>
       <c r="Q9" s="4"/>
       <c r="R9" s="4"/>
@@ -2721,7 +2859,7 @@
       <c r="T9" s="4"/>
       <c r="U9" s="4"/>
     </row>
-    <row r="10" ht="17" spans="1:21">
+    <row r="10" spans="1:21">
       <c r="A10" s="4"/>
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
@@ -2729,14 +2867,14 @@
       <c r="E10" s="4"/>
       <c r="F10" s="4"/>
       <c r="G10" s="4"/>
-      <c r="H10" s="6"/>
-      <c r="I10" s="6"/>
-      <c r="J10" s="6"/>
-      <c r="K10" s="6"/>
-      <c r="L10" s="6"/>
-      <c r="M10" s="6"/>
+      <c r="H10" s="7"/>
+      <c r="I10" s="7"/>
+      <c r="J10" s="7"/>
+      <c r="K10" s="7"/>
+      <c r="L10" s="7"/>
+      <c r="M10" s="7"/>
       <c r="N10" s="4"/>
-      <c r="O10" s="8"/>
+      <c r="O10" s="9"/>
       <c r="P10" s="4"/>
       <c r="Q10" s="4"/>
       <c r="R10" s="4"/>
@@ -2744,7 +2882,7 @@
       <c r="T10" s="4"/>
       <c r="U10" s="4"/>
     </row>
-    <row r="11" ht="17" spans="1:21">
+    <row r="11" spans="1:21">
       <c r="A11" s="4"/>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
@@ -2752,12 +2890,12 @@
       <c r="E11" s="4"/>
       <c r="F11" s="4"/>
       <c r="G11" s="4"/>
-      <c r="H11" s="6"/>
-      <c r="I11" s="6"/>
-      <c r="J11" s="6"/>
-      <c r="K11" s="6"/>
-      <c r="L11" s="6"/>
-      <c r="M11" s="6"/>
+      <c r="H11" s="7"/>
+      <c r="I11" s="7"/>
+      <c r="J11" s="7"/>
+      <c r="K11" s="7"/>
+      <c r="L11" s="7"/>
+      <c r="M11" s="7"/>
       <c r="N11" s="4"/>
       <c r="O11" s="4"/>
       <c r="P11" s="4"/>
@@ -2767,7 +2905,7 @@
       <c r="T11" s="4"/>
       <c r="U11" s="4"/>
     </row>
-    <row r="12" ht="17" spans="1:21">
+    <row r="12" spans="1:21">
       <c r="A12" s="4"/>
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
@@ -2775,12 +2913,12 @@
       <c r="E12" s="4"/>
       <c r="F12" s="4"/>
       <c r="G12" s="4"/>
-      <c r="H12" s="6"/>
-      <c r="I12" s="6"/>
-      <c r="J12" s="6"/>
-      <c r="K12" s="6"/>
-      <c r="L12" s="6"/>
-      <c r="M12" s="6"/>
+      <c r="H12" s="7"/>
+      <c r="I12" s="7"/>
+      <c r="J12" s="7"/>
+      <c r="K12" s="7"/>
+      <c r="L12" s="7"/>
+      <c r="M12" s="7"/>
       <c r="N12" s="4"/>
       <c r="O12" s="4"/>
       <c r="P12" s="4"/>
@@ -2790,7 +2928,7 @@
       <c r="T12" s="4"/>
       <c r="U12" s="4"/>
     </row>
-    <row r="13" ht="17" spans="1:21">
+    <row r="13" spans="1:21">
       <c r="A13" s="4"/>
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
@@ -2798,12 +2936,12 @@
       <c r="E13" s="4"/>
       <c r="F13" s="4"/>
       <c r="G13" s="4"/>
-      <c r="H13" s="6"/>
-      <c r="I13" s="6"/>
-      <c r="J13" s="6"/>
-      <c r="K13" s="6"/>
-      <c r="L13" s="6"/>
-      <c r="M13" s="6"/>
+      <c r="H13" s="7"/>
+      <c r="I13" s="7"/>
+      <c r="J13" s="7"/>
+      <c r="K13" s="7"/>
+      <c r="L13" s="7"/>
+      <c r="M13" s="7"/>
       <c r="N13" s="4"/>
       <c r="O13" s="4"/>
       <c r="P13" s="4"/>
@@ -2813,20 +2951,19 @@
       <c r="T13" s="4"/>
       <c r="U13" s="4"/>
     </row>
-    <row r="14" ht="17" spans="1:21">
-      <c r="A14" s="4"/>
+    <row r="14" spans="1:21">
       <c r="B14" s="4"/>
       <c r="C14" s="4"/>
       <c r="D14" s="4"/>
       <c r="E14" s="4"/>
       <c r="F14" s="4"/>
       <c r="G14" s="4"/>
-      <c r="H14" s="6"/>
-      <c r="I14" s="6"/>
-      <c r="J14" s="6"/>
-      <c r="K14" s="6"/>
-      <c r="L14" s="6"/>
-      <c r="M14" s="6"/>
+      <c r="H14" s="7"/>
+      <c r="I14" s="7"/>
+      <c r="J14" s="7"/>
+      <c r="K14" s="7"/>
+      <c r="L14" s="7"/>
+      <c r="M14" s="7"/>
       <c r="N14" s="4"/>
       <c r="O14" s="4"/>
       <c r="P14" s="4"/>
@@ -2836,7 +2973,7 @@
       <c r="T14" s="4"/>
       <c r="U14" s="4"/>
     </row>
-    <row r="15" ht="17" spans="1:21">
+    <row r="15" spans="1:21">
       <c r="A15" s="4"/>
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
@@ -2844,12 +2981,12 @@
       <c r="E15" s="4"/>
       <c r="F15" s="4"/>
       <c r="G15" s="4"/>
-      <c r="H15" s="6"/>
-      <c r="I15" s="6"/>
-      <c r="J15" s="6"/>
-      <c r="K15" s="6"/>
-      <c r="L15" s="6"/>
-      <c r="M15" s="6"/>
+      <c r="H15" s="7"/>
+      <c r="I15" s="7"/>
+      <c r="J15" s="7"/>
+      <c r="K15" s="7"/>
+      <c r="L15" s="7"/>
+      <c r="M15" s="7"/>
       <c r="N15" s="4"/>
       <c r="O15" s="4"/>
       <c r="P15" s="4"/>
@@ -2859,7 +2996,7 @@
       <c r="T15" s="4"/>
       <c r="U15" s="4"/>
     </row>
-    <row r="16" ht="17" spans="1:21">
+    <row r="16" spans="1:21">
       <c r="A16" s="4"/>
       <c r="B16" s="4"/>
       <c r="C16" s="4"/>
@@ -2867,12 +3004,12 @@
       <c r="E16" s="4"/>
       <c r="F16" s="4"/>
       <c r="G16" s="4"/>
-      <c r="H16" s="6"/>
-      <c r="I16" s="6"/>
-      <c r="J16" s="6"/>
-      <c r="K16" s="6"/>
-      <c r="L16" s="6"/>
-      <c r="M16" s="6"/>
+      <c r="H16" s="7"/>
+      <c r="I16" s="7"/>
+      <c r="J16" s="7"/>
+      <c r="K16" s="7"/>
+      <c r="L16" s="7"/>
+      <c r="M16" s="7"/>
       <c r="N16" s="4"/>
       <c r="O16" s="4"/>
       <c r="P16" s="4"/>
@@ -2882,7 +3019,7 @@
       <c r="T16" s="4"/>
       <c r="U16" s="4"/>
     </row>
-    <row r="17" ht="17" spans="1:21">
+    <row r="17" spans="1:21">
       <c r="A17" s="4"/>
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
@@ -2890,12 +3027,12 @@
       <c r="E17" s="4"/>
       <c r="F17" s="4"/>
       <c r="G17" s="4"/>
-      <c r="H17" s="6"/>
-      <c r="I17" s="6"/>
-      <c r="J17" s="6"/>
-      <c r="K17" s="6"/>
-      <c r="L17" s="6"/>
-      <c r="M17" s="6"/>
+      <c r="H17" s="7"/>
+      <c r="I17" s="7"/>
+      <c r="J17" s="7"/>
+      <c r="K17" s="7"/>
+      <c r="L17" s="7"/>
+      <c r="M17" s="7"/>
       <c r="N17" s="4"/>
       <c r="O17" s="4"/>
       <c r="P17" s="4"/>
@@ -2905,7 +3042,7 @@
       <c r="T17" s="4"/>
       <c r="U17" s="4"/>
     </row>
-    <row r="18" ht="17" spans="1:21">
+    <row r="18" spans="1:21">
       <c r="A18" s="4"/>
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
@@ -2913,12 +3050,12 @@
       <c r="E18" s="4"/>
       <c r="F18" s="4"/>
       <c r="G18" s="4"/>
-      <c r="H18" s="6"/>
-      <c r="I18" s="6"/>
-      <c r="J18" s="6"/>
-      <c r="K18" s="6"/>
-      <c r="L18" s="6"/>
-      <c r="M18" s="6"/>
+      <c r="H18" s="7"/>
+      <c r="I18" s="7"/>
+      <c r="J18" s="7"/>
+      <c r="K18" s="7"/>
+      <c r="L18" s="7"/>
+      <c r="M18" s="7"/>
       <c r="N18" s="4"/>
       <c r="O18" s="4"/>
       <c r="P18" s="4"/>
@@ -2928,7 +3065,7 @@
       <c r="T18" s="4"/>
       <c r="U18" s="4"/>
     </row>
-    <row r="19" ht="17" spans="1:21">
+    <row r="19" spans="1:21">
       <c r="A19" s="4"/>
       <c r="B19" s="4"/>
       <c r="C19" s="4"/>
@@ -2936,12 +3073,12 @@
       <c r="E19" s="4"/>
       <c r="F19" s="4"/>
       <c r="G19" s="4"/>
-      <c r="H19" s="6"/>
-      <c r="I19" s="6"/>
-      <c r="J19" s="6"/>
-      <c r="K19" s="6"/>
-      <c r="L19" s="6"/>
-      <c r="M19" s="6"/>
+      <c r="H19" s="7"/>
+      <c r="I19" s="7"/>
+      <c r="J19" s="7"/>
+      <c r="K19" s="7"/>
+      <c r="L19" s="7"/>
+      <c r="M19" s="7"/>
       <c r="N19" s="4"/>
       <c r="O19" s="4"/>
       <c r="P19" s="4"/>
@@ -2951,7 +3088,7 @@
       <c r="T19" s="4"/>
       <c r="U19" s="4"/>
     </row>
-    <row r="20" ht="17" spans="1:21">
+    <row r="20" spans="1:21">
       <c r="A20" s="4"/>
       <c r="B20" s="4"/>
       <c r="C20" s="4"/>
@@ -2959,12 +3096,12 @@
       <c r="E20" s="4"/>
       <c r="F20" s="4"/>
       <c r="G20" s="4"/>
-      <c r="H20" s="6"/>
-      <c r="I20" s="6"/>
-      <c r="J20" s="6"/>
-      <c r="K20" s="6"/>
-      <c r="L20" s="6"/>
-      <c r="M20" s="6"/>
+      <c r="H20" s="7"/>
+      <c r="I20" s="7"/>
+      <c r="J20" s="7"/>
+      <c r="K20" s="7"/>
+      <c r="L20" s="7"/>
+      <c r="M20" s="7"/>
       <c r="N20" s="4"/>
       <c r="O20" s="4"/>
       <c r="P20" s="4"/>
@@ -2974,7 +3111,7 @@
       <c r="T20" s="4"/>
       <c r="U20" s="4"/>
     </row>
-    <row r="21" ht="17" spans="1:21">
+    <row r="21" spans="1:21">
       <c r="A21" s="4"/>
       <c r="B21" s="4"/>
       <c r="C21" s="4"/>
@@ -2982,12 +3119,12 @@
       <c r="E21" s="4"/>
       <c r="F21" s="4"/>
       <c r="G21" s="4"/>
-      <c r="H21" s="6"/>
-      <c r="I21" s="6"/>
-      <c r="J21" s="6"/>
-      <c r="K21" s="6"/>
-      <c r="L21" s="6"/>
-      <c r="M21" s="6"/>
+      <c r="H21" s="7"/>
+      <c r="I21" s="7"/>
+      <c r="J21" s="7"/>
+      <c r="K21" s="7"/>
+      <c r="L21" s="7"/>
+      <c r="M21" s="7"/>
       <c r="N21" s="4"/>
       <c r="O21" s="4"/>
       <c r="P21" s="4"/>
@@ -2997,7 +3134,7 @@
       <c r="T21" s="4"/>
       <c r="U21" s="4"/>
     </row>
-    <row r="22" ht="17" spans="1:21">
+    <row r="22" spans="1:21">
       <c r="A22" s="4"/>
       <c r="B22" s="4"/>
       <c r="C22" s="4"/>
@@ -3005,12 +3142,12 @@
       <c r="E22" s="4"/>
       <c r="F22" s="4"/>
       <c r="G22" s="4"/>
-      <c r="H22" s="6"/>
-      <c r="I22" s="6"/>
-      <c r="J22" s="6"/>
-      <c r="K22" s="6"/>
-      <c r="L22" s="6"/>
-      <c r="M22" s="6"/>
+      <c r="H22" s="7"/>
+      <c r="I22" s="7"/>
+      <c r="J22" s="7"/>
+      <c r="K22" s="7"/>
+      <c r="L22" s="7"/>
+      <c r="M22" s="7"/>
       <c r="N22" s="4"/>
       <c r="O22" s="4"/>
       <c r="P22" s="4"/>
@@ -3020,7 +3157,7 @@
       <c r="T22" s="4"/>
       <c r="U22" s="4"/>
     </row>
-    <row r="23" ht="17" spans="1:21">
+    <row r="23" spans="1:21">
       <c r="A23" s="4"/>
       <c r="B23" s="4"/>
       <c r="C23" s="4"/>
@@ -3028,12 +3165,12 @@
       <c r="E23" s="4"/>
       <c r="F23" s="4"/>
       <c r="G23" s="4"/>
-      <c r="H23" s="6"/>
-      <c r="I23" s="6"/>
-      <c r="J23" s="6"/>
-      <c r="K23" s="6"/>
-      <c r="L23" s="6"/>
-      <c r="M23" s="6"/>
+      <c r="H23" s="7"/>
+      <c r="I23" s="7"/>
+      <c r="J23" s="7"/>
+      <c r="K23" s="7"/>
+      <c r="L23" s="7"/>
+      <c r="M23" s="7"/>
       <c r="N23" s="4"/>
       <c r="O23" s="4"/>
       <c r="P23" s="4"/>
@@ -3043,7 +3180,7 @@
       <c r="T23" s="4"/>
       <c r="U23" s="4"/>
     </row>
-    <row r="24" ht="17" spans="1:21">
+    <row r="24" spans="1:21">
       <c r="A24" s="4"/>
       <c r="B24" s="4"/>
       <c r="C24" s="4"/>
@@ -3051,12 +3188,12 @@
       <c r="E24" s="4"/>
       <c r="F24" s="4"/>
       <c r="G24" s="4"/>
-      <c r="H24" s="6"/>
-      <c r="I24" s="6"/>
-      <c r="J24" s="6"/>
-      <c r="K24" s="6"/>
-      <c r="L24" s="6"/>
-      <c r="M24" s="6"/>
+      <c r="H24" s="7"/>
+      <c r="I24" s="7"/>
+      <c r="J24" s="7"/>
+      <c r="K24" s="7"/>
+      <c r="L24" s="7"/>
+      <c r="M24" s="7"/>
       <c r="N24" s="4"/>
       <c r="O24" s="4"/>
       <c r="P24" s="4"/>
@@ -3066,7 +3203,7 @@
       <c r="T24" s="4"/>
       <c r="U24" s="4"/>
     </row>
-    <row r="25" ht="17" spans="1:21">
+    <row r="25" spans="1:21">
       <c r="A25" s="4"/>
       <c r="B25" s="4"/>
       <c r="C25" s="4"/>
@@ -3074,12 +3211,12 @@
       <c r="E25" s="4"/>
       <c r="F25" s="4"/>
       <c r="G25" s="4"/>
-      <c r="H25" s="6"/>
-      <c r="I25" s="6"/>
-      <c r="J25" s="6"/>
-      <c r="K25" s="6"/>
-      <c r="L25" s="6"/>
-      <c r="M25" s="6"/>
+      <c r="H25" s="7"/>
+      <c r="I25" s="7"/>
+      <c r="J25" s="7"/>
+      <c r="K25" s="7"/>
+      <c r="L25" s="7"/>
+      <c r="M25" s="7"/>
       <c r="N25" s="4"/>
       <c r="O25" s="4"/>
       <c r="P25" s="4"/>
@@ -3089,7 +3226,7 @@
       <c r="T25" s="4"/>
       <c r="U25" s="4"/>
     </row>
-    <row r="26" ht="17" spans="1:21">
+    <row r="26" spans="1:21">
       <c r="A26" s="4"/>
       <c r="B26" s="4"/>
       <c r="C26" s="4"/>
@@ -3097,12 +3234,12 @@
       <c r="E26" s="4"/>
       <c r="F26" s="4"/>
       <c r="G26" s="4"/>
-      <c r="H26" s="6"/>
-      <c r="I26" s="6"/>
-      <c r="J26" s="6"/>
-      <c r="K26" s="6"/>
-      <c r="L26" s="6"/>
-      <c r="M26" s="6"/>
+      <c r="H26" s="7"/>
+      <c r="I26" s="7"/>
+      <c r="J26" s="7"/>
+      <c r="K26" s="7"/>
+      <c r="L26" s="7"/>
+      <c r="M26" s="7"/>
       <c r="N26" s="4"/>
       <c r="O26" s="4"/>
       <c r="P26" s="4"/>
@@ -3112,7 +3249,7 @@
       <c r="T26" s="4"/>
       <c r="U26" s="4"/>
     </row>
-    <row r="27" ht="17" spans="1:21">
+    <row r="27" spans="1:21">
       <c r="A27" s="4"/>
       <c r="B27" s="4"/>
       <c r="C27" s="4"/>
@@ -3120,12 +3257,12 @@
       <c r="E27" s="4"/>
       <c r="F27" s="4"/>
       <c r="G27" s="4"/>
-      <c r="H27" s="6"/>
-      <c r="I27" s="6"/>
-      <c r="J27" s="6"/>
-      <c r="K27" s="6"/>
-      <c r="L27" s="6"/>
-      <c r="M27" s="6"/>
+      <c r="H27" s="7"/>
+      <c r="I27" s="7"/>
+      <c r="J27" s="7"/>
+      <c r="K27" s="7"/>
+      <c r="L27" s="7"/>
+      <c r="M27" s="7"/>
       <c r="N27" s="4"/>
       <c r="O27" s="4"/>
       <c r="P27" s="4"/>
@@ -3135,7 +3272,7 @@
       <c r="T27" s="4"/>
       <c r="U27" s="4"/>
     </row>
-    <row r="28" ht="17" spans="1:21">
+    <row r="28" spans="1:21">
       <c r="A28" s="4"/>
       <c r="B28" s="4"/>
       <c r="C28" s="4"/>
@@ -3143,12 +3280,12 @@
       <c r="E28" s="4"/>
       <c r="F28" s="4"/>
       <c r="G28" s="4"/>
-      <c r="H28" s="6"/>
-      <c r="I28" s="6"/>
-      <c r="J28" s="6"/>
-      <c r="K28" s="6"/>
-      <c r="L28" s="6"/>
-      <c r="M28" s="6"/>
+      <c r="H28" s="7"/>
+      <c r="I28" s="7"/>
+      <c r="J28" s="7"/>
+      <c r="K28" s="7"/>
+      <c r="L28" s="7"/>
+      <c r="M28" s="7"/>
       <c r="N28" s="4"/>
       <c r="O28" s="4"/>
       <c r="P28" s="4"/>
@@ -3158,7 +3295,7 @@
       <c r="T28" s="4"/>
       <c r="U28" s="4"/>
     </row>
-    <row r="29" ht="17" spans="1:21">
+    <row r="29" spans="1:21">
       <c r="A29" s="4"/>
       <c r="B29" s="4"/>
       <c r="C29" s="4"/>
@@ -3166,12 +3303,12 @@
       <c r="E29" s="4"/>
       <c r="F29" s="4"/>
       <c r="G29" s="4"/>
-      <c r="H29" s="6"/>
-      <c r="I29" s="6"/>
-      <c r="J29" s="6"/>
-      <c r="K29" s="6"/>
-      <c r="L29" s="6"/>
-      <c r="M29" s="6"/>
+      <c r="H29" s="7"/>
+      <c r="I29" s="7"/>
+      <c r="J29" s="7"/>
+      <c r="K29" s="7"/>
+      <c r="L29" s="7"/>
+      <c r="M29" s="7"/>
       <c r="N29" s="4"/>
       <c r="O29" s="4"/>
       <c r="P29" s="4"/>
@@ -3181,7 +3318,7 @@
       <c r="T29" s="4"/>
       <c r="U29" s="4"/>
     </row>
-    <row r="30" ht="17" spans="1:21">
+    <row r="30" spans="1:21">
       <c r="A30" s="4"/>
       <c r="B30" s="4"/>
       <c r="C30" s="4"/>
@@ -3189,12 +3326,12 @@
       <c r="E30" s="4"/>
       <c r="F30" s="4"/>
       <c r="G30" s="4"/>
-      <c r="H30" s="6"/>
-      <c r="I30" s="6"/>
-      <c r="J30" s="6"/>
-      <c r="K30" s="6"/>
-      <c r="L30" s="6"/>
-      <c r="M30" s="6"/>
+      <c r="H30" s="7"/>
+      <c r="I30" s="7"/>
+      <c r="J30" s="7"/>
+      <c r="K30" s="7"/>
+      <c r="L30" s="7"/>
+      <c r="M30" s="7"/>
       <c r="N30" s="4"/>
       <c r="O30" s="4"/>
       <c r="P30" s="4"/>
@@ -3204,7 +3341,7 @@
       <c r="T30" s="4"/>
       <c r="U30" s="4"/>
     </row>
-    <row r="31" ht="17" spans="1:21">
+    <row r="31" spans="1:21">
       <c r="A31" s="4"/>
       <c r="B31" s="4"/>
       <c r="C31" s="4"/>
@@ -3212,12 +3349,12 @@
       <c r="E31" s="4"/>
       <c r="F31" s="4"/>
       <c r="G31" s="4"/>
-      <c r="H31" s="6"/>
-      <c r="I31" s="6"/>
-      <c r="J31" s="6"/>
-      <c r="K31" s="6"/>
-      <c r="L31" s="6"/>
-      <c r="M31" s="6"/>
+      <c r="H31" s="7"/>
+      <c r="I31" s="7"/>
+      <c r="J31" s="7"/>
+      <c r="K31" s="7"/>
+      <c r="L31" s="7"/>
+      <c r="M31" s="7"/>
       <c r="N31" s="4"/>
       <c r="O31" s="4"/>
       <c r="P31" s="4"/>
@@ -3227,7 +3364,7 @@
       <c r="T31" s="4"/>
       <c r="U31" s="4"/>
     </row>
-    <row r="32" ht="17" spans="1:21">
+    <row r="32" spans="1:21">
       <c r="A32" s="4"/>
       <c r="B32" s="4"/>
       <c r="C32" s="4"/>
@@ -3235,12 +3372,12 @@
       <c r="E32" s="4"/>
       <c r="F32" s="4"/>
       <c r="G32" s="4"/>
-      <c r="H32" s="6"/>
-      <c r="I32" s="6"/>
-      <c r="J32" s="6"/>
-      <c r="K32" s="6"/>
-      <c r="L32" s="6"/>
-      <c r="M32" s="6"/>
+      <c r="H32" s="7"/>
+      <c r="I32" s="7"/>
+      <c r="J32" s="7"/>
+      <c r="K32" s="7"/>
+      <c r="L32" s="7"/>
+      <c r="M32" s="7"/>
       <c r="N32" s="4"/>
       <c r="O32" s="4"/>
       <c r="P32" s="4"/>
@@ -3250,7 +3387,7 @@
       <c r="T32" s="4"/>
       <c r="U32" s="4"/>
     </row>
-    <row r="33" ht="17" spans="1:21">
+    <row r="33" spans="1:21">
       <c r="A33" s="4"/>
       <c r="B33" s="4"/>
       <c r="C33" s="4"/>
@@ -3258,12 +3395,12 @@
       <c r="E33" s="4"/>
       <c r="F33" s="4"/>
       <c r="G33" s="4"/>
-      <c r="H33" s="6"/>
-      <c r="I33" s="6"/>
-      <c r="J33" s="6"/>
-      <c r="K33" s="6"/>
-      <c r="L33" s="6"/>
-      <c r="M33" s="6"/>
+      <c r="H33" s="7"/>
+      <c r="I33" s="7"/>
+      <c r="J33" s="7"/>
+      <c r="K33" s="7"/>
+      <c r="L33" s="7"/>
+      <c r="M33" s="7"/>
       <c r="N33" s="4"/>
       <c r="O33" s="4"/>
       <c r="P33" s="4"/>
@@ -3273,7 +3410,7 @@
       <c r="T33" s="4"/>
       <c r="U33" s="4"/>
     </row>
-    <row r="34" ht="17" spans="1:21">
+    <row r="34" spans="1:21">
       <c r="A34" s="4"/>
       <c r="B34" s="4"/>
       <c r="C34" s="4"/>
@@ -3281,12 +3418,12 @@
       <c r="E34" s="4"/>
       <c r="F34" s="4"/>
       <c r="G34" s="4"/>
-      <c r="H34" s="6"/>
-      <c r="I34" s="6"/>
-      <c r="J34" s="6"/>
-      <c r="K34" s="6"/>
-      <c r="L34" s="6"/>
-      <c r="M34" s="6"/>
+      <c r="H34" s="7"/>
+      <c r="I34" s="7"/>
+      <c r="J34" s="7"/>
+      <c r="K34" s="7"/>
+      <c r="L34" s="7"/>
+      <c r="M34" s="7"/>
       <c r="N34" s="4"/>
       <c r="O34" s="4"/>
       <c r="P34" s="4"/>
@@ -3296,7 +3433,7 @@
       <c r="T34" s="4"/>
       <c r="U34" s="4"/>
     </row>
-    <row r="35" ht="17" spans="1:21">
+    <row r="35" spans="1:21">
       <c r="A35" s="4"/>
       <c r="B35" s="4"/>
       <c r="C35" s="4"/>
@@ -3304,12 +3441,12 @@
       <c r="E35" s="4"/>
       <c r="F35" s="4"/>
       <c r="G35" s="4"/>
-      <c r="H35" s="6"/>
-      <c r="I35" s="6"/>
-      <c r="J35" s="6"/>
-      <c r="K35" s="6"/>
-      <c r="L35" s="6"/>
-      <c r="M35" s="6"/>
+      <c r="H35" s="7"/>
+      <c r="I35" s="7"/>
+      <c r="J35" s="7"/>
+      <c r="K35" s="7"/>
+      <c r="L35" s="7"/>
+      <c r="M35" s="7"/>
       <c r="N35" s="4"/>
       <c r="O35" s="4"/>
       <c r="P35" s="4"/>
@@ -3319,7 +3456,7 @@
       <c r="T35" s="4"/>
       <c r="U35" s="4"/>
     </row>
-    <row r="36" ht="17" spans="1:21">
+    <row r="36" spans="1:21">
       <c r="A36" s="4"/>
       <c r="B36" s="4"/>
       <c r="C36" s="4"/>
@@ -3327,12 +3464,12 @@
       <c r="E36" s="4"/>
       <c r="F36" s="4"/>
       <c r="G36" s="4"/>
-      <c r="H36" s="6"/>
-      <c r="I36" s="6"/>
-      <c r="J36" s="6"/>
-      <c r="K36" s="6"/>
-      <c r="L36" s="6"/>
-      <c r="M36" s="6"/>
+      <c r="H36" s="7"/>
+      <c r="I36" s="7"/>
+      <c r="J36" s="7"/>
+      <c r="K36" s="7"/>
+      <c r="L36" s="7"/>
+      <c r="M36" s="7"/>
       <c r="N36" s="4"/>
       <c r="O36" s="4"/>
       <c r="P36" s="4"/>
@@ -3342,7 +3479,7 @@
       <c r="T36" s="4"/>
       <c r="U36" s="4"/>
     </row>
-    <row r="37" ht="17" spans="1:21">
+    <row r="37" spans="1:21">
       <c r="A37" s="4"/>
       <c r="B37" s="4"/>
       <c r="C37" s="4"/>
@@ -3350,12 +3487,12 @@
       <c r="E37" s="4"/>
       <c r="F37" s="4"/>
       <c r="G37" s="4"/>
-      <c r="H37" s="6"/>
-      <c r="I37" s="6"/>
-      <c r="J37" s="6"/>
-      <c r="K37" s="6"/>
-      <c r="L37" s="6"/>
-      <c r="M37" s="6"/>
+      <c r="H37" s="7"/>
+      <c r="I37" s="7"/>
+      <c r="J37" s="7"/>
+      <c r="K37" s="7"/>
+      <c r="L37" s="7"/>
+      <c r="M37" s="7"/>
       <c r="N37" s="4"/>
       <c r="O37" s="4"/>
       <c r="P37" s="4"/>
@@ -3365,7 +3502,7 @@
       <c r="T37" s="4"/>
       <c r="U37" s="4"/>
     </row>
-    <row r="38" ht="17" spans="1:21">
+    <row r="38" spans="1:21">
       <c r="A38" s="4"/>
       <c r="B38" s="4"/>
       <c r="C38" s="4"/>
@@ -3373,12 +3510,12 @@
       <c r="E38" s="4"/>
       <c r="F38" s="4"/>
       <c r="G38" s="4"/>
-      <c r="H38" s="6"/>
-      <c r="I38" s="6"/>
-      <c r="J38" s="6"/>
-      <c r="K38" s="6"/>
-      <c r="L38" s="6"/>
-      <c r="M38" s="6"/>
+      <c r="H38" s="7"/>
+      <c r="I38" s="7"/>
+      <c r="J38" s="7"/>
+      <c r="K38" s="7"/>
+      <c r="L38" s="7"/>
+      <c r="M38" s="7"/>
       <c r="N38" s="4"/>
       <c r="O38" s="4"/>
       <c r="P38" s="4"/>
@@ -3388,7 +3525,7 @@
       <c r="T38" s="4"/>
       <c r="U38" s="4"/>
     </row>
-    <row r="39" ht="17" spans="1:21">
+    <row r="39" spans="1:21">
       <c r="A39" s="4"/>
       <c r="B39" s="4"/>
       <c r="C39" s="4"/>
@@ -3396,12 +3533,12 @@
       <c r="E39" s="4"/>
       <c r="F39" s="4"/>
       <c r="G39" s="4"/>
-      <c r="H39" s="6"/>
-      <c r="I39" s="6"/>
-      <c r="J39" s="6"/>
-      <c r="K39" s="6"/>
-      <c r="L39" s="6"/>
-      <c r="M39" s="6"/>
+      <c r="H39" s="7"/>
+      <c r="I39" s="7"/>
+      <c r="J39" s="7"/>
+      <c r="K39" s="7"/>
+      <c r="L39" s="7"/>
+      <c r="M39" s="7"/>
       <c r="N39" s="4"/>
       <c r="O39" s="4"/>
       <c r="P39" s="4"/>
@@ -3411,7 +3548,7 @@
       <c r="T39" s="4"/>
       <c r="U39" s="4"/>
     </row>
-    <row r="40" ht="17" spans="1:21">
+    <row r="40" spans="1:21">
       <c r="A40" s="4"/>
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
@@ -3419,12 +3556,12 @@
       <c r="E40" s="4"/>
       <c r="F40" s="4"/>
       <c r="G40" s="4"/>
-      <c r="H40" s="6"/>
-      <c r="I40" s="6"/>
-      <c r="J40" s="6"/>
-      <c r="K40" s="6"/>
-      <c r="L40" s="6"/>
-      <c r="M40" s="6"/>
+      <c r="H40" s="7"/>
+      <c r="I40" s="7"/>
+      <c r="J40" s="7"/>
+      <c r="K40" s="7"/>
+      <c r="L40" s="7"/>
+      <c r="M40" s="7"/>
       <c r="N40" s="4"/>
       <c r="O40" s="4"/>
       <c r="P40" s="4"/>
@@ -3434,7 +3571,7 @@
       <c r="T40" s="4"/>
       <c r="U40" s="4"/>
     </row>
-    <row r="41" ht="17" spans="1:21">
+    <row r="41" spans="1:21">
       <c r="A41" s="4"/>
       <c r="B41" s="4"/>
       <c r="C41" s="4"/>
@@ -3442,12 +3579,12 @@
       <c r="E41" s="4"/>
       <c r="F41" s="4"/>
       <c r="G41" s="4"/>
-      <c r="H41" s="6"/>
-      <c r="I41" s="6"/>
-      <c r="J41" s="6"/>
-      <c r="K41" s="6"/>
-      <c r="L41" s="6"/>
-      <c r="M41" s="6"/>
+      <c r="H41" s="7"/>
+      <c r="I41" s="7"/>
+      <c r="J41" s="7"/>
+      <c r="K41" s="7"/>
+      <c r="L41" s="7"/>
+      <c r="M41" s="7"/>
       <c r="N41" s="4"/>
       <c r="O41" s="4"/>
       <c r="P41" s="4"/>
@@ -3457,7 +3594,7 @@
       <c r="T41" s="4"/>
       <c r="U41" s="4"/>
     </row>
-    <row r="42" ht="17" spans="1:21">
+    <row r="42" spans="1:21">
       <c r="A42" s="4"/>
       <c r="B42" s="4"/>
       <c r="C42" s="4"/>
@@ -3465,12 +3602,12 @@
       <c r="E42" s="4"/>
       <c r="F42" s="4"/>
       <c r="G42" s="4"/>
-      <c r="H42" s="6"/>
-      <c r="I42" s="6"/>
-      <c r="J42" s="6"/>
-      <c r="K42" s="6"/>
-      <c r="L42" s="6"/>
-      <c r="M42" s="6"/>
+      <c r="H42" s="7"/>
+      <c r="I42" s="7"/>
+      <c r="J42" s="7"/>
+      <c r="K42" s="7"/>
+      <c r="L42" s="7"/>
+      <c r="M42" s="7"/>
       <c r="N42" s="4"/>
       <c r="O42" s="4"/>
       <c r="P42" s="4"/>
@@ -3480,7 +3617,7 @@
       <c r="T42" s="4"/>
       <c r="U42" s="4"/>
     </row>
-    <row r="43" ht="17" spans="1:21">
+    <row r="43" spans="1:21">
       <c r="A43" s="4"/>
       <c r="B43" s="4"/>
       <c r="C43" s="4"/>
@@ -3488,12 +3625,12 @@
       <c r="E43" s="4"/>
       <c r="F43" s="4"/>
       <c r="G43" s="4"/>
-      <c r="H43" s="6"/>
-      <c r="I43" s="6"/>
-      <c r="J43" s="6"/>
-      <c r="K43" s="6"/>
-      <c r="L43" s="6"/>
-      <c r="M43" s="6"/>
+      <c r="H43" s="7"/>
+      <c r="I43" s="7"/>
+      <c r="J43" s="7"/>
+      <c r="K43" s="7"/>
+      <c r="L43" s="7"/>
+      <c r="M43" s="7"/>
       <c r="N43" s="4"/>
       <c r="O43" s="4"/>
       <c r="P43" s="4"/>
@@ -3503,7 +3640,7 @@
       <c r="T43" s="4"/>
       <c r="U43" s="4"/>
     </row>
-    <row r="44" ht="17" spans="1:21">
+    <row r="44" spans="1:21">
       <c r="A44" s="4"/>
       <c r="B44" s="4"/>
       <c r="C44" s="4"/>
@@ -3511,12 +3648,12 @@
       <c r="E44" s="4"/>
       <c r="F44" s="4"/>
       <c r="G44" s="4"/>
-      <c r="H44" s="6"/>
-      <c r="I44" s="6"/>
-      <c r="J44" s="6"/>
-      <c r="K44" s="6"/>
-      <c r="L44" s="6"/>
-      <c r="M44" s="6"/>
+      <c r="H44" s="7"/>
+      <c r="I44" s="7"/>
+      <c r="J44" s="7"/>
+      <c r="K44" s="7"/>
+      <c r="L44" s="7"/>
+      <c r="M44" s="7"/>
       <c r="N44" s="4"/>
       <c r="O44" s="4"/>
       <c r="P44" s="4"/>
@@ -3526,7 +3663,7 @@
       <c r="T44" s="4"/>
       <c r="U44" s="4"/>
     </row>
-    <row r="45" ht="17" spans="1:21">
+    <row r="45" spans="1:21">
       <c r="A45" s="4"/>
       <c r="B45" s="4"/>
       <c r="C45" s="4"/>
@@ -3534,12 +3671,12 @@
       <c r="E45" s="4"/>
       <c r="F45" s="4"/>
       <c r="G45" s="4"/>
-      <c r="H45" s="6"/>
-      <c r="I45" s="6"/>
-      <c r="J45" s="6"/>
-      <c r="K45" s="6"/>
-      <c r="L45" s="6"/>
-      <c r="M45" s="6"/>
+      <c r="H45" s="7"/>
+      <c r="I45" s="7"/>
+      <c r="J45" s="7"/>
+      <c r="K45" s="7"/>
+      <c r="L45" s="7"/>
+      <c r="M45" s="7"/>
       <c r="N45" s="4"/>
       <c r="O45" s="4"/>
       <c r="P45" s="4"/>
@@ -3549,7 +3686,7 @@
       <c r="T45" s="4"/>
       <c r="U45" s="4"/>
     </row>
-    <row r="46" ht="17" spans="1:21">
+    <row r="46" spans="1:21">
       <c r="A46" s="4"/>
       <c r="B46" s="4"/>
       <c r="C46" s="4"/>
@@ -3557,12 +3694,12 @@
       <c r="E46" s="4"/>
       <c r="F46" s="4"/>
       <c r="G46" s="4"/>
-      <c r="H46" s="6"/>
-      <c r="I46" s="6"/>
-      <c r="J46" s="6"/>
-      <c r="K46" s="6"/>
-      <c r="L46" s="6"/>
-      <c r="M46" s="6"/>
+      <c r="H46" s="7"/>
+      <c r="I46" s="7"/>
+      <c r="J46" s="7"/>
+      <c r="K46" s="7"/>
+      <c r="L46" s="7"/>
+      <c r="M46" s="7"/>
       <c r="N46" s="4"/>
       <c r="O46" s="4"/>
       <c r="P46" s="4"/>
@@ -3572,7 +3709,7 @@
       <c r="T46" s="4"/>
       <c r="U46" s="4"/>
     </row>
-    <row r="47" ht="17" spans="1:21">
+    <row r="47" spans="1:21">
       <c r="A47" s="4"/>
       <c r="B47" s="4"/>
       <c r="C47" s="4"/>
@@ -3580,12 +3717,12 @@
       <c r="E47" s="4"/>
       <c r="F47" s="4"/>
       <c r="G47" s="4"/>
-      <c r="H47" s="6"/>
-      <c r="I47" s="6"/>
-      <c r="J47" s="6"/>
-      <c r="K47" s="6"/>
-      <c r="L47" s="6"/>
-      <c r="M47" s="6"/>
+      <c r="H47" s="7"/>
+      <c r="I47" s="7"/>
+      <c r="J47" s="7"/>
+      <c r="K47" s="7"/>
+      <c r="L47" s="7"/>
+      <c r="M47" s="7"/>
       <c r="N47" s="4"/>
       <c r="O47" s="4"/>
       <c r="P47" s="4"/>
@@ -3595,7 +3732,7 @@
       <c r="T47" s="4"/>
       <c r="U47" s="4"/>
     </row>
-    <row r="48" ht="17" spans="1:21">
+    <row r="48" spans="1:21">
       <c r="A48" s="4"/>
       <c r="B48" s="4"/>
       <c r="C48" s="4"/>
@@ -3603,12 +3740,12 @@
       <c r="E48" s="4"/>
       <c r="F48" s="4"/>
       <c r="G48" s="4"/>
-      <c r="H48" s="6"/>
-      <c r="I48" s="6"/>
-      <c r="J48" s="6"/>
-      <c r="K48" s="6"/>
-      <c r="L48" s="6"/>
-      <c r="M48" s="6"/>
+      <c r="H48" s="7"/>
+      <c r="I48" s="7"/>
+      <c r="J48" s="7"/>
+      <c r="K48" s="7"/>
+      <c r="L48" s="7"/>
+      <c r="M48" s="7"/>
       <c r="N48" s="4"/>
       <c r="O48" s="4"/>
       <c r="P48" s="4"/>
@@ -3618,7 +3755,7 @@
       <c r="T48" s="4"/>
       <c r="U48" s="4"/>
     </row>
-    <row r="49" ht="17" spans="1:21">
+    <row r="49" spans="1:21">
       <c r="A49" s="4"/>
       <c r="B49" s="4"/>
       <c r="C49" s="4"/>
@@ -3626,12 +3763,12 @@
       <c r="E49" s="4"/>
       <c r="F49" s="4"/>
       <c r="G49" s="4"/>
-      <c r="H49" s="6"/>
-      <c r="I49" s="6"/>
-      <c r="J49" s="6"/>
-      <c r="K49" s="6"/>
-      <c r="L49" s="6"/>
-      <c r="M49" s="6"/>
+      <c r="H49" s="7"/>
+      <c r="I49" s="7"/>
+      <c r="J49" s="7"/>
+      <c r="K49" s="7"/>
+      <c r="L49" s="7"/>
+      <c r="M49" s="7"/>
       <c r="N49" s="4"/>
       <c r="O49" s="4"/>
       <c r="P49" s="4"/>
@@ -3641,7 +3778,7 @@
       <c r="T49" s="4"/>
       <c r="U49" s="4"/>
     </row>
-    <row r="50" ht="17" spans="1:21">
+    <row r="50" spans="1:21">
       <c r="A50" s="4"/>
       <c r="B50" s="4"/>
       <c r="C50" s="4"/>
@@ -3649,12 +3786,12 @@
       <c r="E50" s="4"/>
       <c r="F50" s="4"/>
       <c r="G50" s="4"/>
-      <c r="H50" s="6"/>
-      <c r="I50" s="6"/>
-      <c r="J50" s="6"/>
-      <c r="K50" s="6"/>
-      <c r="L50" s="6"/>
-      <c r="M50" s="6"/>
+      <c r="H50" s="7"/>
+      <c r="I50" s="7"/>
+      <c r="J50" s="7"/>
+      <c r="K50" s="7"/>
+      <c r="L50" s="7"/>
+      <c r="M50" s="7"/>
       <c r="N50" s="4"/>
       <c r="O50" s="4"/>
       <c r="P50" s="4"/>
@@ -3665,3615 +3802,3615 @@
       <c r="U50" s="4"/>
     </row>
     <row r="51" spans="1:21">
-      <c r="H51" s="10"/>
-      <c r="I51" s="10"/>
-      <c r="J51" s="10"/>
-      <c r="K51" s="10"/>
-      <c r="L51" s="10"/>
-      <c r="M51" s="10"/>
+      <c r="H51" s="11"/>
+      <c r="I51" s="11"/>
+      <c r="J51" s="11"/>
+      <c r="K51" s="11"/>
+      <c r="L51" s="11"/>
+      <c r="M51" s="11"/>
     </row>
     <row r="52" spans="1:21">
-      <c r="H52" s="10"/>
-      <c r="I52" s="10"/>
-      <c r="J52" s="10"/>
-      <c r="K52" s="10"/>
-      <c r="L52" s="10"/>
-      <c r="M52" s="10"/>
+      <c r="H52" s="11"/>
+      <c r="I52" s="11"/>
+      <c r="J52" s="11"/>
+      <c r="K52" s="11"/>
+      <c r="L52" s="11"/>
+      <c r="M52" s="11"/>
     </row>
     <row r="53" spans="1:21">
-      <c r="H53" s="10"/>
-      <c r="I53" s="10"/>
-      <c r="J53" s="10"/>
-      <c r="K53" s="10"/>
-      <c r="L53" s="10"/>
-      <c r="M53" s="10"/>
+      <c r="H53" s="11"/>
+      <c r="I53" s="11"/>
+      <c r="J53" s="11"/>
+      <c r="K53" s="11"/>
+      <c r="L53" s="11"/>
+      <c r="M53" s="11"/>
     </row>
     <row r="54" spans="1:21">
-      <c r="H54" s="10"/>
-      <c r="I54" s="10"/>
-      <c r="J54" s="10"/>
-      <c r="K54" s="10"/>
-      <c r="L54" s="10"/>
-      <c r="M54" s="10"/>
+      <c r="H54" s="11"/>
+      <c r="I54" s="11"/>
+      <c r="J54" s="11"/>
+      <c r="K54" s="11"/>
+      <c r="L54" s="11"/>
+      <c r="M54" s="11"/>
     </row>
     <row r="55" spans="1:21">
-      <c r="H55" s="10"/>
-      <c r="I55" s="10"/>
-      <c r="J55" s="10"/>
-      <c r="K55" s="10"/>
-      <c r="L55" s="10"/>
-      <c r="M55" s="10"/>
+      <c r="H55" s="11"/>
+      <c r="I55" s="11"/>
+      <c r="J55" s="11"/>
+      <c r="K55" s="11"/>
+      <c r="L55" s="11"/>
+      <c r="M55" s="11"/>
     </row>
     <row r="56" spans="1:21">
-      <c r="H56" s="10"/>
-      <c r="I56" s="10"/>
-      <c r="J56" s="10"/>
-      <c r="K56" s="10"/>
-      <c r="L56" s="10"/>
-      <c r="M56" s="10"/>
+      <c r="H56" s="11"/>
+      <c r="I56" s="11"/>
+      <c r="J56" s="11"/>
+      <c r="K56" s="11"/>
+      <c r="L56" s="11"/>
+      <c r="M56" s="11"/>
     </row>
     <row r="57" spans="1:21">
-      <c r="H57" s="10"/>
-      <c r="I57" s="10"/>
-      <c r="J57" s="10"/>
-      <c r="K57" s="10"/>
-      <c r="L57" s="10"/>
-      <c r="M57" s="10"/>
+      <c r="H57" s="11"/>
+      <c r="I57" s="11"/>
+      <c r="J57" s="11"/>
+      <c r="K57" s="11"/>
+      <c r="L57" s="11"/>
+      <c r="M57" s="11"/>
     </row>
     <row r="58" spans="1:21">
-      <c r="H58" s="10"/>
-      <c r="I58" s="10"/>
-      <c r="J58" s="10"/>
-      <c r="K58" s="10"/>
-      <c r="L58" s="10"/>
-      <c r="M58" s="10"/>
+      <c r="H58" s="11"/>
+      <c r="I58" s="11"/>
+      <c r="J58" s="11"/>
+      <c r="K58" s="11"/>
+      <c r="L58" s="11"/>
+      <c r="M58" s="11"/>
     </row>
     <row r="59" spans="1:21">
-      <c r="H59" s="10"/>
-      <c r="I59" s="10"/>
-      <c r="J59" s="10"/>
-      <c r="K59" s="10"/>
-      <c r="L59" s="10"/>
-      <c r="M59" s="10"/>
+      <c r="H59" s="11"/>
+      <c r="I59" s="11"/>
+      <c r="J59" s="11"/>
+      <c r="K59" s="11"/>
+      <c r="L59" s="11"/>
+      <c r="M59" s="11"/>
     </row>
     <row r="60" spans="1:21">
-      <c r="H60" s="10"/>
-      <c r="I60" s="10"/>
-      <c r="J60" s="10"/>
-      <c r="K60" s="10"/>
-      <c r="L60" s="10"/>
-      <c r="M60" s="10"/>
+      <c r="H60" s="11"/>
+      <c r="I60" s="11"/>
+      <c r="J60" s="11"/>
+      <c r="K60" s="11"/>
+      <c r="L60" s="11"/>
+      <c r="M60" s="11"/>
     </row>
     <row r="61" spans="1:21">
-      <c r="H61" s="10"/>
-      <c r="I61" s="10"/>
-      <c r="J61" s="10"/>
-      <c r="K61" s="10"/>
-      <c r="L61" s="10"/>
-      <c r="M61" s="10"/>
+      <c r="H61" s="11"/>
+      <c r="I61" s="11"/>
+      <c r="J61" s="11"/>
+      <c r="K61" s="11"/>
+      <c r="L61" s="11"/>
+      <c r="M61" s="11"/>
     </row>
     <row r="62" spans="1:21">
-      <c r="H62" s="10"/>
-      <c r="I62" s="10"/>
-      <c r="J62" s="10"/>
-      <c r="K62" s="10"/>
-      <c r="L62" s="10"/>
-      <c r="M62" s="10"/>
+      <c r="H62" s="11"/>
+      <c r="I62" s="11"/>
+      <c r="J62" s="11"/>
+      <c r="K62" s="11"/>
+      <c r="L62" s="11"/>
+      <c r="M62" s="11"/>
     </row>
     <row r="63" spans="1:21">
-      <c r="H63" s="10"/>
-      <c r="I63" s="10"/>
-      <c r="J63" s="10"/>
-      <c r="K63" s="10"/>
-      <c r="L63" s="10"/>
-      <c r="M63" s="10"/>
+      <c r="H63" s="11"/>
+      <c r="I63" s="11"/>
+      <c r="J63" s="11"/>
+      <c r="K63" s="11"/>
+      <c r="L63" s="11"/>
+      <c r="M63" s="11"/>
     </row>
     <row r="64" spans="1:21">
-      <c r="H64" s="10"/>
-      <c r="I64" s="10"/>
-      <c r="J64" s="10"/>
-      <c r="K64" s="10"/>
-      <c r="L64" s="10"/>
-      <c r="M64" s="10"/>
+      <c r="H64" s="11"/>
+      <c r="I64" s="11"/>
+      <c r="J64" s="11"/>
+      <c r="K64" s="11"/>
+      <c r="L64" s="11"/>
+      <c r="M64" s="11"/>
     </row>
     <row r="65" spans="8:13">
-      <c r="H65" s="10"/>
-      <c r="I65" s="10"/>
-      <c r="J65" s="10"/>
-      <c r="K65" s="10"/>
-      <c r="L65" s="10"/>
-      <c r="M65" s="10"/>
+      <c r="H65" s="11"/>
+      <c r="I65" s="11"/>
+      <c r="J65" s="11"/>
+      <c r="K65" s="11"/>
+      <c r="L65" s="11"/>
+      <c r="M65" s="11"/>
     </row>
     <row r="66" spans="8:13">
-      <c r="H66" s="10"/>
-      <c r="I66" s="10"/>
-      <c r="J66" s="10"/>
-      <c r="K66" s="10"/>
-      <c r="L66" s="10"/>
-      <c r="M66" s="10"/>
+      <c r="H66" s="11"/>
+      <c r="I66" s="11"/>
+      <c r="J66" s="11"/>
+      <c r="K66" s="11"/>
+      <c r="L66" s="11"/>
+      <c r="M66" s="11"/>
     </row>
     <row r="67" spans="8:13">
-      <c r="H67" s="10"/>
-      <c r="I67" s="10"/>
-      <c r="J67" s="10"/>
-      <c r="K67" s="10"/>
-      <c r="L67" s="10"/>
-      <c r="M67" s="10"/>
+      <c r="H67" s="11"/>
+      <c r="I67" s="11"/>
+      <c r="J67" s="11"/>
+      <c r="K67" s="11"/>
+      <c r="L67" s="11"/>
+      <c r="M67" s="11"/>
     </row>
     <row r="68" spans="8:13">
-      <c r="H68" s="10"/>
-      <c r="I68" s="10"/>
-      <c r="J68" s="10"/>
-      <c r="K68" s="10"/>
-      <c r="L68" s="10"/>
-      <c r="M68" s="10"/>
+      <c r="H68" s="11"/>
+      <c r="I68" s="11"/>
+      <c r="J68" s="11"/>
+      <c r="K68" s="11"/>
+      <c r="L68" s="11"/>
+      <c r="M68" s="11"/>
     </row>
     <row r="69" spans="8:13">
-      <c r="H69" s="10"/>
-      <c r="I69" s="10"/>
-      <c r="J69" s="10"/>
-      <c r="K69" s="10"/>
-      <c r="L69" s="10"/>
-      <c r="M69" s="10"/>
+      <c r="H69" s="11"/>
+      <c r="I69" s="11"/>
+      <c r="J69" s="11"/>
+      <c r="K69" s="11"/>
+      <c r="L69" s="11"/>
+      <c r="M69" s="11"/>
     </row>
     <row r="70" spans="8:13">
-      <c r="H70" s="10"/>
-      <c r="I70" s="10"/>
-      <c r="J70" s="10"/>
-      <c r="K70" s="10"/>
-      <c r="L70" s="10"/>
-      <c r="M70" s="10"/>
+      <c r="H70" s="11"/>
+      <c r="I70" s="11"/>
+      <c r="J70" s="11"/>
+      <c r="K70" s="11"/>
+      <c r="L70" s="11"/>
+      <c r="M70" s="11"/>
     </row>
     <row r="71" spans="8:13">
-      <c r="H71" s="10"/>
-      <c r="I71" s="10"/>
-      <c r="J71" s="10"/>
-      <c r="K71" s="10"/>
-      <c r="L71" s="10"/>
-      <c r="M71" s="10"/>
+      <c r="H71" s="11"/>
+      <c r="I71" s="11"/>
+      <c r="J71" s="11"/>
+      <c r="K71" s="11"/>
+      <c r="L71" s="11"/>
+      <c r="M71" s="11"/>
     </row>
     <row r="72" spans="8:13">
-      <c r="H72" s="10"/>
-      <c r="I72" s="10"/>
-      <c r="J72" s="10"/>
-      <c r="K72" s="10"/>
-      <c r="L72" s="10"/>
-      <c r="M72" s="10"/>
+      <c r="H72" s="11"/>
+      <c r="I72" s="11"/>
+      <c r="J72" s="11"/>
+      <c r="K72" s="11"/>
+      <c r="L72" s="11"/>
+      <c r="M72" s="11"/>
     </row>
     <row r="73" spans="8:13">
-      <c r="H73" s="10"/>
-      <c r="I73" s="10"/>
-      <c r="J73" s="10"/>
-      <c r="K73" s="10"/>
-      <c r="L73" s="10"/>
-      <c r="M73" s="10"/>
+      <c r="H73" s="11"/>
+      <c r="I73" s="11"/>
+      <c r="J73" s="11"/>
+      <c r="K73" s="11"/>
+      <c r="L73" s="11"/>
+      <c r="M73" s="11"/>
     </row>
     <row r="74" spans="8:13">
-      <c r="H74" s="10"/>
-      <c r="I74" s="10"/>
-      <c r="J74" s="10"/>
-      <c r="K74" s="10"/>
-      <c r="L74" s="10"/>
-      <c r="M74" s="10"/>
+      <c r="H74" s="11"/>
+      <c r="I74" s="11"/>
+      <c r="J74" s="11"/>
+      <c r="K74" s="11"/>
+      <c r="L74" s="11"/>
+      <c r="M74" s="11"/>
     </row>
     <row r="75" spans="8:13">
-      <c r="H75" s="10"/>
-      <c r="I75" s="10"/>
-      <c r="J75" s="10"/>
-      <c r="K75" s="10"/>
-      <c r="L75" s="10"/>
-      <c r="M75" s="10"/>
+      <c r="H75" s="11"/>
+      <c r="I75" s="11"/>
+      <c r="J75" s="11"/>
+      <c r="K75" s="11"/>
+      <c r="L75" s="11"/>
+      <c r="M75" s="11"/>
     </row>
     <row r="76" spans="8:13">
-      <c r="H76" s="10"/>
-      <c r="I76" s="10"/>
-      <c r="J76" s="10"/>
-      <c r="K76" s="10"/>
-      <c r="L76" s="10"/>
-      <c r="M76" s="10"/>
+      <c r="H76" s="11"/>
+      <c r="I76" s="11"/>
+      <c r="J76" s="11"/>
+      <c r="K76" s="11"/>
+      <c r="L76" s="11"/>
+      <c r="M76" s="11"/>
     </row>
     <row r="77" spans="8:13">
-      <c r="H77" s="10"/>
-      <c r="I77" s="10"/>
-      <c r="J77" s="10"/>
-      <c r="K77" s="10"/>
-      <c r="L77" s="10"/>
-      <c r="M77" s="10"/>
+      <c r="H77" s="11"/>
+      <c r="I77" s="11"/>
+      <c r="J77" s="11"/>
+      <c r="K77" s="11"/>
+      <c r="L77" s="11"/>
+      <c r="M77" s="11"/>
     </row>
     <row r="78" spans="8:13">
-      <c r="H78" s="10"/>
-      <c r="I78" s="10"/>
-      <c r="J78" s="10"/>
-      <c r="K78" s="10"/>
-      <c r="L78" s="10"/>
-      <c r="M78" s="10"/>
+      <c r="H78" s="11"/>
+      <c r="I78" s="11"/>
+      <c r="J78" s="11"/>
+      <c r="K78" s="11"/>
+      <c r="L78" s="11"/>
+      <c r="M78" s="11"/>
     </row>
     <row r="79" spans="8:13">
-      <c r="H79" s="10"/>
-      <c r="I79" s="10"/>
-      <c r="J79" s="10"/>
-      <c r="K79" s="10"/>
-      <c r="L79" s="10"/>
-      <c r="M79" s="10"/>
+      <c r="H79" s="11"/>
+      <c r="I79" s="11"/>
+      <c r="J79" s="11"/>
+      <c r="K79" s="11"/>
+      <c r="L79" s="11"/>
+      <c r="M79" s="11"/>
     </row>
     <row r="80" spans="8:13">
-      <c r="H80" s="10"/>
-      <c r="I80" s="10"/>
-      <c r="J80" s="10"/>
-      <c r="K80" s="10"/>
-      <c r="L80" s="10"/>
-      <c r="M80" s="10"/>
+      <c r="H80" s="11"/>
+      <c r="I80" s="11"/>
+      <c r="J80" s="11"/>
+      <c r="K80" s="11"/>
+      <c r="L80" s="11"/>
+      <c r="M80" s="11"/>
     </row>
     <row r="81" spans="8:13">
-      <c r="H81" s="10"/>
-      <c r="I81" s="10"/>
-      <c r="J81" s="10"/>
-      <c r="K81" s="10"/>
-      <c r="L81" s="10"/>
-      <c r="M81" s="10"/>
+      <c r="H81" s="11"/>
+      <c r="I81" s="11"/>
+      <c r="J81" s="11"/>
+      <c r="K81" s="11"/>
+      <c r="L81" s="11"/>
+      <c r="M81" s="11"/>
     </row>
     <row r="82" spans="8:13">
-      <c r="H82" s="10"/>
-      <c r="I82" s="10"/>
-      <c r="J82" s="10"/>
-      <c r="K82" s="10"/>
-      <c r="L82" s="10"/>
-      <c r="M82" s="10"/>
+      <c r="H82" s="11"/>
+      <c r="I82" s="11"/>
+      <c r="J82" s="11"/>
+      <c r="K82" s="11"/>
+      <c r="L82" s="11"/>
+      <c r="M82" s="11"/>
     </row>
     <row r="83" spans="8:13">
-      <c r="H83" s="10"/>
-      <c r="I83" s="10"/>
-      <c r="J83" s="10"/>
-      <c r="K83" s="10"/>
-      <c r="L83" s="10"/>
-      <c r="M83" s="10"/>
+      <c r="H83" s="11"/>
+      <c r="I83" s="11"/>
+      <c r="J83" s="11"/>
+      <c r="K83" s="11"/>
+      <c r="L83" s="11"/>
+      <c r="M83" s="11"/>
     </row>
     <row r="84" spans="8:13">
-      <c r="H84" s="10"/>
-      <c r="I84" s="10"/>
-      <c r="J84" s="10"/>
-      <c r="K84" s="10"/>
-      <c r="L84" s="10"/>
-      <c r="M84" s="10"/>
+      <c r="H84" s="11"/>
+      <c r="I84" s="11"/>
+      <c r="J84" s="11"/>
+      <c r="K84" s="11"/>
+      <c r="L84" s="11"/>
+      <c r="M84" s="11"/>
     </row>
     <row r="85" spans="8:13">
-      <c r="H85" s="10"/>
-      <c r="I85" s="10"/>
-      <c r="J85" s="10"/>
-      <c r="K85" s="10"/>
-      <c r="L85" s="10"/>
-      <c r="M85" s="10"/>
+      <c r="H85" s="11"/>
+      <c r="I85" s="11"/>
+      <c r="J85" s="11"/>
+      <c r="K85" s="11"/>
+      <c r="L85" s="11"/>
+      <c r="M85" s="11"/>
     </row>
     <row r="86" spans="8:13">
-      <c r="H86" s="10"/>
-      <c r="I86" s="10"/>
-      <c r="J86" s="10"/>
-      <c r="K86" s="10"/>
-      <c r="L86" s="10"/>
-      <c r="M86" s="10"/>
+      <c r="H86" s="11"/>
+      <c r="I86" s="11"/>
+      <c r="J86" s="11"/>
+      <c r="K86" s="11"/>
+      <c r="L86" s="11"/>
+      <c r="M86" s="11"/>
     </row>
     <row r="87" spans="8:13">
-      <c r="H87" s="10"/>
-      <c r="I87" s="10"/>
-      <c r="J87" s="10"/>
-      <c r="K87" s="10"/>
-      <c r="L87" s="10"/>
-      <c r="M87" s="10"/>
+      <c r="H87" s="11"/>
+      <c r="I87" s="11"/>
+      <c r="J87" s="11"/>
+      <c r="K87" s="11"/>
+      <c r="L87" s="11"/>
+      <c r="M87" s="11"/>
     </row>
     <row r="88" spans="8:13">
-      <c r="H88" s="10"/>
-      <c r="I88" s="10"/>
-      <c r="J88" s="10"/>
-      <c r="K88" s="10"/>
-      <c r="L88" s="10"/>
-      <c r="M88" s="10"/>
+      <c r="H88" s="11"/>
+      <c r="I88" s="11"/>
+      <c r="J88" s="11"/>
+      <c r="K88" s="11"/>
+      <c r="L88" s="11"/>
+      <c r="M88" s="11"/>
     </row>
     <row r="89" spans="8:13">
-      <c r="H89" s="10"/>
-      <c r="I89" s="10"/>
-      <c r="J89" s="10"/>
-      <c r="K89" s="10"/>
-      <c r="L89" s="10"/>
-      <c r="M89" s="10"/>
+      <c r="H89" s="11"/>
+      <c r="I89" s="11"/>
+      <c r="J89" s="11"/>
+      <c r="K89" s="11"/>
+      <c r="L89" s="11"/>
+      <c r="M89" s="11"/>
     </row>
     <row r="90" spans="8:13">
-      <c r="H90" s="10"/>
-      <c r="I90" s="10"/>
-      <c r="J90" s="10"/>
-      <c r="K90" s="10"/>
-      <c r="L90" s="10"/>
-      <c r="M90" s="10"/>
+      <c r="H90" s="11"/>
+      <c r="I90" s="11"/>
+      <c r="J90" s="11"/>
+      <c r="K90" s="11"/>
+      <c r="L90" s="11"/>
+      <c r="M90" s="11"/>
     </row>
     <row r="91" spans="8:13">
-      <c r="H91" s="10"/>
-      <c r="I91" s="10"/>
-      <c r="J91" s="10"/>
-      <c r="K91" s="10"/>
-      <c r="L91" s="10"/>
-      <c r="M91" s="10"/>
+      <c r="H91" s="11"/>
+      <c r="I91" s="11"/>
+      <c r="J91" s="11"/>
+      <c r="K91" s="11"/>
+      <c r="L91" s="11"/>
+      <c r="M91" s="11"/>
     </row>
     <row r="92" spans="8:13">
-      <c r="H92" s="10"/>
-      <c r="I92" s="10"/>
-      <c r="J92" s="10"/>
-      <c r="K92" s="10"/>
-      <c r="L92" s="10"/>
-      <c r="M92" s="10"/>
+      <c r="H92" s="11"/>
+      <c r="I92" s="11"/>
+      <c r="J92" s="11"/>
+      <c r="K92" s="11"/>
+      <c r="L92" s="11"/>
+      <c r="M92" s="11"/>
     </row>
     <row r="93" spans="8:13">
-      <c r="H93" s="10"/>
-      <c r="I93" s="10"/>
-      <c r="J93" s="10"/>
-      <c r="K93" s="10"/>
-      <c r="L93" s="10"/>
-      <c r="M93" s="10"/>
+      <c r="H93" s="11"/>
+      <c r="I93" s="11"/>
+      <c r="J93" s="11"/>
+      <c r="K93" s="11"/>
+      <c r="L93" s="11"/>
+      <c r="M93" s="11"/>
     </row>
     <row r="94" spans="8:13">
-      <c r="H94" s="10"/>
-      <c r="I94" s="10"/>
-      <c r="J94" s="10"/>
-      <c r="K94" s="10"/>
-      <c r="L94" s="10"/>
-      <c r="M94" s="10"/>
+      <c r="H94" s="11"/>
+      <c r="I94" s="11"/>
+      <c r="J94" s="11"/>
+      <c r="K94" s="11"/>
+      <c r="L94" s="11"/>
+      <c r="M94" s="11"/>
     </row>
     <row r="95" spans="8:13">
-      <c r="H95" s="10"/>
-      <c r="I95" s="10"/>
-      <c r="J95" s="10"/>
-      <c r="K95" s="10"/>
-      <c r="L95" s="10"/>
-      <c r="M95" s="10"/>
+      <c r="H95" s="11"/>
+      <c r="I95" s="11"/>
+      <c r="J95" s="11"/>
+      <c r="K95" s="11"/>
+      <c r="L95" s="11"/>
+      <c r="M95" s="11"/>
     </row>
     <row r="96" spans="8:13">
-      <c r="H96" s="10"/>
-      <c r="I96" s="10"/>
-      <c r="J96" s="10"/>
-      <c r="K96" s="10"/>
-      <c r="L96" s="10"/>
-      <c r="M96" s="10"/>
+      <c r="H96" s="11"/>
+      <c r="I96" s="11"/>
+      <c r="J96" s="11"/>
+      <c r="K96" s="11"/>
+      <c r="L96" s="11"/>
+      <c r="M96" s="11"/>
     </row>
     <row r="97" spans="8:13">
-      <c r="H97" s="10"/>
-      <c r="I97" s="10"/>
-      <c r="J97" s="10"/>
-      <c r="K97" s="10"/>
-      <c r="L97" s="10"/>
-      <c r="M97" s="10"/>
+      <c r="H97" s="11"/>
+      <c r="I97" s="11"/>
+      <c r="J97" s="11"/>
+      <c r="K97" s="11"/>
+      <c r="L97" s="11"/>
+      <c r="M97" s="11"/>
     </row>
     <row r="98" spans="8:13">
-      <c r="H98" s="10"/>
-      <c r="I98" s="10"/>
-      <c r="J98" s="10"/>
-      <c r="K98" s="10"/>
-      <c r="L98" s="10"/>
-      <c r="M98" s="10"/>
+      <c r="H98" s="11"/>
+      <c r="I98" s="11"/>
+      <c r="J98" s="11"/>
+      <c r="K98" s="11"/>
+      <c r="L98" s="11"/>
+      <c r="M98" s="11"/>
     </row>
     <row r="99" spans="8:13">
-      <c r="H99" s="10"/>
-      <c r="I99" s="10"/>
-      <c r="J99" s="10"/>
-      <c r="K99" s="10"/>
-      <c r="L99" s="10"/>
-      <c r="M99" s="10"/>
+      <c r="H99" s="11"/>
+      <c r="I99" s="11"/>
+      <c r="J99" s="11"/>
+      <c r="K99" s="11"/>
+      <c r="L99" s="11"/>
+      <c r="M99" s="11"/>
     </row>
     <row r="100" spans="8:13">
-      <c r="H100" s="10"/>
-      <c r="I100" s="10"/>
-      <c r="J100" s="10"/>
-      <c r="K100" s="10"/>
-      <c r="L100" s="10"/>
-      <c r="M100" s="10"/>
+      <c r="H100" s="11"/>
+      <c r="I100" s="11"/>
+      <c r="J100" s="11"/>
+      <c r="K100" s="11"/>
+      <c r="L100" s="11"/>
+      <c r="M100" s="11"/>
     </row>
     <row r="101" spans="8:13">
-      <c r="H101" s="10"/>
-      <c r="I101" s="10"/>
-      <c r="J101" s="10"/>
-      <c r="K101" s="10"/>
-      <c r="L101" s="10"/>
-      <c r="M101" s="10"/>
+      <c r="H101" s="11"/>
+      <c r="I101" s="11"/>
+      <c r="J101" s="11"/>
+      <c r="K101" s="11"/>
+      <c r="L101" s="11"/>
+      <c r="M101" s="11"/>
     </row>
     <row r="102" spans="8:13">
-      <c r="H102" s="10"/>
-      <c r="I102" s="10"/>
-      <c r="J102" s="10"/>
-      <c r="K102" s="10"/>
-      <c r="L102" s="10"/>
-      <c r="M102" s="10"/>
+      <c r="H102" s="11"/>
+      <c r="I102" s="11"/>
+      <c r="J102" s="11"/>
+      <c r="K102" s="11"/>
+      <c r="L102" s="11"/>
+      <c r="M102" s="11"/>
     </row>
     <row r="103" spans="8:13">
-      <c r="H103" s="10"/>
-      <c r="I103" s="10"/>
-      <c r="J103" s="10"/>
-      <c r="K103" s="10"/>
-      <c r="L103" s="10"/>
-      <c r="M103" s="10"/>
+      <c r="H103" s="11"/>
+      <c r="I103" s="11"/>
+      <c r="J103" s="11"/>
+      <c r="K103" s="11"/>
+      <c r="L103" s="11"/>
+      <c r="M103" s="11"/>
     </row>
     <row r="104" spans="8:13">
-      <c r="H104" s="10"/>
-      <c r="I104" s="10"/>
-      <c r="J104" s="10"/>
-      <c r="K104" s="10"/>
-      <c r="L104" s="10"/>
-      <c r="M104" s="10"/>
+      <c r="H104" s="11"/>
+      <c r="I104" s="11"/>
+      <c r="J104" s="11"/>
+      <c r="K104" s="11"/>
+      <c r="L104" s="11"/>
+      <c r="M104" s="11"/>
     </row>
     <row r="105" spans="8:13">
-      <c r="H105" s="10"/>
-      <c r="I105" s="10"/>
-      <c r="J105" s="10"/>
-      <c r="K105" s="10"/>
-      <c r="L105" s="10"/>
-      <c r="M105" s="10"/>
+      <c r="H105" s="11"/>
+      <c r="I105" s="11"/>
+      <c r="J105" s="11"/>
+      <c r="K105" s="11"/>
+      <c r="L105" s="11"/>
+      <c r="M105" s="11"/>
     </row>
     <row r="106" spans="8:13">
-      <c r="H106" s="10"/>
-      <c r="I106" s="10"/>
-      <c r="J106" s="10"/>
-      <c r="K106" s="10"/>
-      <c r="L106" s="10"/>
-      <c r="M106" s="10"/>
+      <c r="H106" s="11"/>
+      <c r="I106" s="11"/>
+      <c r="J106" s="11"/>
+      <c r="K106" s="11"/>
+      <c r="L106" s="11"/>
+      <c r="M106" s="11"/>
     </row>
     <row r="107" spans="8:13">
-      <c r="H107" s="10"/>
-      <c r="I107" s="10"/>
-      <c r="J107" s="10"/>
-      <c r="K107" s="10"/>
-      <c r="L107" s="10"/>
-      <c r="M107" s="10"/>
+      <c r="H107" s="11"/>
+      <c r="I107" s="11"/>
+      <c r="J107" s="11"/>
+      <c r="K107" s="11"/>
+      <c r="L107" s="11"/>
+      <c r="M107" s="11"/>
     </row>
     <row r="108" spans="8:13">
-      <c r="H108" s="10"/>
-      <c r="I108" s="10"/>
-      <c r="J108" s="10"/>
-      <c r="K108" s="10"/>
-      <c r="L108" s="10"/>
-      <c r="M108" s="10"/>
+      <c r="H108" s="11"/>
+      <c r="I108" s="11"/>
+      <c r="J108" s="11"/>
+      <c r="K108" s="11"/>
+      <c r="L108" s="11"/>
+      <c r="M108" s="11"/>
     </row>
     <row r="109" spans="8:13">
-      <c r="H109" s="10"/>
-      <c r="I109" s="10"/>
-      <c r="J109" s="10"/>
-      <c r="K109" s="10"/>
-      <c r="L109" s="10"/>
-      <c r="M109" s="10"/>
+      <c r="H109" s="11"/>
+      <c r="I109" s="11"/>
+      <c r="J109" s="11"/>
+      <c r="K109" s="11"/>
+      <c r="L109" s="11"/>
+      <c r="M109" s="11"/>
     </row>
     <row r="110" spans="8:13">
-      <c r="H110" s="10"/>
-      <c r="I110" s="10"/>
-      <c r="J110" s="10"/>
-      <c r="K110" s="10"/>
-      <c r="L110" s="10"/>
-      <c r="M110" s="10"/>
+      <c r="H110" s="11"/>
+      <c r="I110" s="11"/>
+      <c r="J110" s="11"/>
+      <c r="K110" s="11"/>
+      <c r="L110" s="11"/>
+      <c r="M110" s="11"/>
     </row>
     <row r="111" spans="8:13">
-      <c r="H111" s="10"/>
-      <c r="I111" s="10"/>
-      <c r="J111" s="10"/>
-      <c r="K111" s="10"/>
-      <c r="L111" s="10"/>
-      <c r="M111" s="10"/>
+      <c r="H111" s="11"/>
+      <c r="I111" s="11"/>
+      <c r="J111" s="11"/>
+      <c r="K111" s="11"/>
+      <c r="L111" s="11"/>
+      <c r="M111" s="11"/>
     </row>
     <row r="112" spans="8:13">
-      <c r="H112" s="10"/>
-      <c r="I112" s="10"/>
-      <c r="J112" s="10"/>
-      <c r="K112" s="10"/>
-      <c r="L112" s="10"/>
-      <c r="M112" s="10"/>
+      <c r="H112" s="11"/>
+      <c r="I112" s="11"/>
+      <c r="J112" s="11"/>
+      <c r="K112" s="11"/>
+      <c r="L112" s="11"/>
+      <c r="M112" s="11"/>
     </row>
     <row r="113" spans="8:13">
-      <c r="H113" s="10"/>
-      <c r="I113" s="10"/>
-      <c r="J113" s="10"/>
-      <c r="K113" s="10"/>
-      <c r="L113" s="10"/>
-      <c r="M113" s="10"/>
+      <c r="H113" s="11"/>
+      <c r="I113" s="11"/>
+      <c r="J113" s="11"/>
+      <c r="K113" s="11"/>
+      <c r="L113" s="11"/>
+      <c r="M113" s="11"/>
     </row>
     <row r="114" spans="8:13">
-      <c r="H114" s="10"/>
-      <c r="I114" s="10"/>
-      <c r="J114" s="10"/>
-      <c r="K114" s="10"/>
-      <c r="L114" s="10"/>
-      <c r="M114" s="10"/>
+      <c r="H114" s="11"/>
+      <c r="I114" s="11"/>
+      <c r="J114" s="11"/>
+      <c r="K114" s="11"/>
+      <c r="L114" s="11"/>
+      <c r="M114" s="11"/>
     </row>
     <row r="115" spans="8:13">
-      <c r="H115" s="10"/>
-      <c r="I115" s="10"/>
-      <c r="J115" s="10"/>
-      <c r="K115" s="10"/>
-      <c r="L115" s="10"/>
-      <c r="M115" s="10"/>
+      <c r="H115" s="11"/>
+      <c r="I115" s="11"/>
+      <c r="J115" s="11"/>
+      <c r="K115" s="11"/>
+      <c r="L115" s="11"/>
+      <c r="M115" s="11"/>
     </row>
     <row r="116" spans="8:13">
-      <c r="H116" s="10"/>
-      <c r="I116" s="10"/>
-      <c r="J116" s="10"/>
-      <c r="K116" s="10"/>
-      <c r="L116" s="10"/>
-      <c r="M116" s="10"/>
+      <c r="H116" s="11"/>
+      <c r="I116" s="11"/>
+      <c r="J116" s="11"/>
+      <c r="K116" s="11"/>
+      <c r="L116" s="11"/>
+      <c r="M116" s="11"/>
     </row>
     <row r="117" spans="8:13">
-      <c r="H117" s="10"/>
-      <c r="I117" s="10"/>
-      <c r="J117" s="10"/>
-      <c r="K117" s="10"/>
-      <c r="L117" s="10"/>
-      <c r="M117" s="10"/>
+      <c r="H117" s="11"/>
+      <c r="I117" s="11"/>
+      <c r="J117" s="11"/>
+      <c r="K117" s="11"/>
+      <c r="L117" s="11"/>
+      <c r="M117" s="11"/>
     </row>
     <row r="118" spans="8:13">
-      <c r="H118" s="10"/>
-      <c r="I118" s="10"/>
-      <c r="J118" s="10"/>
-      <c r="K118" s="10"/>
-      <c r="L118" s="10"/>
-      <c r="M118" s="10"/>
+      <c r="H118" s="11"/>
+      <c r="I118" s="11"/>
+      <c r="J118" s="11"/>
+      <c r="K118" s="11"/>
+      <c r="L118" s="11"/>
+      <c r="M118" s="11"/>
     </row>
     <row r="119" spans="8:13">
-      <c r="H119" s="10"/>
-      <c r="I119" s="10"/>
-      <c r="J119" s="10"/>
-      <c r="K119" s="10"/>
-      <c r="L119" s="10"/>
-      <c r="M119" s="10"/>
+      <c r="H119" s="11"/>
+      <c r="I119" s="11"/>
+      <c r="J119" s="11"/>
+      <c r="K119" s="11"/>
+      <c r="L119" s="11"/>
+      <c r="M119" s="11"/>
     </row>
     <row r="120" spans="8:13">
-      <c r="H120" s="10"/>
-      <c r="I120" s="10"/>
-      <c r="J120" s="10"/>
-      <c r="K120" s="10"/>
-      <c r="L120" s="10"/>
-      <c r="M120" s="10"/>
+      <c r="H120" s="11"/>
+      <c r="I120" s="11"/>
+      <c r="J120" s="11"/>
+      <c r="K120" s="11"/>
+      <c r="L120" s="11"/>
+      <c r="M120" s="11"/>
     </row>
     <row r="121" spans="8:13">
-      <c r="H121" s="10"/>
-      <c r="I121" s="10"/>
-      <c r="J121" s="10"/>
-      <c r="K121" s="10"/>
-      <c r="L121" s="10"/>
-      <c r="M121" s="10"/>
+      <c r="H121" s="11"/>
+      <c r="I121" s="11"/>
+      <c r="J121" s="11"/>
+      <c r="K121" s="11"/>
+      <c r="L121" s="11"/>
+      <c r="M121" s="11"/>
     </row>
     <row r="122" spans="8:13">
-      <c r="H122" s="10"/>
-      <c r="I122" s="10"/>
-      <c r="J122" s="10"/>
-      <c r="K122" s="10"/>
-      <c r="L122" s="10"/>
-      <c r="M122" s="10"/>
+      <c r="H122" s="11"/>
+      <c r="I122" s="11"/>
+      <c r="J122" s="11"/>
+      <c r="K122" s="11"/>
+      <c r="L122" s="11"/>
+      <c r="M122" s="11"/>
     </row>
     <row r="123" spans="8:13">
-      <c r="H123" s="10"/>
-      <c r="I123" s="10"/>
-      <c r="J123" s="10"/>
-      <c r="K123" s="10"/>
-      <c r="L123" s="10"/>
-      <c r="M123" s="10"/>
+      <c r="H123" s="11"/>
+      <c r="I123" s="11"/>
+      <c r="J123" s="11"/>
+      <c r="K123" s="11"/>
+      <c r="L123" s="11"/>
+      <c r="M123" s="11"/>
     </row>
     <row r="124" spans="8:13">
-      <c r="H124" s="10"/>
-      <c r="I124" s="10"/>
-      <c r="J124" s="10"/>
-      <c r="K124" s="10"/>
-      <c r="L124" s="10"/>
-      <c r="M124" s="10"/>
+      <c r="H124" s="11"/>
+      <c r="I124" s="11"/>
+      <c r="J124" s="11"/>
+      <c r="K124" s="11"/>
+      <c r="L124" s="11"/>
+      <c r="M124" s="11"/>
     </row>
     <row r="125" spans="8:13">
-      <c r="H125" s="10"/>
-      <c r="I125" s="10"/>
-      <c r="J125" s="10"/>
-      <c r="K125" s="10"/>
-      <c r="L125" s="10"/>
-      <c r="M125" s="10"/>
+      <c r="H125" s="11"/>
+      <c r="I125" s="11"/>
+      <c r="J125" s="11"/>
+      <c r="K125" s="11"/>
+      <c r="L125" s="11"/>
+      <c r="M125" s="11"/>
     </row>
     <row r="126" spans="8:13">
-      <c r="H126" s="10"/>
-      <c r="I126" s="10"/>
-      <c r="J126" s="10"/>
-      <c r="K126" s="10"/>
-      <c r="L126" s="10"/>
-      <c r="M126" s="10"/>
+      <c r="H126" s="11"/>
+      <c r="I126" s="11"/>
+      <c r="J126" s="11"/>
+      <c r="K126" s="11"/>
+      <c r="L126" s="11"/>
+      <c r="M126" s="11"/>
     </row>
     <row r="127" spans="8:13">
-      <c r="H127" s="10"/>
-      <c r="I127" s="10"/>
-      <c r="J127" s="10"/>
-      <c r="K127" s="10"/>
-      <c r="L127" s="10"/>
-      <c r="M127" s="10"/>
+      <c r="H127" s="11"/>
+      <c r="I127" s="11"/>
+      <c r="J127" s="11"/>
+      <c r="K127" s="11"/>
+      <c r="L127" s="11"/>
+      <c r="M127" s="11"/>
     </row>
     <row r="128" spans="8:13">
-      <c r="H128" s="10"/>
-      <c r="I128" s="10"/>
-      <c r="J128" s="10"/>
-      <c r="K128" s="10"/>
-      <c r="L128" s="10"/>
-      <c r="M128" s="10"/>
+      <c r="H128" s="11"/>
+      <c r="I128" s="11"/>
+      <c r="J128" s="11"/>
+      <c r="K128" s="11"/>
+      <c r="L128" s="11"/>
+      <c r="M128" s="11"/>
     </row>
     <row r="129" spans="8:13">
-      <c r="H129" s="10"/>
-      <c r="I129" s="10"/>
-      <c r="J129" s="10"/>
-      <c r="K129" s="10"/>
-      <c r="L129" s="10"/>
-      <c r="M129" s="10"/>
+      <c r="H129" s="11"/>
+      <c r="I129" s="11"/>
+      <c r="J129" s="11"/>
+      <c r="K129" s="11"/>
+      <c r="L129" s="11"/>
+      <c r="M129" s="11"/>
     </row>
     <row r="130" spans="8:13">
-      <c r="H130" s="10"/>
-      <c r="I130" s="10"/>
-      <c r="J130" s="10"/>
-      <c r="K130" s="10"/>
-      <c r="L130" s="10"/>
-      <c r="M130" s="10"/>
+      <c r="H130" s="11"/>
+      <c r="I130" s="11"/>
+      <c r="J130" s="11"/>
+      <c r="K130" s="11"/>
+      <c r="L130" s="11"/>
+      <c r="M130" s="11"/>
     </row>
     <row r="131" spans="8:13">
-      <c r="H131" s="10"/>
-      <c r="I131" s="10"/>
-      <c r="J131" s="10"/>
-      <c r="K131" s="10"/>
-      <c r="L131" s="10"/>
-      <c r="M131" s="10"/>
+      <c r="H131" s="11"/>
+      <c r="I131" s="11"/>
+      <c r="J131" s="11"/>
+      <c r="K131" s="11"/>
+      <c r="L131" s="11"/>
+      <c r="M131" s="11"/>
     </row>
     <row r="132" spans="8:13">
-      <c r="H132" s="10"/>
-      <c r="I132" s="10"/>
-      <c r="J132" s="10"/>
-      <c r="K132" s="10"/>
-      <c r="L132" s="10"/>
-      <c r="M132" s="10"/>
+      <c r="H132" s="11"/>
+      <c r="I132" s="11"/>
+      <c r="J132" s="11"/>
+      <c r="K132" s="11"/>
+      <c r="L132" s="11"/>
+      <c r="M132" s="11"/>
     </row>
     <row r="133" spans="8:13">
-      <c r="H133" s="10"/>
-      <c r="I133" s="10"/>
-      <c r="J133" s="10"/>
-      <c r="K133" s="10"/>
-      <c r="L133" s="10"/>
-      <c r="M133" s="10"/>
+      <c r="H133" s="11"/>
+      <c r="I133" s="11"/>
+      <c r="J133" s="11"/>
+      <c r="K133" s="11"/>
+      <c r="L133" s="11"/>
+      <c r="M133" s="11"/>
     </row>
     <row r="134" spans="8:13">
-      <c r="H134" s="10"/>
-      <c r="I134" s="10"/>
-      <c r="J134" s="10"/>
-      <c r="K134" s="10"/>
-      <c r="L134" s="10"/>
-      <c r="M134" s="10"/>
+      <c r="H134" s="11"/>
+      <c r="I134" s="11"/>
+      <c r="J134" s="11"/>
+      <c r="K134" s="11"/>
+      <c r="L134" s="11"/>
+      <c r="M134" s="11"/>
     </row>
     <row r="135" spans="8:13">
-      <c r="H135" s="10"/>
-      <c r="I135" s="10"/>
-      <c r="J135" s="10"/>
-      <c r="K135" s="10"/>
-      <c r="L135" s="10"/>
-      <c r="M135" s="10"/>
+      <c r="H135" s="11"/>
+      <c r="I135" s="11"/>
+      <c r="J135" s="11"/>
+      <c r="K135" s="11"/>
+      <c r="L135" s="11"/>
+      <c r="M135" s="11"/>
     </row>
     <row r="136" spans="8:13">
-      <c r="H136" s="10"/>
-      <c r="I136" s="10"/>
-      <c r="J136" s="10"/>
-      <c r="K136" s="10"/>
-      <c r="L136" s="10"/>
-      <c r="M136" s="10"/>
+      <c r="H136" s="11"/>
+      <c r="I136" s="11"/>
+      <c r="J136" s="11"/>
+      <c r="K136" s="11"/>
+      <c r="L136" s="11"/>
+      <c r="M136" s="11"/>
     </row>
     <row r="137" spans="8:13">
-      <c r="H137" s="10"/>
-      <c r="I137" s="10"/>
-      <c r="J137" s="10"/>
-      <c r="K137" s="10"/>
-      <c r="L137" s="10"/>
-      <c r="M137" s="10"/>
+      <c r="H137" s="11"/>
+      <c r="I137" s="11"/>
+      <c r="J137" s="11"/>
+      <c r="K137" s="11"/>
+      <c r="L137" s="11"/>
+      <c r="M137" s="11"/>
     </row>
     <row r="138" spans="8:13">
-      <c r="H138" s="10"/>
-      <c r="I138" s="10"/>
-      <c r="J138" s="10"/>
-      <c r="K138" s="10"/>
-      <c r="L138" s="10"/>
-      <c r="M138" s="10"/>
+      <c r="H138" s="11"/>
+      <c r="I138" s="11"/>
+      <c r="J138" s="11"/>
+      <c r="K138" s="11"/>
+      <c r="L138" s="11"/>
+      <c r="M138" s="11"/>
     </row>
     <row r="139" spans="8:13">
-      <c r="H139" s="10"/>
-      <c r="I139" s="10"/>
-      <c r="J139" s="10"/>
-      <c r="K139" s="10"/>
-      <c r="L139" s="10"/>
-      <c r="M139" s="10"/>
+      <c r="H139" s="11"/>
+      <c r="I139" s="11"/>
+      <c r="J139" s="11"/>
+      <c r="K139" s="11"/>
+      <c r="L139" s="11"/>
+      <c r="M139" s="11"/>
     </row>
     <row r="140" spans="8:13">
-      <c r="H140" s="10"/>
-      <c r="I140" s="10"/>
-      <c r="J140" s="10"/>
-      <c r="K140" s="10"/>
-      <c r="L140" s="10"/>
-      <c r="M140" s="10"/>
+      <c r="H140" s="11"/>
+      <c r="I140" s="11"/>
+      <c r="J140" s="11"/>
+      <c r="K140" s="11"/>
+      <c r="L140" s="11"/>
+      <c r="M140" s="11"/>
     </row>
     <row r="141" spans="8:13">
-      <c r="H141" s="10"/>
-      <c r="I141" s="10"/>
-      <c r="J141" s="10"/>
-      <c r="K141" s="10"/>
-      <c r="L141" s="10"/>
-      <c r="M141" s="10"/>
+      <c r="H141" s="11"/>
+      <c r="I141" s="11"/>
+      <c r="J141" s="11"/>
+      <c r="K141" s="11"/>
+      <c r="L141" s="11"/>
+      <c r="M141" s="11"/>
     </row>
     <row r="142" spans="8:13">
-      <c r="H142" s="10"/>
-      <c r="I142" s="10"/>
-      <c r="J142" s="10"/>
-      <c r="K142" s="10"/>
-      <c r="L142" s="10"/>
-      <c r="M142" s="10"/>
+      <c r="H142" s="11"/>
+      <c r="I142" s="11"/>
+      <c r="J142" s="11"/>
+      <c r="K142" s="11"/>
+      <c r="L142" s="11"/>
+      <c r="M142" s="11"/>
     </row>
     <row r="143" spans="8:13">
-      <c r="H143" s="10"/>
-      <c r="I143" s="10"/>
-      <c r="J143" s="10"/>
-      <c r="K143" s="10"/>
-      <c r="L143" s="10"/>
-      <c r="M143" s="10"/>
+      <c r="H143" s="11"/>
+      <c r="I143" s="11"/>
+      <c r="J143" s="11"/>
+      <c r="K143" s="11"/>
+      <c r="L143" s="11"/>
+      <c r="M143" s="11"/>
     </row>
     <row r="144" spans="8:13">
-      <c r="H144" s="10"/>
-      <c r="I144" s="10"/>
-      <c r="J144" s="10"/>
-      <c r="K144" s="10"/>
-      <c r="L144" s="10"/>
-      <c r="M144" s="10"/>
+      <c r="H144" s="11"/>
+      <c r="I144" s="11"/>
+      <c r="J144" s="11"/>
+      <c r="K144" s="11"/>
+      <c r="L144" s="11"/>
+      <c r="M144" s="11"/>
     </row>
     <row r="145" spans="8:13">
-      <c r="H145" s="10"/>
-      <c r="I145" s="10"/>
-      <c r="J145" s="10"/>
-      <c r="K145" s="10"/>
-      <c r="L145" s="10"/>
-      <c r="M145" s="10"/>
+      <c r="H145" s="11"/>
+      <c r="I145" s="11"/>
+      <c r="J145" s="11"/>
+      <c r="K145" s="11"/>
+      <c r="L145" s="11"/>
+      <c r="M145" s="11"/>
     </row>
     <row r="146" spans="8:13">
-      <c r="H146" s="10"/>
-      <c r="I146" s="10"/>
-      <c r="J146" s="10"/>
-      <c r="K146" s="10"/>
-      <c r="L146" s="10"/>
-      <c r="M146" s="10"/>
+      <c r="H146" s="11"/>
+      <c r="I146" s="11"/>
+      <c r="J146" s="11"/>
+      <c r="K146" s="11"/>
+      <c r="L146" s="11"/>
+      <c r="M146" s="11"/>
     </row>
     <row r="147" spans="8:13">
-      <c r="H147" s="10"/>
-      <c r="I147" s="10"/>
-      <c r="J147" s="10"/>
-      <c r="K147" s="10"/>
-      <c r="L147" s="10"/>
-      <c r="M147" s="10"/>
+      <c r="H147" s="11"/>
+      <c r="I147" s="11"/>
+      <c r="J147" s="11"/>
+      <c r="K147" s="11"/>
+      <c r="L147" s="11"/>
+      <c r="M147" s="11"/>
     </row>
     <row r="148" spans="8:13">
-      <c r="H148" s="10"/>
-      <c r="I148" s="10"/>
-      <c r="J148" s="10"/>
-      <c r="K148" s="10"/>
-      <c r="L148" s="10"/>
-      <c r="M148" s="10"/>
+      <c r="H148" s="11"/>
+      <c r="I148" s="11"/>
+      <c r="J148" s="11"/>
+      <c r="K148" s="11"/>
+      <c r="L148" s="11"/>
+      <c r="M148" s="11"/>
     </row>
     <row r="149" spans="8:13">
-      <c r="H149" s="10"/>
-      <c r="I149" s="10"/>
-      <c r="J149" s="10"/>
-      <c r="K149" s="10"/>
-      <c r="L149" s="10"/>
-      <c r="M149" s="10"/>
+      <c r="H149" s="11"/>
+      <c r="I149" s="11"/>
+      <c r="J149" s="11"/>
+      <c r="K149" s="11"/>
+      <c r="L149" s="11"/>
+      <c r="M149" s="11"/>
     </row>
     <row r="150" spans="8:13">
-      <c r="H150" s="10"/>
-      <c r="I150" s="10"/>
-      <c r="J150" s="10"/>
-      <c r="K150" s="10"/>
-      <c r="L150" s="10"/>
-      <c r="M150" s="10"/>
+      <c r="H150" s="11"/>
+      <c r="I150" s="11"/>
+      <c r="J150" s="11"/>
+      <c r="K150" s="11"/>
+      <c r="L150" s="11"/>
+      <c r="M150" s="11"/>
     </row>
     <row r="151" spans="8:13">
-      <c r="H151" s="10"/>
-      <c r="I151" s="10"/>
-      <c r="J151" s="10"/>
-      <c r="K151" s="10"/>
-      <c r="L151" s="10"/>
-      <c r="M151" s="10"/>
+      <c r="H151" s="11"/>
+      <c r="I151" s="11"/>
+      <c r="J151" s="11"/>
+      <c r="K151" s="11"/>
+      <c r="L151" s="11"/>
+      <c r="M151" s="11"/>
     </row>
     <row r="152" spans="8:13">
-      <c r="H152" s="10"/>
-      <c r="I152" s="10"/>
-      <c r="J152" s="10"/>
-      <c r="K152" s="10"/>
-      <c r="L152" s="10"/>
-      <c r="M152" s="10"/>
+      <c r="H152" s="11"/>
+      <c r="I152" s="11"/>
+      <c r="J152" s="11"/>
+      <c r="K152" s="11"/>
+      <c r="L152" s="11"/>
+      <c r="M152" s="11"/>
     </row>
     <row r="153" spans="8:13">
-      <c r="H153" s="10"/>
-      <c r="I153" s="10"/>
-      <c r="J153" s="10"/>
-      <c r="K153" s="10"/>
-      <c r="L153" s="10"/>
-      <c r="M153" s="10"/>
+      <c r="H153" s="11"/>
+      <c r="I153" s="11"/>
+      <c r="J153" s="11"/>
+      <c r="K153" s="11"/>
+      <c r="L153" s="11"/>
+      <c r="M153" s="11"/>
     </row>
     <row r="154" spans="8:13">
-      <c r="H154" s="10"/>
-      <c r="I154" s="10"/>
-      <c r="J154" s="10"/>
-      <c r="K154" s="10"/>
-      <c r="L154" s="10"/>
-      <c r="M154" s="10"/>
+      <c r="H154" s="11"/>
+      <c r="I154" s="11"/>
+      <c r="J154" s="11"/>
+      <c r="K154" s="11"/>
+      <c r="L154" s="11"/>
+      <c r="M154" s="11"/>
     </row>
     <row r="155" spans="8:13">
-      <c r="H155" s="10"/>
-      <c r="I155" s="10"/>
-      <c r="J155" s="10"/>
-      <c r="K155" s="10"/>
-      <c r="L155" s="10"/>
-      <c r="M155" s="10"/>
+      <c r="H155" s="11"/>
+      <c r="I155" s="11"/>
+      <c r="J155" s="11"/>
+      <c r="K155" s="11"/>
+      <c r="L155" s="11"/>
+      <c r="M155" s="11"/>
     </row>
     <row r="156" spans="8:13">
-      <c r="H156" s="10"/>
-      <c r="I156" s="10"/>
-      <c r="J156" s="10"/>
-      <c r="K156" s="10"/>
-      <c r="L156" s="10"/>
-      <c r="M156" s="10"/>
+      <c r="H156" s="11"/>
+      <c r="I156" s="11"/>
+      <c r="J156" s="11"/>
+      <c r="K156" s="11"/>
+      <c r="L156" s="11"/>
+      <c r="M156" s="11"/>
     </row>
     <row r="157" spans="8:13">
-      <c r="H157" s="10"/>
-      <c r="I157" s="10"/>
-      <c r="J157" s="10"/>
-      <c r="K157" s="10"/>
-      <c r="L157" s="10"/>
-      <c r="M157" s="10"/>
+      <c r="H157" s="11"/>
+      <c r="I157" s="11"/>
+      <c r="J157" s="11"/>
+      <c r="K157" s="11"/>
+      <c r="L157" s="11"/>
+      <c r="M157" s="11"/>
     </row>
     <row r="158" spans="8:13">
-      <c r="H158" s="10"/>
-      <c r="I158" s="10"/>
-      <c r="J158" s="10"/>
-      <c r="K158" s="10"/>
-      <c r="L158" s="10"/>
-      <c r="M158" s="10"/>
+      <c r="H158" s="11"/>
+      <c r="I158" s="11"/>
+      <c r="J158" s="11"/>
+      <c r="K158" s="11"/>
+      <c r="L158" s="11"/>
+      <c r="M158" s="11"/>
     </row>
     <row r="159" spans="8:13">
-      <c r="H159" s="10"/>
-      <c r="I159" s="10"/>
-      <c r="J159" s="10"/>
-      <c r="K159" s="10"/>
-      <c r="L159" s="10"/>
-      <c r="M159" s="10"/>
+      <c r="H159" s="11"/>
+      <c r="I159" s="11"/>
+      <c r="J159" s="11"/>
+      <c r="K159" s="11"/>
+      <c r="L159" s="11"/>
+      <c r="M159" s="11"/>
     </row>
     <row r="160" spans="8:13">
-      <c r="H160" s="10"/>
-      <c r="I160" s="10"/>
-      <c r="J160" s="10"/>
-      <c r="K160" s="10"/>
-      <c r="L160" s="10"/>
-      <c r="M160" s="10"/>
+      <c r="H160" s="11"/>
+      <c r="I160" s="11"/>
+      <c r="J160" s="11"/>
+      <c r="K160" s="11"/>
+      <c r="L160" s="11"/>
+      <c r="M160" s="11"/>
     </row>
     <row r="161" spans="8:13">
-      <c r="H161" s="10"/>
-      <c r="I161" s="10"/>
-      <c r="J161" s="10"/>
-      <c r="K161" s="10"/>
-      <c r="L161" s="10"/>
-      <c r="M161" s="10"/>
+      <c r="H161" s="11"/>
+      <c r="I161" s="11"/>
+      <c r="J161" s="11"/>
+      <c r="K161" s="11"/>
+      <c r="L161" s="11"/>
+      <c r="M161" s="11"/>
     </row>
     <row r="162" spans="8:13">
-      <c r="H162" s="10"/>
-      <c r="I162" s="10"/>
-      <c r="J162" s="10"/>
-      <c r="K162" s="10"/>
-      <c r="L162" s="10"/>
-      <c r="M162" s="10"/>
+      <c r="H162" s="11"/>
+      <c r="I162" s="11"/>
+      <c r="J162" s="11"/>
+      <c r="K162" s="11"/>
+      <c r="L162" s="11"/>
+      <c r="M162" s="11"/>
     </row>
     <row r="163" spans="8:13">
-      <c r="H163" s="10"/>
-      <c r="I163" s="10"/>
-      <c r="J163" s="10"/>
-      <c r="K163" s="10"/>
-      <c r="L163" s="10"/>
-      <c r="M163" s="10"/>
+      <c r="H163" s="11"/>
+      <c r="I163" s="11"/>
+      <c r="J163" s="11"/>
+      <c r="K163" s="11"/>
+      <c r="L163" s="11"/>
+      <c r="M163" s="11"/>
     </row>
     <row r="164" spans="8:13">
-      <c r="H164" s="10"/>
-      <c r="I164" s="10"/>
-      <c r="J164" s="10"/>
-      <c r="K164" s="10"/>
-      <c r="L164" s="10"/>
-      <c r="M164" s="10"/>
+      <c r="H164" s="11"/>
+      <c r="I164" s="11"/>
+      <c r="J164" s="11"/>
+      <c r="K164" s="11"/>
+      <c r="L164" s="11"/>
+      <c r="M164" s="11"/>
     </row>
     <row r="165" spans="8:13">
-      <c r="H165" s="10"/>
-      <c r="I165" s="10"/>
-      <c r="J165" s="10"/>
-      <c r="K165" s="10"/>
-      <c r="L165" s="10"/>
-      <c r="M165" s="10"/>
+      <c r="H165" s="11"/>
+      <c r="I165" s="11"/>
+      <c r="J165" s="11"/>
+      <c r="K165" s="11"/>
+      <c r="L165" s="11"/>
+      <c r="M165" s="11"/>
     </row>
     <row r="166" spans="8:13">
-      <c r="H166" s="10"/>
-      <c r="I166" s="10"/>
-      <c r="J166" s="10"/>
-      <c r="K166" s="10"/>
-      <c r="L166" s="10"/>
-      <c r="M166" s="10"/>
+      <c r="H166" s="11"/>
+      <c r="I166" s="11"/>
+      <c r="J166" s="11"/>
+      <c r="K166" s="11"/>
+      <c r="L166" s="11"/>
+      <c r="M166" s="11"/>
     </row>
     <row r="167" spans="8:13">
-      <c r="H167" s="10"/>
-      <c r="I167" s="10"/>
-      <c r="J167" s="10"/>
-      <c r="K167" s="10"/>
-      <c r="L167" s="10"/>
-      <c r="M167" s="10"/>
+      <c r="H167" s="11"/>
+      <c r="I167" s="11"/>
+      <c r="J167" s="11"/>
+      <c r="K167" s="11"/>
+      <c r="L167" s="11"/>
+      <c r="M167" s="11"/>
     </row>
     <row r="168" spans="8:13">
-      <c r="H168" s="10"/>
-      <c r="I168" s="10"/>
-      <c r="J168" s="10"/>
-      <c r="K168" s="10"/>
-      <c r="L168" s="10"/>
-      <c r="M168" s="10"/>
+      <c r="H168" s="11"/>
+      <c r="I168" s="11"/>
+      <c r="J168" s="11"/>
+      <c r="K168" s="11"/>
+      <c r="L168" s="11"/>
+      <c r="M168" s="11"/>
     </row>
     <row r="169" spans="8:13">
-      <c r="H169" s="10"/>
-      <c r="I169" s="10"/>
-      <c r="J169" s="10"/>
-      <c r="K169" s="10"/>
-      <c r="L169" s="10"/>
-      <c r="M169" s="10"/>
+      <c r="H169" s="11"/>
+      <c r="I169" s="11"/>
+      <c r="J169" s="11"/>
+      <c r="K169" s="11"/>
+      <c r="L169" s="11"/>
+      <c r="M169" s="11"/>
     </row>
     <row r="170" spans="8:13">
-      <c r="H170" s="10"/>
-      <c r="I170" s="10"/>
-      <c r="J170" s="10"/>
-      <c r="K170" s="10"/>
-      <c r="L170" s="10"/>
-      <c r="M170" s="10"/>
+      <c r="H170" s="11"/>
+      <c r="I170" s="11"/>
+      <c r="J170" s="11"/>
+      <c r="K170" s="11"/>
+      <c r="L170" s="11"/>
+      <c r="M170" s="11"/>
     </row>
     <row r="171" spans="8:13">
-      <c r="H171" s="10"/>
-      <c r="I171" s="10"/>
-      <c r="J171" s="10"/>
-      <c r="K171" s="10"/>
-      <c r="L171" s="10"/>
-      <c r="M171" s="10"/>
+      <c r="H171" s="11"/>
+      <c r="I171" s="11"/>
+      <c r="J171" s="11"/>
+      <c r="K171" s="11"/>
+      <c r="L171" s="11"/>
+      <c r="M171" s="11"/>
     </row>
     <row r="172" spans="8:13">
-      <c r="H172" s="10"/>
-      <c r="I172" s="10"/>
-      <c r="J172" s="10"/>
-      <c r="K172" s="10"/>
-      <c r="L172" s="10"/>
-      <c r="M172" s="10"/>
+      <c r="H172" s="11"/>
+      <c r="I172" s="11"/>
+      <c r="J172" s="11"/>
+      <c r="K172" s="11"/>
+      <c r="L172" s="11"/>
+      <c r="M172" s="11"/>
     </row>
     <row r="173" spans="8:13">
-      <c r="H173" s="10"/>
-      <c r="I173" s="10"/>
-      <c r="J173" s="10"/>
-      <c r="K173" s="10"/>
-      <c r="L173" s="10"/>
-      <c r="M173" s="10"/>
+      <c r="H173" s="11"/>
+      <c r="I173" s="11"/>
+      <c r="J173" s="11"/>
+      <c r="K173" s="11"/>
+      <c r="L173" s="11"/>
+      <c r="M173" s="11"/>
     </row>
     <row r="174" spans="8:13">
-      <c r="H174" s="10"/>
-      <c r="I174" s="10"/>
-      <c r="J174" s="10"/>
-      <c r="K174" s="10"/>
-      <c r="L174" s="10"/>
-      <c r="M174" s="10"/>
+      <c r="H174" s="11"/>
+      <c r="I174" s="11"/>
+      <c r="J174" s="11"/>
+      <c r="K174" s="11"/>
+      <c r="L174" s="11"/>
+      <c r="M174" s="11"/>
     </row>
     <row r="175" spans="8:13">
-      <c r="H175" s="10"/>
-      <c r="I175" s="10"/>
-      <c r="J175" s="10"/>
-      <c r="K175" s="10"/>
-      <c r="L175" s="10"/>
-      <c r="M175" s="10"/>
+      <c r="H175" s="11"/>
+      <c r="I175" s="11"/>
+      <c r="J175" s="11"/>
+      <c r="K175" s="11"/>
+      <c r="L175" s="11"/>
+      <c r="M175" s="11"/>
     </row>
     <row r="176" spans="8:13">
-      <c r="H176" s="10"/>
-      <c r="I176" s="10"/>
-      <c r="J176" s="10"/>
-      <c r="K176" s="10"/>
-      <c r="L176" s="10"/>
-      <c r="M176" s="10"/>
+      <c r="H176" s="11"/>
+      <c r="I176" s="11"/>
+      <c r="J176" s="11"/>
+      <c r="K176" s="11"/>
+      <c r="L176" s="11"/>
+      <c r="M176" s="11"/>
     </row>
     <row r="177" spans="8:13">
-      <c r="H177" s="10"/>
-      <c r="I177" s="10"/>
-      <c r="J177" s="10"/>
-      <c r="K177" s="10"/>
-      <c r="L177" s="10"/>
-      <c r="M177" s="10"/>
+      <c r="H177" s="11"/>
+      <c r="I177" s="11"/>
+      <c r="J177" s="11"/>
+      <c r="K177" s="11"/>
+      <c r="L177" s="11"/>
+      <c r="M177" s="11"/>
     </row>
     <row r="178" spans="8:13">
-      <c r="H178" s="10"/>
-      <c r="I178" s="10"/>
-      <c r="J178" s="10"/>
-      <c r="K178" s="10"/>
-      <c r="L178" s="10"/>
-      <c r="M178" s="10"/>
+      <c r="H178" s="11"/>
+      <c r="I178" s="11"/>
+      <c r="J178" s="11"/>
+      <c r="K178" s="11"/>
+      <c r="L178" s="11"/>
+      <c r="M178" s="11"/>
     </row>
     <row r="179" spans="8:13">
-      <c r="H179" s="10"/>
-      <c r="I179" s="10"/>
-      <c r="J179" s="10"/>
-      <c r="K179" s="10"/>
-      <c r="L179" s="10"/>
-      <c r="M179" s="10"/>
+      <c r="H179" s="11"/>
+      <c r="I179" s="11"/>
+      <c r="J179" s="11"/>
+      <c r="K179" s="11"/>
+      <c r="L179" s="11"/>
+      <c r="M179" s="11"/>
     </row>
     <row r="180" spans="8:13">
-      <c r="H180" s="10"/>
-      <c r="I180" s="10"/>
-      <c r="J180" s="10"/>
-      <c r="K180" s="10"/>
-      <c r="L180" s="10"/>
-      <c r="M180" s="10"/>
+      <c r="H180" s="11"/>
+      <c r="I180" s="11"/>
+      <c r="J180" s="11"/>
+      <c r="K180" s="11"/>
+      <c r="L180" s="11"/>
+      <c r="M180" s="11"/>
     </row>
     <row r="181" spans="8:13">
-      <c r="H181" s="10"/>
-      <c r="I181" s="10"/>
-      <c r="J181" s="10"/>
-      <c r="K181" s="10"/>
-      <c r="L181" s="10"/>
-      <c r="M181" s="10"/>
+      <c r="H181" s="11"/>
+      <c r="I181" s="11"/>
+      <c r="J181" s="11"/>
+      <c r="K181" s="11"/>
+      <c r="L181" s="11"/>
+      <c r="M181" s="11"/>
     </row>
     <row r="182" spans="8:13">
-      <c r="H182" s="10"/>
-      <c r="I182" s="10"/>
-      <c r="J182" s="10"/>
-      <c r="K182" s="10"/>
-      <c r="L182" s="10"/>
-      <c r="M182" s="10"/>
+      <c r="H182" s="11"/>
+      <c r="I182" s="11"/>
+      <c r="J182" s="11"/>
+      <c r="K182" s="11"/>
+      <c r="L182" s="11"/>
+      <c r="M182" s="11"/>
     </row>
     <row r="183" spans="8:13">
-      <c r="H183" s="10"/>
-      <c r="I183" s="10"/>
-      <c r="J183" s="10"/>
-      <c r="K183" s="10"/>
-      <c r="L183" s="10"/>
-      <c r="M183" s="10"/>
+      <c r="H183" s="11"/>
+      <c r="I183" s="11"/>
+      <c r="J183" s="11"/>
+      <c r="K183" s="11"/>
+      <c r="L183" s="11"/>
+      <c r="M183" s="11"/>
     </row>
     <row r="184" spans="8:13">
-      <c r="H184" s="10"/>
-      <c r="I184" s="10"/>
-      <c r="J184" s="10"/>
-      <c r="K184" s="10"/>
-      <c r="L184" s="10"/>
-      <c r="M184" s="10"/>
+      <c r="H184" s="11"/>
+      <c r="I184" s="11"/>
+      <c r="J184" s="11"/>
+      <c r="K184" s="11"/>
+      <c r="L184" s="11"/>
+      <c r="M184" s="11"/>
     </row>
     <row r="185" spans="8:13">
-      <c r="H185" s="10"/>
-      <c r="I185" s="10"/>
-      <c r="J185" s="10"/>
-      <c r="K185" s="10"/>
-      <c r="L185" s="10"/>
-      <c r="M185" s="10"/>
+      <c r="H185" s="11"/>
+      <c r="I185" s="11"/>
+      <c r="J185" s="11"/>
+      <c r="K185" s="11"/>
+      <c r="L185" s="11"/>
+      <c r="M185" s="11"/>
     </row>
     <row r="186" spans="8:13">
-      <c r="H186" s="10"/>
-      <c r="I186" s="10"/>
-      <c r="J186" s="10"/>
-      <c r="K186" s="10"/>
-      <c r="L186" s="10"/>
-      <c r="M186" s="10"/>
+      <c r="H186" s="11"/>
+      <c r="I186" s="11"/>
+      <c r="J186" s="11"/>
+      <c r="K186" s="11"/>
+      <c r="L186" s="11"/>
+      <c r="M186" s="11"/>
     </row>
     <row r="187" spans="8:13">
-      <c r="H187" s="10"/>
-      <c r="I187" s="10"/>
-      <c r="J187" s="10"/>
-      <c r="K187" s="10"/>
-      <c r="L187" s="10"/>
-      <c r="M187" s="10"/>
+      <c r="H187" s="11"/>
+      <c r="I187" s="11"/>
+      <c r="J187" s="11"/>
+      <c r="K187" s="11"/>
+      <c r="L187" s="11"/>
+      <c r="M187" s="11"/>
     </row>
     <row r="188" spans="8:13">
-      <c r="H188" s="10"/>
-      <c r="I188" s="10"/>
-      <c r="J188" s="10"/>
-      <c r="K188" s="10"/>
-      <c r="L188" s="10"/>
-      <c r="M188" s="10"/>
+      <c r="H188" s="11"/>
+      <c r="I188" s="11"/>
+      <c r="J188" s="11"/>
+      <c r="K188" s="11"/>
+      <c r="L188" s="11"/>
+      <c r="M188" s="11"/>
     </row>
     <row r="189" spans="8:13">
-      <c r="H189" s="10"/>
-      <c r="I189" s="10"/>
-      <c r="J189" s="10"/>
-      <c r="K189" s="10"/>
-      <c r="L189" s="10"/>
-      <c r="M189" s="10"/>
+      <c r="H189" s="11"/>
+      <c r="I189" s="11"/>
+      <c r="J189" s="11"/>
+      <c r="K189" s="11"/>
+      <c r="L189" s="11"/>
+      <c r="M189" s="11"/>
     </row>
     <row r="190" spans="8:13">
-      <c r="H190" s="10"/>
-      <c r="I190" s="10"/>
-      <c r="J190" s="10"/>
-      <c r="K190" s="10"/>
-      <c r="L190" s="10"/>
-      <c r="M190" s="10"/>
+      <c r="H190" s="11"/>
+      <c r="I190" s="11"/>
+      <c r="J190" s="11"/>
+      <c r="K190" s="11"/>
+      <c r="L190" s="11"/>
+      <c r="M190" s="11"/>
     </row>
     <row r="191" spans="8:13">
-      <c r="H191" s="10"/>
-      <c r="I191" s="10"/>
-      <c r="J191" s="10"/>
-      <c r="K191" s="10"/>
-      <c r="L191" s="10"/>
-      <c r="M191" s="10"/>
+      <c r="H191" s="11"/>
+      <c r="I191" s="11"/>
+      <c r="J191" s="11"/>
+      <c r="K191" s="11"/>
+      <c r="L191" s="11"/>
+      <c r="M191" s="11"/>
     </row>
     <row r="192" spans="8:13">
-      <c r="H192" s="10"/>
-      <c r="I192" s="10"/>
-      <c r="J192" s="10"/>
-      <c r="K192" s="10"/>
-      <c r="L192" s="10"/>
-      <c r="M192" s="10"/>
+      <c r="H192" s="11"/>
+      <c r="I192" s="11"/>
+      <c r="J192" s="11"/>
+      <c r="K192" s="11"/>
+      <c r="L192" s="11"/>
+      <c r="M192" s="11"/>
     </row>
     <row r="193" spans="8:13">
-      <c r="H193" s="10"/>
-      <c r="I193" s="10"/>
-      <c r="J193" s="10"/>
-      <c r="K193" s="10"/>
-      <c r="L193" s="10"/>
-      <c r="M193" s="10"/>
+      <c r="H193" s="11"/>
+      <c r="I193" s="11"/>
+      <c r="J193" s="11"/>
+      <c r="K193" s="11"/>
+      <c r="L193" s="11"/>
+      <c r="M193" s="11"/>
     </row>
     <row r="194" spans="8:13">
-      <c r="H194" s="10"/>
-      <c r="I194" s="10"/>
-      <c r="J194" s="10"/>
-      <c r="K194" s="10"/>
-      <c r="L194" s="10"/>
-      <c r="M194" s="10"/>
+      <c r="H194" s="11"/>
+      <c r="I194" s="11"/>
+      <c r="J194" s="11"/>
+      <c r="K194" s="11"/>
+      <c r="L194" s="11"/>
+      <c r="M194" s="11"/>
     </row>
     <row r="195" spans="8:13">
-      <c r="H195" s="10"/>
-      <c r="I195" s="10"/>
-      <c r="J195" s="10"/>
-      <c r="K195" s="10"/>
-      <c r="L195" s="10"/>
-      <c r="M195" s="10"/>
+      <c r="H195" s="11"/>
+      <c r="I195" s="11"/>
+      <c r="J195" s="11"/>
+      <c r="K195" s="11"/>
+      <c r="L195" s="11"/>
+      <c r="M195" s="11"/>
     </row>
     <row r="196" spans="8:13">
-      <c r="H196" s="10"/>
-      <c r="I196" s="10"/>
-      <c r="J196" s="10"/>
-      <c r="K196" s="10"/>
-      <c r="L196" s="10"/>
-      <c r="M196" s="10"/>
+      <c r="H196" s="11"/>
+      <c r="I196" s="11"/>
+      <c r="J196" s="11"/>
+      <c r="K196" s="11"/>
+      <c r="L196" s="11"/>
+      <c r="M196" s="11"/>
     </row>
     <row r="197" spans="8:13">
-      <c r="H197" s="10"/>
-      <c r="I197" s="10"/>
-      <c r="J197" s="10"/>
-      <c r="K197" s="10"/>
-      <c r="L197" s="10"/>
-      <c r="M197" s="10"/>
+      <c r="H197" s="11"/>
+      <c r="I197" s="11"/>
+      <c r="J197" s="11"/>
+      <c r="K197" s="11"/>
+      <c r="L197" s="11"/>
+      <c r="M197" s="11"/>
     </row>
     <row r="198" spans="8:13">
-      <c r="H198" s="10"/>
-      <c r="I198" s="10"/>
-      <c r="J198" s="10"/>
-      <c r="K198" s="10"/>
-      <c r="L198" s="10"/>
-      <c r="M198" s="10"/>
+      <c r="H198" s="11"/>
+      <c r="I198" s="11"/>
+      <c r="J198" s="11"/>
+      <c r="K198" s="11"/>
+      <c r="L198" s="11"/>
+      <c r="M198" s="11"/>
     </row>
     <row r="199" spans="8:13">
-      <c r="H199" s="10"/>
-      <c r="I199" s="10"/>
-      <c r="J199" s="10"/>
-      <c r="K199" s="10"/>
-      <c r="L199" s="10"/>
-      <c r="M199" s="10"/>
+      <c r="H199" s="11"/>
+      <c r="I199" s="11"/>
+      <c r="J199" s="11"/>
+      <c r="K199" s="11"/>
+      <c r="L199" s="11"/>
+      <c r="M199" s="11"/>
     </row>
     <row r="200" spans="8:13">
-      <c r="H200" s="10"/>
-      <c r="I200" s="10"/>
-      <c r="J200" s="10"/>
-      <c r="K200" s="10"/>
-      <c r="L200" s="10"/>
-      <c r="M200" s="10"/>
+      <c r="H200" s="11"/>
+      <c r="I200" s="11"/>
+      <c r="J200" s="11"/>
+      <c r="K200" s="11"/>
+      <c r="L200" s="11"/>
+      <c r="M200" s="11"/>
     </row>
     <row r="201" spans="8:13">
-      <c r="H201" s="10"/>
-      <c r="I201" s="10"/>
-      <c r="J201" s="10"/>
-      <c r="K201" s="10"/>
-      <c r="L201" s="10"/>
-      <c r="M201" s="10"/>
+      <c r="H201" s="11"/>
+      <c r="I201" s="11"/>
+      <c r="J201" s="11"/>
+      <c r="K201" s="11"/>
+      <c r="L201" s="11"/>
+      <c r="M201" s="11"/>
     </row>
     <row r="202" spans="8:13">
-      <c r="H202" s="10"/>
-      <c r="I202" s="10"/>
-      <c r="J202" s="10"/>
-      <c r="K202" s="10"/>
-      <c r="L202" s="10"/>
-      <c r="M202" s="10"/>
+      <c r="H202" s="11"/>
+      <c r="I202" s="11"/>
+      <c r="J202" s="11"/>
+      <c r="K202" s="11"/>
+      <c r="L202" s="11"/>
+      <c r="M202" s="11"/>
     </row>
     <row r="203" spans="8:13">
-      <c r="H203" s="10"/>
-      <c r="I203" s="10"/>
-      <c r="J203" s="10"/>
-      <c r="K203" s="10"/>
-      <c r="L203" s="10"/>
-      <c r="M203" s="10"/>
+      <c r="H203" s="11"/>
+      <c r="I203" s="11"/>
+      <c r="J203" s="11"/>
+      <c r="K203" s="11"/>
+      <c r="L203" s="11"/>
+      <c r="M203" s="11"/>
     </row>
     <row r="204" spans="8:13">
-      <c r="H204" s="10"/>
-      <c r="I204" s="10"/>
-      <c r="J204" s="10"/>
-      <c r="K204" s="10"/>
-      <c r="L204" s="10"/>
-      <c r="M204" s="10"/>
+      <c r="H204" s="11"/>
+      <c r="I204" s="11"/>
+      <c r="J204" s="11"/>
+      <c r="K204" s="11"/>
+      <c r="L204" s="11"/>
+      <c r="M204" s="11"/>
     </row>
     <row r="205" spans="8:13">
-      <c r="H205" s="10"/>
-      <c r="I205" s="10"/>
-      <c r="J205" s="10"/>
-      <c r="K205" s="10"/>
-      <c r="L205" s="10"/>
-      <c r="M205" s="10"/>
+      <c r="H205" s="11"/>
+      <c r="I205" s="11"/>
+      <c r="J205" s="11"/>
+      <c r="K205" s="11"/>
+      <c r="L205" s="11"/>
+      <c r="M205" s="11"/>
     </row>
     <row r="206" spans="8:13">
-      <c r="H206" s="10"/>
-      <c r="I206" s="10"/>
-      <c r="J206" s="10"/>
-      <c r="K206" s="10"/>
-      <c r="L206" s="10"/>
-      <c r="M206" s="10"/>
+      <c r="H206" s="11"/>
+      <c r="I206" s="11"/>
+      <c r="J206" s="11"/>
+      <c r="K206" s="11"/>
+      <c r="L206" s="11"/>
+      <c r="M206" s="11"/>
     </row>
     <row r="207" spans="8:13">
-      <c r="H207" s="10"/>
-      <c r="I207" s="10"/>
-      <c r="J207" s="10"/>
-      <c r="K207" s="10"/>
-      <c r="L207" s="10"/>
-      <c r="M207" s="10"/>
+      <c r="H207" s="11"/>
+      <c r="I207" s="11"/>
+      <c r="J207" s="11"/>
+      <c r="K207" s="11"/>
+      <c r="L207" s="11"/>
+      <c r="M207" s="11"/>
     </row>
     <row r="208" spans="8:13">
-      <c r="H208" s="10"/>
-      <c r="I208" s="10"/>
-      <c r="J208" s="10"/>
-      <c r="K208" s="10"/>
-      <c r="L208" s="10"/>
-      <c r="M208" s="10"/>
+      <c r="H208" s="11"/>
+      <c r="I208" s="11"/>
+      <c r="J208" s="11"/>
+      <c r="K208" s="11"/>
+      <c r="L208" s="11"/>
+      <c r="M208" s="11"/>
     </row>
     <row r="209" spans="8:13">
-      <c r="H209" s="10"/>
-      <c r="I209" s="10"/>
-      <c r="J209" s="10"/>
-      <c r="K209" s="10"/>
-      <c r="L209" s="10"/>
-      <c r="M209" s="10"/>
+      <c r="H209" s="11"/>
+      <c r="I209" s="11"/>
+      <c r="J209" s="11"/>
+      <c r="K209" s="11"/>
+      <c r="L209" s="11"/>
+      <c r="M209" s="11"/>
     </row>
     <row r="210" spans="8:13">
-      <c r="H210" s="10"/>
-      <c r="I210" s="10"/>
-      <c r="J210" s="10"/>
-      <c r="K210" s="10"/>
-      <c r="L210" s="10"/>
-      <c r="M210" s="10"/>
+      <c r="H210" s="11"/>
+      <c r="I210" s="11"/>
+      <c r="J210" s="11"/>
+      <c r="K210" s="11"/>
+      <c r="L210" s="11"/>
+      <c r="M210" s="11"/>
     </row>
     <row r="211" spans="8:13">
-      <c r="H211" s="10"/>
-      <c r="I211" s="10"/>
-      <c r="J211" s="10"/>
-      <c r="K211" s="10"/>
-      <c r="L211" s="10"/>
-      <c r="M211" s="10"/>
+      <c r="H211" s="11"/>
+      <c r="I211" s="11"/>
+      <c r="J211" s="11"/>
+      <c r="K211" s="11"/>
+      <c r="L211" s="11"/>
+      <c r="M211" s="11"/>
     </row>
     <row r="212" spans="8:13">
-      <c r="H212" s="10"/>
-      <c r="I212" s="10"/>
-      <c r="J212" s="10"/>
-      <c r="K212" s="10"/>
-      <c r="L212" s="10"/>
-      <c r="M212" s="10"/>
+      <c r="H212" s="11"/>
+      <c r="I212" s="11"/>
+      <c r="J212" s="11"/>
+      <c r="K212" s="11"/>
+      <c r="L212" s="11"/>
+      <c r="M212" s="11"/>
     </row>
     <row r="213" spans="8:13">
-      <c r="H213" s="10"/>
-      <c r="I213" s="10"/>
-      <c r="J213" s="10"/>
-      <c r="K213" s="10"/>
-      <c r="L213" s="10"/>
-      <c r="M213" s="10"/>
+      <c r="H213" s="11"/>
+      <c r="I213" s="11"/>
+      <c r="J213" s="11"/>
+      <c r="K213" s="11"/>
+      <c r="L213" s="11"/>
+      <c r="M213" s="11"/>
     </row>
     <row r="214" spans="8:13">
-      <c r="H214" s="10"/>
-      <c r="I214" s="10"/>
-      <c r="J214" s="10"/>
-      <c r="K214" s="10"/>
-      <c r="L214" s="10"/>
-      <c r="M214" s="10"/>
+      <c r="H214" s="11"/>
+      <c r="I214" s="11"/>
+      <c r="J214" s="11"/>
+      <c r="K214" s="11"/>
+      <c r="L214" s="11"/>
+      <c r="M214" s="11"/>
     </row>
     <row r="215" spans="8:13">
-      <c r="H215" s="10"/>
-      <c r="I215" s="10"/>
-      <c r="J215" s="10"/>
-      <c r="K215" s="10"/>
-      <c r="L215" s="10"/>
-      <c r="M215" s="10"/>
+      <c r="H215" s="11"/>
+      <c r="I215" s="11"/>
+      <c r="J215" s="11"/>
+      <c r="K215" s="11"/>
+      <c r="L215" s="11"/>
+      <c r="M215" s="11"/>
     </row>
     <row r="216" spans="8:13">
-      <c r="H216" s="10"/>
-      <c r="I216" s="10"/>
-      <c r="J216" s="10"/>
-      <c r="K216" s="10"/>
-      <c r="L216" s="10"/>
-      <c r="M216" s="10"/>
+      <c r="H216" s="11"/>
+      <c r="I216" s="11"/>
+      <c r="J216" s="11"/>
+      <c r="K216" s="11"/>
+      <c r="L216" s="11"/>
+      <c r="M216" s="11"/>
     </row>
     <row r="217" spans="8:13">
-      <c r="H217" s="10"/>
-      <c r="I217" s="10"/>
-      <c r="J217" s="10"/>
-      <c r="K217" s="10"/>
-      <c r="L217" s="10"/>
-      <c r="M217" s="10"/>
+      <c r="H217" s="11"/>
+      <c r="I217" s="11"/>
+      <c r="J217" s="11"/>
+      <c r="K217" s="11"/>
+      <c r="L217" s="11"/>
+      <c r="M217" s="11"/>
     </row>
     <row r="218" spans="8:13">
-      <c r="H218" s="10"/>
-      <c r="I218" s="10"/>
-      <c r="J218" s="10"/>
-      <c r="K218" s="10"/>
-      <c r="L218" s="10"/>
-      <c r="M218" s="10"/>
+      <c r="H218" s="11"/>
+      <c r="I218" s="11"/>
+      <c r="J218" s="11"/>
+      <c r="K218" s="11"/>
+      <c r="L218" s="11"/>
+      <c r="M218" s="11"/>
     </row>
     <row r="219" spans="8:13">
-      <c r="H219" s="10"/>
-      <c r="I219" s="10"/>
-      <c r="J219" s="10"/>
-      <c r="K219" s="10"/>
-      <c r="L219" s="10"/>
-      <c r="M219" s="10"/>
+      <c r="H219" s="11"/>
+      <c r="I219" s="11"/>
+      <c r="J219" s="11"/>
+      <c r="K219" s="11"/>
+      <c r="L219" s="11"/>
+      <c r="M219" s="11"/>
     </row>
     <row r="220" spans="8:13">
-      <c r="H220" s="10"/>
-      <c r="I220" s="10"/>
-      <c r="J220" s="10"/>
-      <c r="K220" s="10"/>
-      <c r="L220" s="10"/>
-      <c r="M220" s="10"/>
+      <c r="H220" s="11"/>
+      <c r="I220" s="11"/>
+      <c r="J220" s="11"/>
+      <c r="K220" s="11"/>
+      <c r="L220" s="11"/>
+      <c r="M220" s="11"/>
     </row>
     <row r="221" spans="8:13">
-      <c r="H221" s="10"/>
-      <c r="I221" s="10"/>
-      <c r="J221" s="10"/>
-      <c r="K221" s="10"/>
-      <c r="L221" s="10"/>
-      <c r="M221" s="10"/>
+      <c r="H221" s="11"/>
+      <c r="I221" s="11"/>
+      <c r="J221" s="11"/>
+      <c r="K221" s="11"/>
+      <c r="L221" s="11"/>
+      <c r="M221" s="11"/>
     </row>
     <row r="222" spans="8:13">
-      <c r="H222" s="10"/>
-      <c r="I222" s="10"/>
-      <c r="J222" s="10"/>
-      <c r="K222" s="10"/>
-      <c r="L222" s="10"/>
-      <c r="M222" s="10"/>
+      <c r="H222" s="11"/>
+      <c r="I222" s="11"/>
+      <c r="J222" s="11"/>
+      <c r="K222" s="11"/>
+      <c r="L222" s="11"/>
+      <c r="M222" s="11"/>
     </row>
     <row r="223" spans="8:13">
-      <c r="H223" s="10"/>
-      <c r="I223" s="10"/>
-      <c r="J223" s="10"/>
-      <c r="K223" s="10"/>
-      <c r="L223" s="10"/>
-      <c r="M223" s="10"/>
+      <c r="H223" s="11"/>
+      <c r="I223" s="11"/>
+      <c r="J223" s="11"/>
+      <c r="K223" s="11"/>
+      <c r="L223" s="11"/>
+      <c r="M223" s="11"/>
     </row>
     <row r="224" spans="8:13">
-      <c r="H224" s="10"/>
-      <c r="I224" s="10"/>
-      <c r="J224" s="10"/>
-      <c r="K224" s="10"/>
-      <c r="L224" s="10"/>
-      <c r="M224" s="10"/>
+      <c r="H224" s="11"/>
+      <c r="I224" s="11"/>
+      <c r="J224" s="11"/>
+      <c r="K224" s="11"/>
+      <c r="L224" s="11"/>
+      <c r="M224" s="11"/>
     </row>
     <row r="225" spans="8:13">
-      <c r="H225" s="10"/>
-      <c r="I225" s="10"/>
-      <c r="J225" s="10"/>
-      <c r="K225" s="10"/>
-      <c r="L225" s="10"/>
-      <c r="M225" s="10"/>
+      <c r="H225" s="11"/>
+      <c r="I225" s="11"/>
+      <c r="J225" s="11"/>
+      <c r="K225" s="11"/>
+      <c r="L225" s="11"/>
+      <c r="M225" s="11"/>
     </row>
     <row r="226" spans="8:13">
-      <c r="H226" s="10"/>
-      <c r="I226" s="10"/>
-      <c r="J226" s="10"/>
-      <c r="K226" s="10"/>
-      <c r="L226" s="10"/>
-      <c r="M226" s="10"/>
+      <c r="H226" s="11"/>
+      <c r="I226" s="11"/>
+      <c r="J226" s="11"/>
+      <c r="K226" s="11"/>
+      <c r="L226" s="11"/>
+      <c r="M226" s="11"/>
     </row>
     <row r="227" spans="8:13">
-      <c r="H227" s="10"/>
-      <c r="I227" s="10"/>
-      <c r="J227" s="10"/>
-      <c r="K227" s="10"/>
-      <c r="L227" s="10"/>
-      <c r="M227" s="10"/>
+      <c r="H227" s="11"/>
+      <c r="I227" s="11"/>
+      <c r="J227" s="11"/>
+      <c r="K227" s="11"/>
+      <c r="L227" s="11"/>
+      <c r="M227" s="11"/>
     </row>
     <row r="228" spans="8:13">
-      <c r="H228" s="10"/>
-      <c r="I228" s="10"/>
-      <c r="J228" s="10"/>
-      <c r="K228" s="10"/>
-      <c r="L228" s="10"/>
-      <c r="M228" s="10"/>
+      <c r="H228" s="11"/>
+      <c r="I228" s="11"/>
+      <c r="J228" s="11"/>
+      <c r="K228" s="11"/>
+      <c r="L228" s="11"/>
+      <c r="M228" s="11"/>
     </row>
     <row r="229" spans="8:13">
-      <c r="H229" s="10"/>
-      <c r="I229" s="10"/>
-      <c r="J229" s="10"/>
-      <c r="K229" s="10"/>
-      <c r="L229" s="10"/>
-      <c r="M229" s="10"/>
+      <c r="H229" s="11"/>
+      <c r="I229" s="11"/>
+      <c r="J229" s="11"/>
+      <c r="K229" s="11"/>
+      <c r="L229" s="11"/>
+      <c r="M229" s="11"/>
     </row>
     <row r="230" spans="8:13">
-      <c r="H230" s="10"/>
-      <c r="I230" s="10"/>
-      <c r="J230" s="10"/>
-      <c r="K230" s="10"/>
-      <c r="L230" s="10"/>
-      <c r="M230" s="10"/>
+      <c r="H230" s="11"/>
+      <c r="I230" s="11"/>
+      <c r="J230" s="11"/>
+      <c r="K230" s="11"/>
+      <c r="L230" s="11"/>
+      <c r="M230" s="11"/>
     </row>
     <row r="231" spans="8:13">
-      <c r="H231" s="10"/>
-      <c r="I231" s="10"/>
-      <c r="J231" s="10"/>
-      <c r="K231" s="10"/>
-      <c r="L231" s="10"/>
-      <c r="M231" s="10"/>
+      <c r="H231" s="11"/>
+      <c r="I231" s="11"/>
+      <c r="J231" s="11"/>
+      <c r="K231" s="11"/>
+      <c r="L231" s="11"/>
+      <c r="M231" s="11"/>
     </row>
     <row r="232" spans="8:13">
-      <c r="H232" s="10"/>
-      <c r="I232" s="10"/>
-      <c r="J232" s="10"/>
-      <c r="K232" s="10"/>
-      <c r="L232" s="10"/>
-      <c r="M232" s="10"/>
+      <c r="H232" s="11"/>
+      <c r="I232" s="11"/>
+      <c r="J232" s="11"/>
+      <c r="K232" s="11"/>
+      <c r="L232" s="11"/>
+      <c r="M232" s="11"/>
     </row>
     <row r="233" spans="8:13">
-      <c r="H233" s="10"/>
-      <c r="I233" s="10"/>
-      <c r="J233" s="10"/>
-      <c r="K233" s="10"/>
-      <c r="L233" s="10"/>
-      <c r="M233" s="10"/>
+      <c r="H233" s="11"/>
+      <c r="I233" s="11"/>
+      <c r="J233" s="11"/>
+      <c r="K233" s="11"/>
+      <c r="L233" s="11"/>
+      <c r="M233" s="11"/>
     </row>
     <row r="234" spans="8:13">
-      <c r="H234" s="10"/>
-      <c r="I234" s="10"/>
-      <c r="J234" s="10"/>
-      <c r="K234" s="10"/>
-      <c r="L234" s="10"/>
-      <c r="M234" s="10"/>
+      <c r="H234" s="11"/>
+      <c r="I234" s="11"/>
+      <c r="J234" s="11"/>
+      <c r="K234" s="11"/>
+      <c r="L234" s="11"/>
+      <c r="M234" s="11"/>
     </row>
     <row r="235" spans="8:13">
-      <c r="H235" s="10"/>
-      <c r="I235" s="10"/>
-      <c r="J235" s="10"/>
-      <c r="K235" s="10"/>
-      <c r="L235" s="10"/>
-      <c r="M235" s="10"/>
+      <c r="H235" s="11"/>
+      <c r="I235" s="11"/>
+      <c r="J235" s="11"/>
+      <c r="K235" s="11"/>
+      <c r="L235" s="11"/>
+      <c r="M235" s="11"/>
     </row>
     <row r="236" spans="8:13">
-      <c r="H236" s="10"/>
-      <c r="I236" s="10"/>
-      <c r="J236" s="10"/>
-      <c r="K236" s="10"/>
-      <c r="L236" s="10"/>
-      <c r="M236" s="10"/>
+      <c r="H236" s="11"/>
+      <c r="I236" s="11"/>
+      <c r="J236" s="11"/>
+      <c r="K236" s="11"/>
+      <c r="L236" s="11"/>
+      <c r="M236" s="11"/>
     </row>
     <row r="237" spans="8:13">
-      <c r="H237" s="10"/>
-      <c r="I237" s="10"/>
-      <c r="J237" s="10"/>
-      <c r="K237" s="10"/>
-      <c r="L237" s="10"/>
-      <c r="M237" s="10"/>
+      <c r="H237" s="11"/>
+      <c r="I237" s="11"/>
+      <c r="J237" s="11"/>
+      <c r="K237" s="11"/>
+      <c r="L237" s="11"/>
+      <c r="M237" s="11"/>
     </row>
     <row r="238" spans="8:13">
-      <c r="H238" s="10"/>
-      <c r="I238" s="10"/>
-      <c r="J238" s="10"/>
-      <c r="K238" s="10"/>
-      <c r="L238" s="10"/>
-      <c r="M238" s="10"/>
+      <c r="H238" s="11"/>
+      <c r="I238" s="11"/>
+      <c r="J238" s="11"/>
+      <c r="K238" s="11"/>
+      <c r="L238" s="11"/>
+      <c r="M238" s="11"/>
     </row>
     <row r="239" spans="8:13">
-      <c r="H239" s="10"/>
-      <c r="I239" s="10"/>
-      <c r="J239" s="10"/>
-      <c r="K239" s="10"/>
-      <c r="L239" s="10"/>
-      <c r="M239" s="10"/>
+      <c r="H239" s="11"/>
+      <c r="I239" s="11"/>
+      <c r="J239" s="11"/>
+      <c r="K239" s="11"/>
+      <c r="L239" s="11"/>
+      <c r="M239" s="11"/>
     </row>
     <row r="240" spans="8:13">
-      <c r="H240" s="10"/>
-      <c r="I240" s="10"/>
-      <c r="J240" s="10"/>
-      <c r="K240" s="10"/>
-      <c r="L240" s="10"/>
-      <c r="M240" s="10"/>
+      <c r="H240" s="11"/>
+      <c r="I240" s="11"/>
+      <c r="J240" s="11"/>
+      <c r="K240" s="11"/>
+      <c r="L240" s="11"/>
+      <c r="M240" s="11"/>
     </row>
     <row r="241" spans="8:13">
-      <c r="H241" s="10"/>
-      <c r="I241" s="10"/>
-      <c r="J241" s="10"/>
-      <c r="K241" s="10"/>
-      <c r="L241" s="10"/>
-      <c r="M241" s="10"/>
+      <c r="H241" s="11"/>
+      <c r="I241" s="11"/>
+      <c r="J241" s="11"/>
+      <c r="K241" s="11"/>
+      <c r="L241" s="11"/>
+      <c r="M241" s="11"/>
     </row>
     <row r="242" spans="8:13">
-      <c r="H242" s="10"/>
-      <c r="I242" s="10"/>
-      <c r="J242" s="10"/>
-      <c r="K242" s="10"/>
-      <c r="L242" s="10"/>
-      <c r="M242" s="10"/>
+      <c r="H242" s="11"/>
+      <c r="I242" s="11"/>
+      <c r="J242" s="11"/>
+      <c r="K242" s="11"/>
+      <c r="L242" s="11"/>
+      <c r="M242" s="11"/>
     </row>
     <row r="243" spans="8:13">
-      <c r="H243" s="10"/>
-      <c r="I243" s="10"/>
-      <c r="J243" s="10"/>
-      <c r="K243" s="10"/>
-      <c r="L243" s="10"/>
-      <c r="M243" s="10"/>
+      <c r="H243" s="11"/>
+      <c r="I243" s="11"/>
+      <c r="J243" s="11"/>
+      <c r="K243" s="11"/>
+      <c r="L243" s="11"/>
+      <c r="M243" s="11"/>
     </row>
     <row r="244" spans="8:13">
-      <c r="H244" s="10"/>
-      <c r="I244" s="10"/>
-      <c r="J244" s="10"/>
-      <c r="K244" s="10"/>
-      <c r="L244" s="10"/>
-      <c r="M244" s="10"/>
+      <c r="H244" s="11"/>
+      <c r="I244" s="11"/>
+      <c r="J244" s="11"/>
+      <c r="K244" s="11"/>
+      <c r="L244" s="11"/>
+      <c r="M244" s="11"/>
     </row>
     <row r="245" spans="8:13">
-      <c r="H245" s="10"/>
-      <c r="I245" s="10"/>
-      <c r="J245" s="10"/>
-      <c r="K245" s="10"/>
-      <c r="L245" s="10"/>
-      <c r="M245" s="10"/>
+      <c r="H245" s="11"/>
+      <c r="I245" s="11"/>
+      <c r="J245" s="11"/>
+      <c r="K245" s="11"/>
+      <c r="L245" s="11"/>
+      <c r="M245" s="11"/>
     </row>
     <row r="246" spans="8:13">
-      <c r="H246" s="10"/>
-      <c r="I246" s="10"/>
-      <c r="J246" s="10"/>
-      <c r="K246" s="10"/>
-      <c r="L246" s="10"/>
-      <c r="M246" s="10"/>
+      <c r="H246" s="11"/>
+      <c r="I246" s="11"/>
+      <c r="J246" s="11"/>
+      <c r="K246" s="11"/>
+      <c r="L246" s="11"/>
+      <c r="M246" s="11"/>
     </row>
     <row r="247" spans="8:13">
-      <c r="H247" s="10"/>
-      <c r="I247" s="10"/>
-      <c r="J247" s="10"/>
-      <c r="K247" s="10"/>
-      <c r="L247" s="10"/>
-      <c r="M247" s="10"/>
+      <c r="H247" s="11"/>
+      <c r="I247" s="11"/>
+      <c r="J247" s="11"/>
+      <c r="K247" s="11"/>
+      <c r="L247" s="11"/>
+      <c r="M247" s="11"/>
     </row>
     <row r="248" spans="8:13">
-      <c r="H248" s="10"/>
-      <c r="I248" s="10"/>
-      <c r="J248" s="10"/>
-      <c r="K248" s="10"/>
-      <c r="L248" s="10"/>
-      <c r="M248" s="10"/>
+      <c r="H248" s="11"/>
+      <c r="I248" s="11"/>
+      <c r="J248" s="11"/>
+      <c r="K248" s="11"/>
+      <c r="L248" s="11"/>
+      <c r="M248" s="11"/>
     </row>
     <row r="249" spans="8:13">
-      <c r="H249" s="10"/>
-      <c r="I249" s="10"/>
-      <c r="J249" s="10"/>
-      <c r="K249" s="10"/>
-      <c r="L249" s="10"/>
-      <c r="M249" s="10"/>
+      <c r="H249" s="11"/>
+      <c r="I249" s="11"/>
+      <c r="J249" s="11"/>
+      <c r="K249" s="11"/>
+      <c r="L249" s="11"/>
+      <c r="M249" s="11"/>
     </row>
     <row r="250" spans="8:13">
-      <c r="H250" s="10"/>
-      <c r="I250" s="10"/>
-      <c r="J250" s="10"/>
-      <c r="K250" s="10"/>
-      <c r="L250" s="10"/>
-      <c r="M250" s="10"/>
+      <c r="H250" s="11"/>
+      <c r="I250" s="11"/>
+      <c r="J250" s="11"/>
+      <c r="K250" s="11"/>
+      <c r="L250" s="11"/>
+      <c r="M250" s="11"/>
     </row>
     <row r="251" spans="8:13">
-      <c r="H251" s="10"/>
-      <c r="I251" s="10"/>
-      <c r="J251" s="10"/>
-      <c r="K251" s="10"/>
-      <c r="L251" s="10"/>
-      <c r="M251" s="10"/>
+      <c r="H251" s="11"/>
+      <c r="I251" s="11"/>
+      <c r="J251" s="11"/>
+      <c r="K251" s="11"/>
+      <c r="L251" s="11"/>
+      <c r="M251" s="11"/>
     </row>
     <row r="252" spans="8:13">
-      <c r="H252" s="10"/>
-      <c r="I252" s="10"/>
-      <c r="J252" s="10"/>
-      <c r="K252" s="10"/>
-      <c r="L252" s="10"/>
-      <c r="M252" s="10"/>
+      <c r="H252" s="11"/>
+      <c r="I252" s="11"/>
+      <c r="J252" s="11"/>
+      <c r="K252" s="11"/>
+      <c r="L252" s="11"/>
+      <c r="M252" s="11"/>
     </row>
     <row r="253" spans="8:13">
-      <c r="H253" s="10"/>
-      <c r="I253" s="10"/>
-      <c r="J253" s="10"/>
-      <c r="K253" s="10"/>
-      <c r="L253" s="10"/>
-      <c r="M253" s="10"/>
+      <c r="H253" s="11"/>
+      <c r="I253" s="11"/>
+      <c r="J253" s="11"/>
+      <c r="K253" s="11"/>
+      <c r="L253" s="11"/>
+      <c r="M253" s="11"/>
     </row>
     <row r="254" spans="8:13">
-      <c r="H254" s="10"/>
-      <c r="I254" s="10"/>
-      <c r="J254" s="10"/>
-      <c r="K254" s="10"/>
-      <c r="L254" s="10"/>
-      <c r="M254" s="10"/>
+      <c r="H254" s="11"/>
+      <c r="I254" s="11"/>
+      <c r="J254" s="11"/>
+      <c r="K254" s="11"/>
+      <c r="L254" s="11"/>
+      <c r="M254" s="11"/>
     </row>
     <row r="255" spans="8:13">
-      <c r="H255" s="10"/>
-      <c r="I255" s="10"/>
-      <c r="J255" s="10"/>
-      <c r="K255" s="10"/>
-      <c r="L255" s="10"/>
-      <c r="M255" s="10"/>
+      <c r="H255" s="11"/>
+      <c r="I255" s="11"/>
+      <c r="J255" s="11"/>
+      <c r="K255" s="11"/>
+      <c r="L255" s="11"/>
+      <c r="M255" s="11"/>
     </row>
     <row r="256" spans="8:13">
-      <c r="H256" s="10"/>
-      <c r="I256" s="10"/>
-      <c r="J256" s="10"/>
-      <c r="K256" s="10"/>
-      <c r="L256" s="10"/>
-      <c r="M256" s="10"/>
+      <c r="H256" s="11"/>
+      <c r="I256" s="11"/>
+      <c r="J256" s="11"/>
+      <c r="K256" s="11"/>
+      <c r="L256" s="11"/>
+      <c r="M256" s="11"/>
     </row>
     <row r="257" spans="8:13">
-      <c r="H257" s="10"/>
-      <c r="I257" s="10"/>
-      <c r="J257" s="10"/>
-      <c r="K257" s="10"/>
-      <c r="L257" s="10"/>
-      <c r="M257" s="10"/>
+      <c r="H257" s="11"/>
+      <c r="I257" s="11"/>
+      <c r="J257" s="11"/>
+      <c r="K257" s="11"/>
+      <c r="L257" s="11"/>
+      <c r="M257" s="11"/>
     </row>
     <row r="258" spans="8:13">
-      <c r="H258" s="10"/>
-      <c r="I258" s="10"/>
-      <c r="J258" s="10"/>
-      <c r="K258" s="10"/>
-      <c r="L258" s="10"/>
-      <c r="M258" s="10"/>
+      <c r="H258" s="11"/>
+      <c r="I258" s="11"/>
+      <c r="J258" s="11"/>
+      <c r="K258" s="11"/>
+      <c r="L258" s="11"/>
+      <c r="M258" s="11"/>
     </row>
     <row r="259" spans="8:13">
-      <c r="H259" s="10"/>
-      <c r="I259" s="10"/>
-      <c r="J259" s="10"/>
-      <c r="K259" s="10"/>
-      <c r="L259" s="10"/>
-      <c r="M259" s="10"/>
+      <c r="H259" s="11"/>
+      <c r="I259" s="11"/>
+      <c r="J259" s="11"/>
+      <c r="K259" s="11"/>
+      <c r="L259" s="11"/>
+      <c r="M259" s="11"/>
     </row>
     <row r="260" spans="8:13">
-      <c r="H260" s="10"/>
-      <c r="I260" s="10"/>
-      <c r="J260" s="10"/>
-      <c r="K260" s="10"/>
-      <c r="L260" s="10"/>
-      <c r="M260" s="10"/>
+      <c r="H260" s="11"/>
+      <c r="I260" s="11"/>
+      <c r="J260" s="11"/>
+      <c r="K260" s="11"/>
+      <c r="L260" s="11"/>
+      <c r="M260" s="11"/>
     </row>
     <row r="261" spans="8:13">
-      <c r="H261" s="10"/>
-      <c r="I261" s="10"/>
-      <c r="J261" s="10"/>
-      <c r="K261" s="10"/>
-      <c r="L261" s="10"/>
-      <c r="M261" s="10"/>
+      <c r="H261" s="11"/>
+      <c r="I261" s="11"/>
+      <c r="J261" s="11"/>
+      <c r="K261" s="11"/>
+      <c r="L261" s="11"/>
+      <c r="M261" s="11"/>
     </row>
     <row r="262" spans="8:13">
-      <c r="H262" s="10"/>
-      <c r="I262" s="10"/>
-      <c r="J262" s="10"/>
-      <c r="K262" s="10"/>
-      <c r="L262" s="10"/>
-      <c r="M262" s="10"/>
+      <c r="H262" s="11"/>
+      <c r="I262" s="11"/>
+      <c r="J262" s="11"/>
+      <c r="K262" s="11"/>
+      <c r="L262" s="11"/>
+      <c r="M262" s="11"/>
     </row>
     <row r="263" spans="8:13">
-      <c r="H263" s="10"/>
-      <c r="I263" s="10"/>
-      <c r="J263" s="10"/>
-      <c r="K263" s="10"/>
-      <c r="L263" s="10"/>
-      <c r="M263" s="10"/>
+      <c r="H263" s="11"/>
+      <c r="I263" s="11"/>
+      <c r="J263" s="11"/>
+      <c r="K263" s="11"/>
+      <c r="L263" s="11"/>
+      <c r="M263" s="11"/>
     </row>
     <row r="264" spans="8:13">
-      <c r="H264" s="10"/>
-      <c r="I264" s="10"/>
-      <c r="J264" s="10"/>
-      <c r="K264" s="10"/>
-      <c r="L264" s="10"/>
-      <c r="M264" s="10"/>
+      <c r="H264" s="11"/>
+      <c r="I264" s="11"/>
+      <c r="J264" s="11"/>
+      <c r="K264" s="11"/>
+      <c r="L264" s="11"/>
+      <c r="M264" s="11"/>
     </row>
     <row r="265" spans="8:13">
-      <c r="H265" s="10"/>
-      <c r="I265" s="10"/>
-      <c r="J265" s="10"/>
-      <c r="K265" s="10"/>
-      <c r="L265" s="10"/>
-      <c r="M265" s="10"/>
+      <c r="H265" s="11"/>
+      <c r="I265" s="11"/>
+      <c r="J265" s="11"/>
+      <c r="K265" s="11"/>
+      <c r="L265" s="11"/>
+      <c r="M265" s="11"/>
     </row>
     <row r="266" spans="8:13">
-      <c r="H266" s="10"/>
-      <c r="I266" s="10"/>
-      <c r="J266" s="10"/>
-      <c r="K266" s="10"/>
-      <c r="L266" s="10"/>
-      <c r="M266" s="10"/>
+      <c r="H266" s="11"/>
+      <c r="I266" s="11"/>
+      <c r="J266" s="11"/>
+      <c r="K266" s="11"/>
+      <c r="L266" s="11"/>
+      <c r="M266" s="11"/>
     </row>
     <row r="267" spans="8:13">
-      <c r="H267" s="10"/>
-      <c r="I267" s="10"/>
-      <c r="J267" s="10"/>
-      <c r="K267" s="10"/>
-      <c r="L267" s="10"/>
-      <c r="M267" s="10"/>
+      <c r="H267" s="11"/>
+      <c r="I267" s="11"/>
+      <c r="J267" s="11"/>
+      <c r="K267" s="11"/>
+      <c r="L267" s="11"/>
+      <c r="M267" s="11"/>
     </row>
     <row r="268" spans="8:13">
-      <c r="H268" s="10"/>
-      <c r="I268" s="10"/>
-      <c r="J268" s="10"/>
-      <c r="K268" s="10"/>
-      <c r="L268" s="10"/>
-      <c r="M268" s="10"/>
+      <c r="H268" s="11"/>
+      <c r="I268" s="11"/>
+      <c r="J268" s="11"/>
+      <c r="K268" s="11"/>
+      <c r="L268" s="11"/>
+      <c r="M268" s="11"/>
     </row>
     <row r="269" spans="8:13">
-      <c r="H269" s="10"/>
-      <c r="I269" s="10"/>
-      <c r="J269" s="10"/>
-      <c r="K269" s="10"/>
-      <c r="L269" s="10"/>
-      <c r="M269" s="10"/>
+      <c r="H269" s="11"/>
+      <c r="I269" s="11"/>
+      <c r="J269" s="11"/>
+      <c r="K269" s="11"/>
+      <c r="L269" s="11"/>
+      <c r="M269" s="11"/>
     </row>
     <row r="270" spans="8:13">
-      <c r="H270" s="10"/>
-      <c r="I270" s="10"/>
-      <c r="J270" s="10"/>
-      <c r="K270" s="10"/>
-      <c r="L270" s="10"/>
-      <c r="M270" s="10"/>
+      <c r="H270" s="11"/>
+      <c r="I270" s="11"/>
+      <c r="J270" s="11"/>
+      <c r="K270" s="11"/>
+      <c r="L270" s="11"/>
+      <c r="M270" s="11"/>
     </row>
     <row r="271" spans="8:13">
-      <c r="H271" s="10"/>
-      <c r="I271" s="10"/>
-      <c r="J271" s="10"/>
-      <c r="K271" s="10"/>
-      <c r="L271" s="10"/>
-      <c r="M271" s="10"/>
+      <c r="H271" s="11"/>
+      <c r="I271" s="11"/>
+      <c r="J271" s="11"/>
+      <c r="K271" s="11"/>
+      <c r="L271" s="11"/>
+      <c r="M271" s="11"/>
     </row>
     <row r="272" spans="8:13">
-      <c r="H272" s="10"/>
-      <c r="I272" s="10"/>
-      <c r="J272" s="10"/>
-      <c r="K272" s="10"/>
-      <c r="L272" s="10"/>
-      <c r="M272" s="10"/>
+      <c r="H272" s="11"/>
+      <c r="I272" s="11"/>
+      <c r="J272" s="11"/>
+      <c r="K272" s="11"/>
+      <c r="L272" s="11"/>
+      <c r="M272" s="11"/>
     </row>
     <row r="273" spans="8:13">
-      <c r="H273" s="10"/>
-      <c r="I273" s="10"/>
-      <c r="J273" s="10"/>
-      <c r="K273" s="10"/>
-      <c r="L273" s="10"/>
-      <c r="M273" s="10"/>
+      <c r="H273" s="11"/>
+      <c r="I273" s="11"/>
+      <c r="J273" s="11"/>
+      <c r="K273" s="11"/>
+      <c r="L273" s="11"/>
+      <c r="M273" s="11"/>
     </row>
     <row r="274" spans="8:13">
-      <c r="H274" s="10"/>
-      <c r="I274" s="10"/>
-      <c r="J274" s="10"/>
-      <c r="K274" s="10"/>
-      <c r="L274" s="10"/>
-      <c r="M274" s="10"/>
+      <c r="H274" s="11"/>
+      <c r="I274" s="11"/>
+      <c r="J274" s="11"/>
+      <c r="K274" s="11"/>
+      <c r="L274" s="11"/>
+      <c r="M274" s="11"/>
     </row>
     <row r="275" spans="8:13">
-      <c r="H275" s="10"/>
-      <c r="I275" s="10"/>
-      <c r="J275" s="10"/>
-      <c r="K275" s="10"/>
-      <c r="L275" s="10"/>
-      <c r="M275" s="10"/>
+      <c r="H275" s="11"/>
+      <c r="I275" s="11"/>
+      <c r="J275" s="11"/>
+      <c r="K275" s="11"/>
+      <c r="L275" s="11"/>
+      <c r="M275" s="11"/>
     </row>
     <row r="276" spans="8:13">
-      <c r="H276" s="10"/>
-      <c r="I276" s="10"/>
-      <c r="J276" s="10"/>
-      <c r="K276" s="10"/>
-      <c r="L276" s="10"/>
-      <c r="M276" s="10"/>
+      <c r="H276" s="11"/>
+      <c r="I276" s="11"/>
+      <c r="J276" s="11"/>
+      <c r="K276" s="11"/>
+      <c r="L276" s="11"/>
+      <c r="M276" s="11"/>
     </row>
     <row r="277" spans="8:13">
-      <c r="H277" s="10"/>
-      <c r="I277" s="10"/>
-      <c r="J277" s="10"/>
-      <c r="K277" s="10"/>
-      <c r="L277" s="10"/>
-      <c r="M277" s="10"/>
+      <c r="H277" s="11"/>
+      <c r="I277" s="11"/>
+      <c r="J277" s="11"/>
+      <c r="K277" s="11"/>
+      <c r="L277" s="11"/>
+      <c r="M277" s="11"/>
     </row>
     <row r="278" spans="8:13">
-      <c r="H278" s="10"/>
-      <c r="I278" s="10"/>
-      <c r="J278" s="10"/>
-      <c r="K278" s="10"/>
-      <c r="L278" s="10"/>
-      <c r="M278" s="10"/>
+      <c r="H278" s="11"/>
+      <c r="I278" s="11"/>
+      <c r="J278" s="11"/>
+      <c r="K278" s="11"/>
+      <c r="L278" s="11"/>
+      <c r="M278" s="11"/>
     </row>
     <row r="279" spans="8:13">
-      <c r="H279" s="10"/>
-      <c r="I279" s="10"/>
-      <c r="J279" s="10"/>
-      <c r="K279" s="10"/>
-      <c r="L279" s="10"/>
-      <c r="M279" s="10"/>
+      <c r="H279" s="11"/>
+      <c r="I279" s="11"/>
+      <c r="J279" s="11"/>
+      <c r="K279" s="11"/>
+      <c r="L279" s="11"/>
+      <c r="M279" s="11"/>
     </row>
     <row r="280" spans="8:13">
-      <c r="H280" s="10"/>
-      <c r="I280" s="10"/>
-      <c r="J280" s="10"/>
-      <c r="K280" s="10"/>
-      <c r="L280" s="10"/>
-      <c r="M280" s="10"/>
+      <c r="H280" s="11"/>
+      <c r="I280" s="11"/>
+      <c r="J280" s="11"/>
+      <c r="K280" s="11"/>
+      <c r="L280" s="11"/>
+      <c r="M280" s="11"/>
     </row>
     <row r="281" spans="8:13">
-      <c r="H281" s="10"/>
-      <c r="I281" s="10"/>
-      <c r="J281" s="10"/>
-      <c r="K281" s="10"/>
-      <c r="L281" s="10"/>
-      <c r="M281" s="10"/>
+      <c r="H281" s="11"/>
+      <c r="I281" s="11"/>
+      <c r="J281" s="11"/>
+      <c r="K281" s="11"/>
+      <c r="L281" s="11"/>
+      <c r="M281" s="11"/>
     </row>
     <row r="282" spans="8:13">
-      <c r="H282" s="10"/>
-      <c r="I282" s="10"/>
-      <c r="J282" s="10"/>
-      <c r="K282" s="10"/>
-      <c r="L282" s="10"/>
-      <c r="M282" s="10"/>
+      <c r="H282" s="11"/>
+      <c r="I282" s="11"/>
+      <c r="J282" s="11"/>
+      <c r="K282" s="11"/>
+      <c r="L282" s="11"/>
+      <c r="M282" s="11"/>
     </row>
     <row r="283" spans="8:13">
-      <c r="H283" s="10"/>
-      <c r="I283" s="10"/>
-      <c r="J283" s="10"/>
-      <c r="K283" s="10"/>
-      <c r="L283" s="10"/>
-      <c r="M283" s="10"/>
+      <c r="H283" s="11"/>
+      <c r="I283" s="11"/>
+      <c r="J283" s="11"/>
+      <c r="K283" s="11"/>
+      <c r="L283" s="11"/>
+      <c r="M283" s="11"/>
     </row>
     <row r="284" spans="8:13">
-      <c r="H284" s="10"/>
-      <c r="I284" s="10"/>
-      <c r="J284" s="10"/>
-      <c r="K284" s="10"/>
-      <c r="L284" s="10"/>
-      <c r="M284" s="10"/>
+      <c r="H284" s="11"/>
+      <c r="I284" s="11"/>
+      <c r="J284" s="11"/>
+      <c r="K284" s="11"/>
+      <c r="L284" s="11"/>
+      <c r="M284" s="11"/>
     </row>
     <row r="285" spans="8:13">
-      <c r="H285" s="10"/>
-      <c r="I285" s="10"/>
-      <c r="J285" s="10"/>
-      <c r="K285" s="10"/>
-      <c r="L285" s="10"/>
-      <c r="M285" s="10"/>
+      <c r="H285" s="11"/>
+      <c r="I285" s="11"/>
+      <c r="J285" s="11"/>
+      <c r="K285" s="11"/>
+      <c r="L285" s="11"/>
+      <c r="M285" s="11"/>
     </row>
     <row r="286" spans="8:13">
-      <c r="H286" s="10"/>
-      <c r="I286" s="10"/>
-      <c r="J286" s="10"/>
-      <c r="K286" s="10"/>
-      <c r="L286" s="10"/>
-      <c r="M286" s="10"/>
+      <c r="H286" s="11"/>
+      <c r="I286" s="11"/>
+      <c r="J286" s="11"/>
+      <c r="K286" s="11"/>
+      <c r="L286" s="11"/>
+      <c r="M286" s="11"/>
     </row>
     <row r="287" spans="8:13">
-      <c r="H287" s="10"/>
-      <c r="I287" s="10"/>
-      <c r="J287" s="10"/>
-      <c r="K287" s="10"/>
-      <c r="L287" s="10"/>
-      <c r="M287" s="10"/>
+      <c r="H287" s="11"/>
+      <c r="I287" s="11"/>
+      <c r="J287" s="11"/>
+      <c r="K287" s="11"/>
+      <c r="L287" s="11"/>
+      <c r="M287" s="11"/>
     </row>
     <row r="288" spans="8:13">
-      <c r="H288" s="10"/>
-      <c r="I288" s="10"/>
-      <c r="J288" s="10"/>
-      <c r="K288" s="10"/>
-      <c r="L288" s="10"/>
-      <c r="M288" s="10"/>
+      <c r="H288" s="11"/>
+      <c r="I288" s="11"/>
+      <c r="J288" s="11"/>
+      <c r="K288" s="11"/>
+      <c r="L288" s="11"/>
+      <c r="M288" s="11"/>
     </row>
     <row r="289" spans="8:13">
-      <c r="H289" s="10"/>
-      <c r="I289" s="10"/>
-      <c r="J289" s="10"/>
-      <c r="K289" s="10"/>
-      <c r="L289" s="10"/>
-      <c r="M289" s="10"/>
+      <c r="H289" s="11"/>
+      <c r="I289" s="11"/>
+      <c r="J289" s="11"/>
+      <c r="K289" s="11"/>
+      <c r="L289" s="11"/>
+      <c r="M289" s="11"/>
     </row>
     <row r="290" spans="8:13">
-      <c r="H290" s="10"/>
-      <c r="I290" s="10"/>
-      <c r="J290" s="10"/>
-      <c r="K290" s="10"/>
-      <c r="L290" s="10"/>
-      <c r="M290" s="10"/>
+      <c r="H290" s="11"/>
+      <c r="I290" s="11"/>
+      <c r="J290" s="11"/>
+      <c r="K290" s="11"/>
+      <c r="L290" s="11"/>
+      <c r="M290" s="11"/>
     </row>
     <row r="291" spans="8:13">
-      <c r="H291" s="10"/>
-      <c r="I291" s="10"/>
-      <c r="J291" s="10"/>
-      <c r="K291" s="10"/>
-      <c r="L291" s="10"/>
-      <c r="M291" s="10"/>
+      <c r="H291" s="11"/>
+      <c r="I291" s="11"/>
+      <c r="J291" s="11"/>
+      <c r="K291" s="11"/>
+      <c r="L291" s="11"/>
+      <c r="M291" s="11"/>
     </row>
     <row r="292" spans="8:13">
-      <c r="H292" s="10"/>
-      <c r="I292" s="10"/>
-      <c r="J292" s="10"/>
-      <c r="K292" s="10"/>
-      <c r="L292" s="10"/>
-      <c r="M292" s="10"/>
+      <c r="H292" s="11"/>
+      <c r="I292" s="11"/>
+      <c r="J292" s="11"/>
+      <c r="K292" s="11"/>
+      <c r="L292" s="11"/>
+      <c r="M292" s="11"/>
     </row>
     <row r="293" spans="8:13">
-      <c r="H293" s="10"/>
-      <c r="I293" s="10"/>
-      <c r="J293" s="10"/>
-      <c r="K293" s="10"/>
-      <c r="L293" s="10"/>
-      <c r="M293" s="10"/>
+      <c r="H293" s="11"/>
+      <c r="I293" s="11"/>
+      <c r="J293" s="11"/>
+      <c r="K293" s="11"/>
+      <c r="L293" s="11"/>
+      <c r="M293" s="11"/>
     </row>
     <row r="294" spans="8:13">
-      <c r="H294" s="10"/>
-      <c r="I294" s="10"/>
-      <c r="J294" s="10"/>
-      <c r="K294" s="10"/>
-      <c r="L294" s="10"/>
-      <c r="M294" s="10"/>
+      <c r="H294" s="11"/>
+      <c r="I294" s="11"/>
+      <c r="J294" s="11"/>
+      <c r="K294" s="11"/>
+      <c r="L294" s="11"/>
+      <c r="M294" s="11"/>
     </row>
     <row r="295" spans="8:13">
-      <c r="H295" s="10"/>
-      <c r="I295" s="10"/>
-      <c r="J295" s="10"/>
-      <c r="K295" s="10"/>
-      <c r="L295" s="10"/>
-      <c r="M295" s="10"/>
+      <c r="H295" s="11"/>
+      <c r="I295" s="11"/>
+      <c r="J295" s="11"/>
+      <c r="K295" s="11"/>
+      <c r="L295" s="11"/>
+      <c r="M295" s="11"/>
     </row>
     <row r="296" spans="8:13">
-      <c r="H296" s="10"/>
-      <c r="I296" s="10"/>
-      <c r="J296" s="10"/>
-      <c r="K296" s="10"/>
-      <c r="L296" s="10"/>
-      <c r="M296" s="10"/>
+      <c r="H296" s="11"/>
+      <c r="I296" s="11"/>
+      <c r="J296" s="11"/>
+      <c r="K296" s="11"/>
+      <c r="L296" s="11"/>
+      <c r="M296" s="11"/>
     </row>
     <row r="297" spans="8:13">
-      <c r="H297" s="10"/>
-      <c r="I297" s="10"/>
-      <c r="J297" s="10"/>
-      <c r="K297" s="10"/>
-      <c r="L297" s="10"/>
-      <c r="M297" s="10"/>
+      <c r="H297" s="11"/>
+      <c r="I297" s="11"/>
+      <c r="J297" s="11"/>
+      <c r="K297" s="11"/>
+      <c r="L297" s="11"/>
+      <c r="M297" s="11"/>
     </row>
     <row r="298" spans="8:13">
-      <c r="H298" s="10"/>
-      <c r="I298" s="10"/>
-      <c r="J298" s="10"/>
-      <c r="K298" s="10"/>
-      <c r="L298" s="10"/>
-      <c r="M298" s="10"/>
+      <c r="H298" s="11"/>
+      <c r="I298" s="11"/>
+      <c r="J298" s="11"/>
+      <c r="K298" s="11"/>
+      <c r="L298" s="11"/>
+      <c r="M298" s="11"/>
     </row>
     <row r="299" spans="8:13">
-      <c r="H299" s="10"/>
-      <c r="I299" s="10"/>
-      <c r="J299" s="10"/>
-      <c r="K299" s="10"/>
-      <c r="L299" s="10"/>
-      <c r="M299" s="10"/>
+      <c r="H299" s="11"/>
+      <c r="I299" s="11"/>
+      <c r="J299" s="11"/>
+      <c r="K299" s="11"/>
+      <c r="L299" s="11"/>
+      <c r="M299" s="11"/>
     </row>
     <row r="300" spans="8:13">
-      <c r="H300" s="10"/>
-      <c r="I300" s="10"/>
-      <c r="J300" s="10"/>
-      <c r="K300" s="10"/>
-      <c r="L300" s="10"/>
-      <c r="M300" s="10"/>
+      <c r="H300" s="11"/>
+      <c r="I300" s="11"/>
+      <c r="J300" s="11"/>
+      <c r="K300" s="11"/>
+      <c r="L300" s="11"/>
+      <c r="M300" s="11"/>
     </row>
     <row r="301" spans="8:13">
-      <c r="H301" s="10"/>
-      <c r="I301" s="10"/>
-      <c r="J301" s="10"/>
-      <c r="K301" s="10"/>
-      <c r="L301" s="10"/>
-      <c r="M301" s="10"/>
+      <c r="H301" s="11"/>
+      <c r="I301" s="11"/>
+      <c r="J301" s="11"/>
+      <c r="K301" s="11"/>
+      <c r="L301" s="11"/>
+      <c r="M301" s="11"/>
     </row>
     <row r="302" spans="8:13">
-      <c r="H302" s="10"/>
-      <c r="I302" s="10"/>
-      <c r="J302" s="10"/>
-      <c r="K302" s="10"/>
-      <c r="L302" s="10"/>
-      <c r="M302" s="10"/>
+      <c r="H302" s="11"/>
+      <c r="I302" s="11"/>
+      <c r="J302" s="11"/>
+      <c r="K302" s="11"/>
+      <c r="L302" s="11"/>
+      <c r="M302" s="11"/>
     </row>
     <row r="303" spans="8:13">
-      <c r="H303" s="10"/>
-      <c r="I303" s="10"/>
-      <c r="J303" s="10"/>
-      <c r="K303" s="10"/>
-      <c r="L303" s="10"/>
-      <c r="M303" s="10"/>
+      <c r="H303" s="11"/>
+      <c r="I303" s="11"/>
+      <c r="J303" s="11"/>
+      <c r="K303" s="11"/>
+      <c r="L303" s="11"/>
+      <c r="M303" s="11"/>
     </row>
     <row r="304" spans="8:13">
-      <c r="H304" s="10"/>
-      <c r="I304" s="10"/>
-      <c r="J304" s="10"/>
-      <c r="K304" s="10"/>
-      <c r="L304" s="10"/>
-      <c r="M304" s="10"/>
+      <c r="H304" s="11"/>
+      <c r="I304" s="11"/>
+      <c r="J304" s="11"/>
+      <c r="K304" s="11"/>
+      <c r="L304" s="11"/>
+      <c r="M304" s="11"/>
     </row>
     <row r="305" spans="8:13">
-      <c r="H305" s="10"/>
-      <c r="I305" s="10"/>
-      <c r="J305" s="10"/>
-      <c r="K305" s="10"/>
-      <c r="L305" s="10"/>
-      <c r="M305" s="10"/>
+      <c r="H305" s="11"/>
+      <c r="I305" s="11"/>
+      <c r="J305" s="11"/>
+      <c r="K305" s="11"/>
+      <c r="L305" s="11"/>
+      <c r="M305" s="11"/>
     </row>
     <row r="306" spans="8:13">
-      <c r="H306" s="10"/>
-      <c r="I306" s="10"/>
-      <c r="J306" s="10"/>
-      <c r="K306" s="10"/>
-      <c r="L306" s="10"/>
-      <c r="M306" s="10"/>
+      <c r="H306" s="11"/>
+      <c r="I306" s="11"/>
+      <c r="J306" s="11"/>
+      <c r="K306" s="11"/>
+      <c r="L306" s="11"/>
+      <c r="M306" s="11"/>
     </row>
     <row r="307" spans="8:13">
-      <c r="H307" s="10"/>
-      <c r="I307" s="10"/>
-      <c r="J307" s="10"/>
-      <c r="K307" s="10"/>
-      <c r="L307" s="10"/>
-      <c r="M307" s="10"/>
+      <c r="H307" s="11"/>
+      <c r="I307" s="11"/>
+      <c r="J307" s="11"/>
+      <c r="K307" s="11"/>
+      <c r="L307" s="11"/>
+      <c r="M307" s="11"/>
     </row>
     <row r="308" spans="8:13">
-      <c r="H308" s="10"/>
-      <c r="I308" s="10"/>
-      <c r="J308" s="10"/>
-      <c r="K308" s="10"/>
-      <c r="L308" s="10"/>
-      <c r="M308" s="10"/>
+      <c r="H308" s="11"/>
+      <c r="I308" s="11"/>
+      <c r="J308" s="11"/>
+      <c r="K308" s="11"/>
+      <c r="L308" s="11"/>
+      <c r="M308" s="11"/>
     </row>
     <row r="309" spans="8:13">
-      <c r="H309" s="10"/>
-      <c r="I309" s="10"/>
-      <c r="J309" s="10"/>
-      <c r="K309" s="10"/>
-      <c r="L309" s="10"/>
-      <c r="M309" s="10"/>
+      <c r="H309" s="11"/>
+      <c r="I309" s="11"/>
+      <c r="J309" s="11"/>
+      <c r="K309" s="11"/>
+      <c r="L309" s="11"/>
+      <c r="M309" s="11"/>
     </row>
     <row r="310" spans="8:13">
-      <c r="H310" s="10"/>
-      <c r="I310" s="10"/>
-      <c r="J310" s="10"/>
-      <c r="K310" s="10"/>
-      <c r="L310" s="10"/>
-      <c r="M310" s="10"/>
+      <c r="H310" s="11"/>
+      <c r="I310" s="11"/>
+      <c r="J310" s="11"/>
+      <c r="K310" s="11"/>
+      <c r="L310" s="11"/>
+      <c r="M310" s="11"/>
     </row>
     <row r="311" spans="8:13">
-      <c r="H311" s="10"/>
-      <c r="I311" s="10"/>
-      <c r="J311" s="10"/>
-      <c r="K311" s="10"/>
-      <c r="L311" s="10"/>
-      <c r="M311" s="10"/>
+      <c r="H311" s="11"/>
+      <c r="I311" s="11"/>
+      <c r="J311" s="11"/>
+      <c r="K311" s="11"/>
+      <c r="L311" s="11"/>
+      <c r="M311" s="11"/>
     </row>
     <row r="312" spans="8:13">
-      <c r="H312" s="10"/>
-      <c r="I312" s="10"/>
-      <c r="J312" s="10"/>
-      <c r="K312" s="10"/>
-      <c r="L312" s="10"/>
-      <c r="M312" s="10"/>
+      <c r="H312" s="11"/>
+      <c r="I312" s="11"/>
+      <c r="J312" s="11"/>
+      <c r="K312" s="11"/>
+      <c r="L312" s="11"/>
+      <c r="M312" s="11"/>
     </row>
     <row r="313" spans="8:13">
-      <c r="H313" s="10"/>
-      <c r="I313" s="10"/>
-      <c r="J313" s="10"/>
-      <c r="K313" s="10"/>
-      <c r="L313" s="10"/>
-      <c r="M313" s="10"/>
+      <c r="H313" s="11"/>
+      <c r="I313" s="11"/>
+      <c r="J313" s="11"/>
+      <c r="K313" s="11"/>
+      <c r="L313" s="11"/>
+      <c r="M313" s="11"/>
     </row>
     <row r="314" spans="8:13">
-      <c r="H314" s="10"/>
-      <c r="I314" s="10"/>
-      <c r="J314" s="10"/>
-      <c r="K314" s="10"/>
-      <c r="L314" s="10"/>
-      <c r="M314" s="10"/>
+      <c r="H314" s="11"/>
+      <c r="I314" s="11"/>
+      <c r="J314" s="11"/>
+      <c r="K314" s="11"/>
+      <c r="L314" s="11"/>
+      <c r="M314" s="11"/>
     </row>
     <row r="315" spans="8:13">
-      <c r="H315" s="10"/>
-      <c r="I315" s="10"/>
-      <c r="J315" s="10"/>
-      <c r="K315" s="10"/>
-      <c r="L315" s="10"/>
-      <c r="M315" s="10"/>
+      <c r="H315" s="11"/>
+      <c r="I315" s="11"/>
+      <c r="J315" s="11"/>
+      <c r="K315" s="11"/>
+      <c r="L315" s="11"/>
+      <c r="M315" s="11"/>
     </row>
     <row r="316" spans="8:13">
-      <c r="H316" s="10"/>
-      <c r="I316" s="10"/>
-      <c r="J316" s="10"/>
-      <c r="K316" s="10"/>
-      <c r="L316" s="10"/>
-      <c r="M316" s="10"/>
+      <c r="H316" s="11"/>
+      <c r="I316" s="11"/>
+      <c r="J316" s="11"/>
+      <c r="K316" s="11"/>
+      <c r="L316" s="11"/>
+      <c r="M316" s="11"/>
     </row>
     <row r="317" spans="8:13">
-      <c r="H317" s="10"/>
-      <c r="I317" s="10"/>
-      <c r="J317" s="10"/>
-      <c r="K317" s="10"/>
-      <c r="L317" s="10"/>
-      <c r="M317" s="10"/>
+      <c r="H317" s="11"/>
+      <c r="I317" s="11"/>
+      <c r="J317" s="11"/>
+      <c r="K317" s="11"/>
+      <c r="L317" s="11"/>
+      <c r="M317" s="11"/>
     </row>
     <row r="318" spans="8:13">
-      <c r="H318" s="10"/>
-      <c r="I318" s="10"/>
-      <c r="J318" s="10"/>
-      <c r="K318" s="10"/>
-      <c r="L318" s="10"/>
-      <c r="M318" s="10"/>
+      <c r="H318" s="11"/>
+      <c r="I318" s="11"/>
+      <c r="J318" s="11"/>
+      <c r="K318" s="11"/>
+      <c r="L318" s="11"/>
+      <c r="M318" s="11"/>
     </row>
     <row r="319" spans="8:13">
-      <c r="H319" s="10"/>
-      <c r="I319" s="10"/>
-      <c r="J319" s="10"/>
-      <c r="K319" s="10"/>
-      <c r="L319" s="10"/>
-      <c r="M319" s="10"/>
+      <c r="H319" s="11"/>
+      <c r="I319" s="11"/>
+      <c r="J319" s="11"/>
+      <c r="K319" s="11"/>
+      <c r="L319" s="11"/>
+      <c r="M319" s="11"/>
     </row>
     <row r="320" spans="8:13">
-      <c r="H320" s="10"/>
-      <c r="I320" s="10"/>
-      <c r="J320" s="10"/>
-      <c r="K320" s="10"/>
-      <c r="L320" s="10"/>
-      <c r="M320" s="10"/>
+      <c r="H320" s="11"/>
+      <c r="I320" s="11"/>
+      <c r="J320" s="11"/>
+      <c r="K320" s="11"/>
+      <c r="L320" s="11"/>
+      <c r="M320" s="11"/>
     </row>
     <row r="321" spans="8:13">
-      <c r="H321" s="10"/>
-      <c r="I321" s="10"/>
-      <c r="J321" s="10"/>
-      <c r="K321" s="10"/>
-      <c r="L321" s="10"/>
-      <c r="M321" s="10"/>
+      <c r="H321" s="11"/>
+      <c r="I321" s="11"/>
+      <c r="J321" s="11"/>
+      <c r="K321" s="11"/>
+      <c r="L321" s="11"/>
+      <c r="M321" s="11"/>
     </row>
     <row r="322" spans="8:13">
-      <c r="H322" s="10"/>
-      <c r="I322" s="10"/>
-      <c r="J322" s="10"/>
-      <c r="K322" s="10"/>
-      <c r="L322" s="10"/>
-      <c r="M322" s="10"/>
+      <c r="H322" s="11"/>
+      <c r="I322" s="11"/>
+      <c r="J322" s="11"/>
+      <c r="K322" s="11"/>
+      <c r="L322" s="11"/>
+      <c r="M322" s="11"/>
     </row>
     <row r="323" spans="8:13">
-      <c r="H323" s="10"/>
-      <c r="I323" s="10"/>
-      <c r="J323" s="10"/>
-      <c r="K323" s="10"/>
-      <c r="L323" s="10"/>
-      <c r="M323" s="10"/>
+      <c r="H323" s="11"/>
+      <c r="I323" s="11"/>
+      <c r="J323" s="11"/>
+      <c r="K323" s="11"/>
+      <c r="L323" s="11"/>
+      <c r="M323" s="11"/>
     </row>
     <row r="324" spans="8:13">
-      <c r="H324" s="10"/>
-      <c r="I324" s="10"/>
-      <c r="J324" s="10"/>
-      <c r="K324" s="10"/>
-      <c r="L324" s="10"/>
-      <c r="M324" s="10"/>
+      <c r="H324" s="11"/>
+      <c r="I324" s="11"/>
+      <c r="J324" s="11"/>
+      <c r="K324" s="11"/>
+      <c r="L324" s="11"/>
+      <c r="M324" s="11"/>
     </row>
     <row r="325" spans="8:13">
-      <c r="H325" s="10"/>
-      <c r="I325" s="10"/>
-      <c r="J325" s="10"/>
-      <c r="K325" s="10"/>
-      <c r="L325" s="10"/>
-      <c r="M325" s="10"/>
+      <c r="H325" s="11"/>
+      <c r="I325" s="11"/>
+      <c r="J325" s="11"/>
+      <c r="K325" s="11"/>
+      <c r="L325" s="11"/>
+      <c r="M325" s="11"/>
     </row>
     <row r="326" spans="8:13">
-      <c r="H326" s="10"/>
-      <c r="I326" s="10"/>
-      <c r="J326" s="10"/>
-      <c r="K326" s="10"/>
-      <c r="L326" s="10"/>
-      <c r="M326" s="10"/>
+      <c r="H326" s="11"/>
+      <c r="I326" s="11"/>
+      <c r="J326" s="11"/>
+      <c r="K326" s="11"/>
+      <c r="L326" s="11"/>
+      <c r="M326" s="11"/>
     </row>
     <row r="327" spans="8:13">
-      <c r="H327" s="10"/>
-      <c r="I327" s="10"/>
-      <c r="J327" s="10"/>
-      <c r="K327" s="10"/>
-      <c r="L327" s="10"/>
-      <c r="M327" s="10"/>
+      <c r="H327" s="11"/>
+      <c r="I327" s="11"/>
+      <c r="J327" s="11"/>
+      <c r="K327" s="11"/>
+      <c r="L327" s="11"/>
+      <c r="M327" s="11"/>
     </row>
     <row r="328" spans="8:13">
-      <c r="H328" s="10"/>
-      <c r="I328" s="10"/>
-      <c r="J328" s="10"/>
-      <c r="K328" s="10"/>
-      <c r="L328" s="10"/>
-      <c r="M328" s="10"/>
+      <c r="H328" s="11"/>
+      <c r="I328" s="11"/>
+      <c r="J328" s="11"/>
+      <c r="K328" s="11"/>
+      <c r="L328" s="11"/>
+      <c r="M328" s="11"/>
     </row>
     <row r="329" spans="8:13">
-      <c r="H329" s="10"/>
-      <c r="I329" s="10"/>
-      <c r="J329" s="10"/>
-      <c r="K329" s="10"/>
-      <c r="L329" s="10"/>
-      <c r="M329" s="10"/>
+      <c r="H329" s="11"/>
+      <c r="I329" s="11"/>
+      <c r="J329" s="11"/>
+      <c r="K329" s="11"/>
+      <c r="L329" s="11"/>
+      <c r="M329" s="11"/>
     </row>
     <row r="330" spans="8:13">
-      <c r="H330" s="10"/>
-      <c r="I330" s="10"/>
-      <c r="J330" s="10"/>
-      <c r="K330" s="10"/>
-      <c r="L330" s="10"/>
-      <c r="M330" s="10"/>
+      <c r="H330" s="11"/>
+      <c r="I330" s="11"/>
+      <c r="J330" s="11"/>
+      <c r="K330" s="11"/>
+      <c r="L330" s="11"/>
+      <c r="M330" s="11"/>
     </row>
     <row r="331" spans="8:13">
-      <c r="H331" s="10"/>
-      <c r="I331" s="10"/>
-      <c r="J331" s="10"/>
-      <c r="K331" s="10"/>
-      <c r="L331" s="10"/>
-      <c r="M331" s="10"/>
+      <c r="H331" s="11"/>
+      <c r="I331" s="11"/>
+      <c r="J331" s="11"/>
+      <c r="K331" s="11"/>
+      <c r="L331" s="11"/>
+      <c r="M331" s="11"/>
     </row>
     <row r="332" spans="8:13">
-      <c r="H332" s="10"/>
-      <c r="I332" s="10"/>
-      <c r="J332" s="10"/>
-      <c r="K332" s="10"/>
-      <c r="L332" s="10"/>
-      <c r="M332" s="10"/>
+      <c r="H332" s="11"/>
+      <c r="I332" s="11"/>
+      <c r="J332" s="11"/>
+      <c r="K332" s="11"/>
+      <c r="L332" s="11"/>
+      <c r="M332" s="11"/>
     </row>
     <row r="333" spans="8:13">
-      <c r="H333" s="10"/>
-      <c r="I333" s="10"/>
-      <c r="J333" s="10"/>
-      <c r="K333" s="10"/>
-      <c r="L333" s="10"/>
-      <c r="M333" s="10"/>
+      <c r="H333" s="11"/>
+      <c r="I333" s="11"/>
+      <c r="J333" s="11"/>
+      <c r="K333" s="11"/>
+      <c r="L333" s="11"/>
+      <c r="M333" s="11"/>
     </row>
     <row r="334" spans="8:13">
-      <c r="H334" s="10"/>
-      <c r="I334" s="10"/>
-      <c r="J334" s="10"/>
-      <c r="K334" s="10"/>
-      <c r="L334" s="10"/>
-      <c r="M334" s="10"/>
+      <c r="H334" s="11"/>
+      <c r="I334" s="11"/>
+      <c r="J334" s="11"/>
+      <c r="K334" s="11"/>
+      <c r="L334" s="11"/>
+      <c r="M334" s="11"/>
     </row>
     <row r="335" spans="8:13">
-      <c r="H335" s="10"/>
-      <c r="I335" s="10"/>
-      <c r="J335" s="10"/>
-      <c r="K335" s="10"/>
-      <c r="L335" s="10"/>
-      <c r="M335" s="10"/>
+      <c r="H335" s="11"/>
+      <c r="I335" s="11"/>
+      <c r="J335" s="11"/>
+      <c r="K335" s="11"/>
+      <c r="L335" s="11"/>
+      <c r="M335" s="11"/>
     </row>
     <row r="336" spans="8:13">
-      <c r="H336" s="10"/>
-      <c r="I336" s="10"/>
-      <c r="J336" s="10"/>
-      <c r="K336" s="10"/>
-      <c r="L336" s="10"/>
-      <c r="M336" s="10"/>
+      <c r="H336" s="11"/>
+      <c r="I336" s="11"/>
+      <c r="J336" s="11"/>
+      <c r="K336" s="11"/>
+      <c r="L336" s="11"/>
+      <c r="M336" s="11"/>
     </row>
     <row r="337" spans="8:13">
-      <c r="H337" s="10"/>
-      <c r="I337" s="10"/>
-      <c r="J337" s="10"/>
-      <c r="K337" s="10"/>
-      <c r="L337" s="10"/>
-      <c r="M337" s="10"/>
+      <c r="H337" s="11"/>
+      <c r="I337" s="11"/>
+      <c r="J337" s="11"/>
+      <c r="K337" s="11"/>
+      <c r="L337" s="11"/>
+      <c r="M337" s="11"/>
     </row>
     <row r="338" spans="8:13">
-      <c r="H338" s="10"/>
-      <c r="I338" s="10"/>
-      <c r="J338" s="10"/>
-      <c r="K338" s="10"/>
-      <c r="L338" s="10"/>
-      <c r="M338" s="10"/>
+      <c r="H338" s="11"/>
+      <c r="I338" s="11"/>
+      <c r="J338" s="11"/>
+      <c r="K338" s="11"/>
+      <c r="L338" s="11"/>
+      <c r="M338" s="11"/>
     </row>
     <row r="339" spans="8:13">
-      <c r="H339" s="10"/>
-      <c r="I339" s="10"/>
-      <c r="J339" s="10"/>
-      <c r="K339" s="10"/>
-      <c r="L339" s="10"/>
-      <c r="M339" s="10"/>
+      <c r="H339" s="11"/>
+      <c r="I339" s="11"/>
+      <c r="J339" s="11"/>
+      <c r="K339" s="11"/>
+      <c r="L339" s="11"/>
+      <c r="M339" s="11"/>
     </row>
     <row r="340" spans="8:13">
-      <c r="H340" s="10"/>
-      <c r="I340" s="10"/>
-      <c r="J340" s="10"/>
-      <c r="K340" s="10"/>
-      <c r="L340" s="10"/>
-      <c r="M340" s="10"/>
+      <c r="H340" s="11"/>
+      <c r="I340" s="11"/>
+      <c r="J340" s="11"/>
+      <c r="K340" s="11"/>
+      <c r="L340" s="11"/>
+      <c r="M340" s="11"/>
     </row>
     <row r="341" spans="8:13">
-      <c r="H341" s="10"/>
-      <c r="I341" s="10"/>
-      <c r="J341" s="10"/>
-      <c r="K341" s="10"/>
-      <c r="L341" s="10"/>
-      <c r="M341" s="10"/>
+      <c r="H341" s="11"/>
+      <c r="I341" s="11"/>
+      <c r="J341" s="11"/>
+      <c r="K341" s="11"/>
+      <c r="L341" s="11"/>
+      <c r="M341" s="11"/>
     </row>
     <row r="342" spans="8:13">
-      <c r="H342" s="10"/>
-      <c r="I342" s="10"/>
-      <c r="J342" s="10"/>
-      <c r="K342" s="10"/>
-      <c r="L342" s="10"/>
-      <c r="M342" s="10"/>
+      <c r="H342" s="11"/>
+      <c r="I342" s="11"/>
+      <c r="J342" s="11"/>
+      <c r="K342" s="11"/>
+      <c r="L342" s="11"/>
+      <c r="M342" s="11"/>
     </row>
     <row r="343" spans="8:13">
-      <c r="H343" s="10"/>
-      <c r="I343" s="10"/>
-      <c r="J343" s="10"/>
-      <c r="K343" s="10"/>
-      <c r="L343" s="10"/>
-      <c r="M343" s="10"/>
+      <c r="H343" s="11"/>
+      <c r="I343" s="11"/>
+      <c r="J343" s="11"/>
+      <c r="K343" s="11"/>
+      <c r="L343" s="11"/>
+      <c r="M343" s="11"/>
     </row>
     <row r="344" spans="8:13">
-      <c r="H344" s="10"/>
-      <c r="I344" s="10"/>
-      <c r="J344" s="10"/>
-      <c r="K344" s="10"/>
-      <c r="L344" s="10"/>
-      <c r="M344" s="10"/>
+      <c r="H344" s="11"/>
+      <c r="I344" s="11"/>
+      <c r="J344" s="11"/>
+      <c r="K344" s="11"/>
+      <c r="L344" s="11"/>
+      <c r="M344" s="11"/>
     </row>
     <row r="345" spans="8:13">
-      <c r="H345" s="10"/>
-      <c r="I345" s="10"/>
-      <c r="J345" s="10"/>
-      <c r="K345" s="10"/>
-      <c r="L345" s="10"/>
-      <c r="M345" s="10"/>
+      <c r="H345" s="11"/>
+      <c r="I345" s="11"/>
+      <c r="J345" s="11"/>
+      <c r="K345" s="11"/>
+      <c r="L345" s="11"/>
+      <c r="M345" s="11"/>
     </row>
     <row r="346" spans="8:13">
-      <c r="H346" s="10"/>
-      <c r="I346" s="10"/>
-      <c r="J346" s="10"/>
-      <c r="K346" s="10"/>
-      <c r="L346" s="10"/>
-      <c r="M346" s="10"/>
+      <c r="H346" s="11"/>
+      <c r="I346" s="11"/>
+      <c r="J346" s="11"/>
+      <c r="K346" s="11"/>
+      <c r="L346" s="11"/>
+      <c r="M346" s="11"/>
     </row>
     <row r="347" spans="8:13">
-      <c r="H347" s="10"/>
-      <c r="I347" s="10"/>
-      <c r="J347" s="10"/>
-      <c r="K347" s="10"/>
-      <c r="L347" s="10"/>
-      <c r="M347" s="10"/>
+      <c r="H347" s="11"/>
+      <c r="I347" s="11"/>
+      <c r="J347" s="11"/>
+      <c r="K347" s="11"/>
+      <c r="L347" s="11"/>
+      <c r="M347" s="11"/>
     </row>
     <row r="348" spans="8:13">
-      <c r="H348" s="10"/>
-      <c r="I348" s="10"/>
-      <c r="J348" s="10"/>
-      <c r="K348" s="10"/>
-      <c r="L348" s="10"/>
-      <c r="M348" s="10"/>
+      <c r="H348" s="11"/>
+      <c r="I348" s="11"/>
+      <c r="J348" s="11"/>
+      <c r="K348" s="11"/>
+      <c r="L348" s="11"/>
+      <c r="M348" s="11"/>
     </row>
     <row r="349" spans="8:13">
-      <c r="H349" s="10"/>
-      <c r="I349" s="10"/>
-      <c r="J349" s="10"/>
-      <c r="K349" s="10"/>
-      <c r="L349" s="10"/>
-      <c r="M349" s="10"/>
+      <c r="H349" s="11"/>
+      <c r="I349" s="11"/>
+      <c r="J349" s="11"/>
+      <c r="K349" s="11"/>
+      <c r="L349" s="11"/>
+      <c r="M349" s="11"/>
     </row>
     <row r="350" spans="8:13">
-      <c r="H350" s="10"/>
-      <c r="I350" s="10"/>
-      <c r="J350" s="10"/>
-      <c r="K350" s="10"/>
-      <c r="L350" s="10"/>
-      <c r="M350" s="10"/>
+      <c r="H350" s="11"/>
+      <c r="I350" s="11"/>
+      <c r="J350" s="11"/>
+      <c r="K350" s="11"/>
+      <c r="L350" s="11"/>
+      <c r="M350" s="11"/>
     </row>
     <row r="351" spans="8:13">
-      <c r="H351" s="10"/>
-      <c r="I351" s="10"/>
-      <c r="J351" s="10"/>
-      <c r="K351" s="10"/>
-      <c r="L351" s="10"/>
-      <c r="M351" s="10"/>
+      <c r="H351" s="11"/>
+      <c r="I351" s="11"/>
+      <c r="J351" s="11"/>
+      <c r="K351" s="11"/>
+      <c r="L351" s="11"/>
+      <c r="M351" s="11"/>
     </row>
     <row r="352" spans="8:13">
-      <c r="H352" s="10"/>
-      <c r="I352" s="10"/>
-      <c r="J352" s="10"/>
-      <c r="K352" s="10"/>
-      <c r="L352" s="10"/>
-      <c r="M352" s="10"/>
+      <c r="H352" s="11"/>
+      <c r="I352" s="11"/>
+      <c r="J352" s="11"/>
+      <c r="K352" s="11"/>
+      <c r="L352" s="11"/>
+      <c r="M352" s="11"/>
     </row>
     <row r="353" spans="8:13">
-      <c r="H353" s="10"/>
-      <c r="I353" s="10"/>
-      <c r="J353" s="10"/>
-      <c r="K353" s="10"/>
-      <c r="L353" s="10"/>
-      <c r="M353" s="10"/>
+      <c r="H353" s="11"/>
+      <c r="I353" s="11"/>
+      <c r="J353" s="11"/>
+      <c r="K353" s="11"/>
+      <c r="L353" s="11"/>
+      <c r="M353" s="11"/>
     </row>
     <row r="354" spans="8:13">
-      <c r="H354" s="10"/>
-      <c r="I354" s="10"/>
-      <c r="J354" s="10"/>
-      <c r="K354" s="10"/>
-      <c r="L354" s="10"/>
-      <c r="M354" s="10"/>
+      <c r="H354" s="11"/>
+      <c r="I354" s="11"/>
+      <c r="J354" s="11"/>
+      <c r="K354" s="11"/>
+      <c r="L354" s="11"/>
+      <c r="M354" s="11"/>
     </row>
     <row r="355" spans="8:13">
-      <c r="H355" s="10"/>
-      <c r="I355" s="10"/>
-      <c r="J355" s="10"/>
-      <c r="K355" s="10"/>
-      <c r="L355" s="10"/>
-      <c r="M355" s="10"/>
+      <c r="H355" s="11"/>
+      <c r="I355" s="11"/>
+      <c r="J355" s="11"/>
+      <c r="K355" s="11"/>
+      <c r="L355" s="11"/>
+      <c r="M355" s="11"/>
     </row>
     <row r="356" spans="8:13">
-      <c r="H356" s="10"/>
-      <c r="I356" s="10"/>
-      <c r="J356" s="10"/>
-      <c r="K356" s="10"/>
-      <c r="L356" s="10"/>
-      <c r="M356" s="10"/>
+      <c r="H356" s="11"/>
+      <c r="I356" s="11"/>
+      <c r="J356" s="11"/>
+      <c r="K356" s="11"/>
+      <c r="L356" s="11"/>
+      <c r="M356" s="11"/>
     </row>
     <row r="357" spans="8:13">
-      <c r="H357" s="10"/>
-      <c r="I357" s="10"/>
-      <c r="J357" s="10"/>
-      <c r="K357" s="10"/>
-      <c r="L357" s="10"/>
-      <c r="M357" s="10"/>
+      <c r="H357" s="11"/>
+      <c r="I357" s="11"/>
+      <c r="J357" s="11"/>
+      <c r="K357" s="11"/>
+      <c r="L357" s="11"/>
+      <c r="M357" s="11"/>
     </row>
     <row r="358" spans="8:13">
-      <c r="H358" s="10"/>
-      <c r="I358" s="10"/>
-      <c r="J358" s="10"/>
-      <c r="K358" s="10"/>
-      <c r="L358" s="10"/>
-      <c r="M358" s="10"/>
+      <c r="H358" s="11"/>
+      <c r="I358" s="11"/>
+      <c r="J358" s="11"/>
+      <c r="K358" s="11"/>
+      <c r="L358" s="11"/>
+      <c r="M358" s="11"/>
     </row>
     <row r="359" spans="8:13">
-      <c r="H359" s="10"/>
-      <c r="I359" s="10"/>
-      <c r="J359" s="10"/>
-      <c r="K359" s="10"/>
-      <c r="L359" s="10"/>
-      <c r="M359" s="10"/>
+      <c r="H359" s="11"/>
+      <c r="I359" s="11"/>
+      <c r="J359" s="11"/>
+      <c r="K359" s="11"/>
+      <c r="L359" s="11"/>
+      <c r="M359" s="11"/>
     </row>
     <row r="360" spans="8:13">
-      <c r="H360" s="10"/>
-      <c r="I360" s="10"/>
-      <c r="J360" s="10"/>
-      <c r="K360" s="10"/>
-      <c r="L360" s="10"/>
-      <c r="M360" s="10"/>
+      <c r="H360" s="11"/>
+      <c r="I360" s="11"/>
+      <c r="J360" s="11"/>
+      <c r="K360" s="11"/>
+      <c r="L360" s="11"/>
+      <c r="M360" s="11"/>
     </row>
     <row r="361" spans="8:13">
-      <c r="H361" s="10"/>
-      <c r="I361" s="10"/>
-      <c r="J361" s="10"/>
-      <c r="K361" s="10"/>
-      <c r="L361" s="10"/>
-      <c r="M361" s="10"/>
+      <c r="H361" s="11"/>
+      <c r="I361" s="11"/>
+      <c r="J361" s="11"/>
+      <c r="K361" s="11"/>
+      <c r="L361" s="11"/>
+      <c r="M361" s="11"/>
     </row>
     <row r="362" spans="8:13">
-      <c r="H362" s="10"/>
-      <c r="I362" s="10"/>
-      <c r="J362" s="10"/>
-      <c r="K362" s="10"/>
-      <c r="L362" s="10"/>
-      <c r="M362" s="10"/>
+      <c r="H362" s="11"/>
+      <c r="I362" s="11"/>
+      <c r="J362" s="11"/>
+      <c r="K362" s="11"/>
+      <c r="L362" s="11"/>
+      <c r="M362" s="11"/>
     </row>
     <row r="363" spans="8:13">
-      <c r="H363" s="10"/>
-      <c r="I363" s="10"/>
-      <c r="J363" s="10"/>
-      <c r="K363" s="10"/>
-      <c r="L363" s="10"/>
-      <c r="M363" s="10"/>
+      <c r="H363" s="11"/>
+      <c r="I363" s="11"/>
+      <c r="J363" s="11"/>
+      <c r="K363" s="11"/>
+      <c r="L363" s="11"/>
+      <c r="M363" s="11"/>
     </row>
     <row r="364" spans="8:13">
-      <c r="H364" s="10"/>
-      <c r="I364" s="10"/>
-      <c r="J364" s="10"/>
-      <c r="K364" s="10"/>
-      <c r="L364" s="10"/>
-      <c r="M364" s="10"/>
+      <c r="H364" s="11"/>
+      <c r="I364" s="11"/>
+      <c r="J364" s="11"/>
+      <c r="K364" s="11"/>
+      <c r="L364" s="11"/>
+      <c r="M364" s="11"/>
     </row>
     <row r="365" spans="8:13">
-      <c r="H365" s="10"/>
-      <c r="I365" s="10"/>
-      <c r="J365" s="10"/>
-      <c r="K365" s="10"/>
-      <c r="L365" s="10"/>
-      <c r="M365" s="10"/>
+      <c r="H365" s="11"/>
+      <c r="I365" s="11"/>
+      <c r="J365" s="11"/>
+      <c r="K365" s="11"/>
+      <c r="L365" s="11"/>
+      <c r="M365" s="11"/>
     </row>
     <row r="366" spans="8:13">
-      <c r="H366" s="10"/>
-      <c r="I366" s="10"/>
-      <c r="J366" s="10"/>
-      <c r="K366" s="10"/>
-      <c r="L366" s="10"/>
-      <c r="M366" s="10"/>
+      <c r="H366" s="11"/>
+      <c r="I366" s="11"/>
+      <c r="J366" s="11"/>
+      <c r="K366" s="11"/>
+      <c r="L366" s="11"/>
+      <c r="M366" s="11"/>
     </row>
     <row r="367" spans="8:13">
-      <c r="H367" s="10"/>
-      <c r="I367" s="10"/>
-      <c r="J367" s="10"/>
-      <c r="K367" s="10"/>
-      <c r="L367" s="10"/>
-      <c r="M367" s="10"/>
+      <c r="H367" s="11"/>
+      <c r="I367" s="11"/>
+      <c r="J367" s="11"/>
+      <c r="K367" s="11"/>
+      <c r="L367" s="11"/>
+      <c r="M367" s="11"/>
     </row>
     <row r="368" spans="8:13">
-      <c r="H368" s="10"/>
-      <c r="I368" s="10"/>
-      <c r="J368" s="10"/>
-      <c r="K368" s="10"/>
-      <c r="L368" s="10"/>
-      <c r="M368" s="10"/>
+      <c r="H368" s="11"/>
+      <c r="I368" s="11"/>
+      <c r="J368" s="11"/>
+      <c r="K368" s="11"/>
+      <c r="L368" s="11"/>
+      <c r="M368" s="11"/>
     </row>
     <row r="369" spans="8:13">
-      <c r="H369" s="10"/>
-      <c r="I369" s="10"/>
-      <c r="J369" s="10"/>
-      <c r="K369" s="10"/>
-      <c r="L369" s="10"/>
-      <c r="M369" s="10"/>
+      <c r="H369" s="11"/>
+      <c r="I369" s="11"/>
+      <c r="J369" s="11"/>
+      <c r="K369" s="11"/>
+      <c r="L369" s="11"/>
+      <c r="M369" s="11"/>
     </row>
     <row r="370" spans="8:13">
-      <c r="H370" s="10"/>
-      <c r="I370" s="10"/>
-      <c r="J370" s="10"/>
-      <c r="K370" s="10"/>
-      <c r="L370" s="10"/>
-      <c r="M370" s="10"/>
+      <c r="H370" s="11"/>
+      <c r="I370" s="11"/>
+      <c r="J370" s="11"/>
+      <c r="K370" s="11"/>
+      <c r="L370" s="11"/>
+      <c r="M370" s="11"/>
     </row>
     <row r="371" spans="8:13">
-      <c r="H371" s="10"/>
-      <c r="I371" s="10"/>
-      <c r="J371" s="10"/>
-      <c r="K371" s="10"/>
-      <c r="L371" s="10"/>
-      <c r="M371" s="10"/>
+      <c r="H371" s="11"/>
+      <c r="I371" s="11"/>
+      <c r="J371" s="11"/>
+      <c r="K371" s="11"/>
+      <c r="L371" s="11"/>
+      <c r="M371" s="11"/>
     </row>
     <row r="372" spans="8:13">
-      <c r="H372" s="10"/>
-      <c r="I372" s="10"/>
-      <c r="J372" s="10"/>
-      <c r="K372" s="10"/>
-      <c r="L372" s="10"/>
-      <c r="M372" s="10"/>
+      <c r="H372" s="11"/>
+      <c r="I372" s="11"/>
+      <c r="J372" s="11"/>
+      <c r="K372" s="11"/>
+      <c r="L372" s="11"/>
+      <c r="M372" s="11"/>
     </row>
     <row r="373" spans="8:13">
-      <c r="H373" s="10"/>
-      <c r="I373" s="10"/>
-      <c r="J373" s="10"/>
-      <c r="K373" s="10"/>
-      <c r="L373" s="10"/>
-      <c r="M373" s="10"/>
+      <c r="H373" s="11"/>
+      <c r="I373" s="11"/>
+      <c r="J373" s="11"/>
+      <c r="K373" s="11"/>
+      <c r="L373" s="11"/>
+      <c r="M373" s="11"/>
     </row>
     <row r="374" spans="8:13">
-      <c r="H374" s="10"/>
-      <c r="I374" s="10"/>
-      <c r="J374" s="10"/>
-      <c r="K374" s="10"/>
-      <c r="L374" s="10"/>
-      <c r="M374" s="10"/>
+      <c r="H374" s="11"/>
+      <c r="I374" s="11"/>
+      <c r="J374" s="11"/>
+      <c r="K374" s="11"/>
+      <c r="L374" s="11"/>
+      <c r="M374" s="11"/>
     </row>
     <row r="375" spans="8:13">
-      <c r="H375" s="10"/>
-      <c r="I375" s="10"/>
-      <c r="J375" s="10"/>
-      <c r="K375" s="10"/>
-      <c r="L375" s="10"/>
-      <c r="M375" s="10"/>
+      <c r="H375" s="11"/>
+      <c r="I375" s="11"/>
+      <c r="J375" s="11"/>
+      <c r="K375" s="11"/>
+      <c r="L375" s="11"/>
+      <c r="M375" s="11"/>
     </row>
     <row r="376" spans="8:13">
-      <c r="H376" s="10"/>
-      <c r="I376" s="10"/>
-      <c r="J376" s="10"/>
-      <c r="K376" s="10"/>
-      <c r="L376" s="10"/>
-      <c r="M376" s="10"/>
+      <c r="H376" s="11"/>
+      <c r="I376" s="11"/>
+      <c r="J376" s="11"/>
+      <c r="K376" s="11"/>
+      <c r="L376" s="11"/>
+      <c r="M376" s="11"/>
     </row>
     <row r="377" spans="8:13">
-      <c r="H377" s="10"/>
-      <c r="I377" s="10"/>
-      <c r="J377" s="10"/>
-      <c r="K377" s="10"/>
-      <c r="L377" s="10"/>
-      <c r="M377" s="10"/>
+      <c r="H377" s="11"/>
+      <c r="I377" s="11"/>
+      <c r="J377" s="11"/>
+      <c r="K377" s="11"/>
+      <c r="L377" s="11"/>
+      <c r="M377" s="11"/>
     </row>
     <row r="378" spans="8:13">
-      <c r="H378" s="10"/>
-      <c r="I378" s="10"/>
-      <c r="J378" s="10"/>
-      <c r="K378" s="10"/>
-      <c r="L378" s="10"/>
-      <c r="M378" s="10"/>
+      <c r="H378" s="11"/>
+      <c r="I378" s="11"/>
+      <c r="J378" s="11"/>
+      <c r="K378" s="11"/>
+      <c r="L378" s="11"/>
+      <c r="M378" s="11"/>
     </row>
     <row r="379" spans="8:13">
-      <c r="H379" s="10"/>
-      <c r="I379" s="10"/>
-      <c r="J379" s="10"/>
-      <c r="K379" s="10"/>
-      <c r="L379" s="10"/>
-      <c r="M379" s="10"/>
+      <c r="H379" s="11"/>
+      <c r="I379" s="11"/>
+      <c r="J379" s="11"/>
+      <c r="K379" s="11"/>
+      <c r="L379" s="11"/>
+      <c r="M379" s="11"/>
     </row>
     <row r="380" spans="8:13">
-      <c r="H380" s="10"/>
-      <c r="I380" s="10"/>
-      <c r="J380" s="10"/>
-      <c r="K380" s="10"/>
-      <c r="L380" s="10"/>
-      <c r="M380" s="10"/>
+      <c r="H380" s="11"/>
+      <c r="I380" s="11"/>
+      <c r="J380" s="11"/>
+      <c r="K380" s="11"/>
+      <c r="L380" s="11"/>
+      <c r="M380" s="11"/>
     </row>
     <row r="381" spans="8:13">
-      <c r="H381" s="10"/>
-      <c r="I381" s="10"/>
-      <c r="J381" s="10"/>
-      <c r="K381" s="10"/>
-      <c r="L381" s="10"/>
-      <c r="M381" s="10"/>
+      <c r="H381" s="11"/>
+      <c r="I381" s="11"/>
+      <c r="J381" s="11"/>
+      <c r="K381" s="11"/>
+      <c r="L381" s="11"/>
+      <c r="M381" s="11"/>
     </row>
     <row r="382" spans="8:13">
-      <c r="H382" s="10"/>
-      <c r="I382" s="10"/>
-      <c r="J382" s="10"/>
-      <c r="K382" s="10"/>
-      <c r="L382" s="10"/>
-      <c r="M382" s="10"/>
+      <c r="H382" s="11"/>
+      <c r="I382" s="11"/>
+      <c r="J382" s="11"/>
+      <c r="K382" s="11"/>
+      <c r="L382" s="11"/>
+      <c r="M382" s="11"/>
     </row>
     <row r="383" spans="8:13">
-      <c r="H383" s="10"/>
-      <c r="I383" s="10"/>
-      <c r="J383" s="10"/>
-      <c r="K383" s="10"/>
-      <c r="L383" s="10"/>
-      <c r="M383" s="10"/>
+      <c r="H383" s="11"/>
+      <c r="I383" s="11"/>
+      <c r="J383" s="11"/>
+      <c r="K383" s="11"/>
+      <c r="L383" s="11"/>
+      <c r="M383" s="11"/>
     </row>
     <row r="384" spans="8:13">
-      <c r="H384" s="10"/>
-      <c r="I384" s="10"/>
-      <c r="J384" s="10"/>
-      <c r="K384" s="10"/>
-      <c r="L384" s="10"/>
-      <c r="M384" s="10"/>
+      <c r="H384" s="11"/>
+      <c r="I384" s="11"/>
+      <c r="J384" s="11"/>
+      <c r="K384" s="11"/>
+      <c r="L384" s="11"/>
+      <c r="M384" s="11"/>
     </row>
     <row r="385" spans="8:13">
-      <c r="H385" s="10"/>
-      <c r="I385" s="10"/>
-      <c r="J385" s="10"/>
-      <c r="K385" s="10"/>
-      <c r="L385" s="10"/>
-      <c r="M385" s="10"/>
+      <c r="H385" s="11"/>
+      <c r="I385" s="11"/>
+      <c r="J385" s="11"/>
+      <c r="K385" s="11"/>
+      <c r="L385" s="11"/>
+      <c r="M385" s="11"/>
     </row>
     <row r="386" spans="8:13">
-      <c r="H386" s="10"/>
-      <c r="I386" s="10"/>
-      <c r="J386" s="10"/>
-      <c r="K386" s="10"/>
-      <c r="L386" s="10"/>
-      <c r="M386" s="10"/>
+      <c r="H386" s="11"/>
+      <c r="I386" s="11"/>
+      <c r="J386" s="11"/>
+      <c r="K386" s="11"/>
+      <c r="L386" s="11"/>
+      <c r="M386" s="11"/>
     </row>
     <row r="387" spans="8:13">
-      <c r="H387" s="10"/>
-      <c r="I387" s="10"/>
-      <c r="J387" s="10"/>
-      <c r="K387" s="10"/>
-      <c r="L387" s="10"/>
-      <c r="M387" s="10"/>
+      <c r="H387" s="11"/>
+      <c r="I387" s="11"/>
+      <c r="J387" s="11"/>
+      <c r="K387" s="11"/>
+      <c r="L387" s="11"/>
+      <c r="M387" s="11"/>
     </row>
     <row r="388" spans="8:13">
-      <c r="H388" s="10"/>
-      <c r="I388" s="10"/>
-      <c r="J388" s="10"/>
-      <c r="K388" s="10"/>
-      <c r="L388" s="10"/>
-      <c r="M388" s="10"/>
+      <c r="H388" s="11"/>
+      <c r="I388" s="11"/>
+      <c r="J388" s="11"/>
+      <c r="K388" s="11"/>
+      <c r="L388" s="11"/>
+      <c r="M388" s="11"/>
     </row>
     <row r="389" spans="8:13">
-      <c r="H389" s="10"/>
-      <c r="I389" s="10"/>
-      <c r="J389" s="10"/>
-      <c r="K389" s="10"/>
-      <c r="L389" s="10"/>
-      <c r="M389" s="10"/>
+      <c r="H389" s="11"/>
+      <c r="I389" s="11"/>
+      <c r="J389" s="11"/>
+      <c r="K389" s="11"/>
+      <c r="L389" s="11"/>
+      <c r="M389" s="11"/>
     </row>
     <row r="390" spans="8:13">
-      <c r="H390" s="10"/>
-      <c r="I390" s="10"/>
-      <c r="J390" s="10"/>
-      <c r="K390" s="10"/>
-      <c r="L390" s="10"/>
-      <c r="M390" s="10"/>
+      <c r="H390" s="11"/>
+      <c r="I390" s="11"/>
+      <c r="J390" s="11"/>
+      <c r="K390" s="11"/>
+      <c r="L390" s="11"/>
+      <c r="M390" s="11"/>
     </row>
     <row r="391" spans="8:13">
-      <c r="H391" s="10"/>
-      <c r="I391" s="10"/>
-      <c r="J391" s="10"/>
-      <c r="K391" s="10"/>
-      <c r="L391" s="10"/>
-      <c r="M391" s="10"/>
+      <c r="H391" s="11"/>
+      <c r="I391" s="11"/>
+      <c r="J391" s="11"/>
+      <c r="K391" s="11"/>
+      <c r="L391" s="11"/>
+      <c r="M391" s="11"/>
     </row>
     <row r="392" spans="8:13">
-      <c r="H392" s="10"/>
-      <c r="I392" s="10"/>
-      <c r="J392" s="10"/>
-      <c r="K392" s="10"/>
-      <c r="L392" s="10"/>
-      <c r="M392" s="10"/>
+      <c r="H392" s="11"/>
+      <c r="I392" s="11"/>
+      <c r="J392" s="11"/>
+      <c r="K392" s="11"/>
+      <c r="L392" s="11"/>
+      <c r="M392" s="11"/>
     </row>
     <row r="393" spans="8:13">
-      <c r="H393" s="10"/>
-      <c r="I393" s="10"/>
-      <c r="J393" s="10"/>
-      <c r="K393" s="10"/>
-      <c r="L393" s="10"/>
-      <c r="M393" s="10"/>
+      <c r="H393" s="11"/>
+      <c r="I393" s="11"/>
+      <c r="J393" s="11"/>
+      <c r="K393" s="11"/>
+      <c r="L393" s="11"/>
+      <c r="M393" s="11"/>
     </row>
     <row r="394" spans="8:13">
-      <c r="H394" s="10"/>
-      <c r="I394" s="10"/>
-      <c r="J394" s="10"/>
-      <c r="K394" s="10"/>
-      <c r="L394" s="10"/>
-      <c r="M394" s="10"/>
+      <c r="H394" s="11"/>
+      <c r="I394" s="11"/>
+      <c r="J394" s="11"/>
+      <c r="K394" s="11"/>
+      <c r="L394" s="11"/>
+      <c r="M394" s="11"/>
     </row>
     <row r="395" spans="8:13">
-      <c r="H395" s="10"/>
-      <c r="I395" s="10"/>
-      <c r="J395" s="10"/>
-      <c r="K395" s="10"/>
-      <c r="L395" s="10"/>
-      <c r="M395" s="10"/>
+      <c r="H395" s="11"/>
+      <c r="I395" s="11"/>
+      <c r="J395" s="11"/>
+      <c r="K395" s="11"/>
+      <c r="L395" s="11"/>
+      <c r="M395" s="11"/>
     </row>
     <row r="396" spans="8:13">
-      <c r="H396" s="10"/>
-      <c r="I396" s="10"/>
-      <c r="J396" s="10"/>
-      <c r="K396" s="10"/>
-      <c r="L396" s="10"/>
-      <c r="M396" s="10"/>
+      <c r="H396" s="11"/>
+      <c r="I396" s="11"/>
+      <c r="J396" s="11"/>
+      <c r="K396" s="11"/>
+      <c r="L396" s="11"/>
+      <c r="M396" s="11"/>
     </row>
     <row r="397" spans="8:13">
-      <c r="H397" s="10"/>
-      <c r="I397" s="10"/>
-      <c r="J397" s="10"/>
-      <c r="K397" s="10"/>
-      <c r="L397" s="10"/>
-      <c r="M397" s="10"/>
+      <c r="H397" s="11"/>
+      <c r="I397" s="11"/>
+      <c r="J397" s="11"/>
+      <c r="K397" s="11"/>
+      <c r="L397" s="11"/>
+      <c r="M397" s="11"/>
     </row>
     <row r="398" spans="8:13">
-      <c r="H398" s="10"/>
-      <c r="I398" s="10"/>
-      <c r="J398" s="10"/>
-      <c r="K398" s="10"/>
-      <c r="L398" s="10"/>
-      <c r="M398" s="10"/>
+      <c r="H398" s="11"/>
+      <c r="I398" s="11"/>
+      <c r="J398" s="11"/>
+      <c r="K398" s="11"/>
+      <c r="L398" s="11"/>
+      <c r="M398" s="11"/>
     </row>
     <row r="399" spans="8:13">
-      <c r="H399" s="10"/>
-      <c r="I399" s="10"/>
-      <c r="J399" s="10"/>
-      <c r="K399" s="10"/>
-      <c r="L399" s="10"/>
-      <c r="M399" s="10"/>
+      <c r="H399" s="11"/>
+      <c r="I399" s="11"/>
+      <c r="J399" s="11"/>
+      <c r="K399" s="11"/>
+      <c r="L399" s="11"/>
+      <c r="M399" s="11"/>
     </row>
     <row r="400" spans="8:13">
-      <c r="H400" s="10"/>
-      <c r="I400" s="10"/>
-      <c r="J400" s="10"/>
-      <c r="K400" s="10"/>
-      <c r="L400" s="10"/>
-      <c r="M400" s="10"/>
+      <c r="H400" s="11"/>
+      <c r="I400" s="11"/>
+      <c r="J400" s="11"/>
+      <c r="K400" s="11"/>
+      <c r="L400" s="11"/>
+      <c r="M400" s="11"/>
     </row>
     <row r="401" spans="8:13">
-      <c r="H401" s="10"/>
-      <c r="I401" s="10"/>
-      <c r="J401" s="10"/>
-      <c r="K401" s="10"/>
-      <c r="L401" s="10"/>
-      <c r="M401" s="10"/>
+      <c r="H401" s="11"/>
+      <c r="I401" s="11"/>
+      <c r="J401" s="11"/>
+      <c r="K401" s="11"/>
+      <c r="L401" s="11"/>
+      <c r="M401" s="11"/>
     </row>
     <row r="402" spans="8:13">
-      <c r="H402" s="10"/>
-      <c r="I402" s="10"/>
-      <c r="J402" s="10"/>
-      <c r="K402" s="10"/>
-      <c r="L402" s="10"/>
-      <c r="M402" s="10"/>
+      <c r="H402" s="11"/>
+      <c r="I402" s="11"/>
+      <c r="J402" s="11"/>
+      <c r="K402" s="11"/>
+      <c r="L402" s="11"/>
+      <c r="M402" s="11"/>
     </row>
     <row r="403" spans="8:13">
-      <c r="H403" s="10"/>
-      <c r="I403" s="10"/>
-      <c r="J403" s="10"/>
-      <c r="K403" s="10"/>
-      <c r="L403" s="10"/>
-      <c r="M403" s="10"/>
+      <c r="H403" s="11"/>
+      <c r="I403" s="11"/>
+      <c r="J403" s="11"/>
+      <c r="K403" s="11"/>
+      <c r="L403" s="11"/>
+      <c r="M403" s="11"/>
     </row>
     <row r="404" spans="8:13">
-      <c r="H404" s="10"/>
-      <c r="I404" s="10"/>
-      <c r="J404" s="10"/>
-      <c r="K404" s="10"/>
-      <c r="L404" s="10"/>
-      <c r="M404" s="10"/>
+      <c r="H404" s="11"/>
+      <c r="I404" s="11"/>
+      <c r="J404" s="11"/>
+      <c r="K404" s="11"/>
+      <c r="L404" s="11"/>
+      <c r="M404" s="11"/>
     </row>
     <row r="405" spans="8:13">
-      <c r="H405" s="10"/>
-      <c r="I405" s="10"/>
-      <c r="J405" s="10"/>
-      <c r="K405" s="10"/>
-      <c r="L405" s="10"/>
-      <c r="M405" s="10"/>
+      <c r="H405" s="11"/>
+      <c r="I405" s="11"/>
+      <c r="J405" s="11"/>
+      <c r="K405" s="11"/>
+      <c r="L405" s="11"/>
+      <c r="M405" s="11"/>
     </row>
     <row r="406" spans="8:13">
-      <c r="H406" s="10"/>
-      <c r="I406" s="10"/>
-      <c r="J406" s="10"/>
-      <c r="K406" s="10"/>
-      <c r="L406" s="10"/>
-      <c r="M406" s="10"/>
+      <c r="H406" s="11"/>
+      <c r="I406" s="11"/>
+      <c r="J406" s="11"/>
+      <c r="K406" s="11"/>
+      <c r="L406" s="11"/>
+      <c r="M406" s="11"/>
     </row>
     <row r="407" spans="8:13">
-      <c r="H407" s="10"/>
-      <c r="I407" s="10"/>
-      <c r="J407" s="10"/>
-      <c r="K407" s="10"/>
-      <c r="L407" s="10"/>
-      <c r="M407" s="10"/>
+      <c r="H407" s="11"/>
+      <c r="I407" s="11"/>
+      <c r="J407" s="11"/>
+      <c r="K407" s="11"/>
+      <c r="L407" s="11"/>
+      <c r="M407" s="11"/>
     </row>
     <row r="408" spans="8:13">
-      <c r="H408" s="10"/>
-      <c r="I408" s="10"/>
-      <c r="J408" s="10"/>
-      <c r="K408" s="10"/>
-      <c r="L408" s="10"/>
-      <c r="M408" s="10"/>
+      <c r="H408" s="11"/>
+      <c r="I408" s="11"/>
+      <c r="J408" s="11"/>
+      <c r="K408" s="11"/>
+      <c r="L408" s="11"/>
+      <c r="M408" s="11"/>
     </row>
     <row r="409" spans="8:13">
-      <c r="H409" s="10"/>
-      <c r="I409" s="10"/>
-      <c r="J409" s="10"/>
-      <c r="K409" s="10"/>
-      <c r="L409" s="10"/>
-      <c r="M409" s="10"/>
+      <c r="H409" s="11"/>
+      <c r="I409" s="11"/>
+      <c r="J409" s="11"/>
+      <c r="K409" s="11"/>
+      <c r="L409" s="11"/>
+      <c r="M409" s="11"/>
     </row>
     <row r="410" spans="8:13">
-      <c r="H410" s="10"/>
-      <c r="I410" s="10"/>
-      <c r="J410" s="10"/>
-      <c r="K410" s="10"/>
-      <c r="L410" s="10"/>
-      <c r="M410" s="10"/>
+      <c r="H410" s="11"/>
+      <c r="I410" s="11"/>
+      <c r="J410" s="11"/>
+      <c r="K410" s="11"/>
+      <c r="L410" s="11"/>
+      <c r="M410" s="11"/>
     </row>
     <row r="411" spans="8:13">
-      <c r="H411" s="10"/>
-      <c r="I411" s="10"/>
-      <c r="J411" s="10"/>
-      <c r="K411" s="10"/>
-      <c r="L411" s="10"/>
-      <c r="M411" s="10"/>
+      <c r="H411" s="11"/>
+      <c r="I411" s="11"/>
+      <c r="J411" s="11"/>
+      <c r="K411" s="11"/>
+      <c r="L411" s="11"/>
+      <c r="M411" s="11"/>
     </row>
     <row r="412" spans="8:13">
-      <c r="H412" s="10"/>
-      <c r="I412" s="10"/>
-      <c r="J412" s="10"/>
-      <c r="K412" s="10"/>
-      <c r="L412" s="10"/>
-      <c r="M412" s="10"/>
+      <c r="H412" s="11"/>
+      <c r="I412" s="11"/>
+      <c r="J412" s="11"/>
+      <c r="K412" s="11"/>
+      <c r="L412" s="11"/>
+      <c r="M412" s="11"/>
     </row>
     <row r="413" spans="8:13">
-      <c r="H413" s="10"/>
-      <c r="I413" s="10"/>
-      <c r="J413" s="10"/>
-      <c r="K413" s="10"/>
-      <c r="L413" s="10"/>
-      <c r="M413" s="10"/>
+      <c r="H413" s="11"/>
+      <c r="I413" s="11"/>
+      <c r="J413" s="11"/>
+      <c r="K413" s="11"/>
+      <c r="L413" s="11"/>
+      <c r="M413" s="11"/>
     </row>
     <row r="414" spans="8:13">
-      <c r="H414" s="10"/>
-      <c r="I414" s="10"/>
-      <c r="J414" s="10"/>
-      <c r="K414" s="10"/>
-      <c r="L414" s="10"/>
-      <c r="M414" s="10"/>
+      <c r="H414" s="11"/>
+      <c r="I414" s="11"/>
+      <c r="J414" s="11"/>
+      <c r="K414" s="11"/>
+      <c r="L414" s="11"/>
+      <c r="M414" s="11"/>
     </row>
     <row r="415" spans="8:13">
-      <c r="H415" s="10"/>
-      <c r="I415" s="10"/>
-      <c r="J415" s="10"/>
-      <c r="K415" s="10"/>
-      <c r="L415" s="10"/>
-      <c r="M415" s="10"/>
+      <c r="H415" s="11"/>
+      <c r="I415" s="11"/>
+      <c r="J415" s="11"/>
+      <c r="K415" s="11"/>
+      <c r="L415" s="11"/>
+      <c r="M415" s="11"/>
     </row>
     <row r="416" spans="8:13">
-      <c r="H416" s="10"/>
-      <c r="I416" s="10"/>
-      <c r="J416" s="10"/>
-      <c r="K416" s="10"/>
-      <c r="L416" s="10"/>
-      <c r="M416" s="10"/>
+      <c r="H416" s="11"/>
+      <c r="I416" s="11"/>
+      <c r="J416" s="11"/>
+      <c r="K416" s="11"/>
+      <c r="L416" s="11"/>
+      <c r="M416" s="11"/>
     </row>
     <row r="417" spans="8:13">
-      <c r="H417" s="10"/>
-      <c r="I417" s="10"/>
-      <c r="J417" s="10"/>
-      <c r="K417" s="10"/>
-      <c r="L417" s="10"/>
-      <c r="M417" s="10"/>
+      <c r="H417" s="11"/>
+      <c r="I417" s="11"/>
+      <c r="J417" s="11"/>
+      <c r="K417" s="11"/>
+      <c r="L417" s="11"/>
+      <c r="M417" s="11"/>
     </row>
     <row r="418" spans="8:13">
-      <c r="H418" s="10"/>
-      <c r="I418" s="10"/>
-      <c r="J418" s="10"/>
-      <c r="K418" s="10"/>
-      <c r="L418" s="10"/>
-      <c r="M418" s="10"/>
+      <c r="H418" s="11"/>
+      <c r="I418" s="11"/>
+      <c r="J418" s="11"/>
+      <c r="K418" s="11"/>
+      <c r="L418" s="11"/>
+      <c r="M418" s="11"/>
     </row>
     <row r="419" spans="8:13">
-      <c r="H419" s="10"/>
-      <c r="I419" s="10"/>
-      <c r="J419" s="10"/>
-      <c r="K419" s="10"/>
-      <c r="L419" s="10"/>
-      <c r="M419" s="10"/>
+      <c r="H419" s="11"/>
+      <c r="I419" s="11"/>
+      <c r="J419" s="11"/>
+      <c r="K419" s="11"/>
+      <c r="L419" s="11"/>
+      <c r="M419" s="11"/>
     </row>
     <row r="420" spans="8:13">
-      <c r="H420" s="10"/>
-      <c r="I420" s="10"/>
-      <c r="J420" s="10"/>
-      <c r="K420" s="10"/>
-      <c r="L420" s="10"/>
-      <c r="M420" s="10"/>
+      <c r="H420" s="11"/>
+      <c r="I420" s="11"/>
+      <c r="J420" s="11"/>
+      <c r="K420" s="11"/>
+      <c r="L420" s="11"/>
+      <c r="M420" s="11"/>
     </row>
     <row r="421" spans="8:13">
-      <c r="H421" s="10"/>
-      <c r="I421" s="10"/>
-      <c r="J421" s="10"/>
-      <c r="K421" s="10"/>
-      <c r="L421" s="10"/>
-      <c r="M421" s="10"/>
+      <c r="H421" s="11"/>
+      <c r="I421" s="11"/>
+      <c r="J421" s="11"/>
+      <c r="K421" s="11"/>
+      <c r="L421" s="11"/>
+      <c r="M421" s="11"/>
     </row>
     <row r="422" spans="8:13">
-      <c r="H422" s="10"/>
-      <c r="I422" s="10"/>
-      <c r="J422" s="10"/>
-      <c r="K422" s="10"/>
-      <c r="L422" s="10"/>
-      <c r="M422" s="10"/>
+      <c r="H422" s="11"/>
+      <c r="I422" s="11"/>
+      <c r="J422" s="11"/>
+      <c r="K422" s="11"/>
+      <c r="L422" s="11"/>
+      <c r="M422" s="11"/>
     </row>
     <row r="423" spans="8:13">
-      <c r="H423" s="10"/>
-      <c r="I423" s="10"/>
-      <c r="J423" s="10"/>
-      <c r="K423" s="10"/>
-      <c r="L423" s="10"/>
-      <c r="M423" s="10"/>
+      <c r="H423" s="11"/>
+      <c r="I423" s="11"/>
+      <c r="J423" s="11"/>
+      <c r="K423" s="11"/>
+      <c r="L423" s="11"/>
+      <c r="M423" s="11"/>
     </row>
     <row r="424" spans="8:13">
-      <c r="H424" s="10"/>
-      <c r="I424" s="10"/>
-      <c r="J424" s="10"/>
-      <c r="K424" s="10"/>
-      <c r="L424" s="10"/>
-      <c r="M424" s="10"/>
+      <c r="H424" s="11"/>
+      <c r="I424" s="11"/>
+      <c r="J424" s="11"/>
+      <c r="K424" s="11"/>
+      <c r="L424" s="11"/>
+      <c r="M424" s="11"/>
     </row>
     <row r="425" spans="8:13">
-      <c r="H425" s="10"/>
-      <c r="I425" s="10"/>
-      <c r="J425" s="10"/>
-      <c r="K425" s="10"/>
-      <c r="L425" s="10"/>
-      <c r="M425" s="10"/>
+      <c r="H425" s="11"/>
+      <c r="I425" s="11"/>
+      <c r="J425" s="11"/>
+      <c r="K425" s="11"/>
+      <c r="L425" s="11"/>
+      <c r="M425" s="11"/>
     </row>
     <row r="426" spans="8:13">
-      <c r="H426" s="10"/>
-      <c r="I426" s="10"/>
-      <c r="J426" s="10"/>
-      <c r="K426" s="10"/>
-      <c r="L426" s="10"/>
-      <c r="M426" s="10"/>
+      <c r="H426" s="11"/>
+      <c r="I426" s="11"/>
+      <c r="J426" s="11"/>
+      <c r="K426" s="11"/>
+      <c r="L426" s="11"/>
+      <c r="M426" s="11"/>
     </row>
     <row r="427" spans="8:13">
-      <c r="H427" s="10"/>
-      <c r="I427" s="10"/>
-      <c r="J427" s="10"/>
-      <c r="K427" s="10"/>
-      <c r="L427" s="10"/>
-      <c r="M427" s="10"/>
+      <c r="H427" s="11"/>
+      <c r="I427" s="11"/>
+      <c r="J427" s="11"/>
+      <c r="K427" s="11"/>
+      <c r="L427" s="11"/>
+      <c r="M427" s="11"/>
     </row>
     <row r="428" spans="8:13">
-      <c r="H428" s="10"/>
-      <c r="I428" s="10"/>
-      <c r="J428" s="10"/>
-      <c r="K428" s="10"/>
-      <c r="L428" s="10"/>
-      <c r="M428" s="10"/>
+      <c r="H428" s="11"/>
+      <c r="I428" s="11"/>
+      <c r="J428" s="11"/>
+      <c r="K428" s="11"/>
+      <c r="L428" s="11"/>
+      <c r="M428" s="11"/>
     </row>
     <row r="429" spans="8:13">
-      <c r="H429" s="10"/>
-      <c r="I429" s="10"/>
-      <c r="J429" s="10"/>
-      <c r="K429" s="10"/>
-      <c r="L429" s="10"/>
-      <c r="M429" s="10"/>
+      <c r="H429" s="11"/>
+      <c r="I429" s="11"/>
+      <c r="J429" s="11"/>
+      <c r="K429" s="11"/>
+      <c r="L429" s="11"/>
+      <c r="M429" s="11"/>
     </row>
     <row r="430" spans="8:13">
-      <c r="H430" s="10"/>
-      <c r="I430" s="10"/>
-      <c r="J430" s="10"/>
-      <c r="K430" s="10"/>
-      <c r="L430" s="10"/>
-      <c r="M430" s="10"/>
+      <c r="H430" s="11"/>
+      <c r="I430" s="11"/>
+      <c r="J430" s="11"/>
+      <c r="K430" s="11"/>
+      <c r="L430" s="11"/>
+      <c r="M430" s="11"/>
     </row>
     <row r="431" spans="8:13">
-      <c r="H431" s="10"/>
-      <c r="I431" s="10"/>
-      <c r="J431" s="10"/>
-      <c r="K431" s="10"/>
-      <c r="L431" s="10"/>
-      <c r="M431" s="10"/>
+      <c r="H431" s="11"/>
+      <c r="I431" s="11"/>
+      <c r="J431" s="11"/>
+      <c r="K431" s="11"/>
+      <c r="L431" s="11"/>
+      <c r="M431" s="11"/>
     </row>
     <row r="432" spans="8:13">
-      <c r="H432" s="10"/>
-      <c r="I432" s="10"/>
-      <c r="J432" s="10"/>
-      <c r="K432" s="10"/>
-      <c r="L432" s="10"/>
-      <c r="M432" s="10"/>
+      <c r="H432" s="11"/>
+      <c r="I432" s="11"/>
+      <c r="J432" s="11"/>
+      <c r="K432" s="11"/>
+      <c r="L432" s="11"/>
+      <c r="M432" s="11"/>
     </row>
     <row r="433" spans="8:13">
-      <c r="H433" s="10"/>
-      <c r="I433" s="10"/>
-      <c r="J433" s="10"/>
-      <c r="K433" s="10"/>
-      <c r="L433" s="10"/>
-      <c r="M433" s="10"/>
+      <c r="H433" s="11"/>
+      <c r="I433" s="11"/>
+      <c r="J433" s="11"/>
+      <c r="K433" s="11"/>
+      <c r="L433" s="11"/>
+      <c r="M433" s="11"/>
     </row>
     <row r="434" spans="8:13">
-      <c r="H434" s="10"/>
-      <c r="I434" s="10"/>
-      <c r="J434" s="10"/>
-      <c r="K434" s="10"/>
-      <c r="L434" s="10"/>
-      <c r="M434" s="10"/>
+      <c r="H434" s="11"/>
+      <c r="I434" s="11"/>
+      <c r="J434" s="11"/>
+      <c r="K434" s="11"/>
+      <c r="L434" s="11"/>
+      <c r="M434" s="11"/>
     </row>
     <row r="435" spans="8:13">
-      <c r="H435" s="10"/>
-      <c r="I435" s="10"/>
-      <c r="J435" s="10"/>
-      <c r="K435" s="10"/>
-      <c r="L435" s="10"/>
-      <c r="M435" s="10"/>
+      <c r="H435" s="11"/>
+      <c r="I435" s="11"/>
+      <c r="J435" s="11"/>
+      <c r="K435" s="11"/>
+      <c r="L435" s="11"/>
+      <c r="M435" s="11"/>
     </row>
     <row r="436" spans="8:13">
-      <c r="H436" s="10"/>
-      <c r="I436" s="10"/>
-      <c r="J436" s="10"/>
-      <c r="K436" s="10"/>
-      <c r="L436" s="10"/>
-      <c r="M436" s="10"/>
+      <c r="H436" s="11"/>
+      <c r="I436" s="11"/>
+      <c r="J436" s="11"/>
+      <c r="K436" s="11"/>
+      <c r="L436" s="11"/>
+      <c r="M436" s="11"/>
     </row>
     <row r="437" spans="8:13">
-      <c r="H437" s="10"/>
-      <c r="I437" s="10"/>
-      <c r="J437" s="10"/>
-      <c r="K437" s="10"/>
-      <c r="L437" s="10"/>
-      <c r="M437" s="10"/>
+      <c r="H437" s="11"/>
+      <c r="I437" s="11"/>
+      <c r="J437" s="11"/>
+      <c r="K437" s="11"/>
+      <c r="L437" s="11"/>
+      <c r="M437" s="11"/>
     </row>
     <row r="438" spans="8:13">
-      <c r="H438" s="10"/>
-      <c r="I438" s="10"/>
-      <c r="J438" s="10"/>
-      <c r="K438" s="10"/>
-      <c r="L438" s="10"/>
-      <c r="M438" s="10"/>
+      <c r="H438" s="11"/>
+      <c r="I438" s="11"/>
+      <c r="J438" s="11"/>
+      <c r="K438" s="11"/>
+      <c r="L438" s="11"/>
+      <c r="M438" s="11"/>
     </row>
     <row r="439" spans="8:13">
-      <c r="H439" s="10"/>
-      <c r="I439" s="10"/>
-      <c r="J439" s="10"/>
-      <c r="K439" s="10"/>
-      <c r="L439" s="10"/>
-      <c r="M439" s="10"/>
+      <c r="H439" s="11"/>
+      <c r="I439" s="11"/>
+      <c r="J439" s="11"/>
+      <c r="K439" s="11"/>
+      <c r="L439" s="11"/>
+      <c r="M439" s="11"/>
     </row>
     <row r="440" spans="8:13">
-      <c r="H440" s="10"/>
-      <c r="I440" s="10"/>
-      <c r="J440" s="10"/>
-      <c r="K440" s="10"/>
-      <c r="L440" s="10"/>
-      <c r="M440" s="10"/>
+      <c r="H440" s="11"/>
+      <c r="I440" s="11"/>
+      <c r="J440" s="11"/>
+      <c r="K440" s="11"/>
+      <c r="L440" s="11"/>
+      <c r="M440" s="11"/>
     </row>
     <row r="441" spans="8:13">
-      <c r="H441" s="10"/>
-      <c r="I441" s="10"/>
-      <c r="J441" s="10"/>
-      <c r="K441" s="10"/>
-      <c r="L441" s="10"/>
-      <c r="M441" s="10"/>
+      <c r="H441" s="11"/>
+      <c r="I441" s="11"/>
+      <c r="J441" s="11"/>
+      <c r="K441" s="11"/>
+      <c r="L441" s="11"/>
+      <c r="M441" s="11"/>
     </row>
     <row r="442" spans="8:13">
-      <c r="H442" s="10"/>
-      <c r="I442" s="10"/>
-      <c r="J442" s="10"/>
-      <c r="K442" s="10"/>
-      <c r="L442" s="10"/>
-      <c r="M442" s="10"/>
+      <c r="H442" s="11"/>
+      <c r="I442" s="11"/>
+      <c r="J442" s="11"/>
+      <c r="K442" s="11"/>
+      <c r="L442" s="11"/>
+      <c r="M442" s="11"/>
     </row>
     <row r="443" spans="8:13">
-      <c r="H443" s="10"/>
-      <c r="I443" s="10"/>
-      <c r="J443" s="10"/>
-      <c r="K443" s="10"/>
-      <c r="L443" s="10"/>
-      <c r="M443" s="10"/>
+      <c r="H443" s="11"/>
+      <c r="I443" s="11"/>
+      <c r="J443" s="11"/>
+      <c r="K443" s="11"/>
+      <c r="L443" s="11"/>
+      <c r="M443" s="11"/>
     </row>
     <row r="444" spans="8:13">
-      <c r="H444" s="10"/>
-      <c r="I444" s="10"/>
-      <c r="J444" s="10"/>
-      <c r="K444" s="10"/>
-      <c r="L444" s="10"/>
-      <c r="M444" s="10"/>
+      <c r="H444" s="11"/>
+      <c r="I444" s="11"/>
+      <c r="J444" s="11"/>
+      <c r="K444" s="11"/>
+      <c r="L444" s="11"/>
+      <c r="M444" s="11"/>
     </row>
     <row r="445" spans="8:13">
-      <c r="H445" s="10"/>
-      <c r="I445" s="10"/>
-      <c r="J445" s="10"/>
-      <c r="K445" s="10"/>
-      <c r="L445" s="10"/>
-      <c r="M445" s="10"/>
+      <c r="H445" s="11"/>
+      <c r="I445" s="11"/>
+      <c r="J445" s="11"/>
+      <c r="K445" s="11"/>
+      <c r="L445" s="11"/>
+      <c r="M445" s="11"/>
     </row>
     <row r="446" spans="8:13">
-      <c r="H446" s="10"/>
-      <c r="I446" s="10"/>
-      <c r="J446" s="10"/>
-      <c r="K446" s="10"/>
-      <c r="L446" s="10"/>
-      <c r="M446" s="10"/>
+      <c r="H446" s="11"/>
+      <c r="I446" s="11"/>
+      <c r="J446" s="11"/>
+      <c r="K446" s="11"/>
+      <c r="L446" s="11"/>
+      <c r="M446" s="11"/>
     </row>
     <row r="447" spans="8:13">
-      <c r="H447" s="10"/>
-      <c r="I447" s="10"/>
-      <c r="J447" s="10"/>
-      <c r="K447" s="10"/>
-      <c r="L447" s="10"/>
-      <c r="M447" s="10"/>
+      <c r="H447" s="11"/>
+      <c r="I447" s="11"/>
+      <c r="J447" s="11"/>
+      <c r="K447" s="11"/>
+      <c r="L447" s="11"/>
+      <c r="M447" s="11"/>
     </row>
     <row r="448" spans="8:13">
-      <c r="H448" s="10"/>
-      <c r="I448" s="10"/>
-      <c r="J448" s="10"/>
-      <c r="K448" s="10"/>
-      <c r="L448" s="10"/>
-      <c r="M448" s="10"/>
+      <c r="H448" s="11"/>
+      <c r="I448" s="11"/>
+      <c r="J448" s="11"/>
+      <c r="K448" s="11"/>
+      <c r="L448" s="11"/>
+      <c r="M448" s="11"/>
     </row>
     <row r="449" spans="8:13">
-      <c r="H449" s="10"/>
-      <c r="I449" s="10"/>
-      <c r="J449" s="10"/>
-      <c r="K449" s="10"/>
-      <c r="L449" s="10"/>
-      <c r="M449" s="10"/>
+      <c r="H449" s="11"/>
+      <c r="I449" s="11"/>
+      <c r="J449" s="11"/>
+      <c r="K449" s="11"/>
+      <c r="L449" s="11"/>
+      <c r="M449" s="11"/>
     </row>
     <row r="450" spans="8:13">
-      <c r="H450" s="10"/>
-      <c r="I450" s="10"/>
-      <c r="J450" s="10"/>
-      <c r="K450" s="10"/>
-      <c r="L450" s="10"/>
-      <c r="M450" s="10"/>
+      <c r="H450" s="11"/>
+      <c r="I450" s="11"/>
+      <c r="J450" s="11"/>
+      <c r="K450" s="11"/>
+      <c r="L450" s="11"/>
+      <c r="M450" s="11"/>
     </row>
     <row r="451" spans="8:13">
-      <c r="H451" s="10"/>
-      <c r="I451" s="10"/>
-      <c r="J451" s="10"/>
-      <c r="K451" s="10"/>
-      <c r="L451" s="10"/>
-      <c r="M451" s="10"/>
+      <c r="H451" s="11"/>
+      <c r="I451" s="11"/>
+      <c r="J451" s="11"/>
+      <c r="K451" s="11"/>
+      <c r="L451" s="11"/>
+      <c r="M451" s="11"/>
     </row>
     <row r="452" spans="8:13">
-      <c r="H452" s="10"/>
-      <c r="I452" s="10"/>
-      <c r="J452" s="10"/>
-      <c r="K452" s="10"/>
-      <c r="L452" s="10"/>
-      <c r="M452" s="10"/>
+      <c r="H452" s="11"/>
+      <c r="I452" s="11"/>
+      <c r="J452" s="11"/>
+      <c r="K452" s="11"/>
+      <c r="L452" s="11"/>
+      <c r="M452" s="11"/>
     </row>
     <row r="453" spans="8:13">
-      <c r="H453" s="10"/>
-      <c r="I453" s="10"/>
-      <c r="J453" s="10"/>
-      <c r="K453" s="10"/>
-      <c r="L453" s="10"/>
-      <c r="M453" s="10"/>
+      <c r="H453" s="11"/>
+      <c r="I453" s="11"/>
+      <c r="J453" s="11"/>
+      <c r="K453" s="11"/>
+      <c r="L453" s="11"/>
+      <c r="M453" s="11"/>
     </row>
     <row r="454" spans="8:13">
-      <c r="H454" s="10"/>
-      <c r="I454" s="10"/>
-      <c r="J454" s="10"/>
-      <c r="K454" s="10"/>
-      <c r="L454" s="10"/>
-      <c r="M454" s="10"/>
+      <c r="H454" s="11"/>
+      <c r="I454" s="11"/>
+      <c r="J454" s="11"/>
+      <c r="K454" s="11"/>
+      <c r="L454" s="11"/>
+      <c r="M454" s="11"/>
     </row>
     <row r="455" spans="8:13">
-      <c r="H455" s="10"/>
-      <c r="I455" s="10"/>
-      <c r="J455" s="10"/>
-      <c r="K455" s="10"/>
-      <c r="L455" s="10"/>
-      <c r="M455" s="10"/>
+      <c r="H455" s="11"/>
+      <c r="I455" s="11"/>
+      <c r="J455" s="11"/>
+      <c r="K455" s="11"/>
+      <c r="L455" s="11"/>
+      <c r="M455" s="11"/>
     </row>
     <row r="456" spans="8:13">
-      <c r="H456" s="10"/>
-      <c r="I456" s="10"/>
-      <c r="J456" s="10"/>
-      <c r="K456" s="10"/>
-      <c r="L456" s="10"/>
-      <c r="M456" s="10"/>
+      <c r="H456" s="11"/>
+      <c r="I456" s="11"/>
+      <c r="J456" s="11"/>
+      <c r="K456" s="11"/>
+      <c r="L456" s="11"/>
+      <c r="M456" s="11"/>
     </row>
     <row r="457" spans="8:13">
-      <c r="H457" s="10"/>
-      <c r="I457" s="10"/>
-      <c r="J457" s="10"/>
-      <c r="K457" s="10"/>
-      <c r="L457" s="10"/>
-      <c r="M457" s="10"/>
+      <c r="H457" s="11"/>
+      <c r="I457" s="11"/>
+      <c r="J457" s="11"/>
+      <c r="K457" s="11"/>
+      <c r="L457" s="11"/>
+      <c r="M457" s="11"/>
     </row>
     <row r="458" spans="8:13">
-      <c r="H458" s="10"/>
-      <c r="I458" s="10"/>
-      <c r="J458" s="10"/>
-      <c r="K458" s="10"/>
-      <c r="L458" s="10"/>
-      <c r="M458" s="10"/>
+      <c r="H458" s="11"/>
+      <c r="I458" s="11"/>
+      <c r="J458" s="11"/>
+      <c r="K458" s="11"/>
+      <c r="L458" s="11"/>
+      <c r="M458" s="11"/>
     </row>
     <row r="459" spans="8:13">
-      <c r="H459" s="10"/>
-      <c r="I459" s="10"/>
-      <c r="J459" s="10"/>
-      <c r="K459" s="10"/>
-      <c r="L459" s="10"/>
-      <c r="M459" s="10"/>
+      <c r="H459" s="11"/>
+      <c r="I459" s="11"/>
+      <c r="J459" s="11"/>
+      <c r="K459" s="11"/>
+      <c r="L459" s="11"/>
+      <c r="M459" s="11"/>
     </row>
     <row r="460" spans="8:13">
-      <c r="H460" s="10"/>
-      <c r="I460" s="10"/>
-      <c r="J460" s="10"/>
-      <c r="K460" s="10"/>
-      <c r="L460" s="10"/>
-      <c r="M460" s="10"/>
+      <c r="H460" s="11"/>
+      <c r="I460" s="11"/>
+      <c r="J460" s="11"/>
+      <c r="K460" s="11"/>
+      <c r="L460" s="11"/>
+      <c r="M460" s="11"/>
     </row>
     <row r="461" spans="8:13">
-      <c r="H461" s="10"/>
-      <c r="I461" s="10"/>
-      <c r="J461" s="10"/>
-      <c r="K461" s="10"/>
-      <c r="L461" s="10"/>
-      <c r="M461" s="10"/>
+      <c r="H461" s="11"/>
+      <c r="I461" s="11"/>
+      <c r="J461" s="11"/>
+      <c r="K461" s="11"/>
+      <c r="L461" s="11"/>
+      <c r="M461" s="11"/>
     </row>
     <row r="462" spans="8:13">
-      <c r="H462" s="10"/>
-      <c r="I462" s="10"/>
-      <c r="J462" s="10"/>
-      <c r="K462" s="10"/>
-      <c r="L462" s="10"/>
-      <c r="M462" s="10"/>
+      <c r="H462" s="11"/>
+      <c r="I462" s="11"/>
+      <c r="J462" s="11"/>
+      <c r="K462" s="11"/>
+      <c r="L462" s="11"/>
+      <c r="M462" s="11"/>
     </row>
     <row r="463" spans="8:13">
-      <c r="H463" s="10"/>
-      <c r="I463" s="10"/>
-      <c r="J463" s="10"/>
-      <c r="K463" s="10"/>
-      <c r="L463" s="10"/>
-      <c r="M463" s="10"/>
+      <c r="H463" s="11"/>
+      <c r="I463" s="11"/>
+      <c r="J463" s="11"/>
+      <c r="K463" s="11"/>
+      <c r="L463" s="11"/>
+      <c r="M463" s="11"/>
     </row>
     <row r="464" spans="8:13">
-      <c r="H464" s="10"/>
-      <c r="I464" s="10"/>
-      <c r="J464" s="10"/>
-      <c r="K464" s="10"/>
-      <c r="L464" s="10"/>
-      <c r="M464" s="10"/>
+      <c r="H464" s="11"/>
+      <c r="I464" s="11"/>
+      <c r="J464" s="11"/>
+      <c r="K464" s="11"/>
+      <c r="L464" s="11"/>
+      <c r="M464" s="11"/>
     </row>
     <row r="465" spans="8:13">
-      <c r="H465" s="10"/>
-      <c r="I465" s="10"/>
-      <c r="J465" s="10"/>
-      <c r="K465" s="10"/>
-      <c r="L465" s="10"/>
-      <c r="M465" s="10"/>
+      <c r="H465" s="11"/>
+      <c r="I465" s="11"/>
+      <c r="J465" s="11"/>
+      <c r="K465" s="11"/>
+      <c r="L465" s="11"/>
+      <c r="M465" s="11"/>
     </row>
     <row r="466" spans="8:13">
-      <c r="H466" s="10"/>
-      <c r="I466" s="10"/>
-      <c r="J466" s="10"/>
-      <c r="K466" s="10"/>
-      <c r="L466" s="10"/>
-      <c r="M466" s="10"/>
+      <c r="H466" s="11"/>
+      <c r="I466" s="11"/>
+      <c r="J466" s="11"/>
+      <c r="K466" s="11"/>
+      <c r="L466" s="11"/>
+      <c r="M466" s="11"/>
     </row>
     <row r="467" spans="8:13">
-      <c r="H467" s="10"/>
-      <c r="I467" s="10"/>
-      <c r="J467" s="10"/>
-      <c r="K467" s="10"/>
-      <c r="L467" s="10"/>
-      <c r="M467" s="10"/>
+      <c r="H467" s="11"/>
+      <c r="I467" s="11"/>
+      <c r="J467" s="11"/>
+      <c r="K467" s="11"/>
+      <c r="L467" s="11"/>
+      <c r="M467" s="11"/>
     </row>
     <row r="468" spans="8:13">
-      <c r="H468" s="10"/>
-      <c r="I468" s="10"/>
-      <c r="J468" s="10"/>
-      <c r="K468" s="10"/>
-      <c r="L468" s="10"/>
-      <c r="M468" s="10"/>
+      <c r="H468" s="11"/>
+      <c r="I468" s="11"/>
+      <c r="J468" s="11"/>
+      <c r="K468" s="11"/>
+      <c r="L468" s="11"/>
+      <c r="M468" s="11"/>
     </row>
     <row r="469" spans="8:13">
-      <c r="H469" s="10"/>
-      <c r="I469" s="10"/>
-      <c r="J469" s="10"/>
-      <c r="K469" s="10"/>
-      <c r="L469" s="10"/>
-      <c r="M469" s="10"/>
+      <c r="H469" s="11"/>
+      <c r="I469" s="11"/>
+      <c r="J469" s="11"/>
+      <c r="K469" s="11"/>
+      <c r="L469" s="11"/>
+      <c r="M469" s="11"/>
     </row>
     <row r="470" spans="8:13">
-      <c r="H470" s="10"/>
-      <c r="I470" s="10"/>
-      <c r="J470" s="10"/>
-      <c r="K470" s="10"/>
-      <c r="L470" s="10"/>
-      <c r="M470" s="10"/>
+      <c r="H470" s="11"/>
+      <c r="I470" s="11"/>
+      <c r="J470" s="11"/>
+      <c r="K470" s="11"/>
+      <c r="L470" s="11"/>
+      <c r="M470" s="11"/>
     </row>
     <row r="471" spans="8:13">
-      <c r="H471" s="10"/>
-      <c r="I471" s="10"/>
-      <c r="J471" s="10"/>
-      <c r="K471" s="10"/>
-      <c r="L471" s="10"/>
-      <c r="M471" s="10"/>
+      <c r="H471" s="11"/>
+      <c r="I471" s="11"/>
+      <c r="J471" s="11"/>
+      <c r="K471" s="11"/>
+      <c r="L471" s="11"/>
+      <c r="M471" s="11"/>
     </row>
     <row r="472" spans="8:13">
-      <c r="H472" s="10"/>
-      <c r="I472" s="10"/>
-      <c r="J472" s="10"/>
-      <c r="K472" s="10"/>
-      <c r="L472" s="10"/>
-      <c r="M472" s="10"/>
+      <c r="H472" s="11"/>
+      <c r="I472" s="11"/>
+      <c r="J472" s="11"/>
+      <c r="K472" s="11"/>
+      <c r="L472" s="11"/>
+      <c r="M472" s="11"/>
     </row>
     <row r="473" spans="8:13">
-      <c r="H473" s="10"/>
-      <c r="I473" s="10"/>
-      <c r="J473" s="10"/>
-      <c r="K473" s="10"/>
-      <c r="L473" s="10"/>
-      <c r="M473" s="10"/>
+      <c r="H473" s="11"/>
+      <c r="I473" s="11"/>
+      <c r="J473" s="11"/>
+      <c r="K473" s="11"/>
+      <c r="L473" s="11"/>
+      <c r="M473" s="11"/>
     </row>
     <row r="474" spans="8:13">
-      <c r="H474" s="10"/>
-      <c r="I474" s="10"/>
-      <c r="J474" s="10"/>
-      <c r="K474" s="10"/>
-      <c r="L474" s="10"/>
-      <c r="M474" s="10"/>
+      <c r="H474" s="11"/>
+      <c r="I474" s="11"/>
+      <c r="J474" s="11"/>
+      <c r="K474" s="11"/>
+      <c r="L474" s="11"/>
+      <c r="M474" s="11"/>
     </row>
     <row r="475" spans="8:13">
-      <c r="H475" s="10"/>
-      <c r="I475" s="10"/>
-      <c r="J475" s="10"/>
-      <c r="K475" s="10"/>
-      <c r="L475" s="10"/>
-      <c r="M475" s="10"/>
+      <c r="H475" s="11"/>
+      <c r="I475" s="11"/>
+      <c r="J475" s="11"/>
+      <c r="K475" s="11"/>
+      <c r="L475" s="11"/>
+      <c r="M475" s="11"/>
     </row>
     <row r="476" spans="8:13">
-      <c r="H476" s="10"/>
-      <c r="I476" s="10"/>
-      <c r="J476" s="10"/>
-      <c r="K476" s="10"/>
-      <c r="L476" s="10"/>
-      <c r="M476" s="10"/>
+      <c r="H476" s="11"/>
+      <c r="I476" s="11"/>
+      <c r="J476" s="11"/>
+      <c r="K476" s="11"/>
+      <c r="L476" s="11"/>
+      <c r="M476" s="11"/>
     </row>
     <row r="477" spans="8:13">
-      <c r="H477" s="10"/>
-      <c r="I477" s="10"/>
-      <c r="J477" s="10"/>
-      <c r="K477" s="10"/>
-      <c r="L477" s="10"/>
-      <c r="M477" s="10"/>
+      <c r="H477" s="11"/>
+      <c r="I477" s="11"/>
+      <c r="J477" s="11"/>
+      <c r="K477" s="11"/>
+      <c r="L477" s="11"/>
+      <c r="M477" s="11"/>
     </row>
     <row r="478" spans="8:13">
-      <c r="H478" s="10"/>
-      <c r="I478" s="10"/>
-      <c r="J478" s="10"/>
-      <c r="K478" s="10"/>
-      <c r="L478" s="10"/>
-      <c r="M478" s="10"/>
+      <c r="H478" s="11"/>
+      <c r="I478" s="11"/>
+      <c r="J478" s="11"/>
+      <c r="K478" s="11"/>
+      <c r="L478" s="11"/>
+      <c r="M478" s="11"/>
     </row>
     <row r="479" spans="8:13">
-      <c r="H479" s="10"/>
-      <c r="I479" s="10"/>
-      <c r="J479" s="10"/>
-      <c r="K479" s="10"/>
-      <c r="L479" s="10"/>
-      <c r="M479" s="10"/>
+      <c r="H479" s="11"/>
+      <c r="I479" s="11"/>
+      <c r="J479" s="11"/>
+      <c r="K479" s="11"/>
+      <c r="L479" s="11"/>
+      <c r="M479" s="11"/>
     </row>
     <row r="480" spans="8:13">
-      <c r="H480" s="10"/>
-      <c r="I480" s="10"/>
-      <c r="J480" s="10"/>
-      <c r="K480" s="10"/>
-      <c r="L480" s="10"/>
-      <c r="M480" s="10"/>
+      <c r="H480" s="11"/>
+      <c r="I480" s="11"/>
+      <c r="J480" s="11"/>
+      <c r="K480" s="11"/>
+      <c r="L480" s="11"/>
+      <c r="M480" s="11"/>
     </row>
     <row r="481" spans="8:13">
-      <c r="H481" s="10"/>
-      <c r="I481" s="10"/>
-      <c r="J481" s="10"/>
-      <c r="K481" s="10"/>
-      <c r="L481" s="10"/>
-      <c r="M481" s="10"/>
+      <c r="H481" s="11"/>
+      <c r="I481" s="11"/>
+      <c r="J481" s="11"/>
+      <c r="K481" s="11"/>
+      <c r="L481" s="11"/>
+      <c r="M481" s="11"/>
     </row>
     <row r="482" spans="8:13">
-      <c r="H482" s="10"/>
-      <c r="I482" s="10"/>
-      <c r="J482" s="10"/>
-      <c r="K482" s="10"/>
-      <c r="L482" s="10"/>
-      <c r="M482" s="10"/>
+      <c r="H482" s="11"/>
+      <c r="I482" s="11"/>
+      <c r="J482" s="11"/>
+      <c r="K482" s="11"/>
+      <c r="L482" s="11"/>
+      <c r="M482" s="11"/>
     </row>
     <row r="483" spans="8:13">
-      <c r="H483" s="10"/>
-      <c r="I483" s="10"/>
-      <c r="J483" s="10"/>
-      <c r="K483" s="10"/>
-      <c r="L483" s="10"/>
-      <c r="M483" s="10"/>
+      <c r="H483" s="11"/>
+      <c r="I483" s="11"/>
+      <c r="J483" s="11"/>
+      <c r="K483" s="11"/>
+      <c r="L483" s="11"/>
+      <c r="M483" s="11"/>
     </row>
     <row r="484" spans="8:13">
-      <c r="H484" s="10"/>
-      <c r="I484" s="10"/>
-      <c r="J484" s="10"/>
-      <c r="K484" s="10"/>
-      <c r="L484" s="10"/>
-      <c r="M484" s="10"/>
+      <c r="H484" s="11"/>
+      <c r="I484" s="11"/>
+      <c r="J484" s="11"/>
+      <c r="K484" s="11"/>
+      <c r="L484" s="11"/>
+      <c r="M484" s="11"/>
     </row>
     <row r="485" spans="8:13">
-      <c r="H485" s="10"/>
-      <c r="I485" s="10"/>
-      <c r="J485" s="10"/>
-      <c r="K485" s="10"/>
-      <c r="L485" s="10"/>
-      <c r="M485" s="10"/>
+      <c r="H485" s="11"/>
+      <c r="I485" s="11"/>
+      <c r="J485" s="11"/>
+      <c r="K485" s="11"/>
+      <c r="L485" s="11"/>
+      <c r="M485" s="11"/>
     </row>
     <row r="486" spans="8:13">
-      <c r="H486" s="10"/>
-      <c r="I486" s="10"/>
-      <c r="J486" s="10"/>
-      <c r="K486" s="10"/>
-      <c r="L486" s="10"/>
-      <c r="M486" s="10"/>
+      <c r="H486" s="11"/>
+      <c r="I486" s="11"/>
+      <c r="J486" s="11"/>
+      <c r="K486" s="11"/>
+      <c r="L486" s="11"/>
+      <c r="M486" s="11"/>
     </row>
     <row r="487" spans="8:13">
-      <c r="H487" s="10"/>
-      <c r="I487" s="10"/>
-      <c r="J487" s="10"/>
-      <c r="K487" s="10"/>
-      <c r="L487" s="10"/>
-      <c r="M487" s="10"/>
+      <c r="H487" s="11"/>
+      <c r="I487" s="11"/>
+      <c r="J487" s="11"/>
+      <c r="K487" s="11"/>
+      <c r="L487" s="11"/>
+      <c r="M487" s="11"/>
     </row>
     <row r="488" spans="8:13">
-      <c r="H488" s="10"/>
-      <c r="I488" s="10"/>
-      <c r="J488" s="10"/>
-      <c r="K488" s="10"/>
-      <c r="L488" s="10"/>
-      <c r="M488" s="10"/>
+      <c r="H488" s="11"/>
+      <c r="I488" s="11"/>
+      <c r="J488" s="11"/>
+      <c r="K488" s="11"/>
+      <c r="L488" s="11"/>
+      <c r="M488" s="11"/>
     </row>
     <row r="489" spans="8:13">
-      <c r="H489" s="10"/>
-      <c r="I489" s="10"/>
-      <c r="J489" s="10"/>
-      <c r="K489" s="10"/>
-      <c r="L489" s="10"/>
-      <c r="M489" s="10"/>
+      <c r="H489" s="11"/>
+      <c r="I489" s="11"/>
+      <c r="J489" s="11"/>
+      <c r="K489" s="11"/>
+      <c r="L489" s="11"/>
+      <c r="M489" s="11"/>
     </row>
     <row r="490" spans="8:13">
-      <c r="H490" s="10"/>
-      <c r="I490" s="10"/>
-      <c r="J490" s="10"/>
-      <c r="K490" s="10"/>
-      <c r="L490" s="10"/>
-      <c r="M490" s="10"/>
+      <c r="H490" s="11"/>
+      <c r="I490" s="11"/>
+      <c r="J490" s="11"/>
+      <c r="K490" s="11"/>
+      <c r="L490" s="11"/>
+      <c r="M490" s="11"/>
     </row>
     <row r="491" spans="8:13">
-      <c r="H491" s="10"/>
-      <c r="I491" s="10"/>
-      <c r="J491" s="10"/>
-      <c r="K491" s="10"/>
-      <c r="L491" s="10"/>
-      <c r="M491" s="10"/>
+      <c r="H491" s="11"/>
+      <c r="I491" s="11"/>
+      <c r="J491" s="11"/>
+      <c r="K491" s="11"/>
+      <c r="L491" s="11"/>
+      <c r="M491" s="11"/>
     </row>
     <row r="492" spans="8:13">
-      <c r="H492" s="10"/>
-      <c r="I492" s="10"/>
-      <c r="J492" s="10"/>
-      <c r="K492" s="10"/>
-      <c r="L492" s="10"/>
-      <c r="M492" s="10"/>
+      <c r="H492" s="11"/>
+      <c r="I492" s="11"/>
+      <c r="J492" s="11"/>
+      <c r="K492" s="11"/>
+      <c r="L492" s="11"/>
+      <c r="M492" s="11"/>
     </row>
     <row r="493" spans="8:13">
-      <c r="H493" s="10"/>
-      <c r="I493" s="10"/>
-      <c r="J493" s="10"/>
-      <c r="K493" s="10"/>
-      <c r="L493" s="10"/>
-      <c r="M493" s="10"/>
+      <c r="H493" s="11"/>
+      <c r="I493" s="11"/>
+      <c r="J493" s="11"/>
+      <c r="K493" s="11"/>
+      <c r="L493" s="11"/>
+      <c r="M493" s="11"/>
     </row>
     <row r="494" spans="8:13">
-      <c r="H494" s="10"/>
-      <c r="I494" s="10"/>
-      <c r="J494" s="10"/>
-      <c r="K494" s="10"/>
-      <c r="L494" s="10"/>
-      <c r="M494" s="10"/>
+      <c r="H494" s="11"/>
+      <c r="I494" s="11"/>
+      <c r="J494" s="11"/>
+      <c r="K494" s="11"/>
+      <c r="L494" s="11"/>
+      <c r="M494" s="11"/>
     </row>
     <row r="495" spans="8:13">
-      <c r="H495" s="10"/>
-      <c r="I495" s="10"/>
-      <c r="J495" s="10"/>
-      <c r="K495" s="10"/>
-      <c r="L495" s="10"/>
-      <c r="M495" s="10"/>
+      <c r="H495" s="11"/>
+      <c r="I495" s="11"/>
+      <c r="J495" s="11"/>
+      <c r="K495" s="11"/>
+      <c r="L495" s="11"/>
+      <c r="M495" s="11"/>
     </row>
     <row r="496" spans="8:13">
-      <c r="H496" s="10"/>
-      <c r="I496" s="10"/>
-      <c r="J496" s="10"/>
-      <c r="K496" s="10"/>
-      <c r="L496" s="10"/>
-      <c r="M496" s="10"/>
+      <c r="H496" s="11"/>
+      <c r="I496" s="11"/>
+      <c r="J496" s="11"/>
+      <c r="K496" s="11"/>
+      <c r="L496" s="11"/>
+      <c r="M496" s="11"/>
     </row>
     <row r="497" spans="8:13">
-      <c r="H497" s="10"/>
-      <c r="I497" s="10"/>
-      <c r="J497" s="10"/>
-      <c r="K497" s="10"/>
-      <c r="L497" s="10"/>
-      <c r="M497" s="10"/>
+      <c r="H497" s="11"/>
+      <c r="I497" s="11"/>
+      <c r="J497" s="11"/>
+      <c r="K497" s="11"/>
+      <c r="L497" s="11"/>
+      <c r="M497" s="11"/>
     </row>
     <row r="498" spans="8:13">
-      <c r="H498" s="10"/>
-      <c r="I498" s="10"/>
-      <c r="J498" s="10"/>
-      <c r="K498" s="10"/>
-      <c r="L498" s="10"/>
-      <c r="M498" s="10"/>
+      <c r="H498" s="11"/>
+      <c r="I498" s="11"/>
+      <c r="J498" s="11"/>
+      <c r="K498" s="11"/>
+      <c r="L498" s="11"/>
+      <c r="M498" s="11"/>
     </row>
     <row r="499" spans="8:13">
-      <c r="H499" s="10"/>
-      <c r="I499" s="10"/>
-      <c r="J499" s="10"/>
-      <c r="K499" s="10"/>
-      <c r="L499" s="10"/>
-      <c r="M499" s="10"/>
+      <c r="H499" s="11"/>
+      <c r="I499" s="11"/>
+      <c r="J499" s="11"/>
+      <c r="K499" s="11"/>
+      <c r="L499" s="11"/>
+      <c r="M499" s="11"/>
     </row>
     <row r="500" spans="8:13">
-      <c r="H500" s="10"/>
-      <c r="I500" s="10"/>
-      <c r="J500" s="10"/>
-      <c r="K500" s="10"/>
-      <c r="L500" s="10"/>
-      <c r="M500" s="10"/>
+      <c r="H500" s="11"/>
+      <c r="I500" s="11"/>
+      <c r="J500" s="11"/>
+      <c r="K500" s="11"/>
+      <c r="L500" s="11"/>
+      <c r="M500" s="11"/>
     </row>
   </sheetData>
   <dataValidations count="3">
-    <dataValidation type="list" sqref="N2:N3 N4:N6 N7:N500">
-      <formula1>"首次录入,报名注册更新,正式报名更新,考试时间更新,出分时间更新,考点更新,其他更新"</formula1>
-    </dataValidation>
-    <dataValidation type="list" sqref="S2:S6 S7:S500">
+    <dataValidation type="list" sqref="S8 S2:S7 S9:S500">
       <formula1>"未确认,已确认,已结束,暂停"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="T2:T3 T4:T6 T7:T500">
+    <dataValidation type="list" sqref="T8 T2:T7 T9:T500">
       <formula1>"是,否"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="N2:N6 N7:N8 N9:N500">
+      <formula1>"首次录入,报名注册更新,正式报名更新,考试时间更新,出分时间更新,考点更新,其他更新"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
@@ -7307,45 +7444,45 @@
   <sheetData>
     <row r="1" ht="17" spans="1:11">
       <c r="A1" s="2" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>97</v>
+        <v>108</v>
       </c>
     </row>
     <row r="2" spans="1:11">
       <c r="A2" t="s">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="B2" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -7354,16 +7491,16 @@
         <v>7</v>
       </c>
       <c r="E2" t="s">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="F2" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="G2" t="s">
         <v>25</v>
       </c>
       <c r="H2" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="I2" t="s">
         <v>25</v>
@@ -7377,10 +7514,10 @@
     </row>
     <row r="3" spans="1:11">
       <c r="A3" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="B3" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -7389,16 +7526,16 @@
         <v>0</v>
       </c>
       <c r="E3" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="F3" t="s">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="G3" t="s">
         <v>25</v>
       </c>
       <c r="H3" t="s">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="I3" t="s">
         <v>25</v>
@@ -7412,10 +7549,10 @@
     </row>
     <row r="4" spans="1:11">
       <c r="A4" t="s">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="B4" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="C4">
         <v>8</v>
@@ -7424,16 +7561,16 @@
         <v>15</v>
       </c>
       <c r="E4" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="F4" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="G4" t="s">
         <v>25</v>
       </c>
       <c r="H4" t="s">
-        <v>109</v>
+        <v>120</v>
       </c>
       <c r="I4" t="s">
         <v>25</v>
@@ -7447,10 +7584,10 @@
     </row>
     <row r="5" spans="1:11">
       <c r="A5" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="B5" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -7459,16 +7596,16 @@
         <v>7</v>
       </c>
       <c r="E5" t="s">
+        <v>122</v>
+      </c>
+      <c r="F5" t="s">
         <v>111</v>
-      </c>
-      <c r="F5" t="s">
-        <v>100</v>
       </c>
       <c r="G5" t="s">
         <v>25</v>
       </c>
       <c r="H5" t="s">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="I5" t="s">
         <v>25</v>
@@ -7482,10 +7619,10 @@
     </row>
     <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="B6" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -7494,16 +7631,16 @@
         <v>0</v>
       </c>
       <c r="E6" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="F6" t="s">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="G6" t="s">
         <v>25</v>
       </c>
       <c r="H6" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="I6" t="s">
         <v>25</v>
@@ -7517,10 +7654,10 @@
     </row>
     <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="B7" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="C7">
         <v>1</v>
@@ -7529,16 +7666,16 @@
         <v>7</v>
       </c>
       <c r="E7" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="F7" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="G7" t="s">
         <v>25</v>
       </c>
       <c r="H7" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="I7" t="s">
         <v>25</v>
@@ -7552,10 +7689,10 @@
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="B8" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="C8">
         <v>0</v>
@@ -7564,16 +7701,16 @@
         <v>0</v>
       </c>
       <c r="E8" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="F8" t="s">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="G8" t="s">
         <v>25</v>
       </c>
       <c r="H8" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="I8" t="s">
         <v>25</v>
@@ -7587,10 +7724,10 @@
     </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="B9" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="C9">
         <v>1</v>
@@ -7599,16 +7736,16 @@
         <v>7</v>
       </c>
       <c r="E9" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="F9" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="G9" t="s">
         <v>25</v>
       </c>
       <c r="H9" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="I9" t="s">
         <v>25</v>
@@ -7622,10 +7759,10 @@
     </row>
     <row r="10" spans="1:11">
       <c r="A10" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="B10" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="C10">
         <v>0</v>
@@ -7634,16 +7771,16 @@
         <v>0</v>
       </c>
       <c r="E10" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="F10" t="s">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="G10" t="s">
         <v>25</v>
       </c>
       <c r="H10" t="s">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="I10" t="s">
         <v>25</v>
@@ -7657,10 +7794,10 @@
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="B11" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="C11">
         <v>-7</v>
@@ -7669,16 +7806,16 @@
         <v>-1</v>
       </c>
       <c r="E11" t="s">
-        <v>127</v>
+        <v>138</v>
       </c>
       <c r="F11" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="G11" t="s">
         <v>25</v>
       </c>
       <c r="H11" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="I11" t="s">
         <v>25</v>
@@ -7692,10 +7829,10 @@
     </row>
     <row r="12" spans="1:11">
       <c r="A12" t="s">
-        <v>130</v>
+        <v>141</v>
       </c>
       <c r="B12" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="C12">
         <v>1</v>
@@ -7704,16 +7841,16 @@
         <v>7</v>
       </c>
       <c r="E12" t="s">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="F12" t="s">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="G12" t="s">
         <v>25</v>
       </c>
       <c r="H12" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="I12" t="s">
         <v>25</v>
@@ -7727,10 +7864,10 @@
     </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="B13" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="C13">
         <v>0</v>
@@ -7739,16 +7876,16 @@
         <v>0</v>
       </c>
       <c r="E13" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="F13" t="s">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="G13" t="s">
         <v>25</v>
       </c>
       <c r="H13" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="I13" t="s">
         <v>25</v>
@@ -7762,10 +7899,10 @@
     </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="B14" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="C14">
         <v>0</v>
@@ -7774,22 +7911,22 @@
         <v>0</v>
       </c>
       <c r="E14" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="F14" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="G14" t="s">
         <v>25</v>
       </c>
       <c r="H14" t="s">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="I14" t="s">
         <v>25</v>
       </c>
       <c r="J14" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="K14">
         <v>98</v>
@@ -7817,39 +7954,39 @@
   <sheetData>
     <row r="1" ht="17" spans="1:6">
       <c r="A1" s="2" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" ht="135" spans="1:6">
       <c r="A2" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="B2" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="C2" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="D2" t="s">
-        <v>148</v>
-      </c>
-      <c r="E2" t="s">
-        <v>149</v>
+        <v>159</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>160</v>
       </c>
       <c r="F2" t="s">
         <v>25</v>
@@ -7857,19 +7994,19 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="B3" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="C3" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="D3" t="s">
-        <v>151</v>
+        <v>162</v>
       </c>
       <c r="E3" t="s">
-        <v>152</v>
+        <v>163</v>
       </c>
       <c r="F3" t="s">
         <v>25</v>
@@ -7898,22 +8035,22 @@
   <sheetData>
     <row r="1" ht="17" spans="1:7">
       <c r="A1" s="2" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="G1" s="2" t="s">
         <v>12</v>
@@ -7921,22 +8058,19 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>154</v>
+        <v>165</v>
       </c>
       <c r="B2" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="C2" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="D2" t="s">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="E2" t="s">
-        <v>156</v>
-      </c>
-      <c r="F2" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="G2" t="s">
         <v>25</v>
@@ -7944,22 +8078,19 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="B3" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="C3" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="D3" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="E3" t="s">
-        <v>160</v>
-      </c>
-      <c r="F3" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="G3" t="s">
         <v>25</v>
@@ -7967,22 +8098,19 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="B4" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="C4" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="D4" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="E4" t="s">
-        <v>164</v>
-      </c>
-      <c r="F4" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="G4" t="s">
         <v>25</v>
@@ -7990,23 +8118,21 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="B5" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="C5" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="D5" t="s">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="E5" t="s">
-        <v>167</v>
-      </c>
-      <c r="F5" t="s">
-        <v>168</v>
-      </c>
+        <v>176</v>
+      </c>
+      <c r="F5" s="6"/>
       <c r="G5" t="s">
         <v>25</v>
       </c>
@@ -8031,16 +8157,16 @@
   <sheetData>
     <row r="1" ht="17" spans="1:4">
       <c r="A1" s="2" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -8090,7 +8216,7 @@
         <v>1</v>
       </c>
       <c r="B5" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -8104,7 +8230,7 @@
         <v>1</v>
       </c>
       <c r="B6" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="C6">
         <v>5</v>
@@ -8118,7 +8244,7 @@
         <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="C7">
         <v>6</v>
@@ -8132,7 +8258,7 @@
         <v>1</v>
       </c>
       <c r="B8" t="s">
-        <v>176</v>
+        <v>58</v>
       </c>
       <c r="C8">
         <v>7</v>
@@ -8146,7 +8272,7 @@
         <v>1</v>
       </c>
       <c r="B9" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="C9">
         <v>8</v>
@@ -8157,10 +8283,10 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="B10" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="C10">
         <v>1</v>
@@ -8171,10 +8297,10 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="B11" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="C11">
         <v>2</v>
@@ -8185,10 +8311,10 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="B12" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="C12">
         <v>3</v>
@@ -8199,10 +8325,10 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="B13" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="C13">
         <v>4</v>
@@ -8213,10 +8339,10 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="B14" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="C14">
         <v>5</v>
@@ -8227,10 +8353,10 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="B15" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="C15">
         <v>6</v>
@@ -8241,10 +8367,10 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="B16" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="C16">
         <v>1</v>
@@ -8255,10 +8381,10 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="B17" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="C17">
         <v>2</v>
@@ -8269,10 +8395,10 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="B18" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="C18">
         <v>3</v>
@@ -8283,10 +8409,10 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="B19" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="C19">
         <v>4</v>
@@ -8313,7 +8439,7 @@
   <sheetData>
     <row r="1" ht="23.2" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -8323,71 +8449,71 @@
     </row>
     <row r="3" ht="17" spans="1:6">
       <c r="A3" s="2" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
     </row>
     <row r="4" ht="17" spans="1:6">
       <c r="A4" s="3" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
     </row>
     <row r="5" ht="17" spans="1:6">
       <c r="A5" s="3" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
     </row>
     <row r="6" ht="17" spans="1:6">
       <c r="A6" s="3" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
     </row>
     <row r="7" ht="17" spans="1:6">
       <c r="A7" s="3" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
     </row>
     <row r="8" ht="17" spans="1:6">
       <c r="A8" s="3" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
     </row>
     <row r="9" ht="17" spans="1:6">
       <c r="A9" s="3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
     </row>
     <row r="10" ht="17" spans="1:6">
       <c r="A10" s="3" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>197</v>
+        <v>204</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="5" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="B12" s="5"/>
       <c r="C12" s="5"/>

--- a/小语种考试营销雷达_数据模板_V2.xlsx
+++ b/小语种考试营销雷达_数据模板_V2.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12880" activeTab="1"/>
+    <workbookView windowWidth="28800" windowHeight="12880"/>
   </bookViews>
   <sheets>
     <sheet name="考试基础信息" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="421" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="214">
   <si>
     <t>考试iD</t>
   </si>
@@ -223,6 +223,24 @@
     <t>算了</t>
   </si>
   <si>
+    <t>SP-DELE</t>
+  </si>
+  <si>
+    <t>西语</t>
+  </si>
+  <si>
+    <t>DELE</t>
+  </si>
+  <si>
+    <t>每年13次</t>
+  </si>
+  <si>
+    <t>A1-C3</t>
+  </si>
+  <si>
+    <t>3年</t>
+  </si>
+  <si>
     <t>记录ID</t>
   </si>
   <si>
@@ -329,6 +347,12 @@
   </si>
   <si>
     <t>2026年9月场</t>
+  </si>
+  <si>
+    <t>SP-DELE-2027-9</t>
+  </si>
+  <si>
+    <t>2027年9月场</t>
   </si>
   <si>
     <t>规则ID</t>
@@ -2123,19 +2147,42 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:13">
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="4"/>
-      <c r="I8" s="4"/>
-      <c r="J8" s="4"/>
+    <row r="8" ht="17" spans="1:13">
+      <c r="A8" t="s">
+        <v>62</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="G8" s="4">
+        <v>1851</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>61</v>
+      </c>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
-      <c r="M8" s="4"/>
+      <c r="M8" s="4" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="9" spans="1:13">
       <c r="B9" s="4"/>
@@ -2208,9 +2255,8 @@
       <c r="M13" s="4"/>
     </row>
     <row r="14" spans="1:13">
-      <c r="B14" s="4"/>
       <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
+      <c r="D14"/>
       <c r="E14" s="4"/>
       <c r="F14" s="4"/>
       <c r="G14" s="4"/>
@@ -2307,7 +2353,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" sqref="M2:M5 M6:M7 M8:M500">
+    <dataValidation type="list" sqref="M2:M6 M7:M8 M9:M500">
       <formula1>"是,否"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2348,13 +2394,13 @@
   <sheetData>
     <row r="1" ht="17" spans="1:21">
       <c r="A1" s="2" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>1</v>
@@ -2363,57 +2409,57 @@
         <v>2</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="N1" s="2" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="O1" s="2" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="P1" s="2" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="Q1" s="2" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="R1" s="2" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="S1" s="2" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="T1" s="2" t="s">
         <v>12</v>
       </c>
       <c r="U1" s="2" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
     </row>
     <row r="2" ht="51" spans="1:21">
       <c r="A2" s="4" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="B2" s="4">
         <v>2026</v>
@@ -2428,7 +2474,7 @@
         <v>15</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G2" s="4">
         <v>7</v>
@@ -2452,29 +2498,29 @@
         <v>46245</v>
       </c>
       <c r="N2" s="4" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="O2" s="4"/>
       <c r="P2" s="9" t="s">
         <v>23</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="R2" s="4"/>
       <c r="S2" s="4" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="T2" s="4" t="s">
         <v>25</v>
       </c>
       <c r="U2" s="4" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
     </row>
     <row r="3" ht="51" spans="1:21">
       <c r="A3" s="4" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B3" s="4">
         <v>2026</v>
@@ -2489,7 +2535,7 @@
         <v>15</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G3" s="4">
         <v>12</v>
@@ -2513,24 +2559,24 @@
         <v>46245</v>
       </c>
       <c r="N3" s="4" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="O3" s="4"/>
       <c r="P3" s="9" t="s">
         <v>23</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="R3" s="4"/>
       <c r="S3" s="4" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="T3" s="4" t="s">
         <v>25</v>
       </c>
       <c r="U3" s="4" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
     </row>
     <row r="4" ht="51" spans="1:21">
@@ -2541,7 +2587,7 @@
         <v>2026</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>27</v>
@@ -2550,7 +2596,7 @@
         <v>28</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="G4" s="4">
         <v>10</v>
@@ -2574,29 +2620,29 @@
         <v>46245</v>
       </c>
       <c r="N4" s="4" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="O4" s="4"/>
       <c r="P4" s="9" t="s">
         <v>23</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="R4" s="4"/>
       <c r="S4" s="4" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="T4" s="4" t="s">
         <v>25</v>
       </c>
       <c r="U4" s="4" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
     </row>
     <row r="5" ht="17" spans="1:21">
       <c r="A5" s="4" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B5" s="4">
         <v>2026</v>
@@ -2611,7 +2657,7 @@
         <v>45</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="G5" s="4">
         <v>11</v>
@@ -2635,29 +2681,29 @@
         <v>46245</v>
       </c>
       <c r="N5" s="4" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="O5" s="4"/>
       <c r="P5" s="4" t="s">
         <v>43</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="R5" s="4"/>
       <c r="S5" s="4" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="T5" s="4" t="s">
         <v>25</v>
       </c>
       <c r="U5" s="4" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
     </row>
     <row r="6" ht="17" spans="1:21">
       <c r="A6" s="4" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="B6" s="4">
         <v>2026</v>
@@ -2672,7 +2718,7 @@
         <v>37</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="G6" s="4">
         <v>8</v>
@@ -2696,29 +2742,29 @@
         <v>46245</v>
       </c>
       <c r="N6" s="4" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="O6" s="4"/>
       <c r="P6" s="10" t="s">
         <v>50</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="R6" s="4"/>
       <c r="S6" s="4" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="T6" s="4" t="s">
         <v>25</v>
       </c>
       <c r="U6" s="4" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
     </row>
     <row r="7" ht="17" spans="1:21">
       <c r="A7" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="B7" s="4">
         <v>2026</v>
@@ -2733,7 +2779,7 @@
         <v>52</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="G7" s="4">
         <v>8</v>
@@ -2757,32 +2803,32 @@
         <v>46245</v>
       </c>
       <c r="N7" s="4" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="O7" s="4"/>
       <c r="P7" s="4" t="s">
         <v>48</v>
       </c>
       <c r="Q7" s="4" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="R7" s="4"/>
       <c r="S7" s="4" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="T7" s="4" t="s">
         <v>25</v>
       </c>
       <c r="U7" s="4" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
     </row>
     <row r="8" ht="17" spans="1:21">
       <c r="A8" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="B8" s="4">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="C8" t="s">
         <v>57</v>
@@ -2794,7 +2840,7 @@
         <v>59</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="G8" s="4">
         <v>9</v>
@@ -2818,46 +2864,82 @@
         <v>46246</v>
       </c>
       <c r="N8" s="4" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="O8" s="4"/>
       <c r="P8" s="4"/>
       <c r="Q8" s="4" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="R8" s="4"/>
       <c r="S8" s="4" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="T8" s="4" t="s">
         <v>25</v>
       </c>
       <c r="U8" s="4" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="9" spans="1:21">
-      <c r="A9" s="4"/>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="7"/>
-      <c r="I9" s="7"/>
-      <c r="J9" s="7"/>
-      <c r="K9" s="7"/>
-      <c r="L9" s="7"/>
-      <c r="M9" s="7"/>
-      <c r="N9" s="4"/>
-      <c r="O9" s="9"/>
+        <v>91</v>
+      </c>
+    </row>
+    <row r="9" ht="17" spans="1:21">
+      <c r="A9" t="s">
+        <v>104</v>
+      </c>
+      <c r="B9" s="4">
+        <v>2027</v>
+      </c>
+      <c r="C9" t="s">
+        <v>62</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="G9" s="4">
+        <v>9</v>
+      </c>
+      <c r="H9" s="7">
+        <v>46603</v>
+      </c>
+      <c r="I9" s="7">
+        <v>46604</v>
+      </c>
+      <c r="J9" s="7">
+        <v>46609</v>
+      </c>
+      <c r="K9" s="7">
+        <v>46650</v>
+      </c>
+      <c r="L9" s="7">
+        <v>46680</v>
+      </c>
+      <c r="M9" s="7">
+        <v>46246</v>
+      </c>
+      <c r="N9" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="O9" s="4"/>
       <c r="P9" s="4"/>
-      <c r="Q9" s="4"/>
+      <c r="Q9" s="4" t="s">
+        <v>89</v>
+      </c>
       <c r="R9" s="4"/>
-      <c r="S9" s="4"/>
-      <c r="T9" s="4"/>
-      <c r="U9" s="4"/>
+      <c r="S9" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="T9" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="U9" s="4" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="10" spans="1:21">
       <c r="A10" s="4"/>
@@ -7403,14 +7485,14 @@
     </row>
   </sheetData>
   <dataValidations count="3">
-    <dataValidation type="list" sqref="S8 S2:S7 S9:S500">
+    <dataValidation type="list" sqref="N9 N2:N8 N10:N500">
+      <formula1>"首次录入,报名注册更新,正式报名更新,考试时间更新,出分时间更新,考点更新,其他更新"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="S9 S2:S8 S10:S500">
       <formula1>"未确认,已确认,已结束,暂停"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="T8 T2:T7 T9:T500">
+    <dataValidation type="list" sqref="T9 T2:T8 T10:T500">
       <formula1>"是,否"</formula1>
-    </dataValidation>
-    <dataValidation type="list" sqref="N2:N6 N7:N8 N9:N500">
-      <formula1>"首次录入,报名注册更新,正式报名更新,考试时间更新,出分时间更新,考点更新,其他更新"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
@@ -7444,45 +7526,45 @@
   <sheetData>
     <row r="1" ht="17" spans="1:11">
       <c r="A1" s="2" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
     </row>
     <row r="2" spans="1:11">
       <c r="A2" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="B2" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -7491,16 +7573,16 @@
         <v>7</v>
       </c>
       <c r="E2" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="F2" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="G2" t="s">
         <v>25</v>
       </c>
       <c r="H2" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="I2" t="s">
         <v>25</v>
@@ -7514,10 +7596,10 @@
     </row>
     <row r="3" spans="1:11">
       <c r="A3" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="B3" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -7526,16 +7608,16 @@
         <v>0</v>
       </c>
       <c r="E3" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="F3" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="G3" t="s">
         <v>25</v>
       </c>
       <c r="H3" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="I3" t="s">
         <v>25</v>
@@ -7549,10 +7631,10 @@
     </row>
     <row r="4" spans="1:11">
       <c r="A4" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="B4" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C4">
         <v>8</v>
@@ -7561,16 +7643,16 @@
         <v>15</v>
       </c>
       <c r="E4" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="F4" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="G4" t="s">
         <v>25</v>
       </c>
       <c r="H4" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="I4" t="s">
         <v>25</v>
@@ -7584,10 +7666,10 @@
     </row>
     <row r="5" spans="1:11">
       <c r="A5" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="B5" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -7596,16 +7678,16 @@
         <v>7</v>
       </c>
       <c r="E5" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="F5" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="G5" t="s">
         <v>25</v>
       </c>
       <c r="H5" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="I5" t="s">
         <v>25</v>
@@ -7619,10 +7701,10 @@
     </row>
     <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="B6" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -7631,16 +7713,16 @@
         <v>0</v>
       </c>
       <c r="E6" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="F6" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="G6" t="s">
         <v>25</v>
       </c>
       <c r="H6" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="I6" t="s">
         <v>25</v>
@@ -7654,10 +7736,10 @@
     </row>
     <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="B7" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="C7">
         <v>1</v>
@@ -7666,16 +7748,16 @@
         <v>7</v>
       </c>
       <c r="E7" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="F7" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="G7" t="s">
         <v>25</v>
       </c>
       <c r="H7" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="I7" t="s">
         <v>25</v>
@@ -7689,10 +7771,10 @@
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="B8" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="C8">
         <v>0</v>
@@ -7701,16 +7783,16 @@
         <v>0</v>
       </c>
       <c r="E8" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="F8" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="G8" t="s">
         <v>25</v>
       </c>
       <c r="H8" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="I8" t="s">
         <v>25</v>
@@ -7724,10 +7806,10 @@
     </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="B9" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="C9">
         <v>1</v>
@@ -7736,16 +7818,16 @@
         <v>7</v>
       </c>
       <c r="E9" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="F9" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="G9" t="s">
         <v>25</v>
       </c>
       <c r="H9" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="I9" t="s">
         <v>25</v>
@@ -7759,10 +7841,10 @@
     </row>
     <row r="10" spans="1:11">
       <c r="A10" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="B10" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="C10">
         <v>0</v>
@@ -7771,16 +7853,16 @@
         <v>0</v>
       </c>
       <c r="E10" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="F10" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="G10" t="s">
         <v>25</v>
       </c>
       <c r="H10" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="I10" t="s">
         <v>25</v>
@@ -7794,10 +7876,10 @@
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="B11" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="C11">
         <v>-7</v>
@@ -7806,16 +7888,16 @@
         <v>-1</v>
       </c>
       <c r="E11" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="F11" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="G11" t="s">
         <v>25</v>
       </c>
       <c r="H11" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="I11" t="s">
         <v>25</v>
@@ -7829,10 +7911,10 @@
     </row>
     <row r="12" spans="1:11">
       <c r="A12" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="B12" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="C12">
         <v>1</v>
@@ -7841,16 +7923,16 @@
         <v>7</v>
       </c>
       <c r="E12" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="F12" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="G12" t="s">
         <v>25</v>
       </c>
       <c r="H12" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="I12" t="s">
         <v>25</v>
@@ -7864,10 +7946,10 @@
     </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="B13" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="C13">
         <v>0</v>
@@ -7876,16 +7958,16 @@
         <v>0</v>
       </c>
       <c r="E13" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="F13" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="G13" t="s">
         <v>25</v>
       </c>
       <c r="H13" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="I13" t="s">
         <v>25</v>
@@ -7899,10 +7981,10 @@
     </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="B14" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="C14">
         <v>0</v>
@@ -7911,22 +7993,22 @@
         <v>0</v>
       </c>
       <c r="E14" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="F14" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="G14" t="s">
         <v>25</v>
       </c>
       <c r="H14" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="I14" t="s">
         <v>25</v>
       </c>
       <c r="J14" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="K14">
         <v>98</v>
@@ -7954,19 +8036,19 @@
   <sheetData>
     <row r="1" ht="17" spans="1:6">
       <c r="A1" s="2" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>12</v>
@@ -7974,19 +8056,19 @@
     </row>
     <row r="2" ht="135" spans="1:6">
       <c r="A2" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="B2" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="C2" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="D2" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="F2" t="s">
         <v>25</v>
@@ -7994,19 +8076,19 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="B3" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="C3" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="D3" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="E3" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="F3" t="s">
         <v>25</v>
@@ -8035,22 +8117,22 @@
   <sheetData>
     <row r="1" ht="17" spans="1:7">
       <c r="A1" s="2" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="G1" s="2" t="s">
         <v>12</v>
@@ -8058,19 +8140,19 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="B2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C2" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="D2" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="E2" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="G2" t="s">
         <v>25</v>
@@ -8078,19 +8160,19 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="B3" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C3" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="D3" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="E3" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="G3" t="s">
         <v>25</v>
@@ -8098,19 +8180,19 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="B4" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C4" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="D4" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="E4" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="G4" t="s">
         <v>25</v>
@@ -8118,19 +8200,19 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="B5" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="C5" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="D5" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="E5" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="F5" s="6"/>
       <c r="G5" t="s">
@@ -8157,16 +8239,16 @@
   <sheetData>
     <row r="1" ht="17" spans="1:4">
       <c r="A1" s="2" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -8216,7 +8298,7 @@
         <v>1</v>
       </c>
       <c r="B5" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -8230,7 +8312,7 @@
         <v>1</v>
       </c>
       <c r="B6" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="C6">
         <v>5</v>
@@ -8244,7 +8326,7 @@
         <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="C7">
         <v>6</v>
@@ -8272,7 +8354,7 @@
         <v>1</v>
       </c>
       <c r="B9" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="C9">
         <v>8</v>
@@ -8283,10 +8365,10 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="B10" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C10">
         <v>1</v>
@@ -8297,10 +8379,10 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="B11" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C11">
         <v>2</v>
@@ -8311,10 +8393,10 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="B12" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="C12">
         <v>3</v>
@@ -8325,10 +8407,10 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="B13" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="C13">
         <v>4</v>
@@ -8339,10 +8421,10 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="B14" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="C14">
         <v>5</v>
@@ -8353,10 +8435,10 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="B15" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="C15">
         <v>6</v>
@@ -8367,10 +8449,10 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="B16" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="C16">
         <v>1</v>
@@ -8381,10 +8463,10 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="B17" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="C17">
         <v>2</v>
@@ -8395,10 +8477,10 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="B18" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="C18">
         <v>3</v>
@@ -8409,10 +8491,10 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="B19" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="C19">
         <v>4</v>
@@ -8439,7 +8521,7 @@
   <sheetData>
     <row r="1" ht="23.2" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -8449,71 +8531,71 @@
     </row>
     <row r="3" ht="17" spans="1:6">
       <c r="A3" s="2" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
     </row>
     <row r="4" ht="17" spans="1:6">
       <c r="A4" s="3" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
     </row>
     <row r="5" ht="17" spans="1:6">
       <c r="A5" s="3" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
     </row>
     <row r="6" ht="17" spans="1:6">
       <c r="A6" s="3" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
     </row>
     <row r="7" ht="17" spans="1:6">
       <c r="A7" s="3" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
     </row>
     <row r="8" ht="17" spans="1:6">
       <c r="A8" s="3" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
     </row>
     <row r="9" ht="17" spans="1:6">
       <c r="A9" s="3" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
     </row>
     <row r="10" ht="17" spans="1:6">
       <c r="A10" s="3" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="5" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="B12" s="5"/>
       <c r="C12" s="5"/>

--- a/小语种考试营销雷达_数据模板_V2.xlsx
+++ b/小语种考试营销雷达_数据模板_V2.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12880" activeTab="1"/>
+    <workbookView windowWidth="28800" windowHeight="12880"/>
   </bookViews>
   <sheets>
     <sheet name="考试基础信息" sheetId="1" r:id="rId1"/>
@@ -7816,7 +7816,9 @@
       <c r="K2" s="37">
         <v>46208</v>
       </c>
-      <c r="L2" s="37"/>
+      <c r="L2" s="37">
+        <v>46259</v>
+      </c>
       <c r="M2" s="37">
         <v>46247</v>
       </c>
@@ -8058,7 +8060,9 @@
       <c r="K6" s="37">
         <v>46109</v>
       </c>
-      <c r="L6" s="37"/>
+      <c r="L6" s="37">
+        <v>46151</v>
+      </c>
       <c r="M6" s="37">
         <v>46247</v>
       </c>
@@ -8119,7 +8123,9 @@
       <c r="K7" s="41">
         <v>46207</v>
       </c>
-      <c r="L7" s="41"/>
+      <c r="L7" s="41">
+        <v>46254</v>
+      </c>
       <c r="M7" s="41">
         <v>46247</v>
       </c>
@@ -8168,13 +8174,19 @@
       <c r="G8" s="36">
         <v>11</v>
       </c>
-      <c r="H8" s="37"/>
+      <c r="H8" s="37">
+        <v>45896</v>
+      </c>
       <c r="I8" s="37"/>
-      <c r="J8" s="37"/>
+      <c r="J8" s="37">
+        <v>46280</v>
+      </c>
       <c r="K8" s="37">
         <v>46333</v>
       </c>
-      <c r="L8" s="37"/>
+      <c r="L8" s="41">
+        <v>46365</v>
+      </c>
       <c r="M8" s="37">
         <v>46247</v>
       </c>
@@ -8233,7 +8245,9 @@
       <c r="K9" s="41">
         <v>46241</v>
       </c>
-      <c r="L9" s="41"/>
+      <c r="L9" s="41">
+        <v>46248</v>
+      </c>
       <c r="M9" s="41">
         <v>46247</v>
       </c>
@@ -17245,9 +17259,6 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="6">
-    <dataValidation type="list" sqref="N2 N3:N31 N32:N500">
-      <formula1>"首次录入,报名注册更新,正式报名更新,考试时间更新,出分时间更新,考点更新,其他更新"</formula1>
-    </dataValidation>
     <dataValidation type="whole" operator="between" sqref="B2:B500">
       <formula1>2020</formula1>
       <formula2>2100</formula2>
@@ -17258,6 +17269,9 @@
     <dataValidation type="whole" operator="between" sqref="G2:G500">
       <formula1>1</formula1>
       <formula2>12</formula2>
+    </dataValidation>
+    <dataValidation type="list" sqref="N2:N500">
+      <formula1>"首次录入,报名注册更新,正式报名更新,考试时间更新,出分时间更新,考点更新,其他更新"</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="S2:S500">
       <formula1>"未确认,已确认,已结束,暂停"</formula1>
@@ -18909,7 +18923,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{63e75fc7-313a-4575-854f-0c095fdbf6dc}</x14:id>
+          <x14:id>{0ebee17e-fcf2-4bf9-9486-3f950123ca2a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -18945,7 +18959,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{63e75fc7-313a-4575-854f-0c095fdbf6dc}">
+          <x14:cfRule type="dataBar" id="{0ebee17e-fcf2-4bf9-9486-3f950123ca2a}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -23330,7 +23344,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c866bbb5-9e5b-40fa-9ff9-6f0fabfd5e17}</x14:id>
+          <x14:id>{8150708c-ea45-4986-bcda-ea3a048286cf}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23357,7 +23371,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{c866bbb5-9e5b-40fa-9ff9-6f0fabfd5e17}">
+          <x14:cfRule type="dataBar" id="{8150708c-ea45-4986-bcda-ea3a048286cf}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>

--- a/小语种考试营销雷达_数据模板_V2.xlsx
+++ b/小语种考试营销雷达_数据模板_V2.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12880"/>
+    <workbookView windowWidth="28800" windowHeight="12880" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="考试基础信息" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="905" uniqueCount="407">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="871" uniqueCount="407">
   <si>
     <t>考试iD</t>
   </si>
@@ -374,9 +374,6 @@
     <t>备注</t>
   </si>
   <si>
-    <t>状态</t>
-  </si>
-  <si>
     <t>数据版本</t>
   </si>
   <si>
@@ -395,9 +392,6 @@
     <t>考试日期已确认；成绩查询日以官方后续通知为准。</t>
   </si>
   <si>
-    <t>已确认</t>
-  </si>
-  <si>
     <t>2026.08.13</t>
   </si>
   <si>
@@ -411,9 +405,6 @@
   </si>
   <si>
     <t>考试日期已确认；截至2026-08-13，中国大陆报名及出分日期尚未发布。</t>
-  </si>
-  <si>
-    <t>未确认</t>
   </si>
   <si>
     <t>KR-TOPIK-2026-04</t>
@@ -1025,7 +1016,16 @@
     <t>必须与“年度考试场次”的日期字段名保持一致。</t>
   </si>
   <si>
+    <t>状态</t>
+  </si>
+  <si>
+    <t>未确认</t>
+  </si>
+  <si>
     <t>用于考试场次状态标识；未确认信息请勿标记为已确认。</t>
+  </si>
+  <si>
+    <t>已确认</t>
   </si>
   <si>
     <t>已结束</t>
@@ -2366,29 +2366,7 @@
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
     <cellStyle name="Normal" xfId="49"/>
   </cellStyles>
-  <dxfs count="22">
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color rgb="FFA15C00"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFF6E3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color rgb="FF167A4A"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFEAF8F1"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="20">
     <dxf>
       <font>
         <b val="1"/>
@@ -2615,25 +2593,25 @@
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="11"/>
-      <tableStyleElement type="headerRow" dxfId="10"/>
-      <tableStyleElement type="totalRow" dxfId="9"/>
-      <tableStyleElement type="firstColumn" dxfId="8"/>
-      <tableStyleElement type="lastColumn" dxfId="7"/>
-      <tableStyleElement type="firstRowStripe" dxfId="6"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="5"/>
+      <tableStyleElement type="wholeTable" dxfId="9"/>
+      <tableStyleElement type="headerRow" dxfId="8"/>
+      <tableStyleElement type="totalRow" dxfId="7"/>
+      <tableStyleElement type="firstColumn" dxfId="6"/>
+      <tableStyleElement type="lastColumn" dxfId="5"/>
+      <tableStyleElement type="firstRowStripe" dxfId="4"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="3"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="21"/>
-      <tableStyleElement type="totalRow" dxfId="20"/>
-      <tableStyleElement type="firstRowStripe" dxfId="19"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="18"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="17"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="16"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="15"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="14"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="13"/>
-      <tableStyleElement type="pageFieldValues" dxfId="12"/>
+      <tableStyleElement type="headerRow" dxfId="19"/>
+      <tableStyleElement type="totalRow" dxfId="18"/>
+      <tableStyleElement type="firstRowStripe" dxfId="17"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="16"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="15"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="14"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="13"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="12"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="11"/>
+      <tableStyleElement type="pageFieldValues" dxfId="10"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -7697,7 +7675,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:U500"/>
+  <dimension ref="A1:T500"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -7713,11 +7691,11 @@
     <col min="16" max="16" width="40" customWidth="1"/>
     <col min="17" max="17" width="20" customWidth="1"/>
     <col min="18" max="18" width="28" customWidth="1"/>
-    <col min="19" max="20" width="12" customWidth="1"/>
-    <col min="21" max="21" width="14" customWidth="1"/>
+    <col min="19" max="19" width="12" customWidth="1"/>
+    <col min="20" max="20" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" spans="1:21">
+    <row r="1" ht="30" customHeight="1" spans="1:20">
       <c r="A1" s="19" t="s">
         <v>93</v>
       </c>
@@ -7773,18 +7751,15 @@
         <v>108</v>
       </c>
       <c r="S1" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="T1" s="19" t="s">
         <v>109</v>
       </c>
-      <c r="T1" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="U1" s="19" t="s">
+    </row>
+    <row r="2" ht="42" customHeight="1" spans="1:20">
+      <c r="A2" s="3" t="s">
         <v>110</v>
-      </c>
-    </row>
-    <row r="2" ht="42" customHeight="1" spans="1:21">
-      <c r="A2" s="3" t="s">
-        <v>111</v>
       </c>
       <c r="B2" s="3">
         <v>2026</v>
@@ -7799,7 +7774,7 @@
         <v>14</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G2" s="36">
         <v>7</v>
@@ -7823,31 +7798,28 @@
         <v>46247</v>
       </c>
       <c r="N2" s="38" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="O2" s="3"/>
       <c r="P2" s="39" t="s">
         <v>22</v>
       </c>
       <c r="Q2" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="R2" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="R2" s="3" t="s">
+      <c r="S2" s="38" t="s">
+        <v>23</v>
+      </c>
+      <c r="T2" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="S2" s="38" t="s">
+    </row>
+    <row r="3" ht="42" customHeight="1" spans="1:20">
+      <c r="A3" s="4" t="s">
         <v>116</v>
-      </c>
-      <c r="T2" s="38" t="s">
-        <v>23</v>
-      </c>
-      <c r="U2" s="3" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="3" ht="42" customHeight="1" spans="1:21">
-      <c r="A3" s="4" t="s">
-        <v>118</v>
       </c>
       <c r="B3" s="4">
         <v>2026</v>
@@ -7862,7 +7834,7 @@
         <v>14</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="G3" s="40">
         <v>12</v>
@@ -7878,31 +7850,28 @@
         <v>46247</v>
       </c>
       <c r="N3" s="38" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="O3" s="4"/>
       <c r="P3" s="42" t="s">
+        <v>118</v>
+      </c>
+      <c r="Q3" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="R3" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="S3" s="43" t="s">
+        <v>23</v>
+      </c>
+      <c r="T3" s="4" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="4" ht="42" customHeight="1" spans="1:20">
+      <c r="A4" s="3" t="s">
         <v>120</v>
-      </c>
-      <c r="Q3" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="R3" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="S3" s="43" t="s">
-        <v>122</v>
-      </c>
-      <c r="T3" s="43" t="s">
-        <v>23</v>
-      </c>
-      <c r="U3" s="4" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="4" ht="42" customHeight="1" spans="1:21">
-      <c r="A4" s="3" t="s">
-        <v>123</v>
       </c>
       <c r="B4" s="3">
         <v>2026</v>
@@ -7917,7 +7886,7 @@
         <v>26</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="G4" s="36">
         <v>4</v>
@@ -7941,31 +7910,28 @@
         <v>46247</v>
       </c>
       <c r="N4" s="38" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="O4" s="3"/>
       <c r="P4" s="39" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="Q4" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="R4" s="3" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="S4" s="38" t="s">
-        <v>116</v>
-      </c>
-      <c r="T4" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="U4" s="3" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="5" ht="42" customHeight="1" spans="1:21">
+      <c r="T4" s="3" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="5" ht="42" customHeight="1" spans="1:20">
       <c r="A5" s="4" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B5" s="4">
         <v>2026</v>
@@ -7980,7 +7946,7 @@
         <v>26</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="G5" s="40">
         <v>10</v>
@@ -8004,31 +7970,28 @@
         <v>46247</v>
       </c>
       <c r="N5" s="38" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="O5" s="4"/>
       <c r="P5" s="42" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="R5" s="4" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="S5" s="43" t="s">
-        <v>116</v>
-      </c>
-      <c r="T5" s="43" t="s">
         <v>23</v>
       </c>
-      <c r="U5" s="4" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="6" ht="42" customHeight="1" spans="1:21">
+      <c r="T5" s="4" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="6" ht="42" customHeight="1" spans="1:20">
       <c r="A6" s="3" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B6" s="3">
         <v>2026</v>
@@ -8043,7 +8006,7 @@
         <v>47</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="G6" s="36">
         <v>3</v>
@@ -8067,31 +8030,28 @@
         <v>46247</v>
       </c>
       <c r="N6" s="38" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="O6" s="3"/>
       <c r="P6" s="39" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="Q6" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="R6" s="3" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="S6" s="38" t="s">
-        <v>116</v>
-      </c>
-      <c r="T6" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="U6" s="3" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="7" ht="42" customHeight="1" spans="1:21">
+      <c r="T6" s="3" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="7" ht="42" customHeight="1" spans="1:20">
       <c r="A7" s="4" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="B7" s="4">
         <v>2026</v>
@@ -8106,7 +8066,7 @@
         <v>47</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="G7" s="40">
         <v>7</v>
@@ -8130,31 +8090,28 @@
         <v>46247</v>
       </c>
       <c r="N7" s="38" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="O7" s="4"/>
       <c r="P7" s="42" t="s">
         <v>54</v>
       </c>
       <c r="Q7" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="R7" s="4" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="S7" s="43" t="s">
-        <v>116</v>
-      </c>
-      <c r="T7" s="43" t="s">
         <v>23</v>
       </c>
-      <c r="U7" s="4" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="8" ht="42" customHeight="1" spans="1:21">
+      <c r="T7" s="4" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="8" ht="42" customHeight="1" spans="1:20">
       <c r="A8" s="3" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="B8" s="3">
         <v>2026</v>
@@ -8169,7 +8126,7 @@
         <v>47</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="G8" s="36">
         <v>11</v>
@@ -8191,31 +8148,28 @@
         <v>46247</v>
       </c>
       <c r="N8" s="38" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="O8" s="3"/>
       <c r="P8" s="39" t="s">
         <v>54</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="R8" s="3" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="S8" s="38" t="s">
-        <v>122</v>
-      </c>
-      <c r="T8" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="U8" s="3" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="9" ht="42" customHeight="1" spans="1:21">
+      <c r="T8" s="3" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="9" ht="42" customHeight="1" spans="1:20">
       <c r="A9" s="4" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B9" s="4">
         <v>2026</v>
@@ -8230,7 +8184,7 @@
         <v>37</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="G9" s="40">
         <v>8</v>
@@ -8252,31 +8206,28 @@
         <v>46247</v>
       </c>
       <c r="N9" s="38" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="O9" s="4"/>
       <c r="P9" s="42" t="s">
+        <v>139</v>
+      </c>
+      <c r="Q9" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="R9" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="S9" s="43" t="s">
+        <v>23</v>
+      </c>
+      <c r="T9" s="4" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="10" ht="42" customHeight="1" spans="1:20">
+      <c r="A10" s="24" t="s">
         <v>142</v>
-      </c>
-      <c r="Q9" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="R9" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="S9" s="43" t="s">
-        <v>116</v>
-      </c>
-      <c r="T9" s="43" t="s">
-        <v>23</v>
-      </c>
-      <c r="U9" s="4" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="10" ht="42" customHeight="1" spans="1:21">
-      <c r="A10" s="24" t="s">
-        <v>145</v>
       </c>
       <c r="B10" s="24">
         <v>2026</v>
@@ -8291,7 +8242,7 @@
         <v>56</v>
       </c>
       <c r="F10" s="24" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="G10" s="44">
         <v>1</v>
@@ -8307,29 +8258,26 @@
         <v>46247</v>
       </c>
       <c r="N10" s="38" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="O10" s="4"/>
       <c r="P10" s="46" t="s">
         <v>63</v>
       </c>
       <c r="Q10" s="24" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="R10" s="24"/>
       <c r="S10" s="47" t="s">
-        <v>116</v>
-      </c>
-      <c r="T10" s="47" t="s">
         <v>23</v>
       </c>
-      <c r="U10" s="24" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="11" ht="42" customHeight="1" spans="1:21">
+      <c r="T10" s="24" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="11" ht="42" customHeight="1" spans="1:20">
       <c r="A11" s="24" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="B11" s="24">
         <v>2026</v>
@@ -8344,7 +8292,7 @@
         <v>56</v>
       </c>
       <c r="F11" s="24" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="G11" s="44">
         <v>3</v>
@@ -8360,29 +8308,26 @@
         <v>46247</v>
       </c>
       <c r="N11" s="38" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="O11" s="24"/>
       <c r="P11" s="46" t="s">
         <v>63</v>
       </c>
       <c r="Q11" s="24" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="R11" s="24"/>
       <c r="S11" s="47" t="s">
-        <v>116</v>
-      </c>
-      <c r="T11" s="47" t="s">
         <v>23</v>
       </c>
-      <c r="U11" s="24" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="12" ht="42" customHeight="1" spans="1:21">
+      <c r="T11" s="24" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="12" ht="42" customHeight="1" spans="1:20">
       <c r="A12" s="24" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="B12" s="24">
         <v>2026</v>
@@ -8397,7 +8342,7 @@
         <v>56</v>
       </c>
       <c r="F12" s="24" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="G12" s="44">
         <v>5</v>
@@ -8413,29 +8358,26 @@
         <v>46247</v>
       </c>
       <c r="N12" s="38" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="O12" s="24"/>
       <c r="P12" s="46" t="s">
         <v>63</v>
       </c>
       <c r="Q12" s="24" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="R12" s="24"/>
       <c r="S12" s="47" t="s">
-        <v>116</v>
-      </c>
-      <c r="T12" s="47" t="s">
         <v>23</v>
       </c>
-      <c r="U12" s="24" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="13" ht="42" customHeight="1" spans="1:21">
+      <c r="T12" s="24" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="13" ht="42" customHeight="1" spans="1:20">
       <c r="A13" s="24" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="B13" s="24">
         <v>2026</v>
@@ -8450,7 +8392,7 @@
         <v>56</v>
       </c>
       <c r="F13" s="24" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="G13" s="44">
         <v>6</v>
@@ -8466,29 +8408,26 @@
         <v>46247</v>
       </c>
       <c r="N13" s="38" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="O13" s="24"/>
       <c r="P13" s="46" t="s">
         <v>63</v>
       </c>
       <c r="Q13" s="24" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="R13" s="24"/>
       <c r="S13" s="47" t="s">
-        <v>116</v>
-      </c>
-      <c r="T13" s="47" t="s">
         <v>23</v>
       </c>
-      <c r="U13" s="24" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="14" ht="42" customHeight="1" spans="1:21">
+      <c r="T13" s="24" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="14" ht="42" customHeight="1" spans="1:20">
       <c r="A14" s="24" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="B14" s="24">
         <v>2026</v>
@@ -8503,7 +8442,7 @@
         <v>56</v>
       </c>
       <c r="F14" s="24" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G14" s="44">
         <v>7</v>
@@ -8519,29 +8458,26 @@
         <v>46247</v>
       </c>
       <c r="N14" s="38" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="O14" s="24"/>
       <c r="P14" s="46" t="s">
         <v>63</v>
       </c>
       <c r="Q14" s="24" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="R14" s="24"/>
       <c r="S14" s="47" t="s">
-        <v>116</v>
-      </c>
-      <c r="T14" s="47" t="s">
         <v>23</v>
       </c>
-      <c r="U14" s="24" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="15" ht="42" customHeight="1" spans="1:21">
+      <c r="T14" s="24" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="15" ht="42" customHeight="1" spans="1:20">
       <c r="A15" s="24" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="B15" s="24">
         <v>2026</v>
@@ -8556,7 +8492,7 @@
         <v>56</v>
       </c>
       <c r="F15" s="24" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="G15" s="44">
         <v>8</v>
@@ -8572,29 +8508,26 @@
         <v>46247</v>
       </c>
       <c r="N15" s="38" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="O15" s="24"/>
       <c r="P15" s="46" t="s">
         <v>63</v>
       </c>
       <c r="Q15" s="24" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="R15" s="24"/>
       <c r="S15" s="47" t="s">
-        <v>116</v>
-      </c>
-      <c r="T15" s="47" t="s">
         <v>23</v>
       </c>
-      <c r="U15" s="24" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="16" ht="42" customHeight="1" spans="1:21">
+      <c r="T15" s="24" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="16" ht="42" customHeight="1" spans="1:20">
       <c r="A16" s="24" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B16" s="24">
         <v>2026</v>
@@ -8609,7 +8542,7 @@
         <v>56</v>
       </c>
       <c r="F16" s="24" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="G16" s="44">
         <v>9</v>
@@ -8625,29 +8558,26 @@
         <v>46247</v>
       </c>
       <c r="N16" s="38" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="O16" s="24"/>
       <c r="P16" s="46" t="s">
         <v>63</v>
       </c>
       <c r="Q16" s="24" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="R16" s="24"/>
       <c r="S16" s="47" t="s">
-        <v>116</v>
-      </c>
-      <c r="T16" s="47" t="s">
         <v>23</v>
       </c>
-      <c r="U16" s="24" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="17" ht="42" customHeight="1" spans="1:21">
+      <c r="T16" s="24" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="17" ht="42" customHeight="1" spans="1:20">
       <c r="A17" s="24" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="B17" s="24">
         <v>2026</v>
@@ -8662,7 +8592,7 @@
         <v>56</v>
       </c>
       <c r="F17" s="24" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="G17" s="44">
         <v>10</v>
@@ -8678,29 +8608,26 @@
         <v>46247</v>
       </c>
       <c r="N17" s="38" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="O17" s="24"/>
       <c r="P17" s="46" t="s">
         <v>63</v>
       </c>
       <c r="Q17" s="24" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="R17" s="24"/>
       <c r="S17" s="47" t="s">
-        <v>116</v>
-      </c>
-      <c r="T17" s="47" t="s">
         <v>23</v>
       </c>
-      <c r="U17" s="24" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="18" ht="42" customHeight="1" spans="1:21">
+      <c r="T17" s="24" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="18" ht="42" customHeight="1" spans="1:20">
       <c r="A18" s="24" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="B18" s="24">
         <v>2026</v>
@@ -8715,7 +8642,7 @@
         <v>56</v>
       </c>
       <c r="F18" s="24" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="G18" s="44">
         <v>11</v>
@@ -8731,29 +8658,26 @@
         <v>46247</v>
       </c>
       <c r="N18" s="38" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="O18" s="24"/>
       <c r="P18" s="46" t="s">
         <v>63</v>
       </c>
       <c r="Q18" s="24" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="R18" s="24"/>
       <c r="S18" s="47" t="s">
-        <v>116</v>
-      </c>
-      <c r="T18" s="47" t="s">
         <v>23</v>
       </c>
-      <c r="U18" s="24" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="19" ht="42" customHeight="1" spans="1:21">
+      <c r="T18" s="24" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="19" ht="42" customHeight="1" spans="1:20">
       <c r="A19" s="24" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="B19" s="24">
         <v>2026</v>
@@ -8768,7 +8692,7 @@
         <v>56</v>
       </c>
       <c r="F19" s="24" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="G19" s="44">
         <v>12</v>
@@ -8784,29 +8708,26 @@
         <v>46247</v>
       </c>
       <c r="N19" s="38" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="O19" s="24"/>
       <c r="P19" s="46" t="s">
         <v>63</v>
       </c>
       <c r="Q19" s="24" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="R19" s="24"/>
       <c r="S19" s="47" t="s">
-        <v>116</v>
-      </c>
-      <c r="T19" s="47" t="s">
         <v>23</v>
       </c>
-      <c r="U19" s="24" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="20" ht="42" customHeight="1" spans="1:21">
+      <c r="T19" s="24" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="20" ht="42" customHeight="1" spans="1:20">
       <c r="A20" s="24" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="B20" s="24">
         <v>2026</v>
@@ -8821,7 +8742,7 @@
         <v>66</v>
       </c>
       <c r="F20" s="24" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="G20" s="44">
         <v>9</v>
@@ -8835,29 +8756,26 @@
         <v>46247</v>
       </c>
       <c r="N20" s="38" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="O20" s="24"/>
       <c r="P20" s="46" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="Q20" s="24" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="R20" s="24"/>
       <c r="S20" s="47" t="s">
-        <v>122</v>
-      </c>
-      <c r="T20" s="47" t="s">
         <v>23</v>
       </c>
-      <c r="U20" s="24" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="21" ht="42" customHeight="1" spans="1:21">
+      <c r="T20" s="24" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="21" ht="42" customHeight="1" spans="1:20">
       <c r="A21" s="24" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="B21" s="24">
         <v>2026</v>
@@ -8872,7 +8790,7 @@
         <v>76</v>
       </c>
       <c r="F21" s="24" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="G21" s="44">
         <v>2</v>
@@ -8892,31 +8810,28 @@
         <v>46247</v>
       </c>
       <c r="N21" s="38" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="O21" s="24"/>
       <c r="P21" s="46" t="s">
         <v>82</v>
       </c>
       <c r="Q21" s="24" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="R21" s="24" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="S21" s="47" t="s">
-        <v>116</v>
-      </c>
-      <c r="T21" s="47" t="s">
         <v>23</v>
       </c>
-      <c r="U21" s="24" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="22" ht="42" customHeight="1" spans="1:21">
+      <c r="T21" s="24" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="22" ht="42" customHeight="1" spans="1:20">
       <c r="A22" s="24" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="B22" s="24">
         <v>2026</v>
@@ -8931,7 +8846,7 @@
         <v>76</v>
       </c>
       <c r="F22" s="24" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="G22" s="44">
         <v>4</v>
@@ -8951,31 +8866,28 @@
         <v>46247</v>
       </c>
       <c r="N22" s="38" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="O22" s="24"/>
       <c r="P22" s="46" t="s">
         <v>82</v>
       </c>
       <c r="Q22" s="24" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="R22" s="24" t="s">
+        <v>167</v>
+      </c>
+      <c r="S22" s="47" t="s">
+        <v>23</v>
+      </c>
+      <c r="T22" s="24" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="23" ht="42" customHeight="1" spans="1:20">
+      <c r="A23" s="24" t="s">
         <v>170</v>
-      </c>
-      <c r="S22" s="47" t="s">
-        <v>116</v>
-      </c>
-      <c r="T22" s="47" t="s">
-        <v>23</v>
-      </c>
-      <c r="U22" s="24" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="23" ht="42" customHeight="1" spans="1:21">
-      <c r="A23" s="24" t="s">
-        <v>173</v>
       </c>
       <c r="B23" s="24">
         <v>2026</v>
@@ -8990,7 +8902,7 @@
         <v>76</v>
       </c>
       <c r="F23" s="24" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="G23" s="44">
         <v>5</v>
@@ -9010,31 +8922,28 @@
         <v>46247</v>
       </c>
       <c r="N23" s="38" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="O23" s="24"/>
       <c r="P23" s="46" t="s">
         <v>82</v>
       </c>
       <c r="Q23" s="24" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="R23" s="24" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="S23" s="47" t="s">
-        <v>116</v>
-      </c>
-      <c r="T23" s="47" t="s">
         <v>23</v>
       </c>
-      <c r="U23" s="24" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="24" ht="42" customHeight="1" spans="1:21">
+      <c r="T23" s="24" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="24" ht="42" customHeight="1" spans="1:20">
       <c r="A24" s="24" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="B24" s="24">
         <v>2026</v>
@@ -9049,7 +8958,7 @@
         <v>76</v>
       </c>
       <c r="F24" s="24" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="G24" s="44">
         <v>10</v>
@@ -9069,31 +8978,28 @@
         <v>46247</v>
       </c>
       <c r="N24" s="38" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="O24" s="24"/>
       <c r="P24" s="46" t="s">
         <v>82</v>
       </c>
       <c r="Q24" s="24" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="R24" s="24" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="S24" s="47" t="s">
-        <v>116</v>
-      </c>
-      <c r="T24" s="47" t="s">
         <v>23</v>
       </c>
-      <c r="U24" s="24" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="25" ht="42" customHeight="1" spans="1:21">
+      <c r="T24" s="24" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="25" ht="42" customHeight="1" spans="1:20">
       <c r="A25" s="24" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="B25" s="24">
         <v>2026</v>
@@ -9108,7 +9014,7 @@
         <v>76</v>
       </c>
       <c r="F25" s="24" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="G25" s="44">
         <v>11</v>
@@ -9128,31 +9034,28 @@
         <v>46247</v>
       </c>
       <c r="N25" s="38" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="O25" s="24"/>
       <c r="P25" s="46" t="s">
         <v>82</v>
       </c>
       <c r="Q25" s="24" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="R25" s="24" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="S25" s="47" t="s">
-        <v>116</v>
-      </c>
-      <c r="T25" s="47" t="s">
         <v>23</v>
       </c>
-      <c r="U25" s="24" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="26" ht="42" customHeight="1" spans="1:21">
+      <c r="T25" s="24" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="26" ht="42" customHeight="1" spans="1:20">
       <c r="A26" s="24" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="B26" s="24">
         <v>2026</v>
@@ -9167,7 +9070,7 @@
         <v>85</v>
       </c>
       <c r="F26" s="24" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="G26" s="44">
         <v>2</v>
@@ -9185,31 +9088,28 @@
         <v>46247</v>
       </c>
       <c r="N26" s="38" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="O26" s="24"/>
       <c r="P26" s="46" t="s">
         <v>92</v>
       </c>
       <c r="Q26" s="24" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="R26" s="24" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="S26" s="47" t="s">
-        <v>116</v>
-      </c>
-      <c r="T26" s="47" t="s">
         <v>23</v>
       </c>
-      <c r="U26" s="24" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="27" ht="42" customHeight="1" spans="1:21">
+      <c r="T26" s="24" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="27" ht="42" customHeight="1" spans="1:20">
       <c r="A27" s="24" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="B27" s="24">
         <v>2026</v>
@@ -9224,7 +9124,7 @@
         <v>85</v>
       </c>
       <c r="F27" s="24" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="G27" s="44">
         <v>4</v>
@@ -9242,31 +9142,28 @@
         <v>46247</v>
       </c>
       <c r="N27" s="38" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="O27" s="24"/>
       <c r="P27" s="46" t="s">
         <v>92</v>
       </c>
       <c r="Q27" s="24" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="R27" s="24" t="s">
+        <v>179</v>
+      </c>
+      <c r="S27" s="47" t="s">
+        <v>23</v>
+      </c>
+      <c r="T27" s="24" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="28" ht="42" customHeight="1" spans="1:20">
+      <c r="A28" s="24" t="s">
         <v>182</v>
-      </c>
-      <c r="S27" s="47" t="s">
-        <v>116</v>
-      </c>
-      <c r="T27" s="47" t="s">
-        <v>23</v>
-      </c>
-      <c r="U27" s="24" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="28" ht="42" customHeight="1" spans="1:21">
-      <c r="A28" s="24" t="s">
-        <v>185</v>
       </c>
       <c r="B28" s="24">
         <v>2026</v>
@@ -9281,7 +9178,7 @@
         <v>85</v>
       </c>
       <c r="F28" s="24" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="G28" s="44">
         <v>6</v>
@@ -9299,31 +9196,28 @@
         <v>46247</v>
       </c>
       <c r="N28" s="38" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="O28" s="24"/>
       <c r="P28" s="46" t="s">
         <v>92</v>
       </c>
       <c r="Q28" s="24" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="R28" s="24" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="S28" s="47" t="s">
-        <v>116</v>
-      </c>
-      <c r="T28" s="47" t="s">
         <v>23</v>
       </c>
-      <c r="U28" s="24" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="29" ht="42" customHeight="1" spans="1:21">
+      <c r="T28" s="24" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="29" ht="42" customHeight="1" spans="1:20">
       <c r="A29" s="24" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="B29" s="24">
         <v>2026</v>
@@ -9338,7 +9232,7 @@
         <v>85</v>
       </c>
       <c r="F29" s="24" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="G29" s="44">
         <v>7</v>
@@ -9356,31 +9250,28 @@
         <v>46247</v>
       </c>
       <c r="N29" s="38" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="O29" s="24"/>
       <c r="P29" s="46" t="s">
         <v>92</v>
       </c>
       <c r="Q29" s="24" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="R29" s="24" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="S29" s="47" t="s">
-        <v>116</v>
-      </c>
-      <c r="T29" s="47" t="s">
         <v>23</v>
       </c>
-      <c r="U29" s="24" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="30" ht="42" customHeight="1" spans="1:21">
+      <c r="T29" s="24" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="30" ht="42" customHeight="1" spans="1:20">
       <c r="A30" s="24" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="B30" s="24">
         <v>2026</v>
@@ -9395,7 +9286,7 @@
         <v>85</v>
       </c>
       <c r="F30" s="24" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="G30" s="44">
         <v>10</v>
@@ -9413,31 +9304,28 @@
         <v>46247</v>
       </c>
       <c r="N30" s="38" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="O30" s="24"/>
       <c r="P30" s="46" t="s">
         <v>92</v>
       </c>
       <c r="Q30" s="24" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="R30" s="24" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="S30" s="47" t="s">
-        <v>116</v>
-      </c>
-      <c r="T30" s="47" t="s">
         <v>23</v>
       </c>
-      <c r="U30" s="24" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="31" ht="42" customHeight="1" spans="1:21">
+      <c r="T30" s="24" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="31" ht="42" customHeight="1" spans="1:20">
       <c r="A31" s="24" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="B31" s="24">
         <v>2026</v>
@@ -9452,7 +9340,7 @@
         <v>85</v>
       </c>
       <c r="F31" s="24" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="G31" s="44">
         <v>12</v>
@@ -9470,31 +9358,28 @@
         <v>46247</v>
       </c>
       <c r="N31" s="38" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="O31" s="24"/>
       <c r="P31" s="46" t="s">
         <v>92</v>
       </c>
       <c r="Q31" s="24" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="R31" s="24" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="S31" s="47" t="s">
-        <v>116</v>
-      </c>
-      <c r="T31" s="47" t="s">
         <v>23</v>
       </c>
-      <c r="U31" s="24" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="32" ht="34" spans="1:21">
+      <c r="T31" s="24" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="32" ht="34" spans="1:20">
       <c r="A32" s="48" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="B32" s="49">
         <v>2027</v>
@@ -9509,7 +9394,7 @@
         <v>47</v>
       </c>
       <c r="F32" s="24" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="G32" s="49">
         <v>3</v>
@@ -9531,33 +9416,30 @@
         <v>46247</v>
       </c>
       <c r="N32" s="50" t="s">
+        <v>112</v>
+      </c>
+      <c r="O32" s="24" t="s">
+        <v>192</v>
+      </c>
+      <c r="P32" s="46" t="s">
+        <v>193</v>
+      </c>
+      <c r="Q32" s="24" t="s">
         <v>113</v>
       </c>
-      <c r="O32" s="24" t="s">
+      <c r="R32" s="24" t="s">
+        <v>194</v>
+      </c>
+      <c r="S32" s="47" t="s">
+        <v>23</v>
+      </c>
+      <c r="T32" s="49" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="33" ht="34" spans="1:20">
+      <c r="A33" s="48" t="s">
         <v>195</v>
-      </c>
-      <c r="P32" s="46" t="s">
-        <v>196</v>
-      </c>
-      <c r="Q32" s="24" t="s">
-        <v>114</v>
-      </c>
-      <c r="R32" s="24" t="s">
-        <v>197</v>
-      </c>
-      <c r="S32" s="47" t="s">
-        <v>116</v>
-      </c>
-      <c r="T32" s="47" t="s">
-        <v>23</v>
-      </c>
-      <c r="U32" s="49" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="33" ht="34" spans="1:21">
-      <c r="A33" s="48" t="s">
-        <v>198</v>
       </c>
       <c r="B33" s="49">
         <v>2027</v>
@@ -9572,7 +9454,7 @@
         <v>47</v>
       </c>
       <c r="F33" s="24" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="G33" s="49">
         <v>7</v>
@@ -9594,33 +9476,30 @@
         <v>46247</v>
       </c>
       <c r="N33" s="50" t="s">
+        <v>112</v>
+      </c>
+      <c r="O33" s="24" t="s">
+        <v>197</v>
+      </c>
+      <c r="P33" s="46" t="s">
+        <v>193</v>
+      </c>
+      <c r="Q33" s="24" t="s">
         <v>113</v>
       </c>
-      <c r="O33" s="24" t="s">
-        <v>200</v>
-      </c>
-      <c r="P33" s="46" t="s">
-        <v>196</v>
-      </c>
-      <c r="Q33" s="24" t="s">
-        <v>114</v>
-      </c>
       <c r="R33" s="24" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="S33" s="47" t="s">
-        <v>116</v>
-      </c>
-      <c r="T33" s="47" t="s">
         <v>23</v>
       </c>
-      <c r="U33" s="49" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="34" ht="34" spans="1:21">
+      <c r="T33" s="49" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="34" ht="34" spans="1:20">
       <c r="A34" s="48" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="B34" s="49">
         <v>2027</v>
@@ -9635,7 +9514,7 @@
         <v>47</v>
       </c>
       <c r="F34" s="24" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="G34" s="49">
         <v>11</v>
@@ -9657,31 +9536,28 @@
         <v>46247</v>
       </c>
       <c r="N34" s="50" t="s">
+        <v>112</v>
+      </c>
+      <c r="O34" s="24" t="s">
+        <v>201</v>
+      </c>
+      <c r="P34" s="46" t="s">
+        <v>193</v>
+      </c>
+      <c r="Q34" s="24" t="s">
         <v>113</v>
       </c>
-      <c r="O34" s="24" t="s">
-        <v>204</v>
-      </c>
-      <c r="P34" s="46" t="s">
-        <v>196</v>
-      </c>
-      <c r="Q34" s="24" t="s">
-        <v>114</v>
-      </c>
       <c r="R34" s="24" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="S34" s="47" t="s">
-        <v>116</v>
-      </c>
-      <c r="T34" s="47" t="s">
         <v>23</v>
       </c>
-      <c r="U34" s="49" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="35" spans="1:21">
+      <c r="T34" s="49" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="35" spans="1:20">
       <c r="A35" s="48"/>
       <c r="B35" s="49"/>
       <c r="C35" s="49"/>
@@ -9701,10 +9577,9 @@
       <c r="Q35" s="24"/>
       <c r="R35" s="24"/>
       <c r="S35" s="47"/>
-      <c r="T35" s="47"/>
-      <c r="U35" s="49"/>
-    </row>
-    <row r="36" spans="1:21">
+      <c r="T35" s="49"/>
+    </row>
+    <row r="36" spans="1:20">
       <c r="A36" s="51"/>
       <c r="B36" s="49"/>
       <c r="C36" s="49"/>
@@ -9724,10 +9599,9 @@
       <c r="Q36" s="24"/>
       <c r="R36" s="24"/>
       <c r="S36" s="47"/>
-      <c r="T36" s="47"/>
-      <c r="U36" s="49"/>
-    </row>
-    <row r="37" customHeight="1" spans="1:21">
+      <c r="T36" s="49"/>
+    </row>
+    <row r="37" customHeight="1" spans="1:20">
       <c r="A37" s="51"/>
       <c r="B37" s="49"/>
       <c r="C37" s="49"/>
@@ -9747,10 +9621,9 @@
       <c r="Q37" s="24"/>
       <c r="R37" s="24"/>
       <c r="S37" s="47"/>
-      <c r="T37" s="47"/>
-      <c r="U37" s="49"/>
-    </row>
-    <row r="38" customHeight="1" spans="1:21">
+      <c r="T37" s="49"/>
+    </row>
+    <row r="38" customHeight="1" spans="1:20">
       <c r="A38" s="51"/>
       <c r="B38" s="49"/>
       <c r="C38" s="49"/>
@@ -9770,10 +9643,9 @@
       <c r="Q38" s="24"/>
       <c r="R38" s="24"/>
       <c r="S38" s="47"/>
-      <c r="T38" s="47"/>
-      <c r="U38" s="49"/>
-    </row>
-    <row r="39" customHeight="1" spans="1:21">
+      <c r="T38" s="49"/>
+    </row>
+    <row r="39" customHeight="1" spans="1:20">
       <c r="A39" s="51"/>
       <c r="B39" s="49"/>
       <c r="C39" s="49"/>
@@ -9793,10 +9665,9 @@
       <c r="Q39" s="24"/>
       <c r="R39" s="24"/>
       <c r="S39" s="47"/>
-      <c r="T39" s="47"/>
-      <c r="U39" s="49"/>
-    </row>
-    <row r="40" spans="1:21">
+      <c r="T39" s="49"/>
+    </row>
+    <row r="40" spans="1:20">
       <c r="A40" s="48"/>
       <c r="B40" s="49"/>
       <c r="C40" s="49"/>
@@ -9816,10 +9687,9 @@
       <c r="Q40" s="24"/>
       <c r="R40" s="24"/>
       <c r="S40" s="47"/>
-      <c r="T40" s="47"/>
-      <c r="U40" s="49"/>
-    </row>
-    <row r="41" spans="1:21">
+      <c r="T40" s="49"/>
+    </row>
+    <row r="41" spans="1:20">
       <c r="A41" s="48"/>
       <c r="B41" s="49"/>
       <c r="C41" s="49"/>
@@ -9839,10 +9709,9 @@
       <c r="Q41" s="24"/>
       <c r="R41" s="24"/>
       <c r="S41" s="47"/>
-      <c r="T41" s="47"/>
-      <c r="U41" s="49"/>
-    </row>
-    <row r="42" spans="1:21">
+      <c r="T41" s="49"/>
+    </row>
+    <row r="42" spans="1:20">
       <c r="A42" s="49"/>
       <c r="B42" s="49"/>
       <c r="C42" s="49"/>
@@ -9862,10 +9731,9 @@
       <c r="Q42" s="24"/>
       <c r="R42" s="24"/>
       <c r="S42" s="47"/>
-      <c r="T42" s="47"/>
-      <c r="U42" s="49"/>
-    </row>
-    <row r="43" spans="1:21">
+      <c r="T42" s="49"/>
+    </row>
+    <row r="43" spans="1:20">
       <c r="A43" s="49"/>
       <c r="B43" s="49"/>
       <c r="C43" s="49"/>
@@ -9885,10 +9753,9 @@
       <c r="Q43" s="24"/>
       <c r="R43" s="24"/>
       <c r="S43" s="47"/>
-      <c r="T43" s="47"/>
-      <c r="U43" s="49"/>
-    </row>
-    <row r="44" spans="1:21">
+      <c r="T43" s="49"/>
+    </row>
+    <row r="44" spans="1:20">
       <c r="A44" s="49"/>
       <c r="B44" s="49"/>
       <c r="C44" s="49"/>
@@ -9908,10 +9775,9 @@
       <c r="Q44" s="24"/>
       <c r="R44" s="24"/>
       <c r="S44" s="47"/>
-      <c r="T44" s="47"/>
-      <c r="U44" s="49"/>
-    </row>
-    <row r="45" spans="1:21">
+      <c r="T44" s="49"/>
+    </row>
+    <row r="45" spans="1:20">
       <c r="A45" s="49"/>
       <c r="B45" s="49"/>
       <c r="C45" s="49"/>
@@ -9931,10 +9797,9 @@
       <c r="Q45" s="24"/>
       <c r="R45" s="24"/>
       <c r="S45" s="47"/>
-      <c r="T45" s="47"/>
-      <c r="U45" s="49"/>
-    </row>
-    <row r="46" spans="1:21">
+      <c r="T45" s="49"/>
+    </row>
+    <row r="46" spans="1:20">
       <c r="A46" s="49"/>
       <c r="B46" s="49"/>
       <c r="C46" s="49"/>
@@ -9954,10 +9819,9 @@
       <c r="Q46" s="24"/>
       <c r="R46" s="24"/>
       <c r="S46" s="47"/>
-      <c r="T46" s="47"/>
-      <c r="U46" s="49"/>
-    </row>
-    <row r="47" spans="1:21">
+      <c r="T46" s="49"/>
+    </row>
+    <row r="47" spans="1:20">
       <c r="A47" s="49"/>
       <c r="B47" s="49"/>
       <c r="C47" s="49"/>
@@ -9977,10 +9841,9 @@
       <c r="Q47" s="24"/>
       <c r="R47" s="24"/>
       <c r="S47" s="47"/>
-      <c r="T47" s="47"/>
-      <c r="U47" s="49"/>
-    </row>
-    <row r="48" spans="1:21">
+      <c r="T47" s="49"/>
+    </row>
+    <row r="48" spans="1:20">
       <c r="A48" s="49"/>
       <c r="B48" s="49"/>
       <c r="C48" s="49"/>
@@ -10000,10 +9863,9 @@
       <c r="Q48" s="24"/>
       <c r="R48" s="24"/>
       <c r="S48" s="47"/>
-      <c r="T48" s="47"/>
-      <c r="U48" s="49"/>
-    </row>
-    <row r="49" spans="1:21">
+      <c r="T48" s="49"/>
+    </row>
+    <row r="49" spans="1:20">
       <c r="A49" s="49"/>
       <c r="B49" s="49"/>
       <c r="C49" s="49"/>
@@ -10023,10 +9885,9 @@
       <c r="Q49" s="24"/>
       <c r="R49" s="24"/>
       <c r="S49" s="47"/>
-      <c r="T49" s="47"/>
-      <c r="U49" s="49"/>
-    </row>
-    <row r="50" spans="1:21">
+      <c r="T49" s="49"/>
+    </row>
+    <row r="50" spans="1:20">
       <c r="A50" s="49"/>
       <c r="B50" s="49"/>
       <c r="C50" s="49"/>
@@ -10046,10 +9907,9 @@
       <c r="Q50" s="24"/>
       <c r="R50" s="24"/>
       <c r="S50" s="47"/>
-      <c r="T50" s="47"/>
-      <c r="U50" s="49"/>
-    </row>
-    <row r="51" customFormat="1" spans="1:21">
+      <c r="T50" s="49"/>
+    </row>
+    <row r="51" customFormat="1" spans="1:20">
       <c r="F51" s="24"/>
       <c r="H51" s="52"/>
       <c r="I51" s="52"/>
@@ -10063,9 +9923,8 @@
       <c r="Q51" s="24"/>
       <c r="R51" s="24"/>
       <c r="S51" s="27"/>
-      <c r="T51" s="27"/>
-    </row>
-    <row r="52" customFormat="1" spans="1:21">
+    </row>
+    <row r="52" customFormat="1" spans="1:20">
       <c r="F52" s="24"/>
       <c r="H52" s="52"/>
       <c r="I52" s="52"/>
@@ -10079,9 +9938,8 @@
       <c r="Q52" s="24"/>
       <c r="R52" s="24"/>
       <c r="S52" s="27"/>
-      <c r="T52" s="27"/>
-    </row>
-    <row r="53" customFormat="1" spans="1:21">
+    </row>
+    <row r="53" customFormat="1" spans="1:20">
       <c r="F53" s="24"/>
       <c r="H53" s="52"/>
       <c r="I53" s="52"/>
@@ -10095,9 +9953,8 @@
       <c r="Q53" s="24"/>
       <c r="R53" s="24"/>
       <c r="S53" s="27"/>
-      <c r="T53" s="27"/>
-    </row>
-    <row r="54" customFormat="1" spans="1:21">
+    </row>
+    <row r="54" customFormat="1" spans="1:20">
       <c r="F54" s="24"/>
       <c r="H54" s="52"/>
       <c r="I54" s="52"/>
@@ -10111,9 +9968,8 @@
       <c r="Q54" s="24"/>
       <c r="R54" s="24"/>
       <c r="S54" s="27"/>
-      <c r="T54" s="27"/>
-    </row>
-    <row r="55" customFormat="1" spans="1:21">
+    </row>
+    <row r="55" customFormat="1" spans="1:20">
       <c r="F55" s="24"/>
       <c r="H55" s="52"/>
       <c r="I55" s="52"/>
@@ -10127,9 +9983,8 @@
       <c r="Q55" s="24"/>
       <c r="R55" s="24"/>
       <c r="S55" s="27"/>
-      <c r="T55" s="27"/>
-    </row>
-    <row r="56" customFormat="1" spans="1:21">
+    </row>
+    <row r="56" customFormat="1" spans="1:20">
       <c r="F56" s="24"/>
       <c r="H56" s="52"/>
       <c r="I56" s="52"/>
@@ -10143,9 +9998,8 @@
       <c r="Q56" s="24"/>
       <c r="R56" s="24"/>
       <c r="S56" s="27"/>
-      <c r="T56" s="27"/>
-    </row>
-    <row r="57" customFormat="1" spans="1:21">
+    </row>
+    <row r="57" customFormat="1" spans="1:20">
       <c r="F57" s="24"/>
       <c r="H57" s="52"/>
       <c r="I57" s="52"/>
@@ -10159,9 +10013,8 @@
       <c r="Q57" s="24"/>
       <c r="R57" s="24"/>
       <c r="S57" s="27"/>
-      <c r="T57" s="27"/>
-    </row>
-    <row r="58" customFormat="1" spans="1:21">
+    </row>
+    <row r="58" customFormat="1" spans="1:20">
       <c r="F58" s="24"/>
       <c r="H58" s="52"/>
       <c r="I58" s="52"/>
@@ -10175,9 +10028,8 @@
       <c r="Q58" s="24"/>
       <c r="R58" s="24"/>
       <c r="S58" s="27"/>
-      <c r="T58" s="27"/>
-    </row>
-    <row r="59" customFormat="1" spans="1:21">
+    </row>
+    <row r="59" customFormat="1" spans="1:20">
       <c r="F59" s="24"/>
       <c r="H59" s="52"/>
       <c r="I59" s="52"/>
@@ -10191,9 +10043,8 @@
       <c r="Q59" s="24"/>
       <c r="R59" s="24"/>
       <c r="S59" s="27"/>
-      <c r="T59" s="27"/>
-    </row>
-    <row r="60" customFormat="1" spans="1:21">
+    </row>
+    <row r="60" customFormat="1" spans="1:20">
       <c r="F60" s="24"/>
       <c r="H60" s="52"/>
       <c r="I60" s="52"/>
@@ -10207,9 +10058,8 @@
       <c r="Q60" s="24"/>
       <c r="R60" s="24"/>
       <c r="S60" s="27"/>
-      <c r="T60" s="27"/>
-    </row>
-    <row r="61" customFormat="1" spans="1:21">
+    </row>
+    <row r="61" customFormat="1" spans="1:20">
       <c r="F61" s="24"/>
       <c r="H61" s="52"/>
       <c r="I61" s="52"/>
@@ -10223,9 +10073,8 @@
       <c r="Q61" s="24"/>
       <c r="R61" s="24"/>
       <c r="S61" s="27"/>
-      <c r="T61" s="27"/>
-    </row>
-    <row r="62" customFormat="1" spans="1:21">
+    </row>
+    <row r="62" customFormat="1" spans="1:20">
       <c r="F62" s="24"/>
       <c r="H62" s="52"/>
       <c r="I62" s="52"/>
@@ -10239,9 +10088,8 @@
       <c r="Q62" s="24"/>
       <c r="R62" s="24"/>
       <c r="S62" s="27"/>
-      <c r="T62" s="27"/>
-    </row>
-    <row r="63" customFormat="1" spans="1:21">
+    </row>
+    <row r="63" customFormat="1" spans="1:20">
       <c r="F63" s="24"/>
       <c r="H63" s="52"/>
       <c r="I63" s="52"/>
@@ -10255,9 +10103,8 @@
       <c r="Q63" s="24"/>
       <c r="R63" s="24"/>
       <c r="S63" s="27"/>
-      <c r="T63" s="27"/>
-    </row>
-    <row r="64" customFormat="1" spans="1:21">
+    </row>
+    <row r="64" customFormat="1" spans="1:20">
       <c r="F64" s="24"/>
       <c r="H64" s="52"/>
       <c r="I64" s="52"/>
@@ -10271,9 +10118,8 @@
       <c r="Q64" s="24"/>
       <c r="R64" s="24"/>
       <c r="S64" s="27"/>
-      <c r="T64" s="27"/>
-    </row>
-    <row r="65" customFormat="1" spans="6:20">
+    </row>
+    <row r="65" customFormat="1" spans="6:19">
       <c r="F65" s="24"/>
       <c r="H65" s="52"/>
       <c r="I65" s="52"/>
@@ -10287,9 +10133,8 @@
       <c r="Q65" s="24"/>
       <c r="R65" s="24"/>
       <c r="S65" s="27"/>
-      <c r="T65" s="27"/>
-    </row>
-    <row r="66" customFormat="1" spans="6:20">
+    </row>
+    <row r="66" customFormat="1" spans="6:19">
       <c r="F66" s="24"/>
       <c r="H66" s="52"/>
       <c r="I66" s="52"/>
@@ -10303,9 +10148,8 @@
       <c r="Q66" s="24"/>
       <c r="R66" s="24"/>
       <c r="S66" s="27"/>
-      <c r="T66" s="27"/>
-    </row>
-    <row r="67" customFormat="1" spans="6:20">
+    </row>
+    <row r="67" customFormat="1" spans="6:19">
       <c r="F67" s="24"/>
       <c r="H67" s="52"/>
       <c r="I67" s="52"/>
@@ -10319,9 +10163,8 @@
       <c r="Q67" s="24"/>
       <c r="R67" s="24"/>
       <c r="S67" s="27"/>
-      <c r="T67" s="27"/>
-    </row>
-    <row r="68" customFormat="1" spans="6:20">
+    </row>
+    <row r="68" customFormat="1" spans="6:19">
       <c r="F68" s="24"/>
       <c r="H68" s="52"/>
       <c r="I68" s="52"/>
@@ -10335,9 +10178,8 @@
       <c r="Q68" s="24"/>
       <c r="R68" s="24"/>
       <c r="S68" s="27"/>
-      <c r="T68" s="27"/>
-    </row>
-    <row r="69" customFormat="1" spans="6:20">
+    </row>
+    <row r="69" customFormat="1" spans="6:19">
       <c r="F69" s="24"/>
       <c r="H69" s="52"/>
       <c r="I69" s="52"/>
@@ -10351,9 +10193,8 @@
       <c r="Q69" s="24"/>
       <c r="R69" s="24"/>
       <c r="S69" s="27"/>
-      <c r="T69" s="27"/>
-    </row>
-    <row r="70" customFormat="1" spans="6:20">
+    </row>
+    <row r="70" customFormat="1" spans="6:19">
       <c r="F70" s="24"/>
       <c r="H70" s="52"/>
       <c r="I70" s="52"/>
@@ -10367,9 +10208,8 @@
       <c r="Q70" s="24"/>
       <c r="R70" s="24"/>
       <c r="S70" s="27"/>
-      <c r="T70" s="27"/>
-    </row>
-    <row r="71" customFormat="1" spans="6:20">
+    </row>
+    <row r="71" customFormat="1" spans="6:19">
       <c r="F71" s="24"/>
       <c r="H71" s="52"/>
       <c r="I71" s="52"/>
@@ -10383,9 +10223,8 @@
       <c r="Q71" s="24"/>
       <c r="R71" s="24"/>
       <c r="S71" s="27"/>
-      <c r="T71" s="27"/>
-    </row>
-    <row r="72" customFormat="1" spans="6:20">
+    </row>
+    <row r="72" customFormat="1" spans="6:19">
       <c r="F72" s="24"/>
       <c r="H72" s="52"/>
       <c r="I72" s="52"/>
@@ -10399,9 +10238,8 @@
       <c r="Q72" s="24"/>
       <c r="R72" s="24"/>
       <c r="S72" s="27"/>
-      <c r="T72" s="27"/>
-    </row>
-    <row r="73" customFormat="1" spans="6:20">
+    </row>
+    <row r="73" customFormat="1" spans="6:19">
       <c r="F73" s="24"/>
       <c r="H73" s="52"/>
       <c r="I73" s="52"/>
@@ -10415,9 +10253,8 @@
       <c r="Q73" s="24"/>
       <c r="R73" s="24"/>
       <c r="S73" s="27"/>
-      <c r="T73" s="27"/>
-    </row>
-    <row r="74" customFormat="1" spans="6:20">
+    </row>
+    <row r="74" customFormat="1" spans="6:19">
       <c r="F74" s="24"/>
       <c r="H74" s="52"/>
       <c r="I74" s="52"/>
@@ -10431,9 +10268,8 @@
       <c r="Q74" s="24"/>
       <c r="R74" s="24"/>
       <c r="S74" s="27"/>
-      <c r="T74" s="27"/>
-    </row>
-    <row r="75" customFormat="1" spans="6:20">
+    </row>
+    <row r="75" customFormat="1" spans="6:19">
       <c r="F75" s="24"/>
       <c r="H75" s="52"/>
       <c r="I75" s="52"/>
@@ -10447,9 +10283,8 @@
       <c r="Q75" s="24"/>
       <c r="R75" s="24"/>
       <c r="S75" s="27"/>
-      <c r="T75" s="27"/>
-    </row>
-    <row r="76" customFormat="1" spans="6:20">
+    </row>
+    <row r="76" customFormat="1" spans="6:19">
       <c r="F76" s="24"/>
       <c r="H76" s="52"/>
       <c r="I76" s="52"/>
@@ -10463,9 +10298,8 @@
       <c r="Q76" s="24"/>
       <c r="R76" s="24"/>
       <c r="S76" s="27"/>
-      <c r="T76" s="27"/>
-    </row>
-    <row r="77" customFormat="1" spans="6:20">
+    </row>
+    <row r="77" customFormat="1" spans="6:19">
       <c r="F77" s="24"/>
       <c r="H77" s="52"/>
       <c r="I77" s="52"/>
@@ -10479,9 +10313,8 @@
       <c r="Q77" s="24"/>
       <c r="R77" s="24"/>
       <c r="S77" s="27"/>
-      <c r="T77" s="27"/>
-    </row>
-    <row r="78" customFormat="1" spans="6:20">
+    </row>
+    <row r="78" customFormat="1" spans="6:19">
       <c r="F78" s="24"/>
       <c r="H78" s="52"/>
       <c r="I78" s="52"/>
@@ -10495,9 +10328,8 @@
       <c r="Q78" s="24"/>
       <c r="R78" s="24"/>
       <c r="S78" s="27"/>
-      <c r="T78" s="27"/>
-    </row>
-    <row r="79" customFormat="1" spans="6:20">
+    </row>
+    <row r="79" customFormat="1" spans="6:19">
       <c r="F79" s="24"/>
       <c r="H79" s="52"/>
       <c r="I79" s="52"/>
@@ -10511,9 +10343,8 @@
       <c r="Q79" s="24"/>
       <c r="R79" s="24"/>
       <c r="S79" s="27"/>
-      <c r="T79" s="27"/>
-    </row>
-    <row r="80" customFormat="1" spans="6:20">
+    </row>
+    <row r="80" customFormat="1" spans="6:19">
       <c r="F80" s="24"/>
       <c r="H80" s="52"/>
       <c r="I80" s="52"/>
@@ -10527,9 +10358,8 @@
       <c r="Q80" s="24"/>
       <c r="R80" s="24"/>
       <c r="S80" s="27"/>
-      <c r="T80" s="27"/>
-    </row>
-    <row r="81" customFormat="1" spans="6:20">
+    </row>
+    <row r="81" customFormat="1" spans="6:19">
       <c r="F81" s="24"/>
       <c r="H81" s="52"/>
       <c r="I81" s="52"/>
@@ -10543,9 +10373,8 @@
       <c r="Q81" s="24"/>
       <c r="R81" s="24"/>
       <c r="S81" s="27"/>
-      <c r="T81" s="27"/>
-    </row>
-    <row r="82" customFormat="1" spans="6:20">
+    </row>
+    <row r="82" customFormat="1" spans="6:19">
       <c r="F82" s="24"/>
       <c r="H82" s="52"/>
       <c r="I82" s="52"/>
@@ -10559,9 +10388,8 @@
       <c r="Q82" s="24"/>
       <c r="R82" s="24"/>
       <c r="S82" s="27"/>
-      <c r="T82" s="27"/>
-    </row>
-    <row r="83" customFormat="1" spans="6:20">
+    </row>
+    <row r="83" customFormat="1" spans="6:19">
       <c r="F83" s="24"/>
       <c r="H83" s="52"/>
       <c r="I83" s="52"/>
@@ -10575,9 +10403,8 @@
       <c r="Q83" s="24"/>
       <c r="R83" s="24"/>
       <c r="S83" s="27"/>
-      <c r="T83" s="27"/>
-    </row>
-    <row r="84" customFormat="1" spans="6:20">
+    </row>
+    <row r="84" customFormat="1" spans="6:19">
       <c r="F84" s="24"/>
       <c r="H84" s="52"/>
       <c r="I84" s="52"/>
@@ -10591,9 +10418,8 @@
       <c r="Q84" s="24"/>
       <c r="R84" s="24"/>
       <c r="S84" s="27"/>
-      <c r="T84" s="27"/>
-    </row>
-    <row r="85" customFormat="1" spans="6:20">
+    </row>
+    <row r="85" customFormat="1" spans="6:19">
       <c r="F85" s="24"/>
       <c r="H85" s="52"/>
       <c r="I85" s="52"/>
@@ -10607,9 +10433,8 @@
       <c r="Q85" s="24"/>
       <c r="R85" s="24"/>
       <c r="S85" s="27"/>
-      <c r="T85" s="27"/>
-    </row>
-    <row r="86" customFormat="1" spans="6:20">
+    </row>
+    <row r="86" customFormat="1" spans="6:19">
       <c r="F86" s="24"/>
       <c r="H86" s="52"/>
       <c r="I86" s="52"/>
@@ -10623,9 +10448,8 @@
       <c r="Q86" s="24"/>
       <c r="R86" s="24"/>
       <c r="S86" s="27"/>
-      <c r="T86" s="27"/>
-    </row>
-    <row r="87" customFormat="1" spans="6:20">
+    </row>
+    <row r="87" customFormat="1" spans="6:19">
       <c r="F87" s="24"/>
       <c r="H87" s="52"/>
       <c r="I87" s="52"/>
@@ -10639,9 +10463,8 @@
       <c r="Q87" s="24"/>
       <c r="R87" s="24"/>
       <c r="S87" s="27"/>
-      <c r="T87" s="27"/>
-    </row>
-    <row r="88" customFormat="1" spans="6:20">
+    </row>
+    <row r="88" customFormat="1" spans="6:19">
       <c r="F88" s="24"/>
       <c r="H88" s="52"/>
       <c r="I88" s="52"/>
@@ -10655,9 +10478,8 @@
       <c r="Q88" s="24"/>
       <c r="R88" s="24"/>
       <c r="S88" s="27"/>
-      <c r="T88" s="27"/>
-    </row>
-    <row r="89" customFormat="1" spans="6:20">
+    </row>
+    <row r="89" customFormat="1" spans="6:19">
       <c r="F89" s="24"/>
       <c r="H89" s="52"/>
       <c r="I89" s="52"/>
@@ -10671,9 +10493,8 @@
       <c r="Q89" s="24"/>
       <c r="R89" s="24"/>
       <c r="S89" s="27"/>
-      <c r="T89" s="27"/>
-    </row>
-    <row r="90" customFormat="1" spans="6:20">
+    </row>
+    <row r="90" customFormat="1" spans="6:19">
       <c r="F90" s="24"/>
       <c r="H90" s="52"/>
       <c r="I90" s="52"/>
@@ -10687,9 +10508,8 @@
       <c r="Q90" s="24"/>
       <c r="R90" s="24"/>
       <c r="S90" s="27"/>
-      <c r="T90" s="27"/>
-    </row>
-    <row r="91" customFormat="1" spans="6:20">
+    </row>
+    <row r="91" customFormat="1" spans="6:19">
       <c r="F91" s="24"/>
       <c r="H91" s="52"/>
       <c r="I91" s="52"/>
@@ -10703,9 +10523,8 @@
       <c r="Q91" s="24"/>
       <c r="R91" s="24"/>
       <c r="S91" s="27"/>
-      <c r="T91" s="27"/>
-    </row>
-    <row r="92" customFormat="1" spans="6:20">
+    </row>
+    <row r="92" customFormat="1" spans="6:19">
       <c r="F92" s="24"/>
       <c r="H92" s="52"/>
       <c r="I92" s="52"/>
@@ -10719,9 +10538,8 @@
       <c r="Q92" s="24"/>
       <c r="R92" s="24"/>
       <c r="S92" s="27"/>
-      <c r="T92" s="27"/>
-    </row>
-    <row r="93" customFormat="1" spans="6:20">
+    </row>
+    <row r="93" customFormat="1" spans="6:19">
       <c r="F93" s="24"/>
       <c r="H93" s="52"/>
       <c r="I93" s="52"/>
@@ -10735,9 +10553,8 @@
       <c r="Q93" s="24"/>
       <c r="R93" s="24"/>
       <c r="S93" s="27"/>
-      <c r="T93" s="27"/>
-    </row>
-    <row r="94" customFormat="1" spans="6:20">
+    </row>
+    <row r="94" customFormat="1" spans="6:19">
       <c r="F94" s="24"/>
       <c r="H94" s="52"/>
       <c r="I94" s="52"/>
@@ -10751,9 +10568,8 @@
       <c r="Q94" s="24"/>
       <c r="R94" s="24"/>
       <c r="S94" s="27"/>
-      <c r="T94" s="27"/>
-    </row>
-    <row r="95" customFormat="1" spans="6:20">
+    </row>
+    <row r="95" customFormat="1" spans="6:19">
       <c r="F95" s="24"/>
       <c r="H95" s="52"/>
       <c r="I95" s="52"/>
@@ -10767,9 +10583,8 @@
       <c r="Q95" s="24"/>
       <c r="R95" s="24"/>
       <c r="S95" s="27"/>
-      <c r="T95" s="27"/>
-    </row>
-    <row r="96" customFormat="1" spans="6:20">
+    </row>
+    <row r="96" customFormat="1" spans="6:19">
       <c r="F96" s="24"/>
       <c r="H96" s="52"/>
       <c r="I96" s="52"/>
@@ -10783,9 +10598,8 @@
       <c r="Q96" s="24"/>
       <c r="R96" s="24"/>
       <c r="S96" s="27"/>
-      <c r="T96" s="27"/>
-    </row>
-    <row r="97" customFormat="1" spans="6:20">
+    </row>
+    <row r="97" customFormat="1" spans="6:19">
       <c r="F97" s="24"/>
       <c r="H97" s="52"/>
       <c r="I97" s="52"/>
@@ -10799,9 +10613,8 @@
       <c r="Q97" s="24"/>
       <c r="R97" s="24"/>
       <c r="S97" s="27"/>
-      <c r="T97" s="27"/>
-    </row>
-    <row r="98" customFormat="1" spans="6:20">
+    </row>
+    <row r="98" customFormat="1" spans="6:19">
       <c r="F98" s="24"/>
       <c r="H98" s="52"/>
       <c r="I98" s="52"/>
@@ -10815,9 +10628,8 @@
       <c r="Q98" s="24"/>
       <c r="R98" s="24"/>
       <c r="S98" s="27"/>
-      <c r="T98" s="27"/>
-    </row>
-    <row r="99" customFormat="1" spans="6:20">
+    </row>
+    <row r="99" customFormat="1" spans="6:19">
       <c r="F99" s="24"/>
       <c r="H99" s="52"/>
       <c r="I99" s="52"/>
@@ -10831,9 +10643,8 @@
       <c r="Q99" s="24"/>
       <c r="R99" s="24"/>
       <c r="S99" s="27"/>
-      <c r="T99" s="27"/>
-    </row>
-    <row r="100" customFormat="1" spans="6:20">
+    </row>
+    <row r="100" customFormat="1" spans="6:19">
       <c r="F100" s="24"/>
       <c r="H100" s="52"/>
       <c r="I100" s="52"/>
@@ -10847,9 +10658,8 @@
       <c r="Q100" s="24"/>
       <c r="R100" s="24"/>
       <c r="S100" s="27"/>
-      <c r="T100" s="27"/>
-    </row>
-    <row r="101" customFormat="1" spans="6:20">
+    </row>
+    <row r="101" customFormat="1" spans="6:19">
       <c r="F101" s="24"/>
       <c r="H101" s="52"/>
       <c r="I101" s="52"/>
@@ -10863,9 +10673,8 @@
       <c r="Q101" s="24"/>
       <c r="R101" s="24"/>
       <c r="S101" s="27"/>
-      <c r="T101" s="27"/>
-    </row>
-    <row r="102" customFormat="1" spans="6:20">
+    </row>
+    <row r="102" customFormat="1" spans="6:19">
       <c r="F102" s="24"/>
       <c r="H102" s="52"/>
       <c r="I102" s="52"/>
@@ -10879,9 +10688,8 @@
       <c r="Q102" s="24"/>
       <c r="R102" s="24"/>
       <c r="S102" s="27"/>
-      <c r="T102" s="27"/>
-    </row>
-    <row r="103" customFormat="1" spans="6:20">
+    </row>
+    <row r="103" customFormat="1" spans="6:19">
       <c r="F103" s="24"/>
       <c r="H103" s="52"/>
       <c r="I103" s="52"/>
@@ -10895,9 +10703,8 @@
       <c r="Q103" s="24"/>
       <c r="R103" s="24"/>
       <c r="S103" s="27"/>
-      <c r="T103" s="27"/>
-    </row>
-    <row r="104" customFormat="1" spans="6:20">
+    </row>
+    <row r="104" customFormat="1" spans="6:19">
       <c r="F104" s="24"/>
       <c r="H104" s="52"/>
       <c r="I104" s="52"/>
@@ -10911,9 +10718,8 @@
       <c r="Q104" s="24"/>
       <c r="R104" s="24"/>
       <c r="S104" s="27"/>
-      <c r="T104" s="27"/>
-    </row>
-    <row r="105" customFormat="1" spans="6:20">
+    </row>
+    <row r="105" customFormat="1" spans="6:19">
       <c r="F105" s="24"/>
       <c r="H105" s="52"/>
       <c r="I105" s="52"/>
@@ -10927,9 +10733,8 @@
       <c r="Q105" s="24"/>
       <c r="R105" s="24"/>
       <c r="S105" s="27"/>
-      <c r="T105" s="27"/>
-    </row>
-    <row r="106" customFormat="1" spans="6:20">
+    </row>
+    <row r="106" customFormat="1" spans="6:19">
       <c r="F106" s="24"/>
       <c r="H106" s="52"/>
       <c r="I106" s="52"/>
@@ -10943,9 +10748,8 @@
       <c r="Q106" s="24"/>
       <c r="R106" s="24"/>
       <c r="S106" s="27"/>
-      <c r="T106" s="27"/>
-    </row>
-    <row r="107" customFormat="1" spans="6:20">
+    </row>
+    <row r="107" customFormat="1" spans="6:19">
       <c r="F107" s="24"/>
       <c r="H107" s="52"/>
       <c r="I107" s="52"/>
@@ -10959,9 +10763,8 @@
       <c r="Q107" s="24"/>
       <c r="R107" s="24"/>
       <c r="S107" s="27"/>
-      <c r="T107" s="27"/>
-    </row>
-    <row r="108" customFormat="1" spans="6:20">
+    </row>
+    <row r="108" customFormat="1" spans="6:19">
       <c r="F108" s="24"/>
       <c r="H108" s="52"/>
       <c r="I108" s="52"/>
@@ -10975,9 +10778,8 @@
       <c r="Q108" s="24"/>
       <c r="R108" s="24"/>
       <c r="S108" s="27"/>
-      <c r="T108" s="27"/>
-    </row>
-    <row r="109" customFormat="1" spans="6:20">
+    </row>
+    <row r="109" customFormat="1" spans="6:19">
       <c r="F109" s="24"/>
       <c r="H109" s="52"/>
       <c r="I109" s="52"/>
@@ -10991,9 +10793,8 @@
       <c r="Q109" s="24"/>
       <c r="R109" s="24"/>
       <c r="S109" s="27"/>
-      <c r="T109" s="27"/>
-    </row>
-    <row r="110" customFormat="1" spans="6:20">
+    </row>
+    <row r="110" customFormat="1" spans="6:19">
       <c r="F110" s="24"/>
       <c r="H110" s="52"/>
       <c r="I110" s="52"/>
@@ -11007,9 +10808,8 @@
       <c r="Q110" s="24"/>
       <c r="R110" s="24"/>
       <c r="S110" s="27"/>
-      <c r="T110" s="27"/>
-    </row>
-    <row r="111" customFormat="1" spans="6:20">
+    </row>
+    <row r="111" customFormat="1" spans="6:19">
       <c r="F111" s="24"/>
       <c r="H111" s="52"/>
       <c r="I111" s="52"/>
@@ -11023,9 +10823,8 @@
       <c r="Q111" s="24"/>
       <c r="R111" s="24"/>
       <c r="S111" s="27"/>
-      <c r="T111" s="27"/>
-    </row>
-    <row r="112" customFormat="1" spans="6:20">
+    </row>
+    <row r="112" customFormat="1" spans="6:19">
       <c r="F112" s="24"/>
       <c r="H112" s="52"/>
       <c r="I112" s="52"/>
@@ -11039,9 +10838,8 @@
       <c r="Q112" s="24"/>
       <c r="R112" s="24"/>
       <c r="S112" s="27"/>
-      <c r="T112" s="27"/>
-    </row>
-    <row r="113" customFormat="1" spans="6:20">
+    </row>
+    <row r="113" customFormat="1" spans="6:19">
       <c r="F113" s="24"/>
       <c r="H113" s="52"/>
       <c r="I113" s="52"/>
@@ -11055,9 +10853,8 @@
       <c r="Q113" s="24"/>
       <c r="R113" s="24"/>
       <c r="S113" s="27"/>
-      <c r="T113" s="27"/>
-    </row>
-    <row r="114" customFormat="1" spans="6:20">
+    </row>
+    <row r="114" customFormat="1" spans="6:19">
       <c r="F114" s="24"/>
       <c r="H114" s="52"/>
       <c r="I114" s="52"/>
@@ -11071,9 +10868,8 @@
       <c r="Q114" s="24"/>
       <c r="R114" s="24"/>
       <c r="S114" s="27"/>
-      <c r="T114" s="27"/>
-    </row>
-    <row r="115" customFormat="1" spans="6:20">
+    </row>
+    <row r="115" customFormat="1" spans="6:19">
       <c r="F115" s="24"/>
       <c r="H115" s="52"/>
       <c r="I115" s="52"/>
@@ -11087,9 +10883,8 @@
       <c r="Q115" s="24"/>
       <c r="R115" s="24"/>
       <c r="S115" s="27"/>
-      <c r="T115" s="27"/>
-    </row>
-    <row r="116" customFormat="1" spans="6:20">
+    </row>
+    <row r="116" customFormat="1" spans="6:19">
       <c r="F116" s="24"/>
       <c r="H116" s="52"/>
       <c r="I116" s="52"/>
@@ -11103,9 +10898,8 @@
       <c r="Q116" s="24"/>
       <c r="R116" s="24"/>
       <c r="S116" s="27"/>
-      <c r="T116" s="27"/>
-    </row>
-    <row r="117" customFormat="1" spans="6:20">
+    </row>
+    <row r="117" customFormat="1" spans="6:19">
       <c r="F117" s="24"/>
       <c r="H117" s="52"/>
       <c r="I117" s="52"/>
@@ -11119,9 +10913,8 @@
       <c r="Q117" s="24"/>
       <c r="R117" s="24"/>
       <c r="S117" s="27"/>
-      <c r="T117" s="27"/>
-    </row>
-    <row r="118" customFormat="1" spans="6:20">
+    </row>
+    <row r="118" customFormat="1" spans="6:19">
       <c r="F118" s="24"/>
       <c r="H118" s="52"/>
       <c r="I118" s="52"/>
@@ -11135,9 +10928,8 @@
       <c r="Q118" s="24"/>
       <c r="R118" s="24"/>
       <c r="S118" s="27"/>
-      <c r="T118" s="27"/>
-    </row>
-    <row r="119" customFormat="1" spans="6:20">
+    </row>
+    <row r="119" customFormat="1" spans="6:19">
       <c r="F119" s="24"/>
       <c r="H119" s="52"/>
       <c r="I119" s="52"/>
@@ -11151,9 +10943,8 @@
       <c r="Q119" s="24"/>
       <c r="R119" s="24"/>
       <c r="S119" s="27"/>
-      <c r="T119" s="27"/>
-    </row>
-    <row r="120" customFormat="1" spans="6:20">
+    </row>
+    <row r="120" customFormat="1" spans="6:19">
       <c r="F120" s="24"/>
       <c r="H120" s="52"/>
       <c r="I120" s="52"/>
@@ -11167,9 +10958,8 @@
       <c r="Q120" s="24"/>
       <c r="R120" s="24"/>
       <c r="S120" s="27"/>
-      <c r="T120" s="27"/>
-    </row>
-    <row r="121" customFormat="1" spans="6:20">
+    </row>
+    <row r="121" customFormat="1" spans="6:19">
       <c r="F121" s="24"/>
       <c r="H121" s="52"/>
       <c r="I121" s="52"/>
@@ -11183,9 +10973,8 @@
       <c r="Q121" s="24"/>
       <c r="R121" s="24"/>
       <c r="S121" s="27"/>
-      <c r="T121" s="27"/>
-    </row>
-    <row r="122" customFormat="1" spans="6:20">
+    </row>
+    <row r="122" customFormat="1" spans="6:19">
       <c r="F122" s="24"/>
       <c r="H122" s="52"/>
       <c r="I122" s="52"/>
@@ -11199,9 +10988,8 @@
       <c r="Q122" s="24"/>
       <c r="R122" s="24"/>
       <c r="S122" s="27"/>
-      <c r="T122" s="27"/>
-    </row>
-    <row r="123" customFormat="1" spans="6:20">
+    </row>
+    <row r="123" customFormat="1" spans="6:19">
       <c r="F123" s="24"/>
       <c r="H123" s="52"/>
       <c r="I123" s="52"/>
@@ -11215,9 +11003,8 @@
       <c r="Q123" s="24"/>
       <c r="R123" s="24"/>
       <c r="S123" s="27"/>
-      <c r="T123" s="27"/>
-    </row>
-    <row r="124" customFormat="1" spans="6:20">
+    </row>
+    <row r="124" customFormat="1" spans="6:19">
       <c r="F124" s="24"/>
       <c r="H124" s="52"/>
       <c r="I124" s="52"/>
@@ -11231,9 +11018,8 @@
       <c r="Q124" s="24"/>
       <c r="R124" s="24"/>
       <c r="S124" s="27"/>
-      <c r="T124" s="27"/>
-    </row>
-    <row r="125" customFormat="1" spans="6:20">
+    </row>
+    <row r="125" customFormat="1" spans="6:19">
       <c r="F125" s="24"/>
       <c r="H125" s="52"/>
       <c r="I125" s="52"/>
@@ -11247,9 +11033,8 @@
       <c r="Q125" s="24"/>
       <c r="R125" s="24"/>
       <c r="S125" s="27"/>
-      <c r="T125" s="27"/>
-    </row>
-    <row r="126" customFormat="1" spans="6:20">
+    </row>
+    <row r="126" customFormat="1" spans="6:19">
       <c r="F126" s="24"/>
       <c r="H126" s="52"/>
       <c r="I126" s="52"/>
@@ -11263,9 +11048,8 @@
       <c r="Q126" s="24"/>
       <c r="R126" s="24"/>
       <c r="S126" s="27"/>
-      <c r="T126" s="27"/>
-    </row>
-    <row r="127" customFormat="1" spans="6:20">
+    </row>
+    <row r="127" customFormat="1" spans="6:19">
       <c r="F127" s="24"/>
       <c r="H127" s="52"/>
       <c r="I127" s="52"/>
@@ -11279,9 +11063,8 @@
       <c r="Q127" s="24"/>
       <c r="R127" s="24"/>
       <c r="S127" s="27"/>
-      <c r="T127" s="27"/>
-    </row>
-    <row r="128" customFormat="1" spans="6:20">
+    </row>
+    <row r="128" customFormat="1" spans="6:19">
       <c r="F128" s="24"/>
       <c r="H128" s="52"/>
       <c r="I128" s="52"/>
@@ -11295,9 +11078,8 @@
       <c r="Q128" s="24"/>
       <c r="R128" s="24"/>
       <c r="S128" s="27"/>
-      <c r="T128" s="27"/>
-    </row>
-    <row r="129" customFormat="1" spans="6:20">
+    </row>
+    <row r="129" customFormat="1" spans="6:19">
       <c r="F129" s="24"/>
       <c r="H129" s="52"/>
       <c r="I129" s="52"/>
@@ -11311,9 +11093,8 @@
       <c r="Q129" s="24"/>
       <c r="R129" s="24"/>
       <c r="S129" s="27"/>
-      <c r="T129" s="27"/>
-    </row>
-    <row r="130" customFormat="1" spans="6:20">
+    </row>
+    <row r="130" customFormat="1" spans="6:19">
       <c r="F130" s="24"/>
       <c r="H130" s="52"/>
       <c r="I130" s="52"/>
@@ -11327,9 +11108,8 @@
       <c r="Q130" s="24"/>
       <c r="R130" s="24"/>
       <c r="S130" s="27"/>
-      <c r="T130" s="27"/>
-    </row>
-    <row r="131" customFormat="1" spans="6:20">
+    </row>
+    <row r="131" customFormat="1" spans="6:19">
       <c r="F131" s="24"/>
       <c r="H131" s="52"/>
       <c r="I131" s="52"/>
@@ -11343,9 +11123,8 @@
       <c r="Q131" s="24"/>
       <c r="R131" s="24"/>
       <c r="S131" s="27"/>
-      <c r="T131" s="27"/>
-    </row>
-    <row r="132" customFormat="1" spans="6:20">
+    </row>
+    <row r="132" customFormat="1" spans="6:19">
       <c r="F132" s="24"/>
       <c r="H132" s="52"/>
       <c r="I132" s="52"/>
@@ -11359,9 +11138,8 @@
       <c r="Q132" s="24"/>
       <c r="R132" s="24"/>
       <c r="S132" s="27"/>
-      <c r="T132" s="27"/>
-    </row>
-    <row r="133" customFormat="1" spans="6:20">
+    </row>
+    <row r="133" customFormat="1" spans="6:19">
       <c r="F133" s="24"/>
       <c r="H133" s="52"/>
       <c r="I133" s="52"/>
@@ -11375,9 +11153,8 @@
       <c r="Q133" s="24"/>
       <c r="R133" s="24"/>
       <c r="S133" s="27"/>
-      <c r="T133" s="27"/>
-    </row>
-    <row r="134" customFormat="1" spans="6:20">
+    </row>
+    <row r="134" customFormat="1" spans="6:19">
       <c r="F134" s="24"/>
       <c r="H134" s="52"/>
       <c r="I134" s="52"/>
@@ -11391,9 +11168,8 @@
       <c r="Q134" s="24"/>
       <c r="R134" s="24"/>
       <c r="S134" s="27"/>
-      <c r="T134" s="27"/>
-    </row>
-    <row r="135" customFormat="1" spans="6:20">
+    </row>
+    <row r="135" customFormat="1" spans="6:19">
       <c r="F135" s="24"/>
       <c r="H135" s="52"/>
       <c r="I135" s="52"/>
@@ -11407,9 +11183,8 @@
       <c r="Q135" s="24"/>
       <c r="R135" s="24"/>
       <c r="S135" s="27"/>
-      <c r="T135" s="27"/>
-    </row>
-    <row r="136" customFormat="1" spans="6:20">
+    </row>
+    <row r="136" customFormat="1" spans="6:19">
       <c r="F136" s="24"/>
       <c r="H136" s="52"/>
       <c r="I136" s="52"/>
@@ -11423,9 +11198,8 @@
       <c r="Q136" s="24"/>
       <c r="R136" s="24"/>
       <c r="S136" s="27"/>
-      <c r="T136" s="27"/>
-    </row>
-    <row r="137" customFormat="1" spans="6:20">
+    </row>
+    <row r="137" customFormat="1" spans="6:19">
       <c r="F137" s="24"/>
       <c r="H137" s="52"/>
       <c r="I137" s="52"/>
@@ -11439,9 +11213,8 @@
       <c r="Q137" s="24"/>
       <c r="R137" s="24"/>
       <c r="S137" s="27"/>
-      <c r="T137" s="27"/>
-    </row>
-    <row r="138" customFormat="1" spans="6:20">
+    </row>
+    <row r="138" customFormat="1" spans="6:19">
       <c r="F138" s="24"/>
       <c r="H138" s="52"/>
       <c r="I138" s="52"/>
@@ -11455,9 +11228,8 @@
       <c r="Q138" s="24"/>
       <c r="R138" s="24"/>
       <c r="S138" s="27"/>
-      <c r="T138" s="27"/>
-    </row>
-    <row r="139" customFormat="1" spans="6:20">
+    </row>
+    <row r="139" customFormat="1" spans="6:19">
       <c r="F139" s="24"/>
       <c r="H139" s="52"/>
       <c r="I139" s="52"/>
@@ -11471,9 +11243,8 @@
       <c r="Q139" s="24"/>
       <c r="R139" s="24"/>
       <c r="S139" s="27"/>
-      <c r="T139" s="27"/>
-    </row>
-    <row r="140" customFormat="1" spans="6:20">
+    </row>
+    <row r="140" customFormat="1" spans="6:19">
       <c r="F140" s="24"/>
       <c r="H140" s="52"/>
       <c r="I140" s="52"/>
@@ -11487,9 +11258,8 @@
       <c r="Q140" s="24"/>
       <c r="R140" s="24"/>
       <c r="S140" s="27"/>
-      <c r="T140" s="27"/>
-    </row>
-    <row r="141" customFormat="1" spans="6:20">
+    </row>
+    <row r="141" customFormat="1" spans="6:19">
       <c r="F141" s="24"/>
       <c r="H141" s="52"/>
       <c r="I141" s="52"/>
@@ -11503,9 +11273,8 @@
       <c r="Q141" s="24"/>
       <c r="R141" s="24"/>
       <c r="S141" s="27"/>
-      <c r="T141" s="27"/>
-    </row>
-    <row r="142" customFormat="1" spans="6:20">
+    </row>
+    <row r="142" customFormat="1" spans="6:19">
       <c r="F142" s="24"/>
       <c r="H142" s="52"/>
       <c r="I142" s="52"/>
@@ -11519,9 +11288,8 @@
       <c r="Q142" s="24"/>
       <c r="R142" s="24"/>
       <c r="S142" s="27"/>
-      <c r="T142" s="27"/>
-    </row>
-    <row r="143" customFormat="1" spans="6:20">
+    </row>
+    <row r="143" customFormat="1" spans="6:19">
       <c r="F143" s="24"/>
       <c r="H143" s="52"/>
       <c r="I143" s="52"/>
@@ -11535,9 +11303,8 @@
       <c r="Q143" s="24"/>
       <c r="R143" s="24"/>
       <c r="S143" s="27"/>
-      <c r="T143" s="27"/>
-    </row>
-    <row r="144" customFormat="1" spans="6:20">
+    </row>
+    <row r="144" customFormat="1" spans="6:19">
       <c r="F144" s="24"/>
       <c r="H144" s="52"/>
       <c r="I144" s="52"/>
@@ -11551,9 +11318,8 @@
       <c r="Q144" s="24"/>
       <c r="R144" s="24"/>
       <c r="S144" s="27"/>
-      <c r="T144" s="27"/>
-    </row>
-    <row r="145" customFormat="1" spans="6:20">
+    </row>
+    <row r="145" customFormat="1" spans="6:19">
       <c r="F145" s="24"/>
       <c r="H145" s="52"/>
       <c r="I145" s="52"/>
@@ -11567,9 +11333,8 @@
       <c r="Q145" s="24"/>
       <c r="R145" s="24"/>
       <c r="S145" s="27"/>
-      <c r="T145" s="27"/>
-    </row>
-    <row r="146" customFormat="1" spans="6:20">
+    </row>
+    <row r="146" customFormat="1" spans="6:19">
       <c r="F146" s="24"/>
       <c r="H146" s="52"/>
       <c r="I146" s="52"/>
@@ -11583,9 +11348,8 @@
       <c r="Q146" s="24"/>
       <c r="R146" s="24"/>
       <c r="S146" s="27"/>
-      <c r="T146" s="27"/>
-    </row>
-    <row r="147" customFormat="1" spans="6:20">
+    </row>
+    <row r="147" customFormat="1" spans="6:19">
       <c r="F147" s="24"/>
       <c r="H147" s="52"/>
       <c r="I147" s="52"/>
@@ -11599,9 +11363,8 @@
       <c r="Q147" s="24"/>
       <c r="R147" s="24"/>
       <c r="S147" s="27"/>
-      <c r="T147" s="27"/>
-    </row>
-    <row r="148" customFormat="1" spans="6:20">
+    </row>
+    <row r="148" customFormat="1" spans="6:19">
       <c r="F148" s="24"/>
       <c r="H148" s="52"/>
       <c r="I148" s="52"/>
@@ -11615,9 +11378,8 @@
       <c r="Q148" s="24"/>
       <c r="R148" s="24"/>
       <c r="S148" s="27"/>
-      <c r="T148" s="27"/>
-    </row>
-    <row r="149" customFormat="1" spans="6:20">
+    </row>
+    <row r="149" customFormat="1" spans="6:19">
       <c r="F149" s="24"/>
       <c r="H149" s="52"/>
       <c r="I149" s="52"/>
@@ -11631,9 +11393,8 @@
       <c r="Q149" s="24"/>
       <c r="R149" s="24"/>
       <c r="S149" s="27"/>
-      <c r="T149" s="27"/>
-    </row>
-    <row r="150" customFormat="1" spans="6:20">
+    </row>
+    <row r="150" customFormat="1" spans="6:19">
       <c r="F150" s="24"/>
       <c r="H150" s="52"/>
       <c r="I150" s="52"/>
@@ -11647,9 +11408,8 @@
       <c r="Q150" s="24"/>
       <c r="R150" s="24"/>
       <c r="S150" s="27"/>
-      <c r="T150" s="27"/>
-    </row>
-    <row r="151" customFormat="1" spans="6:20">
+    </row>
+    <row r="151" customFormat="1" spans="6:19">
       <c r="F151" s="24"/>
       <c r="H151" s="52"/>
       <c r="I151" s="52"/>
@@ -11663,9 +11423,8 @@
       <c r="Q151" s="24"/>
       <c r="R151" s="24"/>
       <c r="S151" s="27"/>
-      <c r="T151" s="27"/>
-    </row>
-    <row r="152" customFormat="1" spans="6:20">
+    </row>
+    <row r="152" customFormat="1" spans="6:19">
       <c r="F152" s="24"/>
       <c r="H152" s="52"/>
       <c r="I152" s="52"/>
@@ -11679,9 +11438,8 @@
       <c r="Q152" s="24"/>
       <c r="R152" s="24"/>
       <c r="S152" s="27"/>
-      <c r="T152" s="27"/>
-    </row>
-    <row r="153" customFormat="1" spans="6:20">
+    </row>
+    <row r="153" customFormat="1" spans="6:19">
       <c r="F153" s="24"/>
       <c r="H153" s="52"/>
       <c r="I153" s="52"/>
@@ -11695,9 +11453,8 @@
       <c r="Q153" s="24"/>
       <c r="R153" s="24"/>
       <c r="S153" s="27"/>
-      <c r="T153" s="27"/>
-    </row>
-    <row r="154" customFormat="1" spans="6:20">
+    </row>
+    <row r="154" customFormat="1" spans="6:19">
       <c r="F154" s="24"/>
       <c r="H154" s="52"/>
       <c r="I154" s="52"/>
@@ -11711,9 +11468,8 @@
       <c r="Q154" s="24"/>
       <c r="R154" s="24"/>
       <c r="S154" s="27"/>
-      <c r="T154" s="27"/>
-    </row>
-    <row r="155" customFormat="1" spans="6:20">
+    </row>
+    <row r="155" customFormat="1" spans="6:19">
       <c r="F155" s="24"/>
       <c r="H155" s="52"/>
       <c r="I155" s="52"/>
@@ -11727,9 +11483,8 @@
       <c r="Q155" s="24"/>
       <c r="R155" s="24"/>
       <c r="S155" s="27"/>
-      <c r="T155" s="27"/>
-    </row>
-    <row r="156" customFormat="1" spans="6:20">
+    </row>
+    <row r="156" customFormat="1" spans="6:19">
       <c r="F156" s="24"/>
       <c r="H156" s="52"/>
       <c r="I156" s="52"/>
@@ -11743,9 +11498,8 @@
       <c r="Q156" s="24"/>
       <c r="R156" s="24"/>
       <c r="S156" s="27"/>
-      <c r="T156" s="27"/>
-    </row>
-    <row r="157" customFormat="1" spans="6:20">
+    </row>
+    <row r="157" customFormat="1" spans="6:19">
       <c r="F157" s="24"/>
       <c r="H157" s="52"/>
       <c r="I157" s="52"/>
@@ -11759,9 +11513,8 @@
       <c r="Q157" s="24"/>
       <c r="R157" s="24"/>
       <c r="S157" s="27"/>
-      <c r="T157" s="27"/>
-    </row>
-    <row r="158" customFormat="1" spans="6:20">
+    </row>
+    <row r="158" customFormat="1" spans="6:19">
       <c r="F158" s="24"/>
       <c r="H158" s="52"/>
       <c r="I158" s="52"/>
@@ -11775,9 +11528,8 @@
       <c r="Q158" s="24"/>
       <c r="R158" s="24"/>
       <c r="S158" s="27"/>
-      <c r="T158" s="27"/>
-    </row>
-    <row r="159" customFormat="1" spans="6:20">
+    </row>
+    <row r="159" customFormat="1" spans="6:19">
       <c r="F159" s="24"/>
       <c r="H159" s="52"/>
       <c r="I159" s="52"/>
@@ -11791,9 +11543,8 @@
       <c r="Q159" s="24"/>
       <c r="R159" s="24"/>
       <c r="S159" s="27"/>
-      <c r="T159" s="27"/>
-    </row>
-    <row r="160" customFormat="1" spans="6:20">
+    </row>
+    <row r="160" customFormat="1" spans="6:19">
       <c r="F160" s="24"/>
       <c r="H160" s="52"/>
       <c r="I160" s="52"/>
@@ -11807,9 +11558,8 @@
       <c r="Q160" s="24"/>
       <c r="R160" s="24"/>
       <c r="S160" s="27"/>
-      <c r="T160" s="27"/>
-    </row>
-    <row r="161" customFormat="1" spans="6:20">
+    </row>
+    <row r="161" customFormat="1" spans="6:19">
       <c r="F161" s="24"/>
       <c r="H161" s="52"/>
       <c r="I161" s="52"/>
@@ -11823,9 +11573,8 @@
       <c r="Q161" s="24"/>
       <c r="R161" s="24"/>
       <c r="S161" s="27"/>
-      <c r="T161" s="27"/>
-    </row>
-    <row r="162" customFormat="1" spans="6:20">
+    </row>
+    <row r="162" customFormat="1" spans="6:19">
       <c r="F162" s="24"/>
       <c r="H162" s="52"/>
       <c r="I162" s="52"/>
@@ -11839,9 +11588,8 @@
       <c r="Q162" s="24"/>
       <c r="R162" s="24"/>
       <c r="S162" s="27"/>
-      <c r="T162" s="27"/>
-    </row>
-    <row r="163" customFormat="1" spans="6:20">
+    </row>
+    <row r="163" customFormat="1" spans="6:19">
       <c r="F163" s="24"/>
       <c r="H163" s="52"/>
       <c r="I163" s="52"/>
@@ -11855,9 +11603,8 @@
       <c r="Q163" s="24"/>
       <c r="R163" s="24"/>
       <c r="S163" s="27"/>
-      <c r="T163" s="27"/>
-    </row>
-    <row r="164" customFormat="1" spans="6:20">
+    </row>
+    <row r="164" customFormat="1" spans="6:19">
       <c r="F164" s="24"/>
       <c r="H164" s="52"/>
       <c r="I164" s="52"/>
@@ -11871,9 +11618,8 @@
       <c r="Q164" s="24"/>
       <c r="R164" s="24"/>
       <c r="S164" s="27"/>
-      <c r="T164" s="27"/>
-    </row>
-    <row r="165" customFormat="1" spans="6:20">
+    </row>
+    <row r="165" customFormat="1" spans="6:19">
       <c r="F165" s="24"/>
       <c r="H165" s="52"/>
       <c r="I165" s="52"/>
@@ -11887,9 +11633,8 @@
       <c r="Q165" s="24"/>
       <c r="R165" s="24"/>
       <c r="S165" s="27"/>
-      <c r="T165" s="27"/>
-    </row>
-    <row r="166" customFormat="1" spans="6:20">
+    </row>
+    <row r="166" customFormat="1" spans="6:19">
       <c r="F166" s="24"/>
       <c r="H166" s="52"/>
       <c r="I166" s="52"/>
@@ -11903,9 +11648,8 @@
       <c r="Q166" s="24"/>
       <c r="R166" s="24"/>
       <c r="S166" s="27"/>
-      <c r="T166" s="27"/>
-    </row>
-    <row r="167" customFormat="1" spans="6:20">
+    </row>
+    <row r="167" customFormat="1" spans="6:19">
       <c r="F167" s="24"/>
       <c r="H167" s="52"/>
       <c r="I167" s="52"/>
@@ -11919,9 +11663,8 @@
       <c r="Q167" s="24"/>
       <c r="R167" s="24"/>
       <c r="S167" s="27"/>
-      <c r="T167" s="27"/>
-    </row>
-    <row r="168" customFormat="1" spans="6:20">
+    </row>
+    <row r="168" customFormat="1" spans="6:19">
       <c r="F168" s="24"/>
       <c r="H168" s="52"/>
       <c r="I168" s="52"/>
@@ -11935,9 +11678,8 @@
       <c r="Q168" s="24"/>
       <c r="R168" s="24"/>
       <c r="S168" s="27"/>
-      <c r="T168" s="27"/>
-    </row>
-    <row r="169" customFormat="1" spans="6:20">
+    </row>
+    <row r="169" customFormat="1" spans="6:19">
       <c r="F169" s="24"/>
       <c r="H169" s="52"/>
       <c r="I169" s="52"/>
@@ -11951,9 +11693,8 @@
       <c r="Q169" s="24"/>
       <c r="R169" s="24"/>
       <c r="S169" s="27"/>
-      <c r="T169" s="27"/>
-    </row>
-    <row r="170" customFormat="1" spans="6:20">
+    </row>
+    <row r="170" customFormat="1" spans="6:19">
       <c r="F170" s="24"/>
       <c r="H170" s="52"/>
       <c r="I170" s="52"/>
@@ -11967,9 +11708,8 @@
       <c r="Q170" s="24"/>
       <c r="R170" s="24"/>
       <c r="S170" s="27"/>
-      <c r="T170" s="27"/>
-    </row>
-    <row r="171" customFormat="1" spans="6:20">
+    </row>
+    <row r="171" customFormat="1" spans="6:19">
       <c r="F171" s="24"/>
       <c r="H171" s="52"/>
       <c r="I171" s="52"/>
@@ -11983,9 +11723,8 @@
       <c r="Q171" s="24"/>
       <c r="R171" s="24"/>
       <c r="S171" s="27"/>
-      <c r="T171" s="27"/>
-    </row>
-    <row r="172" customFormat="1" spans="6:20">
+    </row>
+    <row r="172" customFormat="1" spans="6:19">
       <c r="F172" s="24"/>
       <c r="H172" s="52"/>
       <c r="I172" s="52"/>
@@ -11999,9 +11738,8 @@
       <c r="Q172" s="24"/>
       <c r="R172" s="24"/>
       <c r="S172" s="27"/>
-      <c r="T172" s="27"/>
-    </row>
-    <row r="173" customFormat="1" spans="6:20">
+    </row>
+    <row r="173" customFormat="1" spans="6:19">
       <c r="F173" s="24"/>
       <c r="H173" s="52"/>
       <c r="I173" s="52"/>
@@ -12015,9 +11753,8 @@
       <c r="Q173" s="24"/>
       <c r="R173" s="24"/>
       <c r="S173" s="27"/>
-      <c r="T173" s="27"/>
-    </row>
-    <row r="174" customFormat="1" spans="6:20">
+    </row>
+    <row r="174" customFormat="1" spans="6:19">
       <c r="F174" s="24"/>
       <c r="H174" s="52"/>
       <c r="I174" s="52"/>
@@ -12031,9 +11768,8 @@
       <c r="Q174" s="24"/>
       <c r="R174" s="24"/>
       <c r="S174" s="27"/>
-      <c r="T174" s="27"/>
-    </row>
-    <row r="175" customFormat="1" spans="6:20">
+    </row>
+    <row r="175" customFormat="1" spans="6:19">
       <c r="F175" s="24"/>
       <c r="H175" s="52"/>
       <c r="I175" s="52"/>
@@ -12047,9 +11783,8 @@
       <c r="Q175" s="24"/>
       <c r="R175" s="24"/>
       <c r="S175" s="27"/>
-      <c r="T175" s="27"/>
-    </row>
-    <row r="176" customFormat="1" spans="6:20">
+    </row>
+    <row r="176" customFormat="1" spans="6:19">
       <c r="F176" s="24"/>
       <c r="H176" s="52"/>
       <c r="I176" s="52"/>
@@ -12063,9 +11798,8 @@
       <c r="Q176" s="24"/>
       <c r="R176" s="24"/>
       <c r="S176" s="27"/>
-      <c r="T176" s="27"/>
-    </row>
-    <row r="177" customFormat="1" spans="6:20">
+    </row>
+    <row r="177" customFormat="1" spans="6:19">
       <c r="F177" s="24"/>
       <c r="H177" s="52"/>
       <c r="I177" s="52"/>
@@ -12079,9 +11813,8 @@
       <c r="Q177" s="24"/>
       <c r="R177" s="24"/>
       <c r="S177" s="27"/>
-      <c r="T177" s="27"/>
-    </row>
-    <row r="178" customFormat="1" spans="6:20">
+    </row>
+    <row r="178" customFormat="1" spans="6:19">
       <c r="F178" s="24"/>
       <c r="H178" s="52"/>
       <c r="I178" s="52"/>
@@ -12095,9 +11828,8 @@
       <c r="Q178" s="24"/>
       <c r="R178" s="24"/>
       <c r="S178" s="27"/>
-      <c r="T178" s="27"/>
-    </row>
-    <row r="179" customFormat="1" spans="6:20">
+    </row>
+    <row r="179" customFormat="1" spans="6:19">
       <c r="F179" s="24"/>
       <c r="H179" s="52"/>
       <c r="I179" s="52"/>
@@ -12111,9 +11843,8 @@
       <c r="Q179" s="24"/>
       <c r="R179" s="24"/>
       <c r="S179" s="27"/>
-      <c r="T179" s="27"/>
-    </row>
-    <row r="180" customFormat="1" spans="6:20">
+    </row>
+    <row r="180" customFormat="1" spans="6:19">
       <c r="F180" s="24"/>
       <c r="H180" s="52"/>
       <c r="I180" s="52"/>
@@ -12127,9 +11858,8 @@
       <c r="Q180" s="24"/>
       <c r="R180" s="24"/>
       <c r="S180" s="27"/>
-      <c r="T180" s="27"/>
-    </row>
-    <row r="181" customFormat="1" spans="6:20">
+    </row>
+    <row r="181" customFormat="1" spans="6:19">
       <c r="F181" s="24"/>
       <c r="H181" s="52"/>
       <c r="I181" s="52"/>
@@ -12143,9 +11873,8 @@
       <c r="Q181" s="24"/>
       <c r="R181" s="24"/>
       <c r="S181" s="27"/>
-      <c r="T181" s="27"/>
-    </row>
-    <row r="182" customFormat="1" spans="6:20">
+    </row>
+    <row r="182" customFormat="1" spans="6:19">
       <c r="F182" s="24"/>
       <c r="H182" s="52"/>
       <c r="I182" s="52"/>
@@ -12159,9 +11888,8 @@
       <c r="Q182" s="24"/>
       <c r="R182" s="24"/>
       <c r="S182" s="27"/>
-      <c r="T182" s="27"/>
-    </row>
-    <row r="183" customFormat="1" spans="6:20">
+    </row>
+    <row r="183" customFormat="1" spans="6:19">
       <c r="F183" s="24"/>
       <c r="H183" s="52"/>
       <c r="I183" s="52"/>
@@ -12175,9 +11903,8 @@
       <c r="Q183" s="24"/>
       <c r="R183" s="24"/>
       <c r="S183" s="27"/>
-      <c r="T183" s="27"/>
-    </row>
-    <row r="184" customFormat="1" spans="6:20">
+    </row>
+    <row r="184" customFormat="1" spans="6:19">
       <c r="F184" s="24"/>
       <c r="H184" s="52"/>
       <c r="I184" s="52"/>
@@ -12191,9 +11918,8 @@
       <c r="Q184" s="24"/>
       <c r="R184" s="24"/>
       <c r="S184" s="27"/>
-      <c r="T184" s="27"/>
-    </row>
-    <row r="185" customFormat="1" spans="6:20">
+    </row>
+    <row r="185" customFormat="1" spans="6:19">
       <c r="F185" s="24"/>
       <c r="H185" s="52"/>
       <c r="I185" s="52"/>
@@ -12207,9 +11933,8 @@
       <c r="Q185" s="24"/>
       <c r="R185" s="24"/>
       <c r="S185" s="27"/>
-      <c r="T185" s="27"/>
-    </row>
-    <row r="186" customFormat="1" spans="6:20">
+    </row>
+    <row r="186" customFormat="1" spans="6:19">
       <c r="F186" s="24"/>
       <c r="H186" s="52"/>
       <c r="I186" s="52"/>
@@ -12223,9 +11948,8 @@
       <c r="Q186" s="24"/>
       <c r="R186" s="24"/>
       <c r="S186" s="27"/>
-      <c r="T186" s="27"/>
-    </row>
-    <row r="187" customFormat="1" spans="6:20">
+    </row>
+    <row r="187" customFormat="1" spans="6:19">
       <c r="F187" s="24"/>
       <c r="H187" s="52"/>
       <c r="I187" s="52"/>
@@ -12239,9 +11963,8 @@
       <c r="Q187" s="24"/>
       <c r="R187" s="24"/>
       <c r="S187" s="27"/>
-      <c r="T187" s="27"/>
-    </row>
-    <row r="188" customFormat="1" spans="6:20">
+    </row>
+    <row r="188" customFormat="1" spans="6:19">
       <c r="F188" s="24"/>
       <c r="H188" s="52"/>
       <c r="I188" s="52"/>
@@ -12255,9 +11978,8 @@
       <c r="Q188" s="24"/>
       <c r="R188" s="24"/>
       <c r="S188" s="27"/>
-      <c r="T188" s="27"/>
-    </row>
-    <row r="189" customFormat="1" spans="6:20">
+    </row>
+    <row r="189" customFormat="1" spans="6:19">
       <c r="F189" s="24"/>
       <c r="H189" s="52"/>
       <c r="I189" s="52"/>
@@ -12271,9 +11993,8 @@
       <c r="Q189" s="24"/>
       <c r="R189" s="24"/>
       <c r="S189" s="27"/>
-      <c r="T189" s="27"/>
-    </row>
-    <row r="190" customFormat="1" spans="6:20">
+    </row>
+    <row r="190" customFormat="1" spans="6:19">
       <c r="F190" s="24"/>
       <c r="H190" s="52"/>
       <c r="I190" s="52"/>
@@ -12287,9 +12008,8 @@
       <c r="Q190" s="24"/>
       <c r="R190" s="24"/>
       <c r="S190" s="27"/>
-      <c r="T190" s="27"/>
-    </row>
-    <row r="191" customFormat="1" spans="6:20">
+    </row>
+    <row r="191" customFormat="1" spans="6:19">
       <c r="F191" s="24"/>
       <c r="H191" s="52"/>
       <c r="I191" s="52"/>
@@ -12303,9 +12023,8 @@
       <c r="Q191" s="24"/>
       <c r="R191" s="24"/>
       <c r="S191" s="27"/>
-      <c r="T191" s="27"/>
-    </row>
-    <row r="192" customFormat="1" spans="6:20">
+    </row>
+    <row r="192" customFormat="1" spans="6:19">
       <c r="F192" s="24"/>
       <c r="H192" s="52"/>
       <c r="I192" s="52"/>
@@ -12319,9 +12038,8 @@
       <c r="Q192" s="24"/>
       <c r="R192" s="24"/>
       <c r="S192" s="27"/>
-      <c r="T192" s="27"/>
-    </row>
-    <row r="193" customFormat="1" spans="6:20">
+    </row>
+    <row r="193" customFormat="1" spans="6:19">
       <c r="F193" s="24"/>
       <c r="H193" s="52"/>
       <c r="I193" s="52"/>
@@ -12335,9 +12053,8 @@
       <c r="Q193" s="24"/>
       <c r="R193" s="24"/>
       <c r="S193" s="27"/>
-      <c r="T193" s="27"/>
-    </row>
-    <row r="194" customFormat="1" spans="6:20">
+    </row>
+    <row r="194" customFormat="1" spans="6:19">
       <c r="F194" s="24"/>
       <c r="H194" s="52"/>
       <c r="I194" s="52"/>
@@ -12351,9 +12068,8 @@
       <c r="Q194" s="24"/>
       <c r="R194" s="24"/>
       <c r="S194" s="27"/>
-      <c r="T194" s="27"/>
-    </row>
-    <row r="195" customFormat="1" spans="6:20">
+    </row>
+    <row r="195" customFormat="1" spans="6:19">
       <c r="F195" s="24"/>
       <c r="H195" s="52"/>
       <c r="I195" s="52"/>
@@ -12367,9 +12083,8 @@
       <c r="Q195" s="24"/>
       <c r="R195" s="24"/>
       <c r="S195" s="27"/>
-      <c r="T195" s="27"/>
-    </row>
-    <row r="196" customFormat="1" spans="6:20">
+    </row>
+    <row r="196" customFormat="1" spans="6:19">
       <c r="F196" s="24"/>
       <c r="H196" s="52"/>
       <c r="I196" s="52"/>
@@ -12383,9 +12098,8 @@
       <c r="Q196" s="24"/>
       <c r="R196" s="24"/>
       <c r="S196" s="27"/>
-      <c r="T196" s="27"/>
-    </row>
-    <row r="197" customFormat="1" spans="6:20">
+    </row>
+    <row r="197" customFormat="1" spans="6:19">
       <c r="F197" s="24"/>
       <c r="H197" s="52"/>
       <c r="I197" s="52"/>
@@ -12399,9 +12113,8 @@
       <c r="Q197" s="24"/>
       <c r="R197" s="24"/>
       <c r="S197" s="27"/>
-      <c r="T197" s="27"/>
-    </row>
-    <row r="198" customFormat="1" spans="6:20">
+    </row>
+    <row r="198" customFormat="1" spans="6:19">
       <c r="F198" s="24"/>
       <c r="H198" s="52"/>
       <c r="I198" s="52"/>
@@ -12415,9 +12128,8 @@
       <c r="Q198" s="24"/>
       <c r="R198" s="24"/>
       <c r="S198" s="27"/>
-      <c r="T198" s="27"/>
-    </row>
-    <row r="199" customFormat="1" spans="6:20">
+    </row>
+    <row r="199" customFormat="1" spans="6:19">
       <c r="F199" s="24"/>
       <c r="H199" s="52"/>
       <c r="I199" s="52"/>
@@ -12431,9 +12143,8 @@
       <c r="Q199" s="24"/>
       <c r="R199" s="24"/>
       <c r="S199" s="27"/>
-      <c r="T199" s="27"/>
-    </row>
-    <row r="200" customFormat="1" spans="6:20">
+    </row>
+    <row r="200" customFormat="1" spans="6:19">
       <c r="F200" s="24"/>
       <c r="H200" s="52"/>
       <c r="I200" s="52"/>
@@ -12447,9 +12158,8 @@
       <c r="Q200" s="24"/>
       <c r="R200" s="24"/>
       <c r="S200" s="27"/>
-      <c r="T200" s="27"/>
-    </row>
-    <row r="201" customFormat="1" spans="6:20">
+    </row>
+    <row r="201" customFormat="1" spans="6:19">
       <c r="F201" s="24"/>
       <c r="H201" s="52"/>
       <c r="I201" s="52"/>
@@ -12463,9 +12173,8 @@
       <c r="Q201" s="24"/>
       <c r="R201" s="24"/>
       <c r="S201" s="27"/>
-      <c r="T201" s="27"/>
-    </row>
-    <row r="202" customFormat="1" spans="6:20">
+    </row>
+    <row r="202" customFormat="1" spans="6:19">
       <c r="F202" s="24"/>
       <c r="H202" s="52"/>
       <c r="I202" s="52"/>
@@ -12479,9 +12188,8 @@
       <c r="Q202" s="24"/>
       <c r="R202" s="24"/>
       <c r="S202" s="27"/>
-      <c r="T202" s="27"/>
-    </row>
-    <row r="203" customFormat="1" spans="6:20">
+    </row>
+    <row r="203" customFormat="1" spans="6:19">
       <c r="F203" s="24"/>
       <c r="H203" s="52"/>
       <c r="I203" s="52"/>
@@ -12495,9 +12203,8 @@
       <c r="Q203" s="24"/>
       <c r="R203" s="24"/>
       <c r="S203" s="27"/>
-      <c r="T203" s="27"/>
-    </row>
-    <row r="204" customFormat="1" spans="6:20">
+    </row>
+    <row r="204" customFormat="1" spans="6:19">
       <c r="F204" s="24"/>
       <c r="H204" s="52"/>
       <c r="I204" s="52"/>
@@ -12511,9 +12218,8 @@
       <c r="Q204" s="24"/>
       <c r="R204" s="24"/>
       <c r="S204" s="27"/>
-      <c r="T204" s="27"/>
-    </row>
-    <row r="205" customFormat="1" spans="6:20">
+    </row>
+    <row r="205" customFormat="1" spans="6:19">
       <c r="F205" s="24"/>
       <c r="H205" s="52"/>
       <c r="I205" s="52"/>
@@ -12527,9 +12233,8 @@
       <c r="Q205" s="24"/>
       <c r="R205" s="24"/>
       <c r="S205" s="27"/>
-      <c r="T205" s="27"/>
-    </row>
-    <row r="206" customFormat="1" spans="6:20">
+    </row>
+    <row r="206" customFormat="1" spans="6:19">
       <c r="F206" s="24"/>
       <c r="H206" s="52"/>
       <c r="I206" s="52"/>
@@ -12543,9 +12248,8 @@
       <c r="Q206" s="24"/>
       <c r="R206" s="24"/>
       <c r="S206" s="27"/>
-      <c r="T206" s="27"/>
-    </row>
-    <row r="207" customFormat="1" spans="6:20">
+    </row>
+    <row r="207" customFormat="1" spans="6:19">
       <c r="F207" s="24"/>
       <c r="H207" s="52"/>
       <c r="I207" s="52"/>
@@ -12559,9 +12263,8 @@
       <c r="Q207" s="24"/>
       <c r="R207" s="24"/>
       <c r="S207" s="27"/>
-      <c r="T207" s="27"/>
-    </row>
-    <row r="208" customFormat="1" spans="6:20">
+    </row>
+    <row r="208" customFormat="1" spans="6:19">
       <c r="F208" s="24"/>
       <c r="H208" s="52"/>
       <c r="I208" s="52"/>
@@ -12575,9 +12278,8 @@
       <c r="Q208" s="24"/>
       <c r="R208" s="24"/>
       <c r="S208" s="27"/>
-      <c r="T208" s="27"/>
-    </row>
-    <row r="209" customFormat="1" spans="6:20">
+    </row>
+    <row r="209" customFormat="1" spans="6:19">
       <c r="F209" s="24"/>
       <c r="H209" s="52"/>
       <c r="I209" s="52"/>
@@ -12591,9 +12293,8 @@
       <c r="Q209" s="24"/>
       <c r="R209" s="24"/>
       <c r="S209" s="27"/>
-      <c r="T209" s="27"/>
-    </row>
-    <row r="210" customFormat="1" spans="6:20">
+    </row>
+    <row r="210" customFormat="1" spans="6:19">
       <c r="F210" s="24"/>
       <c r="H210" s="52"/>
       <c r="I210" s="52"/>
@@ -12607,9 +12308,8 @@
       <c r="Q210" s="24"/>
       <c r="R210" s="24"/>
       <c r="S210" s="27"/>
-      <c r="T210" s="27"/>
-    </row>
-    <row r="211" customFormat="1" spans="6:20">
+    </row>
+    <row r="211" customFormat="1" spans="6:19">
       <c r="F211" s="24"/>
       <c r="H211" s="52"/>
       <c r="I211" s="52"/>
@@ -12623,9 +12323,8 @@
       <c r="Q211" s="24"/>
       <c r="R211" s="24"/>
       <c r="S211" s="27"/>
-      <c r="T211" s="27"/>
-    </row>
-    <row r="212" customFormat="1" spans="6:20">
+    </row>
+    <row r="212" customFormat="1" spans="6:19">
       <c r="F212" s="24"/>
       <c r="H212" s="52"/>
       <c r="I212" s="52"/>
@@ -12639,9 +12338,8 @@
       <c r="Q212" s="24"/>
       <c r="R212" s="24"/>
       <c r="S212" s="27"/>
-      <c r="T212" s="27"/>
-    </row>
-    <row r="213" customFormat="1" spans="6:20">
+    </row>
+    <row r="213" customFormat="1" spans="6:19">
       <c r="F213" s="24"/>
       <c r="H213" s="52"/>
       <c r="I213" s="52"/>
@@ -12655,9 +12353,8 @@
       <c r="Q213" s="24"/>
       <c r="R213" s="24"/>
       <c r="S213" s="27"/>
-      <c r="T213" s="27"/>
-    </row>
-    <row r="214" customFormat="1" spans="6:20">
+    </row>
+    <row r="214" customFormat="1" spans="6:19">
       <c r="F214" s="24"/>
       <c r="H214" s="52"/>
       <c r="I214" s="52"/>
@@ -12671,9 +12368,8 @@
       <c r="Q214" s="24"/>
       <c r="R214" s="24"/>
       <c r="S214" s="27"/>
-      <c r="T214" s="27"/>
-    </row>
-    <row r="215" customFormat="1" spans="6:20">
+    </row>
+    <row r="215" customFormat="1" spans="6:19">
       <c r="F215" s="24"/>
       <c r="H215" s="52"/>
       <c r="I215" s="52"/>
@@ -12687,9 +12383,8 @@
       <c r="Q215" s="24"/>
       <c r="R215" s="24"/>
       <c r="S215" s="27"/>
-      <c r="T215" s="27"/>
-    </row>
-    <row r="216" customFormat="1" spans="6:20">
+    </row>
+    <row r="216" customFormat="1" spans="6:19">
       <c r="F216" s="24"/>
       <c r="H216" s="52"/>
       <c r="I216" s="52"/>
@@ -12703,9 +12398,8 @@
       <c r="Q216" s="24"/>
       <c r="R216" s="24"/>
       <c r="S216" s="27"/>
-      <c r="T216" s="27"/>
-    </row>
-    <row r="217" customFormat="1" spans="6:20">
+    </row>
+    <row r="217" customFormat="1" spans="6:19">
       <c r="F217" s="24"/>
       <c r="H217" s="52"/>
       <c r="I217" s="52"/>
@@ -12719,9 +12413,8 @@
       <c r="Q217" s="24"/>
       <c r="R217" s="24"/>
       <c r="S217" s="27"/>
-      <c r="T217" s="27"/>
-    </row>
-    <row r="218" customFormat="1" spans="6:20">
+    </row>
+    <row r="218" customFormat="1" spans="6:19">
       <c r="F218" s="24"/>
       <c r="H218" s="52"/>
       <c r="I218" s="52"/>
@@ -12735,9 +12428,8 @@
       <c r="Q218" s="24"/>
       <c r="R218" s="24"/>
       <c r="S218" s="27"/>
-      <c r="T218" s="27"/>
-    </row>
-    <row r="219" customFormat="1" spans="6:20">
+    </row>
+    <row r="219" customFormat="1" spans="6:19">
       <c r="F219" s="24"/>
       <c r="H219" s="52"/>
       <c r="I219" s="52"/>
@@ -12751,9 +12443,8 @@
       <c r="Q219" s="24"/>
       <c r="R219" s="24"/>
       <c r="S219" s="27"/>
-      <c r="T219" s="27"/>
-    </row>
-    <row r="220" customFormat="1" spans="6:20">
+    </row>
+    <row r="220" customFormat="1" spans="6:19">
       <c r="F220" s="24"/>
       <c r="H220" s="52"/>
       <c r="I220" s="52"/>
@@ -12767,9 +12458,8 @@
       <c r="Q220" s="24"/>
       <c r="R220" s="24"/>
       <c r="S220" s="27"/>
-      <c r="T220" s="27"/>
-    </row>
-    <row r="221" customFormat="1" spans="6:20">
+    </row>
+    <row r="221" customFormat="1" spans="6:19">
       <c r="F221" s="24"/>
       <c r="H221" s="52"/>
       <c r="I221" s="52"/>
@@ -12783,9 +12473,8 @@
       <c r="Q221" s="24"/>
       <c r="R221" s="24"/>
       <c r="S221" s="27"/>
-      <c r="T221" s="27"/>
-    </row>
-    <row r="222" customFormat="1" spans="6:20">
+    </row>
+    <row r="222" customFormat="1" spans="6:19">
       <c r="F222" s="24"/>
       <c r="H222" s="52"/>
       <c r="I222" s="52"/>
@@ -12799,9 +12488,8 @@
       <c r="Q222" s="24"/>
       <c r="R222" s="24"/>
       <c r="S222" s="27"/>
-      <c r="T222" s="27"/>
-    </row>
-    <row r="223" customFormat="1" spans="6:20">
+    </row>
+    <row r="223" customFormat="1" spans="6:19">
       <c r="F223" s="24"/>
       <c r="H223" s="52"/>
       <c r="I223" s="52"/>
@@ -12815,9 +12503,8 @@
       <c r="Q223" s="24"/>
       <c r="R223" s="24"/>
       <c r="S223" s="27"/>
-      <c r="T223" s="27"/>
-    </row>
-    <row r="224" customFormat="1" spans="6:20">
+    </row>
+    <row r="224" customFormat="1" spans="6:19">
       <c r="F224" s="24"/>
       <c r="H224" s="52"/>
       <c r="I224" s="52"/>
@@ -12831,9 +12518,8 @@
       <c r="Q224" s="24"/>
       <c r="R224" s="24"/>
       <c r="S224" s="27"/>
-      <c r="T224" s="27"/>
-    </row>
-    <row r="225" customFormat="1" spans="6:20">
+    </row>
+    <row r="225" customFormat="1" spans="6:19">
       <c r="F225" s="24"/>
       <c r="H225" s="52"/>
       <c r="I225" s="52"/>
@@ -12847,9 +12533,8 @@
       <c r="Q225" s="24"/>
       <c r="R225" s="24"/>
       <c r="S225" s="27"/>
-      <c r="T225" s="27"/>
-    </row>
-    <row r="226" customFormat="1" spans="6:20">
+    </row>
+    <row r="226" customFormat="1" spans="6:19">
       <c r="F226" s="24"/>
       <c r="H226" s="52"/>
       <c r="I226" s="52"/>
@@ -12863,9 +12548,8 @@
       <c r="Q226" s="24"/>
       <c r="R226" s="24"/>
       <c r="S226" s="27"/>
-      <c r="T226" s="27"/>
-    </row>
-    <row r="227" customFormat="1" spans="6:20">
+    </row>
+    <row r="227" customFormat="1" spans="6:19">
       <c r="F227" s="24"/>
       <c r="H227" s="52"/>
       <c r="I227" s="52"/>
@@ -12879,9 +12563,8 @@
       <c r="Q227" s="24"/>
       <c r="R227" s="24"/>
       <c r="S227" s="27"/>
-      <c r="T227" s="27"/>
-    </row>
-    <row r="228" customFormat="1" spans="6:20">
+    </row>
+    <row r="228" customFormat="1" spans="6:19">
       <c r="F228" s="24"/>
       <c r="H228" s="52"/>
       <c r="I228" s="52"/>
@@ -12895,9 +12578,8 @@
       <c r="Q228" s="24"/>
       <c r="R228" s="24"/>
       <c r="S228" s="27"/>
-      <c r="T228" s="27"/>
-    </row>
-    <row r="229" customFormat="1" spans="6:20">
+    </row>
+    <row r="229" customFormat="1" spans="6:19">
       <c r="F229" s="24"/>
       <c r="H229" s="52"/>
       <c r="I229" s="52"/>
@@ -12911,9 +12593,8 @@
       <c r="Q229" s="24"/>
       <c r="R229" s="24"/>
       <c r="S229" s="27"/>
-      <c r="T229" s="27"/>
-    </row>
-    <row r="230" customFormat="1" spans="6:20">
+    </row>
+    <row r="230" customFormat="1" spans="6:19">
       <c r="F230" s="24"/>
       <c r="H230" s="52"/>
       <c r="I230" s="52"/>
@@ -12927,9 +12608,8 @@
       <c r="Q230" s="24"/>
       <c r="R230" s="24"/>
       <c r="S230" s="27"/>
-      <c r="T230" s="27"/>
-    </row>
-    <row r="231" customFormat="1" spans="6:20">
+    </row>
+    <row r="231" customFormat="1" spans="6:19">
       <c r="F231" s="24"/>
       <c r="H231" s="52"/>
       <c r="I231" s="52"/>
@@ -12943,9 +12623,8 @@
       <c r="Q231" s="24"/>
       <c r="R231" s="24"/>
       <c r="S231" s="27"/>
-      <c r="T231" s="27"/>
-    </row>
-    <row r="232" customFormat="1" spans="6:20">
+    </row>
+    <row r="232" customFormat="1" spans="6:19">
       <c r="F232" s="24"/>
       <c r="H232" s="52"/>
       <c r="I232" s="52"/>
@@ -12959,9 +12638,8 @@
       <c r="Q232" s="24"/>
       <c r="R232" s="24"/>
       <c r="S232" s="27"/>
-      <c r="T232" s="27"/>
-    </row>
-    <row r="233" customFormat="1" spans="6:20">
+    </row>
+    <row r="233" customFormat="1" spans="6:19">
       <c r="F233" s="24"/>
       <c r="H233" s="52"/>
       <c r="I233" s="52"/>
@@ -12975,9 +12653,8 @@
       <c r="Q233" s="24"/>
       <c r="R233" s="24"/>
       <c r="S233" s="27"/>
-      <c r="T233" s="27"/>
-    </row>
-    <row r="234" customFormat="1" spans="6:20">
+    </row>
+    <row r="234" customFormat="1" spans="6:19">
       <c r="F234" s="24"/>
       <c r="H234" s="52"/>
       <c r="I234" s="52"/>
@@ -12991,9 +12668,8 @@
       <c r="Q234" s="24"/>
       <c r="R234" s="24"/>
       <c r="S234" s="27"/>
-      <c r="T234" s="27"/>
-    </row>
-    <row r="235" customFormat="1" spans="6:20">
+    </row>
+    <row r="235" customFormat="1" spans="6:19">
       <c r="F235" s="24"/>
       <c r="H235" s="52"/>
       <c r="I235" s="52"/>
@@ -13007,9 +12683,8 @@
       <c r="Q235" s="24"/>
       <c r="R235" s="24"/>
       <c r="S235" s="27"/>
-      <c r="T235" s="27"/>
-    </row>
-    <row r="236" customFormat="1" spans="6:20">
+    </row>
+    <row r="236" customFormat="1" spans="6:19">
       <c r="F236" s="24"/>
       <c r="H236" s="52"/>
       <c r="I236" s="52"/>
@@ -13023,9 +12698,8 @@
       <c r="Q236" s="24"/>
       <c r="R236" s="24"/>
       <c r="S236" s="27"/>
-      <c r="T236" s="27"/>
-    </row>
-    <row r="237" customFormat="1" spans="6:20">
+    </row>
+    <row r="237" customFormat="1" spans="6:19">
       <c r="F237" s="24"/>
       <c r="H237" s="52"/>
       <c r="I237" s="52"/>
@@ -13039,9 +12713,8 @@
       <c r="Q237" s="24"/>
       <c r="R237" s="24"/>
       <c r="S237" s="27"/>
-      <c r="T237" s="27"/>
-    </row>
-    <row r="238" customFormat="1" spans="6:20">
+    </row>
+    <row r="238" customFormat="1" spans="6:19">
       <c r="F238" s="24"/>
       <c r="H238" s="52"/>
       <c r="I238" s="52"/>
@@ -13055,9 +12728,8 @@
       <c r="Q238" s="24"/>
       <c r="R238" s="24"/>
       <c r="S238" s="27"/>
-      <c r="T238" s="27"/>
-    </row>
-    <row r="239" customFormat="1" spans="6:20">
+    </row>
+    <row r="239" customFormat="1" spans="6:19">
       <c r="F239" s="24"/>
       <c r="H239" s="52"/>
       <c r="I239" s="52"/>
@@ -13071,9 +12743,8 @@
       <c r="Q239" s="24"/>
       <c r="R239" s="24"/>
       <c r="S239" s="27"/>
-      <c r="T239" s="27"/>
-    </row>
-    <row r="240" customFormat="1" spans="6:20">
+    </row>
+    <row r="240" customFormat="1" spans="6:19">
       <c r="F240" s="24"/>
       <c r="H240" s="52"/>
       <c r="I240" s="52"/>
@@ -13087,9 +12758,8 @@
       <c r="Q240" s="24"/>
       <c r="R240" s="24"/>
       <c r="S240" s="27"/>
-      <c r="T240" s="27"/>
-    </row>
-    <row r="241" customFormat="1" spans="6:20">
+    </row>
+    <row r="241" customFormat="1" spans="6:19">
       <c r="F241" s="24"/>
       <c r="H241" s="52"/>
       <c r="I241" s="52"/>
@@ -13103,9 +12773,8 @@
       <c r="Q241" s="24"/>
       <c r="R241" s="24"/>
       <c r="S241" s="27"/>
-      <c r="T241" s="27"/>
-    </row>
-    <row r="242" customFormat="1" spans="6:20">
+    </row>
+    <row r="242" customFormat="1" spans="6:19">
       <c r="F242" s="24"/>
       <c r="H242" s="52"/>
       <c r="I242" s="52"/>
@@ -13119,9 +12788,8 @@
       <c r="Q242" s="24"/>
       <c r="R242" s="24"/>
       <c r="S242" s="27"/>
-      <c r="T242" s="27"/>
-    </row>
-    <row r="243" customFormat="1" spans="6:20">
+    </row>
+    <row r="243" customFormat="1" spans="6:19">
       <c r="F243" s="24"/>
       <c r="H243" s="52"/>
       <c r="I243" s="52"/>
@@ -13135,9 +12803,8 @@
       <c r="Q243" s="24"/>
       <c r="R243" s="24"/>
       <c r="S243" s="27"/>
-      <c r="T243" s="27"/>
-    </row>
-    <row r="244" customFormat="1" spans="6:20">
+    </row>
+    <row r="244" customFormat="1" spans="6:19">
       <c r="F244" s="24"/>
       <c r="H244" s="52"/>
       <c r="I244" s="52"/>
@@ -13151,9 +12818,8 @@
       <c r="Q244" s="24"/>
       <c r="R244" s="24"/>
       <c r="S244" s="27"/>
-      <c r="T244" s="27"/>
-    </row>
-    <row r="245" customFormat="1" spans="6:20">
+    </row>
+    <row r="245" customFormat="1" spans="6:19">
       <c r="F245" s="24"/>
       <c r="H245" s="52"/>
       <c r="I245" s="52"/>
@@ -13167,9 +12833,8 @@
       <c r="Q245" s="24"/>
       <c r="R245" s="24"/>
       <c r="S245" s="27"/>
-      <c r="T245" s="27"/>
-    </row>
-    <row r="246" customFormat="1" spans="6:20">
+    </row>
+    <row r="246" customFormat="1" spans="6:19">
       <c r="F246" s="24"/>
       <c r="H246" s="52"/>
       <c r="I246" s="52"/>
@@ -13183,9 +12848,8 @@
       <c r="Q246" s="24"/>
       <c r="R246" s="24"/>
       <c r="S246" s="27"/>
-      <c r="T246" s="27"/>
-    </row>
-    <row r="247" customFormat="1" spans="6:20">
+    </row>
+    <row r="247" customFormat="1" spans="6:19">
       <c r="F247" s="24"/>
       <c r="H247" s="52"/>
       <c r="I247" s="52"/>
@@ -13199,9 +12863,8 @@
       <c r="Q247" s="24"/>
       <c r="R247" s="24"/>
       <c r="S247" s="27"/>
-      <c r="T247" s="27"/>
-    </row>
-    <row r="248" customFormat="1" spans="6:20">
+    </row>
+    <row r="248" customFormat="1" spans="6:19">
       <c r="F248" s="24"/>
       <c r="H248" s="52"/>
       <c r="I248" s="52"/>
@@ -13215,9 +12878,8 @@
       <c r="Q248" s="24"/>
       <c r="R248" s="24"/>
       <c r="S248" s="27"/>
-      <c r="T248" s="27"/>
-    </row>
-    <row r="249" customFormat="1" spans="6:20">
+    </row>
+    <row r="249" customFormat="1" spans="6:19">
       <c r="F249" s="24"/>
       <c r="H249" s="52"/>
       <c r="I249" s="52"/>
@@ -13231,9 +12893,8 @@
       <c r="Q249" s="24"/>
       <c r="R249" s="24"/>
       <c r="S249" s="27"/>
-      <c r="T249" s="27"/>
-    </row>
-    <row r="250" customFormat="1" spans="6:20">
+    </row>
+    <row r="250" customFormat="1" spans="6:19">
       <c r="F250" s="24"/>
       <c r="H250" s="52"/>
       <c r="I250" s="52"/>
@@ -13247,9 +12908,8 @@
       <c r="Q250" s="24"/>
       <c r="R250" s="24"/>
       <c r="S250" s="27"/>
-      <c r="T250" s="27"/>
-    </row>
-    <row r="251" customFormat="1" spans="6:20">
+    </row>
+    <row r="251" customFormat="1" spans="6:19">
       <c r="F251" s="24"/>
       <c r="H251" s="52"/>
       <c r="I251" s="52"/>
@@ -13263,9 +12923,8 @@
       <c r="Q251" s="24"/>
       <c r="R251" s="24"/>
       <c r="S251" s="27"/>
-      <c r="T251" s="27"/>
-    </row>
-    <row r="252" customFormat="1" spans="6:20">
+    </row>
+    <row r="252" customFormat="1" spans="6:19">
       <c r="F252" s="24"/>
       <c r="H252" s="52"/>
       <c r="I252" s="52"/>
@@ -13279,9 +12938,8 @@
       <c r="Q252" s="24"/>
       <c r="R252" s="24"/>
       <c r="S252" s="27"/>
-      <c r="T252" s="27"/>
-    </row>
-    <row r="253" customFormat="1" spans="6:20">
+    </row>
+    <row r="253" customFormat="1" spans="6:19">
       <c r="F253" s="24"/>
       <c r="H253" s="52"/>
       <c r="I253" s="52"/>
@@ -13295,9 +12953,8 @@
       <c r="Q253" s="24"/>
       <c r="R253" s="24"/>
       <c r="S253" s="27"/>
-      <c r="T253" s="27"/>
-    </row>
-    <row r="254" customFormat="1" spans="6:20">
+    </row>
+    <row r="254" customFormat="1" spans="6:19">
       <c r="F254" s="24"/>
       <c r="H254" s="52"/>
       <c r="I254" s="52"/>
@@ -13311,9 +12968,8 @@
       <c r="Q254" s="24"/>
       <c r="R254" s="24"/>
       <c r="S254" s="27"/>
-      <c r="T254" s="27"/>
-    </row>
-    <row r="255" customFormat="1" spans="6:20">
+    </row>
+    <row r="255" customFormat="1" spans="6:19">
       <c r="F255" s="24"/>
       <c r="H255" s="52"/>
       <c r="I255" s="52"/>
@@ -13327,9 +12983,8 @@
       <c r="Q255" s="24"/>
       <c r="R255" s="24"/>
       <c r="S255" s="27"/>
-      <c r="T255" s="27"/>
-    </row>
-    <row r="256" customFormat="1" spans="6:20">
+    </row>
+    <row r="256" customFormat="1" spans="6:19">
       <c r="F256" s="24"/>
       <c r="H256" s="52"/>
       <c r="I256" s="52"/>
@@ -13343,9 +12998,8 @@
       <c r="Q256" s="24"/>
       <c r="R256" s="24"/>
       <c r="S256" s="27"/>
-      <c r="T256" s="27"/>
-    </row>
-    <row r="257" customFormat="1" spans="6:20">
+    </row>
+    <row r="257" customFormat="1" spans="6:19">
       <c r="F257" s="24"/>
       <c r="H257" s="52"/>
       <c r="I257" s="52"/>
@@ -13359,9 +13013,8 @@
       <c r="Q257" s="24"/>
       <c r="R257" s="24"/>
       <c r="S257" s="27"/>
-      <c r="T257" s="27"/>
-    </row>
-    <row r="258" customFormat="1" spans="6:20">
+    </row>
+    <row r="258" customFormat="1" spans="6:19">
       <c r="F258" s="24"/>
       <c r="H258" s="52"/>
       <c r="I258" s="52"/>
@@ -13375,9 +13028,8 @@
       <c r="Q258" s="24"/>
       <c r="R258" s="24"/>
       <c r="S258" s="27"/>
-      <c r="T258" s="27"/>
-    </row>
-    <row r="259" customFormat="1" spans="6:20">
+    </row>
+    <row r="259" customFormat="1" spans="6:19">
       <c r="F259" s="24"/>
       <c r="H259" s="52"/>
       <c r="I259" s="52"/>
@@ -13391,9 +13043,8 @@
       <c r="Q259" s="24"/>
       <c r="R259" s="24"/>
       <c r="S259" s="27"/>
-      <c r="T259" s="27"/>
-    </row>
-    <row r="260" customFormat="1" spans="6:20">
+    </row>
+    <row r="260" customFormat="1" spans="6:19">
       <c r="F260" s="24"/>
       <c r="H260" s="52"/>
       <c r="I260" s="52"/>
@@ -13407,9 +13058,8 @@
       <c r="Q260" s="24"/>
       <c r="R260" s="24"/>
       <c r="S260" s="27"/>
-      <c r="T260" s="27"/>
-    </row>
-    <row r="261" customFormat="1" spans="6:20">
+    </row>
+    <row r="261" customFormat="1" spans="6:19">
       <c r="F261" s="24"/>
       <c r="H261" s="52"/>
       <c r="I261" s="52"/>
@@ -13423,9 +13073,8 @@
       <c r="Q261" s="24"/>
       <c r="R261" s="24"/>
       <c r="S261" s="27"/>
-      <c r="T261" s="27"/>
-    </row>
-    <row r="262" customFormat="1" spans="6:20">
+    </row>
+    <row r="262" customFormat="1" spans="6:19">
       <c r="F262" s="24"/>
       <c r="H262" s="52"/>
       <c r="I262" s="52"/>
@@ -13439,9 +13088,8 @@
       <c r="Q262" s="24"/>
       <c r="R262" s="24"/>
       <c r="S262" s="27"/>
-      <c r="T262" s="27"/>
-    </row>
-    <row r="263" customFormat="1" spans="6:20">
+    </row>
+    <row r="263" customFormat="1" spans="6:19">
       <c r="F263" s="24"/>
       <c r="H263" s="52"/>
       <c r="I263" s="52"/>
@@ -13455,9 +13103,8 @@
       <c r="Q263" s="24"/>
       <c r="R263" s="24"/>
       <c r="S263" s="27"/>
-      <c r="T263" s="27"/>
-    </row>
-    <row r="264" customFormat="1" spans="6:20">
+    </row>
+    <row r="264" customFormat="1" spans="6:19">
       <c r="F264" s="24"/>
       <c r="H264" s="52"/>
       <c r="I264" s="52"/>
@@ -13471,9 +13118,8 @@
       <c r="Q264" s="24"/>
       <c r="R264" s="24"/>
       <c r="S264" s="27"/>
-      <c r="T264" s="27"/>
-    </row>
-    <row r="265" customFormat="1" spans="6:20">
+    </row>
+    <row r="265" customFormat="1" spans="6:19">
       <c r="F265" s="24"/>
       <c r="H265" s="52"/>
       <c r="I265" s="52"/>
@@ -13487,9 +13133,8 @@
       <c r="Q265" s="24"/>
       <c r="R265" s="24"/>
       <c r="S265" s="27"/>
-      <c r="T265" s="27"/>
-    </row>
-    <row r="266" customFormat="1" spans="6:20">
+    </row>
+    <row r="266" customFormat="1" spans="6:19">
       <c r="F266" s="24"/>
       <c r="H266" s="52"/>
       <c r="I266" s="52"/>
@@ -13503,9 +13148,8 @@
       <c r="Q266" s="24"/>
       <c r="R266" s="24"/>
       <c r="S266" s="27"/>
-      <c r="T266" s="27"/>
-    </row>
-    <row r="267" customFormat="1" spans="6:20">
+    </row>
+    <row r="267" customFormat="1" spans="6:19">
       <c r="F267" s="24"/>
       <c r="H267" s="52"/>
       <c r="I267" s="52"/>
@@ -13519,9 +13163,8 @@
       <c r="Q267" s="24"/>
       <c r="R267" s="24"/>
       <c r="S267" s="27"/>
-      <c r="T267" s="27"/>
-    </row>
-    <row r="268" customFormat="1" spans="6:20">
+    </row>
+    <row r="268" customFormat="1" spans="6:19">
       <c r="F268" s="24"/>
       <c r="H268" s="52"/>
       <c r="I268" s="52"/>
@@ -13535,9 +13178,8 @@
       <c r="Q268" s="24"/>
       <c r="R268" s="24"/>
       <c r="S268" s="27"/>
-      <c r="T268" s="27"/>
-    </row>
-    <row r="269" customFormat="1" spans="6:20">
+    </row>
+    <row r="269" customFormat="1" spans="6:19">
       <c r="F269" s="24"/>
       <c r="H269" s="52"/>
       <c r="I269" s="52"/>
@@ -13551,9 +13193,8 @@
       <c r="Q269" s="24"/>
       <c r="R269" s="24"/>
       <c r="S269" s="27"/>
-      <c r="T269" s="27"/>
-    </row>
-    <row r="270" customFormat="1" spans="6:20">
+    </row>
+    <row r="270" customFormat="1" spans="6:19">
       <c r="F270" s="24"/>
       <c r="H270" s="52"/>
       <c r="I270" s="52"/>
@@ -13567,9 +13208,8 @@
       <c r="Q270" s="24"/>
       <c r="R270" s="24"/>
       <c r="S270" s="27"/>
-      <c r="T270" s="27"/>
-    </row>
-    <row r="271" customFormat="1" spans="6:20">
+    </row>
+    <row r="271" customFormat="1" spans="6:19">
       <c r="F271" s="24"/>
       <c r="H271" s="52"/>
       <c r="I271" s="52"/>
@@ -13583,9 +13223,8 @@
       <c r="Q271" s="24"/>
       <c r="R271" s="24"/>
       <c r="S271" s="27"/>
-      <c r="T271" s="27"/>
-    </row>
-    <row r="272" customFormat="1" spans="6:20">
+    </row>
+    <row r="272" customFormat="1" spans="6:19">
       <c r="F272" s="24"/>
       <c r="H272" s="52"/>
       <c r="I272" s="52"/>
@@ -13599,9 +13238,8 @@
       <c r="Q272" s="24"/>
       <c r="R272" s="24"/>
       <c r="S272" s="27"/>
-      <c r="T272" s="27"/>
-    </row>
-    <row r="273" customFormat="1" spans="6:20">
+    </row>
+    <row r="273" customFormat="1" spans="6:19">
       <c r="F273" s="24"/>
       <c r="H273" s="52"/>
       <c r="I273" s="52"/>
@@ -13615,9 +13253,8 @@
       <c r="Q273" s="24"/>
       <c r="R273" s="24"/>
       <c r="S273" s="27"/>
-      <c r="T273" s="27"/>
-    </row>
-    <row r="274" customFormat="1" spans="6:20">
+    </row>
+    <row r="274" customFormat="1" spans="6:19">
       <c r="F274" s="24"/>
       <c r="H274" s="52"/>
       <c r="I274" s="52"/>
@@ -13631,9 +13268,8 @@
       <c r="Q274" s="24"/>
       <c r="R274" s="24"/>
       <c r="S274" s="27"/>
-      <c r="T274" s="27"/>
-    </row>
-    <row r="275" customFormat="1" spans="6:20">
+    </row>
+    <row r="275" customFormat="1" spans="6:19">
       <c r="F275" s="24"/>
       <c r="H275" s="52"/>
       <c r="I275" s="52"/>
@@ -13647,9 +13283,8 @@
       <c r="Q275" s="24"/>
       <c r="R275" s="24"/>
       <c r="S275" s="27"/>
-      <c r="T275" s="27"/>
-    </row>
-    <row r="276" customFormat="1" spans="6:20">
+    </row>
+    <row r="276" customFormat="1" spans="6:19">
       <c r="F276" s="24"/>
       <c r="H276" s="52"/>
       <c r="I276" s="52"/>
@@ -13663,9 +13298,8 @@
       <c r="Q276" s="24"/>
       <c r="R276" s="24"/>
       <c r="S276" s="27"/>
-      <c r="T276" s="27"/>
-    </row>
-    <row r="277" customFormat="1" spans="6:20">
+    </row>
+    <row r="277" customFormat="1" spans="6:19">
       <c r="F277" s="24"/>
       <c r="H277" s="52"/>
       <c r="I277" s="52"/>
@@ -13679,9 +13313,8 @@
       <c r="Q277" s="24"/>
       <c r="R277" s="24"/>
       <c r="S277" s="27"/>
-      <c r="T277" s="27"/>
-    </row>
-    <row r="278" customFormat="1" spans="6:20">
+    </row>
+    <row r="278" customFormat="1" spans="6:19">
       <c r="F278" s="24"/>
       <c r="H278" s="52"/>
       <c r="I278" s="52"/>
@@ -13695,9 +13328,8 @@
       <c r="Q278" s="24"/>
       <c r="R278" s="24"/>
       <c r="S278" s="27"/>
-      <c r="T278" s="27"/>
-    </row>
-    <row r="279" customFormat="1" spans="6:20">
+    </row>
+    <row r="279" customFormat="1" spans="6:19">
       <c r="F279" s="24"/>
       <c r="H279" s="52"/>
       <c r="I279" s="52"/>
@@ -13711,9 +13343,8 @@
       <c r="Q279" s="24"/>
       <c r="R279" s="24"/>
       <c r="S279" s="27"/>
-      <c r="T279" s="27"/>
-    </row>
-    <row r="280" customFormat="1" spans="6:20">
+    </row>
+    <row r="280" customFormat="1" spans="6:19">
       <c r="F280" s="24"/>
       <c r="H280" s="52"/>
       <c r="I280" s="52"/>
@@ -13727,9 +13358,8 @@
       <c r="Q280" s="24"/>
       <c r="R280" s="24"/>
       <c r="S280" s="27"/>
-      <c r="T280" s="27"/>
-    </row>
-    <row r="281" customFormat="1" spans="6:20">
+    </row>
+    <row r="281" customFormat="1" spans="6:19">
       <c r="F281" s="24"/>
       <c r="H281" s="52"/>
       <c r="I281" s="52"/>
@@ -13743,9 +13373,8 @@
       <c r="Q281" s="24"/>
       <c r="R281" s="24"/>
       <c r="S281" s="27"/>
-      <c r="T281" s="27"/>
-    </row>
-    <row r="282" customFormat="1" spans="6:20">
+    </row>
+    <row r="282" customFormat="1" spans="6:19">
       <c r="F282" s="24"/>
       <c r="H282" s="52"/>
       <c r="I282" s="52"/>
@@ -13759,9 +13388,8 @@
       <c r="Q282" s="24"/>
       <c r="R282" s="24"/>
       <c r="S282" s="27"/>
-      <c r="T282" s="27"/>
-    </row>
-    <row r="283" customFormat="1" spans="6:20">
+    </row>
+    <row r="283" customFormat="1" spans="6:19">
       <c r="F283" s="24"/>
       <c r="H283" s="52"/>
       <c r="I283" s="52"/>
@@ -13775,9 +13403,8 @@
       <c r="Q283" s="24"/>
       <c r="R283" s="24"/>
       <c r="S283" s="27"/>
-      <c r="T283" s="27"/>
-    </row>
-    <row r="284" customFormat="1" spans="6:20">
+    </row>
+    <row r="284" customFormat="1" spans="6:19">
       <c r="F284" s="24"/>
       <c r="H284" s="52"/>
       <c r="I284" s="52"/>
@@ -13791,9 +13418,8 @@
       <c r="Q284" s="24"/>
       <c r="R284" s="24"/>
       <c r="S284" s="27"/>
-      <c r="T284" s="27"/>
-    </row>
-    <row r="285" customFormat="1" spans="6:20">
+    </row>
+    <row r="285" customFormat="1" spans="6:19">
       <c r="F285" s="24"/>
       <c r="H285" s="52"/>
       <c r="I285" s="52"/>
@@ -13807,9 +13433,8 @@
       <c r="Q285" s="24"/>
       <c r="R285" s="24"/>
       <c r="S285" s="27"/>
-      <c r="T285" s="27"/>
-    </row>
-    <row r="286" customFormat="1" spans="6:20">
+    </row>
+    <row r="286" customFormat="1" spans="6:19">
       <c r="F286" s="24"/>
       <c r="H286" s="52"/>
       <c r="I286" s="52"/>
@@ -13823,9 +13448,8 @@
       <c r="Q286" s="24"/>
       <c r="R286" s="24"/>
       <c r="S286" s="27"/>
-      <c r="T286" s="27"/>
-    </row>
-    <row r="287" customFormat="1" spans="6:20">
+    </row>
+    <row r="287" customFormat="1" spans="6:19">
       <c r="F287" s="24"/>
       <c r="H287" s="52"/>
       <c r="I287" s="52"/>
@@ -13839,9 +13463,8 @@
       <c r="Q287" s="24"/>
       <c r="R287" s="24"/>
       <c r="S287" s="27"/>
-      <c r="T287" s="27"/>
-    </row>
-    <row r="288" customFormat="1" spans="6:20">
+    </row>
+    <row r="288" customFormat="1" spans="6:19">
       <c r="F288" s="24"/>
       <c r="H288" s="52"/>
       <c r="I288" s="52"/>
@@ -13855,9 +13478,8 @@
       <c r="Q288" s="24"/>
       <c r="R288" s="24"/>
       <c r="S288" s="27"/>
-      <c r="T288" s="27"/>
-    </row>
-    <row r="289" customFormat="1" spans="6:20">
+    </row>
+    <row r="289" customFormat="1" spans="6:19">
       <c r="F289" s="24"/>
       <c r="H289" s="52"/>
       <c r="I289" s="52"/>
@@ -13871,9 +13493,8 @@
       <c r="Q289" s="24"/>
       <c r="R289" s="24"/>
       <c r="S289" s="27"/>
-      <c r="T289" s="27"/>
-    </row>
-    <row r="290" customFormat="1" spans="6:20">
+    </row>
+    <row r="290" customFormat="1" spans="6:19">
       <c r="F290" s="24"/>
       <c r="H290" s="52"/>
       <c r="I290" s="52"/>
@@ -13887,9 +13508,8 @@
       <c r="Q290" s="24"/>
       <c r="R290" s="24"/>
       <c r="S290" s="27"/>
-      <c r="T290" s="27"/>
-    </row>
-    <row r="291" customFormat="1" spans="6:20">
+    </row>
+    <row r="291" customFormat="1" spans="6:19">
       <c r="F291" s="24"/>
       <c r="H291" s="52"/>
       <c r="I291" s="52"/>
@@ -13903,9 +13523,8 @@
       <c r="Q291" s="24"/>
       <c r="R291" s="24"/>
       <c r="S291" s="27"/>
-      <c r="T291" s="27"/>
-    </row>
-    <row r="292" customFormat="1" spans="6:20">
+    </row>
+    <row r="292" customFormat="1" spans="6:19">
       <c r="F292" s="24"/>
       <c r="H292" s="52"/>
       <c r="I292" s="52"/>
@@ -13919,9 +13538,8 @@
       <c r="Q292" s="24"/>
       <c r="R292" s="24"/>
       <c r="S292" s="27"/>
-      <c r="T292" s="27"/>
-    </row>
-    <row r="293" customFormat="1" spans="6:20">
+    </row>
+    <row r="293" customFormat="1" spans="6:19">
       <c r="F293" s="24"/>
       <c r="H293" s="52"/>
       <c r="I293" s="52"/>
@@ -13935,9 +13553,8 @@
       <c r="Q293" s="24"/>
       <c r="R293" s="24"/>
       <c r="S293" s="27"/>
-      <c r="T293" s="27"/>
-    </row>
-    <row r="294" customFormat="1" spans="6:20">
+    </row>
+    <row r="294" customFormat="1" spans="6:19">
       <c r="F294" s="24"/>
       <c r="H294" s="52"/>
       <c r="I294" s="52"/>
@@ -13951,9 +13568,8 @@
       <c r="Q294" s="24"/>
       <c r="R294" s="24"/>
       <c r="S294" s="27"/>
-      <c r="T294" s="27"/>
-    </row>
-    <row r="295" customFormat="1" spans="6:20">
+    </row>
+    <row r="295" customFormat="1" spans="6:19">
       <c r="F295" s="24"/>
       <c r="H295" s="52"/>
       <c r="I295" s="52"/>
@@ -13967,9 +13583,8 @@
       <c r="Q295" s="24"/>
       <c r="R295" s="24"/>
       <c r="S295" s="27"/>
-      <c r="T295" s="27"/>
-    </row>
-    <row r="296" customFormat="1" spans="6:20">
+    </row>
+    <row r="296" customFormat="1" spans="6:19">
       <c r="F296" s="24"/>
       <c r="H296" s="52"/>
       <c r="I296" s="52"/>
@@ -13983,9 +13598,8 @@
       <c r="Q296" s="24"/>
       <c r="R296" s="24"/>
       <c r="S296" s="27"/>
-      <c r="T296" s="27"/>
-    </row>
-    <row r="297" customFormat="1" spans="6:20">
+    </row>
+    <row r="297" customFormat="1" spans="6:19">
       <c r="F297" s="24"/>
       <c r="H297" s="52"/>
       <c r="I297" s="52"/>
@@ -13999,9 +13613,8 @@
       <c r="Q297" s="24"/>
       <c r="R297" s="24"/>
       <c r="S297" s="27"/>
-      <c r="T297" s="27"/>
-    </row>
-    <row r="298" customFormat="1" spans="6:20">
+    </row>
+    <row r="298" customFormat="1" spans="6:19">
       <c r="F298" s="24"/>
       <c r="H298" s="52"/>
       <c r="I298" s="52"/>
@@ -14015,9 +13628,8 @@
       <c r="Q298" s="24"/>
       <c r="R298" s="24"/>
       <c r="S298" s="27"/>
-      <c r="T298" s="27"/>
-    </row>
-    <row r="299" customFormat="1" spans="6:20">
+    </row>
+    <row r="299" customFormat="1" spans="6:19">
       <c r="F299" s="24"/>
       <c r="H299" s="52"/>
       <c r="I299" s="52"/>
@@ -14031,9 +13643,8 @@
       <c r="Q299" s="24"/>
       <c r="R299" s="24"/>
       <c r="S299" s="27"/>
-      <c r="T299" s="27"/>
-    </row>
-    <row r="300" customFormat="1" spans="6:20">
+    </row>
+    <row r="300" customFormat="1" spans="6:19">
       <c r="F300" s="24"/>
       <c r="H300" s="52"/>
       <c r="I300" s="52"/>
@@ -14047,9 +13658,8 @@
       <c r="Q300" s="24"/>
       <c r="R300" s="24"/>
       <c r="S300" s="27"/>
-      <c r="T300" s="27"/>
-    </row>
-    <row r="301" customFormat="1" spans="6:20">
+    </row>
+    <row r="301" customFormat="1" spans="6:19">
       <c r="F301" s="24"/>
       <c r="H301" s="52"/>
       <c r="I301" s="52"/>
@@ -14063,9 +13673,8 @@
       <c r="Q301" s="24"/>
       <c r="R301" s="24"/>
       <c r="S301" s="27"/>
-      <c r="T301" s="27"/>
-    </row>
-    <row r="302" customFormat="1" spans="6:20">
+    </row>
+    <row r="302" customFormat="1" spans="6:19">
       <c r="F302" s="24"/>
       <c r="H302" s="52"/>
       <c r="I302" s="52"/>
@@ -14079,9 +13688,8 @@
       <c r="Q302" s="24"/>
       <c r="R302" s="24"/>
       <c r="S302" s="27"/>
-      <c r="T302" s="27"/>
-    </row>
-    <row r="303" customFormat="1" spans="6:20">
+    </row>
+    <row r="303" customFormat="1" spans="6:19">
       <c r="F303" s="24"/>
       <c r="H303" s="52"/>
       <c r="I303" s="52"/>
@@ -14095,9 +13703,8 @@
       <c r="Q303" s="24"/>
       <c r="R303" s="24"/>
       <c r="S303" s="27"/>
-      <c r="T303" s="27"/>
-    </row>
-    <row r="304" customFormat="1" spans="6:20">
+    </row>
+    <row r="304" customFormat="1" spans="6:19">
       <c r="F304" s="24"/>
       <c r="H304" s="52"/>
       <c r="I304" s="52"/>
@@ -14111,9 +13718,8 @@
       <c r="Q304" s="24"/>
       <c r="R304" s="24"/>
       <c r="S304" s="27"/>
-      <c r="T304" s="27"/>
-    </row>
-    <row r="305" customFormat="1" spans="6:20">
+    </row>
+    <row r="305" customFormat="1" spans="6:19">
       <c r="F305" s="24"/>
       <c r="H305" s="52"/>
       <c r="I305" s="52"/>
@@ -14127,9 +13733,8 @@
       <c r="Q305" s="24"/>
       <c r="R305" s="24"/>
       <c r="S305" s="27"/>
-      <c r="T305" s="27"/>
-    </row>
-    <row r="306" customFormat="1" spans="6:20">
+    </row>
+    <row r="306" customFormat="1" spans="6:19">
       <c r="F306" s="24"/>
       <c r="H306" s="52"/>
       <c r="I306" s="52"/>
@@ -14143,9 +13748,8 @@
       <c r="Q306" s="24"/>
       <c r="R306" s="24"/>
       <c r="S306" s="27"/>
-      <c r="T306" s="27"/>
-    </row>
-    <row r="307" customFormat="1" spans="6:20">
+    </row>
+    <row r="307" customFormat="1" spans="6:19">
       <c r="F307" s="24"/>
       <c r="H307" s="52"/>
       <c r="I307" s="52"/>
@@ -14159,9 +13763,8 @@
       <c r="Q307" s="24"/>
       <c r="R307" s="24"/>
       <c r="S307" s="27"/>
-      <c r="T307" s="27"/>
-    </row>
-    <row r="308" customFormat="1" spans="6:20">
+    </row>
+    <row r="308" customFormat="1" spans="6:19">
       <c r="F308" s="24"/>
       <c r="H308" s="52"/>
       <c r="I308" s="52"/>
@@ -14175,9 +13778,8 @@
       <c r="Q308" s="24"/>
       <c r="R308" s="24"/>
       <c r="S308" s="27"/>
-      <c r="T308" s="27"/>
-    </row>
-    <row r="309" customFormat="1" spans="6:20">
+    </row>
+    <row r="309" customFormat="1" spans="6:19">
       <c r="F309" s="24"/>
       <c r="H309" s="52"/>
       <c r="I309" s="52"/>
@@ -14191,9 +13793,8 @@
       <c r="Q309" s="24"/>
       <c r="R309" s="24"/>
       <c r="S309" s="27"/>
-      <c r="T309" s="27"/>
-    </row>
-    <row r="310" customFormat="1" spans="6:20">
+    </row>
+    <row r="310" customFormat="1" spans="6:19">
       <c r="F310" s="24"/>
       <c r="H310" s="52"/>
       <c r="I310" s="52"/>
@@ -14207,9 +13808,8 @@
       <c r="Q310" s="24"/>
       <c r="R310" s="24"/>
       <c r="S310" s="27"/>
-      <c r="T310" s="27"/>
-    </row>
-    <row r="311" customFormat="1" spans="6:20">
+    </row>
+    <row r="311" customFormat="1" spans="6:19">
       <c r="F311" s="24"/>
       <c r="H311" s="52"/>
       <c r="I311" s="52"/>
@@ -14223,9 +13823,8 @@
       <c r="Q311" s="24"/>
       <c r="R311" s="24"/>
       <c r="S311" s="27"/>
-      <c r="T311" s="27"/>
-    </row>
-    <row r="312" customFormat="1" spans="6:20">
+    </row>
+    <row r="312" customFormat="1" spans="6:19">
       <c r="F312" s="24"/>
       <c r="H312" s="52"/>
       <c r="I312" s="52"/>
@@ -14239,9 +13838,8 @@
       <c r="Q312" s="24"/>
       <c r="R312" s="24"/>
       <c r="S312" s="27"/>
-      <c r="T312" s="27"/>
-    </row>
-    <row r="313" customFormat="1" spans="6:20">
+    </row>
+    <row r="313" customFormat="1" spans="6:19">
       <c r="F313" s="24"/>
       <c r="H313" s="52"/>
       <c r="I313" s="52"/>
@@ -14255,9 +13853,8 @@
       <c r="Q313" s="24"/>
       <c r="R313" s="24"/>
       <c r="S313" s="27"/>
-      <c r="T313" s="27"/>
-    </row>
-    <row r="314" customFormat="1" spans="6:20">
+    </row>
+    <row r="314" customFormat="1" spans="6:19">
       <c r="F314" s="24"/>
       <c r="H314" s="52"/>
       <c r="I314" s="52"/>
@@ -14271,9 +13868,8 @@
       <c r="Q314" s="24"/>
       <c r="R314" s="24"/>
       <c r="S314" s="27"/>
-      <c r="T314" s="27"/>
-    </row>
-    <row r="315" customFormat="1" spans="6:20">
+    </row>
+    <row r="315" customFormat="1" spans="6:19">
       <c r="F315" s="24"/>
       <c r="H315" s="52"/>
       <c r="I315" s="52"/>
@@ -14287,9 +13883,8 @@
       <c r="Q315" s="24"/>
       <c r="R315" s="24"/>
       <c r="S315" s="27"/>
-      <c r="T315" s="27"/>
-    </row>
-    <row r="316" customFormat="1" spans="6:20">
+    </row>
+    <row r="316" customFormat="1" spans="6:19">
       <c r="F316" s="24"/>
       <c r="H316" s="52"/>
       <c r="I316" s="52"/>
@@ -14303,9 +13898,8 @@
       <c r="Q316" s="24"/>
       <c r="R316" s="24"/>
       <c r="S316" s="27"/>
-      <c r="T316" s="27"/>
-    </row>
-    <row r="317" customFormat="1" spans="6:20">
+    </row>
+    <row r="317" customFormat="1" spans="6:19">
       <c r="F317" s="24"/>
       <c r="H317" s="52"/>
       <c r="I317" s="52"/>
@@ -14319,9 +13913,8 @@
       <c r="Q317" s="24"/>
       <c r="R317" s="24"/>
       <c r="S317" s="27"/>
-      <c r="T317" s="27"/>
-    </row>
-    <row r="318" customFormat="1" spans="6:20">
+    </row>
+    <row r="318" customFormat="1" spans="6:19">
       <c r="F318" s="24"/>
       <c r="H318" s="52"/>
       <c r="I318" s="52"/>
@@ -14335,9 +13928,8 @@
       <c r="Q318" s="24"/>
       <c r="R318" s="24"/>
       <c r="S318" s="27"/>
-      <c r="T318" s="27"/>
-    </row>
-    <row r="319" customFormat="1" spans="6:20">
+    </row>
+    <row r="319" customFormat="1" spans="6:19">
       <c r="F319" s="24"/>
       <c r="H319" s="52"/>
       <c r="I319" s="52"/>
@@ -14351,9 +13943,8 @@
       <c r="Q319" s="24"/>
       <c r="R319" s="24"/>
       <c r="S319" s="27"/>
-      <c r="T319" s="27"/>
-    </row>
-    <row r="320" customFormat="1" spans="6:20">
+    </row>
+    <row r="320" customFormat="1" spans="6:19">
       <c r="F320" s="24"/>
       <c r="H320" s="52"/>
       <c r="I320" s="52"/>
@@ -14367,9 +13958,8 @@
       <c r="Q320" s="24"/>
       <c r="R320" s="24"/>
       <c r="S320" s="27"/>
-      <c r="T320" s="27"/>
-    </row>
-    <row r="321" customFormat="1" spans="6:20">
+    </row>
+    <row r="321" customFormat="1" spans="6:19">
       <c r="F321" s="24"/>
       <c r="H321" s="52"/>
       <c r="I321" s="52"/>
@@ -14383,9 +13973,8 @@
       <c r="Q321" s="24"/>
       <c r="R321" s="24"/>
       <c r="S321" s="27"/>
-      <c r="T321" s="27"/>
-    </row>
-    <row r="322" customFormat="1" spans="6:20">
+    </row>
+    <row r="322" customFormat="1" spans="6:19">
       <c r="F322" s="24"/>
       <c r="H322" s="52"/>
       <c r="I322" s="52"/>
@@ -14399,9 +13988,8 @@
       <c r="Q322" s="24"/>
       <c r="R322" s="24"/>
       <c r="S322" s="27"/>
-      <c r="T322" s="27"/>
-    </row>
-    <row r="323" customFormat="1" spans="6:20">
+    </row>
+    <row r="323" customFormat="1" spans="6:19">
       <c r="F323" s="24"/>
       <c r="H323" s="52"/>
       <c r="I323" s="52"/>
@@ -14415,9 +14003,8 @@
       <c r="Q323" s="24"/>
       <c r="R323" s="24"/>
       <c r="S323" s="27"/>
-      <c r="T323" s="27"/>
-    </row>
-    <row r="324" customFormat="1" spans="6:20">
+    </row>
+    <row r="324" customFormat="1" spans="6:19">
       <c r="F324" s="24"/>
       <c r="H324" s="52"/>
       <c r="I324" s="52"/>
@@ -14431,9 +14018,8 @@
       <c r="Q324" s="24"/>
       <c r="R324" s="24"/>
       <c r="S324" s="27"/>
-      <c r="T324" s="27"/>
-    </row>
-    <row r="325" customFormat="1" spans="6:20">
+    </row>
+    <row r="325" customFormat="1" spans="6:19">
       <c r="F325" s="24"/>
       <c r="H325" s="52"/>
       <c r="I325" s="52"/>
@@ -14447,9 +14033,8 @@
       <c r="Q325" s="24"/>
       <c r="R325" s="24"/>
       <c r="S325" s="27"/>
-      <c r="T325" s="27"/>
-    </row>
-    <row r="326" customFormat="1" spans="6:20">
+    </row>
+    <row r="326" customFormat="1" spans="6:19">
       <c r="F326" s="24"/>
       <c r="H326" s="52"/>
       <c r="I326" s="52"/>
@@ -14463,9 +14048,8 @@
       <c r="Q326" s="24"/>
       <c r="R326" s="24"/>
       <c r="S326" s="27"/>
-      <c r="T326" s="27"/>
-    </row>
-    <row r="327" customFormat="1" spans="6:20">
+    </row>
+    <row r="327" customFormat="1" spans="6:19">
       <c r="F327" s="24"/>
       <c r="H327" s="52"/>
       <c r="I327" s="52"/>
@@ -14479,9 +14063,8 @@
       <c r="Q327" s="24"/>
       <c r="R327" s="24"/>
       <c r="S327" s="27"/>
-      <c r="T327" s="27"/>
-    </row>
-    <row r="328" customFormat="1" spans="6:20">
+    </row>
+    <row r="328" customFormat="1" spans="6:19">
       <c r="F328" s="24"/>
       <c r="H328" s="52"/>
       <c r="I328" s="52"/>
@@ -14495,9 +14078,8 @@
       <c r="Q328" s="24"/>
       <c r="R328" s="24"/>
       <c r="S328" s="27"/>
-      <c r="T328" s="27"/>
-    </row>
-    <row r="329" customFormat="1" spans="6:20">
+    </row>
+    <row r="329" customFormat="1" spans="6:19">
       <c r="F329" s="24"/>
       <c r="H329" s="52"/>
       <c r="I329" s="52"/>
@@ -14511,9 +14093,8 @@
       <c r="Q329" s="24"/>
       <c r="R329" s="24"/>
       <c r="S329" s="27"/>
-      <c r="T329" s="27"/>
-    </row>
-    <row r="330" customFormat="1" spans="6:20">
+    </row>
+    <row r="330" customFormat="1" spans="6:19">
       <c r="F330" s="24"/>
       <c r="H330" s="52"/>
       <c r="I330" s="52"/>
@@ -14527,9 +14108,8 @@
       <c r="Q330" s="24"/>
       <c r="R330" s="24"/>
       <c r="S330" s="27"/>
-      <c r="T330" s="27"/>
-    </row>
-    <row r="331" customFormat="1" spans="6:20">
+    </row>
+    <row r="331" customFormat="1" spans="6:19">
       <c r="F331" s="24"/>
       <c r="H331" s="52"/>
       <c r="I331" s="52"/>
@@ -14543,9 +14123,8 @@
       <c r="Q331" s="24"/>
       <c r="R331" s="24"/>
       <c r="S331" s="27"/>
-      <c r="T331" s="27"/>
-    </row>
-    <row r="332" customFormat="1" spans="6:20">
+    </row>
+    <row r="332" customFormat="1" spans="6:19">
       <c r="F332" s="24"/>
       <c r="H332" s="52"/>
       <c r="I332" s="52"/>
@@ -14559,9 +14138,8 @@
       <c r="Q332" s="24"/>
       <c r="R332" s="24"/>
       <c r="S332" s="27"/>
-      <c r="T332" s="27"/>
-    </row>
-    <row r="333" customFormat="1" spans="6:20">
+    </row>
+    <row r="333" customFormat="1" spans="6:19">
       <c r="F333" s="24"/>
       <c r="H333" s="52"/>
       <c r="I333" s="52"/>
@@ -14575,9 +14153,8 @@
       <c r="Q333" s="24"/>
       <c r="R333" s="24"/>
       <c r="S333" s="27"/>
-      <c r="T333" s="27"/>
-    </row>
-    <row r="334" customFormat="1" spans="6:20">
+    </row>
+    <row r="334" customFormat="1" spans="6:19">
       <c r="F334" s="24"/>
       <c r="H334" s="52"/>
       <c r="I334" s="52"/>
@@ -14591,9 +14168,8 @@
       <c r="Q334" s="24"/>
       <c r="R334" s="24"/>
       <c r="S334" s="27"/>
-      <c r="T334" s="27"/>
-    </row>
-    <row r="335" customFormat="1" spans="6:20">
+    </row>
+    <row r="335" customFormat="1" spans="6:19">
       <c r="F335" s="24"/>
       <c r="H335" s="52"/>
       <c r="I335" s="52"/>
@@ -14607,9 +14183,8 @@
       <c r="Q335" s="24"/>
       <c r="R335" s="24"/>
       <c r="S335" s="27"/>
-      <c r="T335" s="27"/>
-    </row>
-    <row r="336" customFormat="1" spans="6:20">
+    </row>
+    <row r="336" customFormat="1" spans="6:19">
       <c r="F336" s="24"/>
       <c r="H336" s="52"/>
       <c r="I336" s="52"/>
@@ -14623,9 +14198,8 @@
       <c r="Q336" s="24"/>
       <c r="R336" s="24"/>
       <c r="S336" s="27"/>
-      <c r="T336" s="27"/>
-    </row>
-    <row r="337" customFormat="1" spans="6:20">
+    </row>
+    <row r="337" customFormat="1" spans="6:19">
       <c r="F337" s="24"/>
       <c r="H337" s="52"/>
       <c r="I337" s="52"/>
@@ -14639,9 +14213,8 @@
       <c r="Q337" s="24"/>
       <c r="R337" s="24"/>
       <c r="S337" s="27"/>
-      <c r="T337" s="27"/>
-    </row>
-    <row r="338" customFormat="1" spans="6:20">
+    </row>
+    <row r="338" customFormat="1" spans="6:19">
       <c r="F338" s="24"/>
       <c r="H338" s="52"/>
       <c r="I338" s="52"/>
@@ -14655,9 +14228,8 @@
       <c r="Q338" s="24"/>
       <c r="R338" s="24"/>
       <c r="S338" s="27"/>
-      <c r="T338" s="27"/>
-    </row>
-    <row r="339" customFormat="1" spans="6:20">
+    </row>
+    <row r="339" customFormat="1" spans="6:19">
       <c r="F339" s="24"/>
       <c r="H339" s="52"/>
       <c r="I339" s="52"/>
@@ -14671,9 +14243,8 @@
       <c r="Q339" s="24"/>
       <c r="R339" s="24"/>
       <c r="S339" s="27"/>
-      <c r="T339" s="27"/>
-    </row>
-    <row r="340" customFormat="1" spans="6:20">
+    </row>
+    <row r="340" customFormat="1" spans="6:19">
       <c r="F340" s="24"/>
       <c r="H340" s="52"/>
       <c r="I340" s="52"/>
@@ -14687,9 +14258,8 @@
       <c r="Q340" s="24"/>
       <c r="R340" s="24"/>
       <c r="S340" s="27"/>
-      <c r="T340" s="27"/>
-    </row>
-    <row r="341" customFormat="1" spans="6:20">
+    </row>
+    <row r="341" customFormat="1" spans="6:19">
       <c r="F341" s="24"/>
       <c r="H341" s="52"/>
       <c r="I341" s="52"/>
@@ -14703,9 +14273,8 @@
       <c r="Q341" s="24"/>
       <c r="R341" s="24"/>
       <c r="S341" s="27"/>
-      <c r="T341" s="27"/>
-    </row>
-    <row r="342" customFormat="1" spans="6:20">
+    </row>
+    <row r="342" customFormat="1" spans="6:19">
       <c r="F342" s="24"/>
       <c r="H342" s="52"/>
       <c r="I342" s="52"/>
@@ -14719,9 +14288,8 @@
       <c r="Q342" s="24"/>
       <c r="R342" s="24"/>
       <c r="S342" s="27"/>
-      <c r="T342" s="27"/>
-    </row>
-    <row r="343" customFormat="1" spans="6:20">
+    </row>
+    <row r="343" customFormat="1" spans="6:19">
       <c r="F343" s="24"/>
       <c r="H343" s="52"/>
       <c r="I343" s="52"/>
@@ -14735,9 +14303,8 @@
       <c r="Q343" s="24"/>
       <c r="R343" s="24"/>
       <c r="S343" s="27"/>
-      <c r="T343" s="27"/>
-    </row>
-    <row r="344" customFormat="1" spans="6:20">
+    </row>
+    <row r="344" customFormat="1" spans="6:19">
       <c r="F344" s="24"/>
       <c r="H344" s="52"/>
       <c r="I344" s="52"/>
@@ -14751,9 +14318,8 @@
       <c r="Q344" s="24"/>
       <c r="R344" s="24"/>
       <c r="S344" s="27"/>
-      <c r="T344" s="27"/>
-    </row>
-    <row r="345" customFormat="1" spans="6:20">
+    </row>
+    <row r="345" customFormat="1" spans="6:19">
       <c r="F345" s="24"/>
       <c r="H345" s="52"/>
       <c r="I345" s="52"/>
@@ -14767,9 +14333,8 @@
       <c r="Q345" s="24"/>
       <c r="R345" s="24"/>
       <c r="S345" s="27"/>
-      <c r="T345" s="27"/>
-    </row>
-    <row r="346" customFormat="1" spans="6:20">
+    </row>
+    <row r="346" customFormat="1" spans="6:19">
       <c r="F346" s="24"/>
       <c r="H346" s="52"/>
       <c r="I346" s="52"/>
@@ -14783,9 +14348,8 @@
       <c r="Q346" s="24"/>
       <c r="R346" s="24"/>
       <c r="S346" s="27"/>
-      <c r="T346" s="27"/>
-    </row>
-    <row r="347" customFormat="1" spans="6:20">
+    </row>
+    <row r="347" customFormat="1" spans="6:19">
       <c r="F347" s="24"/>
       <c r="H347" s="52"/>
       <c r="I347" s="52"/>
@@ -14799,9 +14363,8 @@
       <c r="Q347" s="24"/>
       <c r="R347" s="24"/>
       <c r="S347" s="27"/>
-      <c r="T347" s="27"/>
-    </row>
-    <row r="348" customFormat="1" spans="6:20">
+    </row>
+    <row r="348" customFormat="1" spans="6:19">
       <c r="F348" s="24"/>
       <c r="H348" s="52"/>
       <c r="I348" s="52"/>
@@ -14815,9 +14378,8 @@
       <c r="Q348" s="24"/>
       <c r="R348" s="24"/>
       <c r="S348" s="27"/>
-      <c r="T348" s="27"/>
-    </row>
-    <row r="349" customFormat="1" spans="6:20">
+    </row>
+    <row r="349" customFormat="1" spans="6:19">
       <c r="F349" s="24"/>
       <c r="H349" s="52"/>
       <c r="I349" s="52"/>
@@ -14831,9 +14393,8 @@
       <c r="Q349" s="24"/>
       <c r="R349" s="24"/>
       <c r="S349" s="27"/>
-      <c r="T349" s="27"/>
-    </row>
-    <row r="350" customFormat="1" spans="6:20">
+    </row>
+    <row r="350" customFormat="1" spans="6:19">
       <c r="F350" s="24"/>
       <c r="H350" s="52"/>
       <c r="I350" s="52"/>
@@ -14847,9 +14408,8 @@
       <c r="Q350" s="24"/>
       <c r="R350" s="24"/>
       <c r="S350" s="27"/>
-      <c r="T350" s="27"/>
-    </row>
-    <row r="351" customFormat="1" spans="6:20">
+    </row>
+    <row r="351" customFormat="1" spans="6:19">
       <c r="F351" s="24"/>
       <c r="H351" s="52"/>
       <c r="I351" s="52"/>
@@ -14863,9 +14423,8 @@
       <c r="Q351" s="24"/>
       <c r="R351" s="24"/>
       <c r="S351" s="27"/>
-      <c r="T351" s="27"/>
-    </row>
-    <row r="352" customFormat="1" spans="6:20">
+    </row>
+    <row r="352" customFormat="1" spans="6:19">
       <c r="F352" s="24"/>
       <c r="H352" s="52"/>
       <c r="I352" s="52"/>
@@ -14879,9 +14438,8 @@
       <c r="Q352" s="24"/>
       <c r="R352" s="24"/>
       <c r="S352" s="27"/>
-      <c r="T352" s="27"/>
-    </row>
-    <row r="353" customFormat="1" spans="6:20">
+    </row>
+    <row r="353" customFormat="1" spans="6:19">
       <c r="F353" s="24"/>
       <c r="H353" s="52"/>
       <c r="I353" s="52"/>
@@ -14895,9 +14453,8 @@
       <c r="Q353" s="24"/>
       <c r="R353" s="24"/>
       <c r="S353" s="27"/>
-      <c r="T353" s="27"/>
-    </row>
-    <row r="354" customFormat="1" spans="6:20">
+    </row>
+    <row r="354" customFormat="1" spans="6:19">
       <c r="F354" s="24"/>
       <c r="H354" s="52"/>
       <c r="I354" s="52"/>
@@ -14911,9 +14468,8 @@
       <c r="Q354" s="24"/>
       <c r="R354" s="24"/>
       <c r="S354" s="27"/>
-      <c r="T354" s="27"/>
-    </row>
-    <row r="355" customFormat="1" spans="6:20">
+    </row>
+    <row r="355" customFormat="1" spans="6:19">
       <c r="F355" s="24"/>
       <c r="H355" s="52"/>
       <c r="I355" s="52"/>
@@ -14927,9 +14483,8 @@
       <c r="Q355" s="24"/>
       <c r="R355" s="24"/>
       <c r="S355" s="27"/>
-      <c r="T355" s="27"/>
-    </row>
-    <row r="356" customFormat="1" spans="6:20">
+    </row>
+    <row r="356" customFormat="1" spans="6:19">
       <c r="F356" s="24"/>
       <c r="H356" s="52"/>
       <c r="I356" s="52"/>
@@ -14943,9 +14498,8 @@
       <c r="Q356" s="24"/>
       <c r="R356" s="24"/>
       <c r="S356" s="27"/>
-      <c r="T356" s="27"/>
-    </row>
-    <row r="357" customFormat="1" spans="6:20">
+    </row>
+    <row r="357" customFormat="1" spans="6:19">
       <c r="F357" s="24"/>
       <c r="H357" s="52"/>
       <c r="I357" s="52"/>
@@ -14959,9 +14513,8 @@
       <c r="Q357" s="24"/>
       <c r="R357" s="24"/>
       <c r="S357" s="27"/>
-      <c r="T357" s="27"/>
-    </row>
-    <row r="358" customFormat="1" spans="6:20">
+    </row>
+    <row r="358" customFormat="1" spans="6:19">
       <c r="F358" s="24"/>
       <c r="H358" s="52"/>
       <c r="I358" s="52"/>
@@ -14975,9 +14528,8 @@
       <c r="Q358" s="24"/>
       <c r="R358" s="24"/>
       <c r="S358" s="27"/>
-      <c r="T358" s="27"/>
-    </row>
-    <row r="359" customFormat="1" spans="6:20">
+    </row>
+    <row r="359" customFormat="1" spans="6:19">
       <c r="F359" s="24"/>
       <c r="H359" s="52"/>
       <c r="I359" s="52"/>
@@ -14991,9 +14543,8 @@
       <c r="Q359" s="24"/>
       <c r="R359" s="24"/>
       <c r="S359" s="27"/>
-      <c r="T359" s="27"/>
-    </row>
-    <row r="360" customFormat="1" spans="6:20">
+    </row>
+    <row r="360" customFormat="1" spans="6:19">
       <c r="F360" s="24"/>
       <c r="H360" s="52"/>
       <c r="I360" s="52"/>
@@ -15007,9 +14558,8 @@
       <c r="Q360" s="24"/>
       <c r="R360" s="24"/>
       <c r="S360" s="27"/>
-      <c r="T360" s="27"/>
-    </row>
-    <row r="361" customFormat="1" spans="6:20">
+    </row>
+    <row r="361" customFormat="1" spans="6:19">
       <c r="F361" s="24"/>
       <c r="H361" s="52"/>
       <c r="I361" s="52"/>
@@ -15023,9 +14573,8 @@
       <c r="Q361" s="24"/>
       <c r="R361" s="24"/>
       <c r="S361" s="27"/>
-      <c r="T361" s="27"/>
-    </row>
-    <row r="362" customFormat="1" spans="6:20">
+    </row>
+    <row r="362" customFormat="1" spans="6:19">
       <c r="F362" s="24"/>
       <c r="H362" s="52"/>
       <c r="I362" s="52"/>
@@ -15039,9 +14588,8 @@
       <c r="Q362" s="24"/>
       <c r="R362" s="24"/>
       <c r="S362" s="27"/>
-      <c r="T362" s="27"/>
-    </row>
-    <row r="363" customFormat="1" spans="6:20">
+    </row>
+    <row r="363" customFormat="1" spans="6:19">
       <c r="F363" s="24"/>
       <c r="H363" s="52"/>
       <c r="I363" s="52"/>
@@ -15055,9 +14603,8 @@
       <c r="Q363" s="24"/>
       <c r="R363" s="24"/>
       <c r="S363" s="27"/>
-      <c r="T363" s="27"/>
-    </row>
-    <row r="364" customFormat="1" spans="6:20">
+    </row>
+    <row r="364" customFormat="1" spans="6:19">
       <c r="F364" s="24"/>
       <c r="H364" s="52"/>
       <c r="I364" s="52"/>
@@ -15071,9 +14618,8 @@
       <c r="Q364" s="24"/>
       <c r="R364" s="24"/>
       <c r="S364" s="27"/>
-      <c r="T364" s="27"/>
-    </row>
-    <row r="365" customFormat="1" spans="6:20">
+    </row>
+    <row r="365" customFormat="1" spans="6:19">
       <c r="F365" s="24"/>
       <c r="H365" s="52"/>
       <c r="I365" s="52"/>
@@ -15087,9 +14633,8 @@
       <c r="Q365" s="24"/>
       <c r="R365" s="24"/>
       <c r="S365" s="27"/>
-      <c r="T365" s="27"/>
-    </row>
-    <row r="366" customFormat="1" spans="6:20">
+    </row>
+    <row r="366" customFormat="1" spans="6:19">
       <c r="F366" s="24"/>
       <c r="H366" s="52"/>
       <c r="I366" s="52"/>
@@ -15103,9 +14648,8 @@
       <c r="Q366" s="24"/>
       <c r="R366" s="24"/>
       <c r="S366" s="27"/>
-      <c r="T366" s="27"/>
-    </row>
-    <row r="367" customFormat="1" spans="6:20">
+    </row>
+    <row r="367" customFormat="1" spans="6:19">
       <c r="F367" s="24"/>
       <c r="H367" s="52"/>
       <c r="I367" s="52"/>
@@ -15119,9 +14663,8 @@
       <c r="Q367" s="24"/>
       <c r="R367" s="24"/>
       <c r="S367" s="27"/>
-      <c r="T367" s="27"/>
-    </row>
-    <row r="368" customFormat="1" spans="6:20">
+    </row>
+    <row r="368" customFormat="1" spans="6:19">
       <c r="F368" s="24"/>
       <c r="H368" s="52"/>
       <c r="I368" s="52"/>
@@ -15135,9 +14678,8 @@
       <c r="Q368" s="24"/>
       <c r="R368" s="24"/>
       <c r="S368" s="27"/>
-      <c r="T368" s="27"/>
-    </row>
-    <row r="369" customFormat="1" spans="6:20">
+    </row>
+    <row r="369" customFormat="1" spans="6:19">
       <c r="F369" s="24"/>
       <c r="H369" s="52"/>
       <c r="I369" s="52"/>
@@ -15151,9 +14693,8 @@
       <c r="Q369" s="24"/>
       <c r="R369" s="24"/>
       <c r="S369" s="27"/>
-      <c r="T369" s="27"/>
-    </row>
-    <row r="370" customFormat="1" spans="6:20">
+    </row>
+    <row r="370" customFormat="1" spans="6:19">
       <c r="F370" s="24"/>
       <c r="H370" s="52"/>
       <c r="I370" s="52"/>
@@ -15167,9 +14708,8 @@
       <c r="Q370" s="24"/>
       <c r="R370" s="24"/>
       <c r="S370" s="27"/>
-      <c r="T370" s="27"/>
-    </row>
-    <row r="371" customFormat="1" spans="6:20">
+    </row>
+    <row r="371" customFormat="1" spans="6:19">
       <c r="F371" s="24"/>
       <c r="H371" s="52"/>
       <c r="I371" s="52"/>
@@ -15183,9 +14723,8 @@
       <c r="Q371" s="24"/>
       <c r="R371" s="24"/>
       <c r="S371" s="27"/>
-      <c r="T371" s="27"/>
-    </row>
-    <row r="372" customFormat="1" spans="6:20">
+    </row>
+    <row r="372" customFormat="1" spans="6:19">
       <c r="F372" s="24"/>
       <c r="H372" s="52"/>
       <c r="I372" s="52"/>
@@ -15199,9 +14738,8 @@
       <c r="Q372" s="24"/>
       <c r="R372" s="24"/>
       <c r="S372" s="27"/>
-      <c r="T372" s="27"/>
-    </row>
-    <row r="373" customFormat="1" spans="6:20">
+    </row>
+    <row r="373" customFormat="1" spans="6:19">
       <c r="F373" s="24"/>
       <c r="H373" s="52"/>
       <c r="I373" s="52"/>
@@ -15215,9 +14753,8 @@
       <c r="Q373" s="24"/>
       <c r="R373" s="24"/>
       <c r="S373" s="27"/>
-      <c r="T373" s="27"/>
-    </row>
-    <row r="374" customFormat="1" spans="6:20">
+    </row>
+    <row r="374" customFormat="1" spans="6:19">
       <c r="F374" s="24"/>
       <c r="H374" s="52"/>
       <c r="I374" s="52"/>
@@ -15231,9 +14768,8 @@
       <c r="Q374" s="24"/>
       <c r="R374" s="24"/>
       <c r="S374" s="27"/>
-      <c r="T374" s="27"/>
-    </row>
-    <row r="375" customFormat="1" spans="6:20">
+    </row>
+    <row r="375" customFormat="1" spans="6:19">
       <c r="F375" s="24"/>
       <c r="H375" s="52"/>
       <c r="I375" s="52"/>
@@ -15247,9 +14783,8 @@
       <c r="Q375" s="24"/>
       <c r="R375" s="24"/>
       <c r="S375" s="27"/>
-      <c r="T375" s="27"/>
-    </row>
-    <row r="376" customFormat="1" spans="6:20">
+    </row>
+    <row r="376" customFormat="1" spans="6:19">
       <c r="F376" s="24"/>
       <c r="H376" s="52"/>
       <c r="I376" s="52"/>
@@ -15263,9 +14798,8 @@
       <c r="Q376" s="24"/>
       <c r="R376" s="24"/>
       <c r="S376" s="27"/>
-      <c r="T376" s="27"/>
-    </row>
-    <row r="377" customFormat="1" spans="6:20">
+    </row>
+    <row r="377" customFormat="1" spans="6:19">
       <c r="F377" s="24"/>
       <c r="H377" s="52"/>
       <c r="I377" s="52"/>
@@ -15279,9 +14813,8 @@
       <c r="Q377" s="24"/>
       <c r="R377" s="24"/>
       <c r="S377" s="27"/>
-      <c r="T377" s="27"/>
-    </row>
-    <row r="378" customFormat="1" spans="6:20">
+    </row>
+    <row r="378" customFormat="1" spans="6:19">
       <c r="F378" s="24"/>
       <c r="H378" s="52"/>
       <c r="I378" s="52"/>
@@ -15295,9 +14828,8 @@
       <c r="Q378" s="24"/>
       <c r="R378" s="24"/>
       <c r="S378" s="27"/>
-      <c r="T378" s="27"/>
-    </row>
-    <row r="379" customFormat="1" spans="6:20">
+    </row>
+    <row r="379" customFormat="1" spans="6:19">
       <c r="F379" s="24"/>
       <c r="H379" s="52"/>
       <c r="I379" s="52"/>
@@ -15311,9 +14843,8 @@
       <c r="Q379" s="24"/>
       <c r="R379" s="24"/>
       <c r="S379" s="27"/>
-      <c r="T379" s="27"/>
-    </row>
-    <row r="380" customFormat="1" spans="6:20">
+    </row>
+    <row r="380" customFormat="1" spans="6:19">
       <c r="F380" s="24"/>
       <c r="H380" s="52"/>
       <c r="I380" s="52"/>
@@ -15327,9 +14858,8 @@
       <c r="Q380" s="24"/>
       <c r="R380" s="24"/>
       <c r="S380" s="27"/>
-      <c r="T380" s="27"/>
-    </row>
-    <row r="381" customFormat="1" spans="6:20">
+    </row>
+    <row r="381" customFormat="1" spans="6:19">
       <c r="F381" s="24"/>
       <c r="H381" s="52"/>
       <c r="I381" s="52"/>
@@ -15343,9 +14873,8 @@
       <c r="Q381" s="24"/>
       <c r="R381" s="24"/>
       <c r="S381" s="27"/>
-      <c r="T381" s="27"/>
-    </row>
-    <row r="382" customFormat="1" spans="6:20">
+    </row>
+    <row r="382" customFormat="1" spans="6:19">
       <c r="F382" s="24"/>
       <c r="H382" s="52"/>
       <c r="I382" s="52"/>
@@ -15359,9 +14888,8 @@
       <c r="Q382" s="24"/>
       <c r="R382" s="24"/>
       <c r="S382" s="27"/>
-      <c r="T382" s="27"/>
-    </row>
-    <row r="383" customFormat="1" spans="6:20">
+    </row>
+    <row r="383" customFormat="1" spans="6:19">
       <c r="F383" s="24"/>
       <c r="H383" s="52"/>
       <c r="I383" s="52"/>
@@ -15375,9 +14903,8 @@
       <c r="Q383" s="24"/>
       <c r="R383" s="24"/>
       <c r="S383" s="27"/>
-      <c r="T383" s="27"/>
-    </row>
-    <row r="384" customFormat="1" spans="6:20">
+    </row>
+    <row r="384" customFormat="1" spans="6:19">
       <c r="F384" s="24"/>
       <c r="H384" s="52"/>
       <c r="I384" s="52"/>
@@ -15391,9 +14918,8 @@
       <c r="Q384" s="24"/>
       <c r="R384" s="24"/>
       <c r="S384" s="27"/>
-      <c r="T384" s="27"/>
-    </row>
-    <row r="385" customFormat="1" spans="6:20">
+    </row>
+    <row r="385" customFormat="1" spans="6:19">
       <c r="F385" s="24"/>
       <c r="H385" s="52"/>
       <c r="I385" s="52"/>
@@ -15407,9 +14933,8 @@
       <c r="Q385" s="24"/>
       <c r="R385" s="24"/>
       <c r="S385" s="27"/>
-      <c r="T385" s="27"/>
-    </row>
-    <row r="386" customFormat="1" spans="6:20">
+    </row>
+    <row r="386" customFormat="1" spans="6:19">
       <c r="F386" s="24"/>
       <c r="H386" s="52"/>
       <c r="I386" s="52"/>
@@ -15423,9 +14948,8 @@
       <c r="Q386" s="24"/>
       <c r="R386" s="24"/>
       <c r="S386" s="27"/>
-      <c r="T386" s="27"/>
-    </row>
-    <row r="387" customFormat="1" spans="6:20">
+    </row>
+    <row r="387" customFormat="1" spans="6:19">
       <c r="F387" s="24"/>
       <c r="H387" s="52"/>
       <c r="I387" s="52"/>
@@ -15439,9 +14963,8 @@
       <c r="Q387" s="24"/>
       <c r="R387" s="24"/>
       <c r="S387" s="27"/>
-      <c r="T387" s="27"/>
-    </row>
-    <row r="388" customFormat="1" spans="6:20">
+    </row>
+    <row r="388" customFormat="1" spans="6:19">
       <c r="F388" s="24"/>
       <c r="H388" s="52"/>
       <c r="I388" s="52"/>
@@ -15455,9 +14978,8 @@
       <c r="Q388" s="24"/>
       <c r="R388" s="24"/>
       <c r="S388" s="27"/>
-      <c r="T388" s="27"/>
-    </row>
-    <row r="389" customFormat="1" spans="6:20">
+    </row>
+    <row r="389" customFormat="1" spans="6:19">
       <c r="F389" s="24"/>
       <c r="H389" s="52"/>
       <c r="I389" s="52"/>
@@ -15471,9 +14993,8 @@
       <c r="Q389" s="24"/>
       <c r="R389" s="24"/>
       <c r="S389" s="27"/>
-      <c r="T389" s="27"/>
-    </row>
-    <row r="390" customFormat="1" spans="6:20">
+    </row>
+    <row r="390" customFormat="1" spans="6:19">
       <c r="F390" s="24"/>
       <c r="H390" s="52"/>
       <c r="I390" s="52"/>
@@ -15487,9 +15008,8 @@
       <c r="Q390" s="24"/>
       <c r="R390" s="24"/>
       <c r="S390" s="27"/>
-      <c r="T390" s="27"/>
-    </row>
-    <row r="391" customFormat="1" spans="6:20">
+    </row>
+    <row r="391" customFormat="1" spans="6:19">
       <c r="F391" s="24"/>
       <c r="H391" s="52"/>
       <c r="I391" s="52"/>
@@ -15503,9 +15023,8 @@
       <c r="Q391" s="24"/>
       <c r="R391" s="24"/>
       <c r="S391" s="27"/>
-      <c r="T391" s="27"/>
-    </row>
-    <row r="392" customFormat="1" spans="6:20">
+    </row>
+    <row r="392" customFormat="1" spans="6:19">
       <c r="F392" s="24"/>
       <c r="H392" s="52"/>
       <c r="I392" s="52"/>
@@ -15519,9 +15038,8 @@
       <c r="Q392" s="24"/>
       <c r="R392" s="24"/>
       <c r="S392" s="27"/>
-      <c r="T392" s="27"/>
-    </row>
-    <row r="393" customFormat="1" spans="6:20">
+    </row>
+    <row r="393" customFormat="1" spans="6:19">
       <c r="F393" s="24"/>
       <c r="H393" s="52"/>
       <c r="I393" s="52"/>
@@ -15535,9 +15053,8 @@
       <c r="Q393" s="24"/>
       <c r="R393" s="24"/>
       <c r="S393" s="27"/>
-      <c r="T393" s="27"/>
-    </row>
-    <row r="394" customFormat="1" spans="6:20">
+    </row>
+    <row r="394" customFormat="1" spans="6:19">
       <c r="F394" s="24"/>
       <c r="H394" s="52"/>
       <c r="I394" s="52"/>
@@ -15551,9 +15068,8 @@
       <c r="Q394" s="24"/>
       <c r="R394" s="24"/>
       <c r="S394" s="27"/>
-      <c r="T394" s="27"/>
-    </row>
-    <row r="395" customFormat="1" spans="6:20">
+    </row>
+    <row r="395" customFormat="1" spans="6:19">
       <c r="F395" s="24"/>
       <c r="H395" s="52"/>
       <c r="I395" s="52"/>
@@ -15567,9 +15083,8 @@
       <c r="Q395" s="24"/>
       <c r="R395" s="24"/>
       <c r="S395" s="27"/>
-      <c r="T395" s="27"/>
-    </row>
-    <row r="396" customFormat="1" spans="6:20">
+    </row>
+    <row r="396" customFormat="1" spans="6:19">
       <c r="F396" s="24"/>
       <c r="H396" s="52"/>
       <c r="I396" s="52"/>
@@ -15583,9 +15098,8 @@
       <c r="Q396" s="24"/>
       <c r="R396" s="24"/>
       <c r="S396" s="27"/>
-      <c r="T396" s="27"/>
-    </row>
-    <row r="397" customFormat="1" spans="6:20">
+    </row>
+    <row r="397" customFormat="1" spans="6:19">
       <c r="F397" s="24"/>
       <c r="H397" s="52"/>
       <c r="I397" s="52"/>
@@ -15599,9 +15113,8 @@
       <c r="Q397" s="24"/>
       <c r="R397" s="24"/>
       <c r="S397" s="27"/>
-      <c r="T397" s="27"/>
-    </row>
-    <row r="398" customFormat="1" spans="6:20">
+    </row>
+    <row r="398" customFormat="1" spans="6:19">
       <c r="F398" s="24"/>
       <c r="H398" s="52"/>
       <c r="I398" s="52"/>
@@ -15615,9 +15128,8 @@
       <c r="Q398" s="24"/>
       <c r="R398" s="24"/>
       <c r="S398" s="27"/>
-      <c r="T398" s="27"/>
-    </row>
-    <row r="399" customFormat="1" spans="6:20">
+    </row>
+    <row r="399" customFormat="1" spans="6:19">
       <c r="F399" s="24"/>
       <c r="H399" s="52"/>
       <c r="I399" s="52"/>
@@ -15631,9 +15143,8 @@
       <c r="Q399" s="24"/>
       <c r="R399" s="24"/>
       <c r="S399" s="27"/>
-      <c r="T399" s="27"/>
-    </row>
-    <row r="400" customFormat="1" spans="6:20">
+    </row>
+    <row r="400" customFormat="1" spans="6:19">
       <c r="F400" s="24"/>
       <c r="H400" s="52"/>
       <c r="I400" s="52"/>
@@ -15647,9 +15158,8 @@
       <c r="Q400" s="24"/>
       <c r="R400" s="24"/>
       <c r="S400" s="27"/>
-      <c r="T400" s="27"/>
-    </row>
-    <row r="401" customFormat="1" spans="6:20">
+    </row>
+    <row r="401" customFormat="1" spans="6:19">
       <c r="F401" s="24"/>
       <c r="H401" s="52"/>
       <c r="I401" s="52"/>
@@ -15663,9 +15173,8 @@
       <c r="Q401" s="24"/>
       <c r="R401" s="24"/>
       <c r="S401" s="27"/>
-      <c r="T401" s="27"/>
-    </row>
-    <row r="402" customFormat="1" spans="6:20">
+    </row>
+    <row r="402" customFormat="1" spans="6:19">
       <c r="F402" s="24"/>
       <c r="H402" s="52"/>
       <c r="I402" s="52"/>
@@ -15679,9 +15188,8 @@
       <c r="Q402" s="24"/>
       <c r="R402" s="24"/>
       <c r="S402" s="27"/>
-      <c r="T402" s="27"/>
-    </row>
-    <row r="403" customFormat="1" spans="6:20">
+    </row>
+    <row r="403" customFormat="1" spans="6:19">
       <c r="F403" s="24"/>
       <c r="H403" s="52"/>
       <c r="I403" s="52"/>
@@ -15695,9 +15203,8 @@
       <c r="Q403" s="24"/>
       <c r="R403" s="24"/>
       <c r="S403" s="27"/>
-      <c r="T403" s="27"/>
-    </row>
-    <row r="404" customFormat="1" spans="6:20">
+    </row>
+    <row r="404" customFormat="1" spans="6:19">
       <c r="F404" s="24"/>
       <c r="H404" s="52"/>
       <c r="I404" s="52"/>
@@ -15711,9 +15218,8 @@
       <c r="Q404" s="24"/>
       <c r="R404" s="24"/>
       <c r="S404" s="27"/>
-      <c r="T404" s="27"/>
-    </row>
-    <row r="405" customFormat="1" spans="6:20">
+    </row>
+    <row r="405" customFormat="1" spans="6:19">
       <c r="F405" s="24"/>
       <c r="H405" s="52"/>
       <c r="I405" s="52"/>
@@ -15727,9 +15233,8 @@
       <c r="Q405" s="24"/>
       <c r="R405" s="24"/>
       <c r="S405" s="27"/>
-      <c r="T405" s="27"/>
-    </row>
-    <row r="406" customFormat="1" spans="6:20">
+    </row>
+    <row r="406" customFormat="1" spans="6:19">
       <c r="F406" s="24"/>
       <c r="H406" s="52"/>
       <c r="I406" s="52"/>
@@ -15743,9 +15248,8 @@
       <c r="Q406" s="24"/>
       <c r="R406" s="24"/>
       <c r="S406" s="27"/>
-      <c r="T406" s="27"/>
-    </row>
-    <row r="407" customFormat="1" spans="6:20">
+    </row>
+    <row r="407" customFormat="1" spans="6:19">
       <c r="F407" s="24"/>
       <c r="H407" s="52"/>
       <c r="I407" s="52"/>
@@ -15759,9 +15263,8 @@
       <c r="Q407" s="24"/>
       <c r="R407" s="24"/>
       <c r="S407" s="27"/>
-      <c r="T407" s="27"/>
-    </row>
-    <row r="408" customFormat="1" spans="6:20">
+    </row>
+    <row r="408" customFormat="1" spans="6:19">
       <c r="F408" s="24"/>
       <c r="H408" s="52"/>
       <c r="I408" s="52"/>
@@ -15775,9 +15278,8 @@
       <c r="Q408" s="24"/>
       <c r="R408" s="24"/>
       <c r="S408" s="27"/>
-      <c r="T408" s="27"/>
-    </row>
-    <row r="409" customFormat="1" spans="6:20">
+    </row>
+    <row r="409" customFormat="1" spans="6:19">
       <c r="F409" s="24"/>
       <c r="H409" s="52"/>
       <c r="I409" s="52"/>
@@ -15791,9 +15293,8 @@
       <c r="Q409" s="24"/>
       <c r="R409" s="24"/>
       <c r="S409" s="27"/>
-      <c r="T409" s="27"/>
-    </row>
-    <row r="410" customFormat="1" spans="6:20">
+    </row>
+    <row r="410" customFormat="1" spans="6:19">
       <c r="F410" s="24"/>
       <c r="H410" s="52"/>
       <c r="I410" s="52"/>
@@ -15807,9 +15308,8 @@
       <c r="Q410" s="24"/>
       <c r="R410" s="24"/>
       <c r="S410" s="27"/>
-      <c r="T410" s="27"/>
-    </row>
-    <row r="411" customFormat="1" spans="6:20">
+    </row>
+    <row r="411" customFormat="1" spans="6:19">
       <c r="F411" s="24"/>
       <c r="H411" s="52"/>
       <c r="I411" s="52"/>
@@ -15823,9 +15323,8 @@
       <c r="Q411" s="24"/>
       <c r="R411" s="24"/>
       <c r="S411" s="27"/>
-      <c r="T411" s="27"/>
-    </row>
-    <row r="412" customFormat="1" spans="6:20">
+    </row>
+    <row r="412" customFormat="1" spans="6:19">
       <c r="F412" s="24"/>
       <c r="H412" s="52"/>
       <c r="I412" s="52"/>
@@ -15839,9 +15338,8 @@
       <c r="Q412" s="24"/>
       <c r="R412" s="24"/>
       <c r="S412" s="27"/>
-      <c r="T412" s="27"/>
-    </row>
-    <row r="413" customFormat="1" spans="6:20">
+    </row>
+    <row r="413" customFormat="1" spans="6:19">
       <c r="F413" s="24"/>
       <c r="H413" s="52"/>
       <c r="I413" s="52"/>
@@ -15855,9 +15353,8 @@
       <c r="Q413" s="24"/>
       <c r="R413" s="24"/>
       <c r="S413" s="27"/>
-      <c r="T413" s="27"/>
-    </row>
-    <row r="414" customFormat="1" spans="6:20">
+    </row>
+    <row r="414" customFormat="1" spans="6:19">
       <c r="F414" s="24"/>
       <c r="H414" s="52"/>
       <c r="I414" s="52"/>
@@ -15871,9 +15368,8 @@
       <c r="Q414" s="24"/>
       <c r="R414" s="24"/>
       <c r="S414" s="27"/>
-      <c r="T414" s="27"/>
-    </row>
-    <row r="415" customFormat="1" spans="6:20">
+    </row>
+    <row r="415" customFormat="1" spans="6:19">
       <c r="F415" s="24"/>
       <c r="H415" s="52"/>
       <c r="I415" s="52"/>
@@ -15887,9 +15383,8 @@
       <c r="Q415" s="24"/>
       <c r="R415" s="24"/>
       <c r="S415" s="27"/>
-      <c r="T415" s="27"/>
-    </row>
-    <row r="416" customFormat="1" spans="6:20">
+    </row>
+    <row r="416" customFormat="1" spans="6:19">
       <c r="F416" s="24"/>
       <c r="H416" s="52"/>
       <c r="I416" s="52"/>
@@ -15903,9 +15398,8 @@
       <c r="Q416" s="24"/>
       <c r="R416" s="24"/>
       <c r="S416" s="27"/>
-      <c r="T416" s="27"/>
-    </row>
-    <row r="417" customFormat="1" spans="6:20">
+    </row>
+    <row r="417" customFormat="1" spans="6:19">
       <c r="F417" s="24"/>
       <c r="H417" s="52"/>
       <c r="I417" s="52"/>
@@ -15919,9 +15413,8 @@
       <c r="Q417" s="24"/>
       <c r="R417" s="24"/>
       <c r="S417" s="27"/>
-      <c r="T417" s="27"/>
-    </row>
-    <row r="418" customFormat="1" spans="6:20">
+    </row>
+    <row r="418" customFormat="1" spans="6:19">
       <c r="F418" s="24"/>
       <c r="H418" s="52"/>
       <c r="I418" s="52"/>
@@ -15935,9 +15428,8 @@
       <c r="Q418" s="24"/>
       <c r="R418" s="24"/>
       <c r="S418" s="27"/>
-      <c r="T418" s="27"/>
-    </row>
-    <row r="419" customFormat="1" spans="6:20">
+    </row>
+    <row r="419" customFormat="1" spans="6:19">
       <c r="F419" s="24"/>
       <c r="H419" s="52"/>
       <c r="I419" s="52"/>
@@ -15951,9 +15443,8 @@
       <c r="Q419" s="24"/>
       <c r="R419" s="24"/>
       <c r="S419" s="27"/>
-      <c r="T419" s="27"/>
-    </row>
-    <row r="420" customFormat="1" spans="6:20">
+    </row>
+    <row r="420" customFormat="1" spans="6:19">
       <c r="F420" s="24"/>
       <c r="H420" s="52"/>
       <c r="I420" s="52"/>
@@ -15967,9 +15458,8 @@
       <c r="Q420" s="24"/>
       <c r="R420" s="24"/>
       <c r="S420" s="27"/>
-      <c r="T420" s="27"/>
-    </row>
-    <row r="421" customFormat="1" spans="6:20">
+    </row>
+    <row r="421" customFormat="1" spans="6:19">
       <c r="F421" s="24"/>
       <c r="H421" s="52"/>
       <c r="I421" s="52"/>
@@ -15983,9 +15473,8 @@
       <c r="Q421" s="24"/>
       <c r="R421" s="24"/>
       <c r="S421" s="27"/>
-      <c r="T421" s="27"/>
-    </row>
-    <row r="422" customFormat="1" spans="6:20">
+    </row>
+    <row r="422" customFormat="1" spans="6:19">
       <c r="F422" s="24"/>
       <c r="H422" s="52"/>
       <c r="I422" s="52"/>
@@ -15999,9 +15488,8 @@
       <c r="Q422" s="24"/>
       <c r="R422" s="24"/>
       <c r="S422" s="27"/>
-      <c r="T422" s="27"/>
-    </row>
-    <row r="423" customFormat="1" spans="6:20">
+    </row>
+    <row r="423" customFormat="1" spans="6:19">
       <c r="F423" s="24"/>
       <c r="H423" s="52"/>
       <c r="I423" s="52"/>
@@ -16015,9 +15503,8 @@
       <c r="Q423" s="24"/>
       <c r="R423" s="24"/>
       <c r="S423" s="27"/>
-      <c r="T423" s="27"/>
-    </row>
-    <row r="424" customFormat="1" spans="6:20">
+    </row>
+    <row r="424" customFormat="1" spans="6:19">
       <c r="F424" s="24"/>
       <c r="H424" s="52"/>
       <c r="I424" s="52"/>
@@ -16031,9 +15518,8 @@
       <c r="Q424" s="24"/>
       <c r="R424" s="24"/>
       <c r="S424" s="27"/>
-      <c r="T424" s="27"/>
-    </row>
-    <row r="425" customFormat="1" spans="6:20">
+    </row>
+    <row r="425" customFormat="1" spans="6:19">
       <c r="F425" s="24"/>
       <c r="H425" s="52"/>
       <c r="I425" s="52"/>
@@ -16047,9 +15533,8 @@
       <c r="Q425" s="24"/>
       <c r="R425" s="24"/>
       <c r="S425" s="27"/>
-      <c r="T425" s="27"/>
-    </row>
-    <row r="426" customFormat="1" spans="6:20">
+    </row>
+    <row r="426" customFormat="1" spans="6:19">
       <c r="F426" s="24"/>
       <c r="H426" s="52"/>
       <c r="I426" s="52"/>
@@ -16063,9 +15548,8 @@
       <c r="Q426" s="24"/>
       <c r="R426" s="24"/>
       <c r="S426" s="27"/>
-      <c r="T426" s="27"/>
-    </row>
-    <row r="427" customFormat="1" spans="6:20">
+    </row>
+    <row r="427" customFormat="1" spans="6:19">
       <c r="F427" s="24"/>
       <c r="H427" s="52"/>
       <c r="I427" s="52"/>
@@ -16079,9 +15563,8 @@
       <c r="Q427" s="24"/>
       <c r="R427" s="24"/>
       <c r="S427" s="27"/>
-      <c r="T427" s="27"/>
-    </row>
-    <row r="428" customFormat="1" spans="6:20">
+    </row>
+    <row r="428" customFormat="1" spans="6:19">
       <c r="F428" s="24"/>
       <c r="H428" s="52"/>
       <c r="I428" s="52"/>
@@ -16095,9 +15578,8 @@
       <c r="Q428" s="24"/>
       <c r="R428" s="24"/>
       <c r="S428" s="27"/>
-      <c r="T428" s="27"/>
-    </row>
-    <row r="429" customFormat="1" spans="6:20">
+    </row>
+    <row r="429" customFormat="1" spans="6:19">
       <c r="F429" s="24"/>
       <c r="H429" s="52"/>
       <c r="I429" s="52"/>
@@ -16111,9 +15593,8 @@
       <c r="Q429" s="24"/>
       <c r="R429" s="24"/>
       <c r="S429" s="27"/>
-      <c r="T429" s="27"/>
-    </row>
-    <row r="430" customFormat="1" spans="6:20">
+    </row>
+    <row r="430" customFormat="1" spans="6:19">
       <c r="F430" s="24"/>
       <c r="H430" s="52"/>
       <c r="I430" s="52"/>
@@ -16127,9 +15608,8 @@
       <c r="Q430" s="24"/>
       <c r="R430" s="24"/>
       <c r="S430" s="27"/>
-      <c r="T430" s="27"/>
-    </row>
-    <row r="431" customFormat="1" spans="6:20">
+    </row>
+    <row r="431" customFormat="1" spans="6:19">
       <c r="F431" s="24"/>
       <c r="H431" s="52"/>
       <c r="I431" s="52"/>
@@ -16143,9 +15623,8 @@
       <c r="Q431" s="24"/>
       <c r="R431" s="24"/>
       <c r="S431" s="27"/>
-      <c r="T431" s="27"/>
-    </row>
-    <row r="432" customFormat="1" spans="6:20">
+    </row>
+    <row r="432" customFormat="1" spans="6:19">
       <c r="F432" s="24"/>
       <c r="H432" s="52"/>
       <c r="I432" s="52"/>
@@ -16159,9 +15638,8 @@
       <c r="Q432" s="24"/>
       <c r="R432" s="24"/>
       <c r="S432" s="27"/>
-      <c r="T432" s="27"/>
-    </row>
-    <row r="433" customFormat="1" spans="6:20">
+    </row>
+    <row r="433" customFormat="1" spans="6:19">
       <c r="F433" s="24"/>
       <c r="H433" s="52"/>
       <c r="I433" s="52"/>
@@ -16175,9 +15653,8 @@
       <c r="Q433" s="24"/>
       <c r="R433" s="24"/>
       <c r="S433" s="27"/>
-      <c r="T433" s="27"/>
-    </row>
-    <row r="434" customFormat="1" spans="6:20">
+    </row>
+    <row r="434" customFormat="1" spans="6:19">
       <c r="F434" s="24"/>
       <c r="H434" s="52"/>
       <c r="I434" s="52"/>
@@ -16191,9 +15668,8 @@
       <c r="Q434" s="24"/>
       <c r="R434" s="24"/>
       <c r="S434" s="27"/>
-      <c r="T434" s="27"/>
-    </row>
-    <row r="435" customFormat="1" spans="6:20">
+    </row>
+    <row r="435" customFormat="1" spans="6:19">
       <c r="F435" s="24"/>
       <c r="H435" s="52"/>
       <c r="I435" s="52"/>
@@ -16207,9 +15683,8 @@
       <c r="Q435" s="24"/>
       <c r="R435" s="24"/>
       <c r="S435" s="27"/>
-      <c r="T435" s="27"/>
-    </row>
-    <row r="436" customFormat="1" spans="6:20">
+    </row>
+    <row r="436" customFormat="1" spans="6:19">
       <c r="F436" s="24"/>
       <c r="H436" s="52"/>
       <c r="I436" s="52"/>
@@ -16223,9 +15698,8 @@
       <c r="Q436" s="24"/>
       <c r="R436" s="24"/>
       <c r="S436" s="27"/>
-      <c r="T436" s="27"/>
-    </row>
-    <row r="437" customFormat="1" spans="6:20">
+    </row>
+    <row r="437" customFormat="1" spans="6:19">
       <c r="F437" s="24"/>
       <c r="H437" s="52"/>
       <c r="I437" s="52"/>
@@ -16239,9 +15713,8 @@
       <c r="Q437" s="24"/>
       <c r="R437" s="24"/>
       <c r="S437" s="27"/>
-      <c r="T437" s="27"/>
-    </row>
-    <row r="438" customFormat="1" spans="6:20">
+    </row>
+    <row r="438" customFormat="1" spans="6:19">
       <c r="F438" s="24"/>
       <c r="H438" s="52"/>
       <c r="I438" s="52"/>
@@ -16255,9 +15728,8 @@
       <c r="Q438" s="24"/>
       <c r="R438" s="24"/>
       <c r="S438" s="27"/>
-      <c r="T438" s="27"/>
-    </row>
-    <row r="439" customFormat="1" spans="6:20">
+    </row>
+    <row r="439" customFormat="1" spans="6:19">
       <c r="F439" s="24"/>
       <c r="H439" s="52"/>
       <c r="I439" s="52"/>
@@ -16271,9 +15743,8 @@
       <c r="Q439" s="24"/>
       <c r="R439" s="24"/>
       <c r="S439" s="27"/>
-      <c r="T439" s="27"/>
-    </row>
-    <row r="440" customFormat="1" spans="6:20">
+    </row>
+    <row r="440" customFormat="1" spans="6:19">
       <c r="F440" s="24"/>
       <c r="H440" s="52"/>
       <c r="I440" s="52"/>
@@ -16287,9 +15758,8 @@
       <c r="Q440" s="24"/>
       <c r="R440" s="24"/>
       <c r="S440" s="27"/>
-      <c r="T440" s="27"/>
-    </row>
-    <row r="441" customFormat="1" spans="6:20">
+    </row>
+    <row r="441" customFormat="1" spans="6:19">
       <c r="F441" s="24"/>
       <c r="H441" s="52"/>
       <c r="I441" s="52"/>
@@ -16303,9 +15773,8 @@
       <c r="Q441" s="24"/>
       <c r="R441" s="24"/>
       <c r="S441" s="27"/>
-      <c r="T441" s="27"/>
-    </row>
-    <row r="442" customFormat="1" spans="6:20">
+    </row>
+    <row r="442" customFormat="1" spans="6:19">
       <c r="F442" s="24"/>
       <c r="H442" s="52"/>
       <c r="I442" s="52"/>
@@ -16319,9 +15788,8 @@
       <c r="Q442" s="24"/>
       <c r="R442" s="24"/>
       <c r="S442" s="27"/>
-      <c r="T442" s="27"/>
-    </row>
-    <row r="443" customFormat="1" spans="6:20">
+    </row>
+    <row r="443" customFormat="1" spans="6:19">
       <c r="F443" s="24"/>
       <c r="H443" s="52"/>
       <c r="I443" s="52"/>
@@ -16335,9 +15803,8 @@
       <c r="Q443" s="24"/>
       <c r="R443" s="24"/>
       <c r="S443" s="27"/>
-      <c r="T443" s="27"/>
-    </row>
-    <row r="444" customFormat="1" spans="6:20">
+    </row>
+    <row r="444" customFormat="1" spans="6:19">
       <c r="F444" s="24"/>
       <c r="H444" s="52"/>
       <c r="I444" s="52"/>
@@ -16351,9 +15818,8 @@
       <c r="Q444" s="24"/>
       <c r="R444" s="24"/>
       <c r="S444" s="27"/>
-      <c r="T444" s="27"/>
-    </row>
-    <row r="445" customFormat="1" spans="6:20">
+    </row>
+    <row r="445" customFormat="1" spans="6:19">
       <c r="F445" s="24"/>
       <c r="H445" s="52"/>
       <c r="I445" s="52"/>
@@ -16367,9 +15833,8 @@
       <c r="Q445" s="24"/>
       <c r="R445" s="24"/>
       <c r="S445" s="27"/>
-      <c r="T445" s="27"/>
-    </row>
-    <row r="446" customFormat="1" spans="6:20">
+    </row>
+    <row r="446" customFormat="1" spans="6:19">
       <c r="F446" s="24"/>
       <c r="H446" s="52"/>
       <c r="I446" s="52"/>
@@ -16383,9 +15848,8 @@
       <c r="Q446" s="24"/>
       <c r="R446" s="24"/>
       <c r="S446" s="27"/>
-      <c r="T446" s="27"/>
-    </row>
-    <row r="447" customFormat="1" spans="6:20">
+    </row>
+    <row r="447" customFormat="1" spans="6:19">
       <c r="F447" s="24"/>
       <c r="H447" s="52"/>
       <c r="I447" s="52"/>
@@ -16399,9 +15863,8 @@
       <c r="Q447" s="24"/>
       <c r="R447" s="24"/>
       <c r="S447" s="27"/>
-      <c r="T447" s="27"/>
-    </row>
-    <row r="448" customFormat="1" spans="6:20">
+    </row>
+    <row r="448" customFormat="1" spans="6:19">
       <c r="F448" s="24"/>
       <c r="H448" s="52"/>
       <c r="I448" s="52"/>
@@ -16415,9 +15878,8 @@
       <c r="Q448" s="24"/>
       <c r="R448" s="24"/>
       <c r="S448" s="27"/>
-      <c r="T448" s="27"/>
-    </row>
-    <row r="449" customFormat="1" spans="6:20">
+    </row>
+    <row r="449" customFormat="1" spans="6:19">
       <c r="F449" s="24"/>
       <c r="H449" s="52"/>
       <c r="I449" s="52"/>
@@ -16431,9 +15893,8 @@
       <c r="Q449" s="24"/>
       <c r="R449" s="24"/>
       <c r="S449" s="27"/>
-      <c r="T449" s="27"/>
-    </row>
-    <row r="450" customFormat="1" spans="6:20">
+    </row>
+    <row r="450" customFormat="1" spans="6:19">
       <c r="F450" s="24"/>
       <c r="H450" s="52"/>
       <c r="I450" s="52"/>
@@ -16447,9 +15908,8 @@
       <c r="Q450" s="24"/>
       <c r="R450" s="24"/>
       <c r="S450" s="27"/>
-      <c r="T450" s="27"/>
-    </row>
-    <row r="451" customFormat="1" spans="6:20">
+    </row>
+    <row r="451" customFormat="1" spans="6:19">
       <c r="F451" s="24"/>
       <c r="H451" s="52"/>
       <c r="I451" s="52"/>
@@ -16463,9 +15923,8 @@
       <c r="Q451" s="24"/>
       <c r="R451" s="24"/>
       <c r="S451" s="27"/>
-      <c r="T451" s="27"/>
-    </row>
-    <row r="452" customFormat="1" spans="6:20">
+    </row>
+    <row r="452" customFormat="1" spans="6:19">
       <c r="F452" s="24"/>
       <c r="H452" s="52"/>
       <c r="I452" s="52"/>
@@ -16479,9 +15938,8 @@
       <c r="Q452" s="24"/>
       <c r="R452" s="24"/>
       <c r="S452" s="27"/>
-      <c r="T452" s="27"/>
-    </row>
-    <row r="453" customFormat="1" spans="6:20">
+    </row>
+    <row r="453" customFormat="1" spans="6:19">
       <c r="F453" s="24"/>
       <c r="H453" s="52"/>
       <c r="I453" s="52"/>
@@ -16495,9 +15953,8 @@
       <c r="Q453" s="24"/>
       <c r="R453" s="24"/>
       <c r="S453" s="27"/>
-      <c r="T453" s="27"/>
-    </row>
-    <row r="454" customFormat="1" spans="6:20">
+    </row>
+    <row r="454" customFormat="1" spans="6:19">
       <c r="F454" s="24"/>
       <c r="H454" s="52"/>
       <c r="I454" s="52"/>
@@ -16511,9 +15968,8 @@
       <c r="Q454" s="24"/>
       <c r="R454" s="24"/>
       <c r="S454" s="27"/>
-      <c r="T454" s="27"/>
-    </row>
-    <row r="455" customFormat="1" spans="6:20">
+    </row>
+    <row r="455" customFormat="1" spans="6:19">
       <c r="F455" s="24"/>
       <c r="H455" s="52"/>
       <c r="I455" s="52"/>
@@ -16527,9 +15983,8 @@
       <c r="Q455" s="24"/>
       <c r="R455" s="24"/>
       <c r="S455" s="27"/>
-      <c r="T455" s="27"/>
-    </row>
-    <row r="456" customFormat="1" spans="6:20">
+    </row>
+    <row r="456" customFormat="1" spans="6:19">
       <c r="F456" s="24"/>
       <c r="H456" s="52"/>
       <c r="I456" s="52"/>
@@ -16543,9 +15998,8 @@
       <c r="Q456" s="24"/>
       <c r="R456" s="24"/>
       <c r="S456" s="27"/>
-      <c r="T456" s="27"/>
-    </row>
-    <row r="457" customFormat="1" spans="6:20">
+    </row>
+    <row r="457" customFormat="1" spans="6:19">
       <c r="F457" s="24"/>
       <c r="H457" s="52"/>
       <c r="I457" s="52"/>
@@ -16559,9 +16013,8 @@
       <c r="Q457" s="24"/>
       <c r="R457" s="24"/>
       <c r="S457" s="27"/>
-      <c r="T457" s="27"/>
-    </row>
-    <row r="458" customFormat="1" spans="6:20">
+    </row>
+    <row r="458" customFormat="1" spans="6:19">
       <c r="F458" s="24"/>
       <c r="H458" s="52"/>
       <c r="I458" s="52"/>
@@ -16575,9 +16028,8 @@
       <c r="Q458" s="24"/>
       <c r="R458" s="24"/>
       <c r="S458" s="27"/>
-      <c r="T458" s="27"/>
-    </row>
-    <row r="459" customFormat="1" spans="6:20">
+    </row>
+    <row r="459" customFormat="1" spans="6:19">
       <c r="F459" s="24"/>
       <c r="H459" s="52"/>
       <c r="I459" s="52"/>
@@ -16591,9 +16043,8 @@
       <c r="Q459" s="24"/>
       <c r="R459" s="24"/>
       <c r="S459" s="27"/>
-      <c r="T459" s="27"/>
-    </row>
-    <row r="460" customFormat="1" spans="6:20">
+    </row>
+    <row r="460" customFormat="1" spans="6:19">
       <c r="F460" s="24"/>
       <c r="H460" s="52"/>
       <c r="I460" s="52"/>
@@ -16607,9 +16058,8 @@
       <c r="Q460" s="24"/>
       <c r="R460" s="24"/>
       <c r="S460" s="27"/>
-      <c r="T460" s="27"/>
-    </row>
-    <row r="461" customFormat="1" spans="6:20">
+    </row>
+    <row r="461" customFormat="1" spans="6:19">
       <c r="F461" s="24"/>
       <c r="H461" s="52"/>
       <c r="I461" s="52"/>
@@ -16623,9 +16073,8 @@
       <c r="Q461" s="24"/>
       <c r="R461" s="24"/>
       <c r="S461" s="27"/>
-      <c r="T461" s="27"/>
-    </row>
-    <row r="462" customFormat="1" spans="6:20">
+    </row>
+    <row r="462" customFormat="1" spans="6:19">
       <c r="F462" s="24"/>
       <c r="H462" s="52"/>
       <c r="I462" s="52"/>
@@ -16639,9 +16088,8 @@
       <c r="Q462" s="24"/>
       <c r="R462" s="24"/>
       <c r="S462" s="27"/>
-      <c r="T462" s="27"/>
-    </row>
-    <row r="463" customFormat="1" spans="6:20">
+    </row>
+    <row r="463" customFormat="1" spans="6:19">
       <c r="F463" s="24"/>
       <c r="H463" s="52"/>
       <c r="I463" s="52"/>
@@ -16655,9 +16103,8 @@
       <c r="Q463" s="24"/>
       <c r="R463" s="24"/>
       <c r="S463" s="27"/>
-      <c r="T463" s="27"/>
-    </row>
-    <row r="464" customFormat="1" spans="6:20">
+    </row>
+    <row r="464" customFormat="1" spans="6:19">
       <c r="F464" s="24"/>
       <c r="H464" s="52"/>
       <c r="I464" s="52"/>
@@ -16671,9 +16118,8 @@
       <c r="Q464" s="24"/>
       <c r="R464" s="24"/>
       <c r="S464" s="27"/>
-      <c r="T464" s="27"/>
-    </row>
-    <row r="465" customFormat="1" spans="6:20">
+    </row>
+    <row r="465" customFormat="1" spans="6:19">
       <c r="F465" s="24"/>
       <c r="H465" s="52"/>
       <c r="I465" s="52"/>
@@ -16687,9 +16133,8 @@
       <c r="Q465" s="24"/>
       <c r="R465" s="24"/>
       <c r="S465" s="27"/>
-      <c r="T465" s="27"/>
-    </row>
-    <row r="466" customFormat="1" spans="6:20">
+    </row>
+    <row r="466" customFormat="1" spans="6:19">
       <c r="F466" s="24"/>
       <c r="H466" s="52"/>
       <c r="I466" s="52"/>
@@ -16703,9 +16148,8 @@
       <c r="Q466" s="24"/>
       <c r="R466" s="24"/>
       <c r="S466" s="27"/>
-      <c r="T466" s="27"/>
-    </row>
-    <row r="467" customFormat="1" spans="6:20">
+    </row>
+    <row r="467" customFormat="1" spans="6:19">
       <c r="F467" s="24"/>
       <c r="H467" s="52"/>
       <c r="I467" s="52"/>
@@ -16719,9 +16163,8 @@
       <c r="Q467" s="24"/>
       <c r="R467" s="24"/>
       <c r="S467" s="27"/>
-      <c r="T467" s="27"/>
-    </row>
-    <row r="468" customFormat="1" spans="6:20">
+    </row>
+    <row r="468" customFormat="1" spans="6:19">
       <c r="F468" s="24"/>
       <c r="H468" s="52"/>
       <c r="I468" s="52"/>
@@ -16735,9 +16178,8 @@
       <c r="Q468" s="24"/>
       <c r="R468" s="24"/>
       <c r="S468" s="27"/>
-      <c r="T468" s="27"/>
-    </row>
-    <row r="469" customFormat="1" spans="6:20">
+    </row>
+    <row r="469" customFormat="1" spans="6:19">
       <c r="F469" s="24"/>
       <c r="H469" s="52"/>
       <c r="I469" s="52"/>
@@ -16751,9 +16193,8 @@
       <c r="Q469" s="24"/>
       <c r="R469" s="24"/>
       <c r="S469" s="27"/>
-      <c r="T469" s="27"/>
-    </row>
-    <row r="470" customFormat="1" spans="6:20">
+    </row>
+    <row r="470" customFormat="1" spans="6:19">
       <c r="F470" s="24"/>
       <c r="H470" s="52"/>
       <c r="I470" s="52"/>
@@ -16767,9 +16208,8 @@
       <c r="Q470" s="24"/>
       <c r="R470" s="24"/>
       <c r="S470" s="27"/>
-      <c r="T470" s="27"/>
-    </row>
-    <row r="471" customFormat="1" spans="6:20">
+    </row>
+    <row r="471" customFormat="1" spans="6:19">
       <c r="F471" s="24"/>
       <c r="H471" s="52"/>
       <c r="I471" s="52"/>
@@ -16783,9 +16223,8 @@
       <c r="Q471" s="24"/>
       <c r="R471" s="24"/>
       <c r="S471" s="27"/>
-      <c r="T471" s="27"/>
-    </row>
-    <row r="472" customFormat="1" spans="6:20">
+    </row>
+    <row r="472" customFormat="1" spans="6:19">
       <c r="F472" s="24"/>
       <c r="H472" s="52"/>
       <c r="I472" s="52"/>
@@ -16799,9 +16238,8 @@
       <c r="Q472" s="24"/>
       <c r="R472" s="24"/>
       <c r="S472" s="27"/>
-      <c r="T472" s="27"/>
-    </row>
-    <row r="473" customFormat="1" spans="6:20">
+    </row>
+    <row r="473" customFormat="1" spans="6:19">
       <c r="F473" s="24"/>
       <c r="H473" s="52"/>
       <c r="I473" s="52"/>
@@ -16815,9 +16253,8 @@
       <c r="Q473" s="24"/>
       <c r="R473" s="24"/>
       <c r="S473" s="27"/>
-      <c r="T473" s="27"/>
-    </row>
-    <row r="474" customFormat="1" spans="6:20">
+    </row>
+    <row r="474" customFormat="1" spans="6:19">
       <c r="F474" s="24"/>
       <c r="H474" s="52"/>
       <c r="I474" s="52"/>
@@ -16831,9 +16268,8 @@
       <c r="Q474" s="24"/>
       <c r="R474" s="24"/>
       <c r="S474" s="27"/>
-      <c r="T474" s="27"/>
-    </row>
-    <row r="475" customFormat="1" spans="6:20">
+    </row>
+    <row r="475" customFormat="1" spans="6:19">
       <c r="F475" s="24"/>
       <c r="H475" s="52"/>
       <c r="I475" s="52"/>
@@ -16847,9 +16283,8 @@
       <c r="Q475" s="24"/>
       <c r="R475" s="24"/>
       <c r="S475" s="27"/>
-      <c r="T475" s="27"/>
-    </row>
-    <row r="476" customFormat="1" spans="6:20">
+    </row>
+    <row r="476" customFormat="1" spans="6:19">
       <c r="F476" s="24"/>
       <c r="H476" s="52"/>
       <c r="I476" s="52"/>
@@ -16863,9 +16298,8 @@
       <c r="Q476" s="24"/>
       <c r="R476" s="24"/>
       <c r="S476" s="27"/>
-      <c r="T476" s="27"/>
-    </row>
-    <row r="477" customFormat="1" spans="6:20">
+    </row>
+    <row r="477" customFormat="1" spans="6:19">
       <c r="F477" s="24"/>
       <c r="H477" s="52"/>
       <c r="I477" s="52"/>
@@ -16879,9 +16313,8 @@
       <c r="Q477" s="24"/>
       <c r="R477" s="24"/>
       <c r="S477" s="27"/>
-      <c r="T477" s="27"/>
-    </row>
-    <row r="478" customFormat="1" spans="6:20">
+    </row>
+    <row r="478" customFormat="1" spans="6:19">
       <c r="F478" s="24"/>
       <c r="H478" s="52"/>
       <c r="I478" s="52"/>
@@ -16895,9 +16328,8 @@
       <c r="Q478" s="24"/>
       <c r="R478" s="24"/>
       <c r="S478" s="27"/>
-      <c r="T478" s="27"/>
-    </row>
-    <row r="479" customFormat="1" spans="6:20">
+    </row>
+    <row r="479" customFormat="1" spans="6:19">
       <c r="F479" s="24"/>
       <c r="H479" s="52"/>
       <c r="I479" s="52"/>
@@ -16911,9 +16343,8 @@
       <c r="Q479" s="24"/>
       <c r="R479" s="24"/>
       <c r="S479" s="27"/>
-      <c r="T479" s="27"/>
-    </row>
-    <row r="480" customFormat="1" spans="6:20">
+    </row>
+    <row r="480" customFormat="1" spans="6:19">
       <c r="F480" s="24"/>
       <c r="H480" s="52"/>
       <c r="I480" s="52"/>
@@ -16927,9 +16358,8 @@
       <c r="Q480" s="24"/>
       <c r="R480" s="24"/>
       <c r="S480" s="27"/>
-      <c r="T480" s="27"/>
-    </row>
-    <row r="481" customFormat="1" spans="6:20">
+    </row>
+    <row r="481" customFormat="1" spans="6:19">
       <c r="F481" s="24"/>
       <c r="H481" s="52"/>
       <c r="I481" s="52"/>
@@ -16943,9 +16373,8 @@
       <c r="Q481" s="24"/>
       <c r="R481" s="24"/>
       <c r="S481" s="27"/>
-      <c r="T481" s="27"/>
-    </row>
-    <row r="482" customFormat="1" spans="6:20">
+    </row>
+    <row r="482" customFormat="1" spans="6:19">
       <c r="F482" s="24"/>
       <c r="H482" s="52"/>
       <c r="I482" s="52"/>
@@ -16959,9 +16388,8 @@
       <c r="Q482" s="24"/>
       <c r="R482" s="24"/>
       <c r="S482" s="27"/>
-      <c r="T482" s="27"/>
-    </row>
-    <row r="483" customFormat="1" spans="6:20">
+    </row>
+    <row r="483" customFormat="1" spans="6:19">
       <c r="F483" s="24"/>
       <c r="H483" s="52"/>
       <c r="I483" s="52"/>
@@ -16975,9 +16403,8 @@
       <c r="Q483" s="24"/>
       <c r="R483" s="24"/>
       <c r="S483" s="27"/>
-      <c r="T483" s="27"/>
-    </row>
-    <row r="484" customFormat="1" spans="6:20">
+    </row>
+    <row r="484" customFormat="1" spans="6:19">
       <c r="F484" s="24"/>
       <c r="H484" s="52"/>
       <c r="I484" s="52"/>
@@ -16991,9 +16418,8 @@
       <c r="Q484" s="24"/>
       <c r="R484" s="24"/>
       <c r="S484" s="27"/>
-      <c r="T484" s="27"/>
-    </row>
-    <row r="485" customFormat="1" spans="6:20">
+    </row>
+    <row r="485" customFormat="1" spans="6:19">
       <c r="F485" s="24"/>
       <c r="H485" s="52"/>
       <c r="I485" s="52"/>
@@ -17007,9 +16433,8 @@
       <c r="Q485" s="24"/>
       <c r="R485" s="24"/>
       <c r="S485" s="27"/>
-      <c r="T485" s="27"/>
-    </row>
-    <row r="486" customFormat="1" spans="6:20">
+    </row>
+    <row r="486" customFormat="1" spans="6:19">
       <c r="F486" s="24"/>
       <c r="H486" s="52"/>
       <c r="I486" s="52"/>
@@ -17023,9 +16448,8 @@
       <c r="Q486" s="24"/>
       <c r="R486" s="24"/>
       <c r="S486" s="27"/>
-      <c r="T486" s="27"/>
-    </row>
-    <row r="487" customFormat="1" spans="6:20">
+    </row>
+    <row r="487" customFormat="1" spans="6:19">
       <c r="F487" s="24"/>
       <c r="H487" s="52"/>
       <c r="I487" s="52"/>
@@ -17039,9 +16463,8 @@
       <c r="Q487" s="24"/>
       <c r="R487" s="24"/>
       <c r="S487" s="27"/>
-      <c r="T487" s="27"/>
-    </row>
-    <row r="488" customFormat="1" spans="6:20">
+    </row>
+    <row r="488" customFormat="1" spans="6:19">
       <c r="F488" s="24"/>
       <c r="H488" s="52"/>
       <c r="I488" s="52"/>
@@ -17055,9 +16478,8 @@
       <c r="Q488" s="24"/>
       <c r="R488" s="24"/>
       <c r="S488" s="27"/>
-      <c r="T488" s="27"/>
-    </row>
-    <row r="489" customFormat="1" spans="6:20">
+    </row>
+    <row r="489" customFormat="1" spans="6:19">
       <c r="F489" s="24"/>
       <c r="H489" s="52"/>
       <c r="I489" s="52"/>
@@ -17071,9 +16493,8 @@
       <c r="Q489" s="24"/>
       <c r="R489" s="24"/>
       <c r="S489" s="27"/>
-      <c r="T489" s="27"/>
-    </row>
-    <row r="490" customFormat="1" spans="6:20">
+    </row>
+    <row r="490" customFormat="1" spans="6:19">
       <c r="F490" s="24"/>
       <c r="H490" s="52"/>
       <c r="I490" s="52"/>
@@ -17087,9 +16508,8 @@
       <c r="Q490" s="24"/>
       <c r="R490" s="24"/>
       <c r="S490" s="27"/>
-      <c r="T490" s="27"/>
-    </row>
-    <row r="491" customFormat="1" spans="6:20">
+    </row>
+    <row r="491" customFormat="1" spans="6:19">
       <c r="F491" s="24"/>
       <c r="H491" s="52"/>
       <c r="I491" s="52"/>
@@ -17103,9 +16523,8 @@
       <c r="Q491" s="24"/>
       <c r="R491" s="24"/>
       <c r="S491" s="27"/>
-      <c r="T491" s="27"/>
-    </row>
-    <row r="492" customFormat="1" spans="6:20">
+    </row>
+    <row r="492" customFormat="1" spans="6:19">
       <c r="F492" s="24"/>
       <c r="H492" s="52"/>
       <c r="I492" s="52"/>
@@ -17119,9 +16538,8 @@
       <c r="Q492" s="24"/>
       <c r="R492" s="24"/>
       <c r="S492" s="27"/>
-      <c r="T492" s="27"/>
-    </row>
-    <row r="493" customFormat="1" spans="6:20">
+    </row>
+    <row r="493" customFormat="1" spans="6:19">
       <c r="F493" s="24"/>
       <c r="H493" s="52"/>
       <c r="I493" s="52"/>
@@ -17135,9 +16553,8 @@
       <c r="Q493" s="24"/>
       <c r="R493" s="24"/>
       <c r="S493" s="27"/>
-      <c r="T493" s="27"/>
-    </row>
-    <row r="494" customFormat="1" spans="6:20">
+    </row>
+    <row r="494" customFormat="1" spans="6:19">
       <c r="F494" s="24"/>
       <c r="H494" s="52"/>
       <c r="I494" s="52"/>
@@ -17151,9 +16568,8 @@
       <c r="Q494" s="24"/>
       <c r="R494" s="24"/>
       <c r="S494" s="27"/>
-      <c r="T494" s="27"/>
-    </row>
-    <row r="495" customFormat="1" spans="6:20">
+    </row>
+    <row r="495" customFormat="1" spans="6:19">
       <c r="F495" s="24"/>
       <c r="H495" s="52"/>
       <c r="I495" s="52"/>
@@ -17167,9 +16583,8 @@
       <c r="Q495" s="24"/>
       <c r="R495" s="24"/>
       <c r="S495" s="27"/>
-      <c r="T495" s="27"/>
-    </row>
-    <row r="496" customFormat="1" spans="6:20">
+    </row>
+    <row r="496" customFormat="1" spans="6:19">
       <c r="F496" s="24"/>
       <c r="H496" s="52"/>
       <c r="I496" s="52"/>
@@ -17183,9 +16598,8 @@
       <c r="Q496" s="24"/>
       <c r="R496" s="24"/>
       <c r="S496" s="27"/>
-      <c r="T496" s="27"/>
-    </row>
-    <row r="497" customFormat="1" spans="6:20">
+    </row>
+    <row r="497" customFormat="1" spans="6:19">
       <c r="F497" s="24"/>
       <c r="H497" s="52"/>
       <c r="I497" s="52"/>
@@ -17199,9 +16613,8 @@
       <c r="Q497" s="24"/>
       <c r="R497" s="24"/>
       <c r="S497" s="27"/>
-      <c r="T497" s="27"/>
-    </row>
-    <row r="498" customFormat="1" spans="6:20">
+    </row>
+    <row r="498" customFormat="1" spans="6:19">
       <c r="F498" s="24"/>
       <c r="H498" s="52"/>
       <c r="I498" s="52"/>
@@ -17215,9 +16628,8 @@
       <c r="Q498" s="24"/>
       <c r="R498" s="24"/>
       <c r="S498" s="27"/>
-      <c r="T498" s="27"/>
-    </row>
-    <row r="499" customFormat="1" spans="6:20">
+    </row>
+    <row r="499" customFormat="1" spans="6:19">
       <c r="F499" s="24"/>
       <c r="H499" s="52"/>
       <c r="I499" s="52"/>
@@ -17231,9 +16643,8 @@
       <c r="Q499" s="24"/>
       <c r="R499" s="24"/>
       <c r="S499" s="27"/>
-      <c r="T499" s="27"/>
-    </row>
-    <row r="500" customFormat="1" spans="6:20">
+    </row>
+    <row r="500" customFormat="1" spans="6:19">
       <c r="F500" s="24"/>
       <c r="H500" s="52"/>
       <c r="I500" s="52"/>
@@ -17247,18 +16658,9 @@
       <c r="Q500" s="24"/>
       <c r="R500" s="24"/>
       <c r="S500" s="27"/>
-      <c r="T500" s="27"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="S2:S500">
-    <cfRule type="containsText" dxfId="0" priority="2" operator="between" text="待确认">
-      <formula>NOT(ISERROR(SEARCH("待确认",S2)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="1" priority="1" operator="between" text="已确认">
-      <formula>NOT(ISERROR(SEARCH("已确认",S2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <dataValidations count="6">
+  <dataValidations count="5">
     <dataValidation type="whole" operator="between" sqref="B2:B500">
       <formula1>2020</formula1>
       <formula2>2100</formula2>
@@ -17274,9 +16676,6 @@
       <formula1>"首次录入,报名注册更新,正式报名更新,考试时间更新,出分时间更新,考点更新,其他更新"</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="S2:S500">
-      <formula1>"未确认,已确认,已结束,暂停"</formula1>
-    </dataValidation>
-    <dataValidation type="list" sqref="T2:T500">
       <formula1>"是,否"</formula1>
     </dataValidation>
   </dataValidations>
@@ -17315,7 +16714,7 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:15">
       <c r="A1" s="28" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="B1" s="28" t="s">
         <v>1</v>
@@ -17327,34 +16726,34 @@
         <v>2</v>
       </c>
       <c r="E1" s="28" t="s">
+        <v>204</v>
+      </c>
+      <c r="F1" s="28" t="s">
+        <v>205</v>
+      </c>
+      <c r="G1" s="28" t="s">
+        <v>206</v>
+      </c>
+      <c r="H1" s="28" t="s">
         <v>207</v>
       </c>
-      <c r="F1" s="28" t="s">
+      <c r="I1" s="28" t="s">
         <v>208</v>
       </c>
-      <c r="G1" s="28" t="s">
+      <c r="J1" s="28" t="s">
         <v>209</v>
       </c>
-      <c r="H1" s="28" t="s">
+      <c r="K1" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="I1" s="28" t="s">
+      <c r="L1" s="28" t="s">
         <v>211</v>
       </c>
-      <c r="J1" s="28" t="s">
+      <c r="M1" s="28" t="s">
         <v>212</v>
       </c>
-      <c r="K1" s="28" t="s">
+      <c r="N1" s="28" t="s">
         <v>213</v>
-      </c>
-      <c r="L1" s="28" t="s">
-        <v>214</v>
-      </c>
-      <c r="M1" s="28" t="s">
-        <v>215</v>
-      </c>
-      <c r="N1" s="28" t="s">
-        <v>216</v>
       </c>
       <c r="O1" s="28" t="s">
         <v>11</v>
@@ -17362,7 +16761,7 @@
     </row>
     <row r="2" ht="78" customHeight="1" spans="1:15">
       <c r="A2" s="29" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="B2" s="29" t="s">
         <v>36</v>
@@ -17371,7 +16770,7 @@
         <v>46</v>
       </c>
       <c r="D2" s="29" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="E2" s="29" t="s">
         <v>101</v>
@@ -17383,22 +16782,22 @@
         <v>30</v>
       </c>
       <c r="H2" s="29" t="s">
+        <v>216</v>
+      </c>
+      <c r="I2" s="30" t="s">
+        <v>217</v>
+      </c>
+      <c r="J2" s="30" t="s">
+        <v>218</v>
+      </c>
+      <c r="K2" s="30" t="s">
         <v>219</v>
       </c>
-      <c r="I2" s="30" t="s">
+      <c r="L2" s="30" t="s">
         <v>220</v>
       </c>
-      <c r="J2" s="30" t="s">
+      <c r="M2" s="30" t="s">
         <v>221</v>
-      </c>
-      <c r="K2" s="30" t="s">
-        <v>222</v>
-      </c>
-      <c r="L2" s="30" t="s">
-        <v>223</v>
-      </c>
-      <c r="M2" s="30" t="s">
-        <v>224</v>
       </c>
       <c r="N2" s="29">
         <v>95</v>
@@ -17409,7 +16808,7 @@
     </row>
     <row r="3" ht="78" customHeight="1" spans="1:15">
       <c r="A3" s="31" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="B3" s="31" t="s">
         <v>13</v>
@@ -17430,22 +16829,22 @@
         <v>7</v>
       </c>
       <c r="H3" s="31" t="s">
+        <v>223</v>
+      </c>
+      <c r="I3" s="32" t="s">
+        <v>224</v>
+      </c>
+      <c r="J3" s="32" t="s">
+        <v>225</v>
+      </c>
+      <c r="K3" s="32" t="s">
         <v>226</v>
       </c>
-      <c r="I3" s="32" t="s">
+      <c r="L3" s="32" t="s">
         <v>227</v>
       </c>
-      <c r="J3" s="32" t="s">
+      <c r="M3" s="32" t="s">
         <v>228</v>
-      </c>
-      <c r="K3" s="32" t="s">
-        <v>229</v>
-      </c>
-      <c r="L3" s="32" t="s">
-        <v>230</v>
-      </c>
-      <c r="M3" s="32" t="s">
-        <v>231</v>
       </c>
       <c r="N3" s="31">
         <v>90</v>
@@ -17456,7 +16855,7 @@
     </row>
     <row r="4" ht="78" customHeight="1" spans="1:15">
       <c r="A4" s="29" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="B4" s="29" t="s">
         <v>25</v>
@@ -17477,22 +16876,22 @@
         <v>7</v>
       </c>
       <c r="H4" s="29" t="s">
+        <v>230</v>
+      </c>
+      <c r="I4" s="30" t="s">
+        <v>231</v>
+      </c>
+      <c r="J4" s="30" t="s">
+        <v>232</v>
+      </c>
+      <c r="K4" s="30" t="s">
         <v>233</v>
       </c>
-      <c r="I4" s="30" t="s">
+      <c r="L4" s="30" t="s">
         <v>234</v>
       </c>
-      <c r="J4" s="30" t="s">
-        <v>235</v>
-      </c>
-      <c r="K4" s="30" t="s">
-        <v>236</v>
-      </c>
-      <c r="L4" s="30" t="s">
-        <v>237</v>
-      </c>
       <c r="M4" s="30" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="N4" s="29">
         <v>92</v>
@@ -17503,7 +16902,7 @@
     </row>
     <row r="5" ht="78" customHeight="1" spans="1:15">
       <c r="A5" s="33" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="B5" s="33" t="s">
         <v>65</v>
@@ -17515,7 +16914,7 @@
         <v>66</v>
       </c>
       <c r="E5" s="33" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="F5" s="33">
         <v>-365</v>
@@ -17524,22 +16923,22 @@
         <v>365</v>
       </c>
       <c r="H5" s="33" t="s">
+        <v>237</v>
+      </c>
+      <c r="I5" s="34" t="s">
+        <v>238</v>
+      </c>
+      <c r="J5" s="34" t="s">
+        <v>239</v>
+      </c>
+      <c r="K5" s="34" t="s">
         <v>240</v>
       </c>
-      <c r="I5" s="34" t="s">
+      <c r="L5" s="34" t="s">
         <v>241</v>
       </c>
-      <c r="J5" s="34" t="s">
-        <v>242</v>
-      </c>
-      <c r="K5" s="34" t="s">
-        <v>243</v>
-      </c>
-      <c r="L5" s="34" t="s">
-        <v>244</v>
-      </c>
       <c r="M5" s="34" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="N5" s="33">
         <v>70</v>
@@ -18923,7 +18322,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0ebee17e-fcf2-4bf9-9486-3f950123ca2a}</x14:id>
+          <x14:id>{6359eedc-8c18-4575-897f-8bcc74696ae4}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -18959,7 +18358,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{0ebee17e-fcf2-4bf9-9486-3f950123ca2a}">
+          <x14:cfRule type="dataBar" id="{6359eedc-8c18-4575-897f-8bcc74696ae4}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -18993,42 +18392,42 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:11">
       <c r="A1" s="19" t="s">
+        <v>242</v>
+      </c>
+      <c r="B1" s="19" t="s">
+        <v>243</v>
+      </c>
+      <c r="C1" s="19" t="s">
+        <v>205</v>
+      </c>
+      <c r="D1" s="19" t="s">
+        <v>206</v>
+      </c>
+      <c r="E1" s="19" t="s">
+        <v>244</v>
+      </c>
+      <c r="F1" s="19" t="s">
         <v>245</v>
       </c>
-      <c r="B1" s="19" t="s">
+      <c r="G1" s="19" t="s">
         <v>246</v>
       </c>
-      <c r="C1" s="19" t="s">
-        <v>208</v>
-      </c>
-      <c r="D1" s="19" t="s">
-        <v>209</v>
-      </c>
-      <c r="E1" s="19" t="s">
+      <c r="H1" s="19" t="s">
         <v>247</v>
       </c>
-      <c r="F1" s="19" t="s">
+      <c r="I1" s="19" t="s">
         <v>248</v>
       </c>
-      <c r="G1" s="19" t="s">
+      <c r="J1" s="19" t="s">
         <v>249</v>
       </c>
-      <c r="H1" s="19" t="s">
-        <v>250</v>
-      </c>
-      <c r="I1" s="19" t="s">
-        <v>251</v>
-      </c>
-      <c r="J1" s="19" t="s">
-        <v>252</v>
-      </c>
       <c r="K1" s="19" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
     </row>
     <row r="2" ht="38" customHeight="1" spans="1:11">
       <c r="A2" s="20" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="B2" s="20" t="s">
         <v>98</v>
@@ -19040,16 +18439,16 @@
         <v>7</v>
       </c>
       <c r="E2" s="20" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="F2" s="21" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="G2" s="21" t="s">
         <v>23</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="I2" s="21" t="s">
         <v>23</v>
@@ -19063,7 +18462,7 @@
     </row>
     <row r="3" ht="38" customHeight="1" spans="1:11">
       <c r="A3" s="22" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="B3" s="22" t="s">
         <v>98</v>
@@ -19075,16 +18474,16 @@
         <v>0</v>
       </c>
       <c r="E3" s="22" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="F3" s="23" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="G3" s="23" t="s">
         <v>23</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="I3" s="23" t="s">
         <v>23</v>
@@ -19098,7 +18497,7 @@
     </row>
     <row r="4" ht="38" customHeight="1" spans="1:11">
       <c r="A4" s="20" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="B4" s="20" t="s">
         <v>99</v>
@@ -19110,16 +18509,16 @@
         <v>15</v>
       </c>
       <c r="E4" s="20" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="F4" s="21" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="G4" s="21" t="s">
         <v>23</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="I4" s="21" t="s">
         <v>23</v>
@@ -19133,7 +18532,7 @@
     </row>
     <row r="5" ht="38" customHeight="1" spans="1:11">
       <c r="A5" s="22" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="B5" s="22" t="s">
         <v>99</v>
@@ -19145,16 +18544,16 @@
         <v>7</v>
       </c>
       <c r="E5" s="22" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="F5" s="23" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="G5" s="23" t="s">
         <v>23</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="I5" s="23" t="s">
         <v>23</v>
@@ -19168,7 +18567,7 @@
     </row>
     <row r="6" ht="38" customHeight="1" spans="1:11">
       <c r="A6" s="20" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="B6" s="20" t="s">
         <v>99</v>
@@ -19180,16 +18579,16 @@
         <v>0</v>
       </c>
       <c r="E6" s="20" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="F6" s="21" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="G6" s="21" t="s">
         <v>23</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="I6" s="21" t="s">
         <v>23</v>
@@ -19203,7 +18602,7 @@
     </row>
     <row r="7" ht="38" customHeight="1" spans="1:11">
       <c r="A7" s="22" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="B7" s="22" t="s">
         <v>100</v>
@@ -19215,16 +18614,16 @@
         <v>7</v>
       </c>
       <c r="E7" s="22" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="F7" s="23" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="G7" s="23" t="s">
         <v>23</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="I7" s="23" t="s">
         <v>23</v>
@@ -19238,7 +18637,7 @@
     </row>
     <row r="8" ht="38" customHeight="1" spans="1:11">
       <c r="A8" s="20" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="B8" s="20" t="s">
         <v>100</v>
@@ -19250,16 +18649,16 @@
         <v>0</v>
       </c>
       <c r="E8" s="20" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="F8" s="21" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="G8" s="21" t="s">
         <v>23</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="I8" s="21" t="s">
         <v>23</v>
@@ -19273,7 +18672,7 @@
     </row>
     <row r="9" ht="38" customHeight="1" spans="1:11">
       <c r="A9" s="22" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="B9" s="22" t="s">
         <v>101</v>
@@ -19285,16 +18684,16 @@
         <v>7</v>
       </c>
       <c r="E9" s="22" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="F9" s="23" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="G9" s="23" t="s">
         <v>23</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="I9" s="23" t="s">
         <v>23</v>
@@ -19308,7 +18707,7 @@
     </row>
     <row r="10" ht="38" customHeight="1" spans="1:11">
       <c r="A10" s="20" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="B10" s="20" t="s">
         <v>101</v>
@@ -19320,16 +18719,16 @@
         <v>0</v>
       </c>
       <c r="E10" s="20" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="F10" s="21" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="G10" s="21" t="s">
         <v>23</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="I10" s="21" t="s">
         <v>23</v>
@@ -19343,7 +18742,7 @@
     </row>
     <row r="11" ht="38" customHeight="1" spans="1:11">
       <c r="A11" s="22" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="B11" s="22" t="s">
         <v>101</v>
@@ -19355,16 +18754,16 @@
         <v>-1</v>
       </c>
       <c r="E11" s="22" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="F11" s="23" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="G11" s="23" t="s">
         <v>23</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="I11" s="23" t="s">
         <v>23</v>
@@ -19378,7 +18777,7 @@
     </row>
     <row r="12" ht="38" customHeight="1" spans="1:11">
       <c r="A12" s="22" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="B12" s="22" t="s">
         <v>102</v>
@@ -19390,16 +18789,16 @@
         <v>0</v>
       </c>
       <c r="E12" s="22" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="F12" s="23" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="G12" s="23" t="s">
         <v>23</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="I12" s="23" t="s">
         <v>23</v>
@@ -19413,7 +18812,7 @@
     </row>
     <row r="13" ht="38" customHeight="1" spans="1:11">
       <c r="A13" s="20" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="B13" s="20" t="s">
         <v>103</v>
@@ -19425,22 +18824,22 @@
         <v>0</v>
       </c>
       <c r="E13" s="20" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="F13" s="21" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="G13" s="21" t="s">
         <v>23</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="I13" s="21" t="s">
         <v>23</v>
       </c>
       <c r="J13" s="21" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="K13" s="21">
         <v>98</v>
@@ -23344,7 +22743,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8150708c-ea45-4986-bcda-ea3a048286cf}</x14:id>
+          <x14:id>{8792fdc1-ee6b-4432-8b2e-1091746fec44}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23371,7 +22770,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{8150708c-ea45-4986-bcda-ea3a048286cf}">
+          <x14:cfRule type="dataBar" id="{8792fdc1-ee6b-4432-8b2e-1091746fec44}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -23402,19 +22801,19 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:6">
       <c r="A1" s="19" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="B1" s="19" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="C1" s="19" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="D1" s="19" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="E1" s="19" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="F1" s="19" t="s">
         <v>11</v>
@@ -23422,19 +22821,19 @@
     </row>
     <row r="2" ht="100" customHeight="1" spans="1:6">
       <c r="A2" s="20" t="s">
+        <v>292</v>
+      </c>
+      <c r="B2" s="20" t="s">
+        <v>293</v>
+      </c>
+      <c r="C2" s="20" t="s">
+        <v>294</v>
+      </c>
+      <c r="D2" s="3" t="s">
         <v>295</v>
       </c>
-      <c r="B2" s="20" t="s">
+      <c r="E2" s="3" t="s">
         <v>296</v>
-      </c>
-      <c r="C2" s="20" t="s">
-        <v>297</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>299</v>
       </c>
       <c r="F2" s="20" t="s">
         <v>23</v>
@@ -23442,19 +22841,19 @@
     </row>
     <row r="3" ht="100" customHeight="1" spans="1:6">
       <c r="A3" s="22" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="B3" s="22" t="s">
         <v>103</v>
       </c>
       <c r="C3" s="22" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="F3" s="22" t="s">
         <v>23</v>
@@ -25478,22 +24877,22 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:7">
       <c r="A1" s="19" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="B1" s="19" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="C1" s="19" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="D1" s="19" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="E1" s="19" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="F1" s="19" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="G1" s="19" t="s">
         <v>11</v>
@@ -25501,19 +24900,19 @@
     </row>
     <row r="2" ht="50" customHeight="1" spans="1:7">
       <c r="A2" s="20" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="B2" s="20" t="s">
         <v>99</v>
       </c>
       <c r="C2" s="20" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="D2" s="20" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="F2" s="25"/>
       <c r="G2" s="20" t="s">
@@ -25522,19 +24921,19 @@
     </row>
     <row r="3" ht="50" customHeight="1" spans="1:7">
       <c r="A3" s="22" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="B3" s="22" t="s">
         <v>99</v>
       </c>
       <c r="C3" s="22" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="D3" s="22" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="F3" s="25"/>
       <c r="G3" s="22" t="s">
@@ -25543,19 +24942,19 @@
     </row>
     <row r="4" ht="50" customHeight="1" spans="1:7">
       <c r="A4" s="20" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="B4" s="20" t="s">
         <v>99</v>
       </c>
       <c r="C4" s="20" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="D4" s="20" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="F4" s="25"/>
       <c r="G4" s="20" t="s">
@@ -25564,19 +24963,19 @@
     </row>
     <row r="5" ht="50" customHeight="1" spans="1:7">
       <c r="A5" s="22" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="B5" s="22" t="s">
         <v>102</v>
       </c>
       <c r="C5" s="22" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="D5" s="22" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="F5" s="25"/>
       <c r="G5" s="22" t="s">
@@ -27594,16 +26993,16 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:4">
       <c r="A1" s="19" t="s">
+        <v>313</v>
+      </c>
+      <c r="B1" s="19" t="s">
+        <v>314</v>
+      </c>
+      <c r="C1" s="19" t="s">
+        <v>315</v>
+      </c>
+      <c r="D1" s="19" t="s">
         <v>316</v>
-      </c>
-      <c r="B1" s="19" t="s">
-        <v>317</v>
-      </c>
-      <c r="C1" s="19" t="s">
-        <v>318</v>
-      </c>
-      <c r="D1" s="19" t="s">
-        <v>319</v>
       </c>
     </row>
     <row r="2" ht="38" customHeight="1" spans="1:4">
@@ -27617,7 +27016,7 @@
         <v>1</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
     </row>
     <row r="3" ht="38" customHeight="1" spans="1:4">
@@ -27631,7 +27030,7 @@
         <v>2</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
     </row>
     <row r="4" ht="38" customHeight="1" spans="1:4">
@@ -27645,7 +27044,7 @@
         <v>3</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
     </row>
     <row r="5" ht="38" customHeight="1" spans="1:4">
@@ -27659,7 +27058,7 @@
         <v>4</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
     </row>
     <row r="6" ht="38" customHeight="1" spans="1:4">
@@ -27673,7 +27072,7 @@
         <v>5</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
     </row>
     <row r="7" ht="38" customHeight="1" spans="1:4">
@@ -27681,13 +27080,13 @@
         <v>1</v>
       </c>
       <c r="B7" s="22" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="C7" s="23">
         <v>6</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
     </row>
     <row r="8" ht="38" customHeight="1" spans="1:4">
@@ -27701,7 +27100,7 @@
         <v>7</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
     </row>
     <row r="9" ht="38" customHeight="1" spans="1:4">
@@ -27709,18 +27108,18 @@
         <v>1</v>
       </c>
       <c r="B9" s="22" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="C9" s="23">
         <v>8</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
     </row>
     <row r="10" ht="38" customHeight="1" spans="1:4">
       <c r="A10" s="20" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="B10" s="20" t="s">
         <v>98</v>
@@ -27729,12 +27128,12 @@
         <v>1</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
     </row>
     <row r="11" ht="38" customHeight="1" spans="1:4">
       <c r="A11" s="22" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="B11" s="22" t="s">
         <v>99</v>
@@ -27743,12 +27142,12 @@
         <v>2</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
     </row>
     <row r="12" ht="38" customHeight="1" spans="1:4">
       <c r="A12" s="20" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="B12" s="20" t="s">
         <v>100</v>
@@ -27757,12 +27156,12 @@
         <v>3</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
     </row>
     <row r="13" ht="38" customHeight="1" spans="1:4">
       <c r="A13" s="22" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="B13" s="22" t="s">
         <v>101</v>
@@ -27771,12 +27170,12 @@
         <v>4</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
     </row>
     <row r="14" ht="38" customHeight="1" spans="1:4">
       <c r="A14" s="20" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="B14" s="20" t="s">
         <v>102</v>
@@ -27785,12 +27184,12 @@
         <v>5</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
     </row>
     <row r="15" ht="38" customHeight="1" spans="1:4">
       <c r="A15" s="22" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="B15" s="22" t="s">
         <v>103</v>
@@ -27799,40 +27198,40 @@
         <v>6</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
     </row>
     <row r="16" ht="38" customHeight="1" spans="1:4">
       <c r="A16" s="20" t="s">
-        <v>109</v>
+        <v>321</v>
       </c>
       <c r="B16" s="20" t="s">
-        <v>122</v>
+        <v>322</v>
       </c>
       <c r="C16" s="21">
         <v>1</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="17" ht="38" customHeight="1" spans="1:4">
       <c r="A17" s="22" t="s">
-        <v>109</v>
+        <v>321</v>
       </c>
       <c r="B17" s="22" t="s">
-        <v>116</v>
+        <v>324</v>
       </c>
       <c r="C17" s="23">
         <v>2</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="18" ht="38" customHeight="1" spans="1:4">
       <c r="A18" s="20" t="s">
-        <v>109</v>
+        <v>321</v>
       </c>
       <c r="B18" s="20" t="s">
         <v>325</v>
@@ -27841,12 +27240,12 @@
         <v>3</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="19" ht="38" customHeight="1" spans="1:4">
       <c r="A19" s="22" t="s">
-        <v>109</v>
+        <v>321</v>
       </c>
       <c r="B19" s="22" t="s">
         <v>326</v>
@@ -27855,7 +27254,7 @@
         <v>4</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="20" ht="38" customHeight="1" spans="1:4">
@@ -27863,7 +27262,7 @@
         <v>104</v>
       </c>
       <c r="B20" s="20" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C20" s="21">
         <v>1</v>
@@ -27930,10 +27329,10 @@
     </row>
     <row r="25" ht="38" customHeight="1" spans="1:4">
       <c r="A25" s="22" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="B25" s="22" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="C25" s="23">
         <v>1</v>
@@ -27944,10 +27343,10 @@
     </row>
     <row r="26" ht="38" customHeight="1" spans="1:4">
       <c r="A26" s="20" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="B26" s="20" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="C26" s="21">
         <v>2</v>
@@ -27958,10 +27357,10 @@
     </row>
     <row r="27" ht="38" customHeight="1" spans="1:4">
       <c r="A27" s="22" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="B27" s="22" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="C27" s="23">
         <v>3</v>
@@ -27972,10 +27371,10 @@
     </row>
     <row r="28" ht="38" customHeight="1" spans="1:4">
       <c r="A28" s="20" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="B28" s="20" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="C28" s="21">
         <v>4</v>
@@ -27986,7 +27385,7 @@
     </row>
     <row r="29" ht="38" customHeight="1" spans="1:4">
       <c r="A29" s="22" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="B29" s="22" t="s">
         <v>340</v>
@@ -28000,7 +27399,7 @@
     </row>
     <row r="30" ht="38" customHeight="1" spans="1:4">
       <c r="A30" s="20" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="B30" s="20" t="s">
         <v>342</v>
@@ -28014,7 +27413,7 @@
     </row>
     <row r="31" ht="38" customHeight="1" spans="1:4">
       <c r="A31" s="22" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="B31" s="22" t="s">
         <v>344</v>
@@ -28045,7 +27444,7 @@
         <v>346</v>
       </c>
       <c r="B33" s="22" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="C33" s="23">
         <v>2</v>
@@ -29457,13 +28856,13 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:A33">
-    <cfRule type="containsText" dxfId="2" priority="1" operator="between" text="语种">
+    <cfRule type="containsText" dxfId="0" priority="1" operator="between" text="语种">
       <formula>NOT(ISERROR(SEARCH("语种",A2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="3" priority="2" operator="between" text="更新类型">
+    <cfRule type="containsText" dxfId="1" priority="2" operator="between" text="更新类型">
       <formula>NOT(ISERROR(SEARCH("更新类型",A2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="4" priority="3" operator="between" text="文案类型">
+    <cfRule type="containsText" dxfId="2" priority="3" operator="between" text="文案类型">
       <formula>NOT(ISERROR(SEARCH("文案类型",A2)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -29697,18 +29096,18 @@
         <v>397</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="22" ht="42" customHeight="1" spans="1:6">
       <c r="A22" s="9" t="s">
-        <v>109</v>
+        <v>321</v>
       </c>
       <c r="B22" s="9" t="s">
         <v>398</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>116</v>
+        <v>324</v>
       </c>
     </row>
     <row r="23" ht="42" customHeight="1" spans="1:6">
@@ -29724,7 +29123,7 @@
     </row>
     <row r="24" ht="42" customHeight="1" spans="1:6">
       <c r="A24" s="9" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B24" s="9" t="s">
         <v>401</v>

--- a/小语种考试营销雷达_数据模板_V2.xlsx
+++ b/小语种考试营销雷达_数据模板_V2.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="871" uniqueCount="407">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="871" uniqueCount="408">
   <si>
     <t>考试iD</t>
   </si>
@@ -353,547 +353,550 @@
     <t>考试日期</t>
   </si>
   <si>
+    <t>预计出分</t>
+  </si>
+  <si>
+    <t>信息更新时间</t>
+  </si>
+  <si>
+    <t>更新类型</t>
+  </si>
+  <si>
+    <t>更新说明</t>
+  </si>
+  <si>
+    <t>官方来源URL</t>
+  </si>
+  <si>
+    <t>适用地区/考点</t>
+  </si>
+  <si>
+    <t>备注</t>
+  </si>
+  <si>
+    <t>数据版本</t>
+  </si>
+  <si>
+    <t>JP-JLPT-2026-07</t>
+  </si>
+  <si>
+    <t>2026年7月场</t>
+  </si>
+  <si>
+    <t>首次录入</t>
+  </si>
+  <si>
+    <t>中国大陆</t>
+  </si>
+  <si>
+    <t>考试日期已确认；成绩查询日以官方后续通知为准。</t>
+  </si>
+  <si>
+    <t>2026.08.13</t>
+  </si>
+  <si>
+    <t>JP-JLPT-2026-12</t>
+  </si>
+  <si>
+    <t>2026年12月场</t>
+  </si>
+  <si>
+    <t>https://www.jlpt.jp/sp/cn/index.html</t>
+  </si>
+  <si>
+    <t>考试日期已确认；截至2026-08-13，中国大陆报名及出分日期尚未发布。</t>
+  </si>
+  <si>
+    <t>KR-TOPIK-2026-04</t>
+  </si>
+  <si>
+    <t>第105届｜2026年4月中国大陆场</t>
+  </si>
+  <si>
+    <t>https://news.neea.cn/TOPIK/1/47EAF4B953C86421E0630632C80A9937.htm</t>
+  </si>
+  <si>
+    <t>TOPIK I、TOPIK II同日分时段考试。</t>
+  </si>
+  <si>
+    <t>KR-TOPIK-2026-10</t>
+  </si>
+  <si>
+    <t>第108届｜2026年10月中国大陆场</t>
+  </si>
+  <si>
+    <t>https://news.neea.cn/TOPIK/1/47EAF4B953C86421E0630632C80A9938.html</t>
+  </si>
+  <si>
+    <t>DE-TESTDAF-2026-03</t>
+  </si>
+  <si>
+    <t>2026年3月中国大陆场</t>
+  </si>
+  <si>
+    <t>https://news.neea.cn/TESTDAF/1/19A11C5BFAD24500B18387181CB00657.htm</t>
+  </si>
+  <si>
+    <t>纸笔考试；预计考后约6周出分。</t>
+  </si>
+  <si>
+    <t>DE-TESTDAF-2026-07</t>
+  </si>
+  <si>
+    <t>2026年7月中国大陆场</t>
+  </si>
+  <si>
+    <t>纸笔考试；具体出分日期以官方通知为准。</t>
+  </si>
+  <si>
+    <t>DE-TESTDAF-2026-11</t>
+  </si>
+  <si>
+    <t>2026年11月中国大陆场</t>
+  </si>
+  <si>
+    <t>考试日期按2026中国大陆年度安排录入；截至2026-08-13报名通知尚待NEEA发布。</t>
+  </si>
+  <si>
+    <t>DE-GOETHE-2026-08</t>
+  </si>
+  <si>
+    <t>2026年8月北京场（多级别）</t>
+  </si>
+  <si>
+    <t>https://www.goethe.de/ins/cn/de/spr/prf/anm.html</t>
+  </si>
+  <si>
+    <t>北京歌德学院</t>
+  </si>
+  <si>
+    <t>8月各级别日期不同：B2 8月7/28日、A2青少年8月13日、C1 8月14日、B1 8月19/20日；考试日期字段填最早日期。</t>
+  </si>
+  <si>
+    <t>JP-JLCT-2026-01</t>
+  </si>
+  <si>
+    <t>2026年1月场</t>
+  </si>
+  <si>
+    <t>JP-JLCT-2026-03</t>
+  </si>
+  <si>
+    <t>2026年3月场</t>
+  </si>
+  <si>
+    <t>JP-JLCT-2026-05</t>
+  </si>
+  <si>
+    <t>2026年5月场</t>
+  </si>
+  <si>
+    <t>JP-JLCT-2026-06</t>
+  </si>
+  <si>
+    <t>2026年6月场</t>
+  </si>
+  <si>
+    <t>JP-JLCT-2026-07</t>
+  </si>
+  <si>
+    <t>JP-JLCT-2026-08</t>
+  </si>
+  <si>
+    <t>2026年8月场</t>
+  </si>
+  <si>
+    <t>JP-JLCT-2026-09</t>
+  </si>
+  <si>
+    <t>2026年9月场</t>
+  </si>
+  <si>
+    <t>JP-JLCT-2026-10</t>
+  </si>
+  <si>
+    <t>2026年10月场</t>
+  </si>
+  <si>
+    <t>JP-JLCT-2026-11</t>
+  </si>
+  <si>
+    <t>2026年11月场</t>
+  </si>
+  <si>
+    <t>JP-JLCT-2026-12</t>
+  </si>
+  <si>
+    <t>FR-TCFTEF-2026-09</t>
+  </si>
+  <si>
+    <t>2026年9月考点场次</t>
+  </si>
+  <si>
+    <t>https://www.france-education-international.fr/test/tcf-tout-public</t>
+  </si>
+  <si>
+    <t>中国授权考点</t>
+  </si>
+  <si>
+    <t>SP-DELE-2026-02</t>
+  </si>
+  <si>
+    <t>2026年2月场</t>
+  </si>
+  <si>
+    <t>全球；中国考点以实际开放为准</t>
+  </si>
+  <si>
+    <t>不同地区/考点开放级别可能不同。</t>
+  </si>
+  <si>
+    <t>SP-DELE-2026-04</t>
+  </si>
+  <si>
+    <t>2026年4月场（仅西班牙）</t>
+  </si>
+  <si>
+    <t>SP-DELE-2026-05</t>
+  </si>
+  <si>
+    <t>5月22日为青少年场，5月23日为普通场；日期字段填首日。</t>
+  </si>
+  <si>
+    <t>SP-DELE-2026-10</t>
+  </si>
+  <si>
+    <t>10月16-17日按级别分场；日期字段填首日。</t>
+  </si>
+  <si>
+    <t>SP-DELE-2026-11</t>
+  </si>
+  <si>
+    <t>11月13-14日按级别分场；日期字段填首日。</t>
+  </si>
+  <si>
+    <t>IT-CILS-2026-02</t>
+  </si>
+  <si>
+    <t>2026年2月19日场</t>
+  </si>
+  <si>
+    <t>全球授权考点；中国考点以实际开放为准</t>
+  </si>
+  <si>
+    <t>不同级别并非每场均开放；请结合官方级别表及考点通知确认。</t>
+  </si>
+  <si>
+    <t>IT-CILS-2026-04</t>
+  </si>
+  <si>
+    <t>2026年4月14日场</t>
+  </si>
+  <si>
+    <t>IT-CILS-2026-06</t>
+  </si>
+  <si>
+    <t>2026年6月16日场</t>
+  </si>
+  <si>
+    <t>IT-CILS-2026-07</t>
+  </si>
+  <si>
+    <t>2026年7月22日场</t>
+  </si>
+  <si>
+    <t>IT-CILS-2026-10</t>
+  </si>
+  <si>
+    <t>2026年10月21日场</t>
+  </si>
+  <si>
+    <t>IT-CILS-2026-12</t>
+  </si>
+  <si>
+    <t>2026年12月3日场</t>
+  </si>
+  <si>
+    <t>DE-TESTDAF-2027-03</t>
+  </si>
+  <si>
+    <t>2027年3月中国大陆场</t>
+  </si>
+  <si>
+    <t>新增2027年3月中国大陆纸笔德福考试场次、报名时间及出分日期。</t>
+  </si>
+  <si>
+    <t>https://www.gast.de/portal/center-search/center-search/exams/china</t>
+  </si>
+  <si>
+    <t>考试编号C069；报名通过中国教育考试院德福报名网站进行。</t>
+  </si>
+  <si>
+    <t>DE-TESTDAF-2027-07</t>
+  </si>
+  <si>
+    <t>2027年7月中国大陆场</t>
+  </si>
+  <si>
+    <t>新增2027年7月中国大陆纸笔德福考试场次、报名时间及出分日期。</t>
+  </si>
+  <si>
+    <t>考试编号C070；报名通过中国教育考试院德福报名网站进行。</t>
+  </si>
+  <si>
+    <t>DE-TESTDAF-2027-11</t>
+  </si>
+  <si>
+    <t>2027年11月中国大陆场</t>
+  </si>
+  <si>
+    <t>新增2027年11月中国大陆纸笔德福考试场次、报名时间及出分日期。</t>
+  </si>
+  <si>
+    <t>考试编号C071；报名通过中国教育考试院德福报名网站进行。</t>
+  </si>
+  <si>
+    <t>内容ID</t>
+  </si>
+  <si>
+    <t>适用节点</t>
+  </si>
+  <si>
+    <t>起始天数</t>
+  </si>
+  <si>
+    <t>结束天数</t>
+  </si>
+  <si>
+    <t>内容类型</t>
+  </si>
+  <si>
+    <t>标题</t>
+  </si>
+  <si>
+    <t>知识点/谈资</t>
+  </si>
+  <si>
+    <t>邀约话术</t>
+  </si>
+  <si>
+    <t>适用人群</t>
+  </si>
+  <si>
+    <t>来源/备注</t>
+  </si>
+  <si>
+    <t>优先级</t>
+  </si>
+  <si>
+    <t>INV-DE-TD-001</t>
+  </si>
+  <si>
+    <t>德福</t>
+  </si>
+  <si>
+    <t>语法易错点</t>
+  </si>
+  <si>
+    <t>德福写作：weil 和 deshalb 别混用</t>
+  </si>
+  <si>
+    <t>weil 引导从句，变位动词放句末；deshalb 是副词，后面仍然是主句语序。写作时可用“原因句 + deshalb 结果句”增强逻辑，但不要写成 weil + 主句语序。</t>
+  </si>
+  <si>
+    <t>最近在准备德福吗？很多同学写作会把 weil 和 deshalb 的语序混在一起。我们整理了一页高频易错点，方便的话可以发你，也可以一起看看你现在最需要补哪一块。</t>
+  </si>
+  <si>
+    <t>德福备考、写作薄弱或准备冲刺的学员</t>
+  </si>
+  <si>
+    <t>示例内容，请维护人员结合课程教研资料核对后使用</t>
+  </si>
+  <si>
+    <t>INV-JP-JLPT-001</t>
+  </si>
+  <si>
+    <t>报名谈资</t>
+  </si>
+  <si>
+    <t>JLPT 报名后，先确定每天的有效学习量</t>
+  </si>
+  <si>
+    <t>报名完成只是起点。建议先用一次模考确认词汇、语法、阅读和听力的失分结构，再把每天学习任务拆成“输入、练习、复盘”三段。</t>
+  </si>
+  <si>
+    <t>JLPT 已经进入报名节点啦。你目前准备报哪个级别？如果还不确定，我可以发你一份级别判断和备考节奏表，帮你把接下来的时间安排清楚。</t>
+  </si>
+  <si>
+    <t>准备报名 JLPT、级别尚未确认的学员</t>
+  </si>
+  <si>
+    <t>示例内容</t>
+  </si>
+  <si>
+    <t>INV-KR-TOPIK-001</t>
+  </si>
+  <si>
+    <t>考试谈资</t>
+  </si>
+  <si>
+    <t>TOPIK 写作并不是词汇越难越好</t>
+  </si>
+  <si>
+    <t>TOPIK 写作更看重任务完成度、逻辑连接和表达准确性。先保证句子结构正确，再逐步加入中高级词汇，比堆砌生词更稳。</t>
+  </si>
+  <si>
+    <t>TOPIK 报名快截止了，你这次准备冲哪个等级？如果写作还没形成稳定框架，我可以把常见题型和备考重点发你参考。</t>
+  </si>
+  <si>
+    <t>TOPIK II 备考或写作薄弱学员</t>
+  </si>
+  <si>
+    <t>INV-FR-001</t>
+  </si>
+  <si>
+    <t>日常</t>
+  </si>
+  <si>
+    <t>知识点</t>
+  </si>
+  <si>
+    <t>法语听力先抓连接词，判断信息走向</t>
+  </si>
+  <si>
+    <t>听到 mais、pourtant、donc、en revanche 等连接词时，要特别注意前后观点的转折或结论，它们常常直接影响正确答案。</t>
+  </si>
+  <si>
+    <t>最近练法语听力时，有没有出现“单词都听到了，但答案还是选错”的情况？可以先从连接词和信息走向入手，我这里有一份听力抓重点的方法清单。</t>
+  </si>
+  <si>
+    <t>法语听力基础薄弱学员</t>
+  </si>
+  <si>
+    <t>规则ID</t>
+  </si>
+  <si>
+    <t>节点类型</t>
+  </si>
+  <si>
+    <t>营销阶段</t>
+  </si>
+  <si>
+    <t>雷达等级</t>
+  </si>
+  <si>
+    <t>本月是否重点</t>
+  </si>
+  <si>
+    <t>顾问建议动作</t>
+  </si>
+  <si>
+    <t>生成企微提醒</t>
+  </si>
+  <si>
+    <t>生成朋友圈</t>
+  </si>
+  <si>
+    <t>R01</t>
+  </si>
+  <si>
+    <t>强提醒期</t>
+  </si>
+  <si>
+    <t>🔴</t>
+  </si>
+  <si>
+    <t>盘点系统目标学员；提醒提前准备注册资料；朋友圈预告</t>
+  </si>
+  <si>
+    <t>R02</t>
+  </si>
+  <si>
+    <t>今日节点</t>
+  </si>
+  <si>
+    <t>🚨</t>
+  </si>
+  <si>
+    <t>当天提醒注册；触达重点意向客户；提醒在读学员</t>
+  </si>
+  <si>
+    <t>R03</t>
+  </si>
+  <si>
+    <t>重点跟进</t>
+  </si>
+  <si>
+    <t>🟡</t>
+  </si>
+  <si>
+    <t>筛选意向客户；学习规划切入；朋友圈预热</t>
+  </si>
+  <si>
+    <t>R04</t>
+  </si>
+  <si>
+    <t>强跟进期</t>
+  </si>
+  <si>
+    <t>重点客户私聊；群内提醒；朋友圈倒计时</t>
+  </si>
+  <si>
+    <t>R05</t>
+  </si>
+  <si>
+    <t>当天报名提醒；重点客户触达；确认报名准备</t>
+  </si>
+  <si>
+    <t>R06</t>
+  </si>
+  <si>
+    <t>截止倒计时</t>
+  </si>
+  <si>
+    <t>排查未报名学员；私聊提醒；朋友圈截止提醒</t>
+  </si>
+  <si>
+    <t>R07</t>
+  </si>
+  <si>
+    <t>最后报名提醒；逐一确认重点学员</t>
+  </si>
+  <si>
+    <t>R08</t>
+  </si>
+  <si>
+    <t>考前期</t>
+  </si>
+  <si>
+    <t>🔵</t>
+  </si>
+  <si>
+    <t>考前关怀；备考资料；铺垫考后规划</t>
+  </si>
+  <si>
+    <t>R09</t>
+  </si>
+  <si>
+    <t>考试日祝福；考后复盘预约；朋友圈考试日内容</t>
+  </si>
+  <si>
+    <t>R10</t>
+  </si>
+  <si>
+    <t>考后复盘</t>
+  </si>
+  <si>
+    <t>🟣</t>
+  </si>
+  <si>
+    <t>考后复盘；下一等级规划；续费/升阶沟通</t>
+  </si>
+  <si>
+    <t>R12</t>
+  </si>
+  <si>
     <t>预计出分日期</t>
-  </si>
-  <si>
-    <t>信息更新时间</t>
-  </si>
-  <si>
-    <t>更新类型</t>
-  </si>
-  <si>
-    <t>更新说明</t>
-  </si>
-  <si>
-    <t>官方来源URL</t>
-  </si>
-  <si>
-    <t>适用地区/考点</t>
-  </si>
-  <si>
-    <t>备注</t>
-  </si>
-  <si>
-    <t>数据版本</t>
-  </si>
-  <si>
-    <t>JP-JLPT-2026-07</t>
-  </si>
-  <si>
-    <t>2026年7月场</t>
-  </si>
-  <si>
-    <t>首次录入</t>
-  </si>
-  <si>
-    <t>中国大陆</t>
-  </si>
-  <si>
-    <t>考试日期已确认；成绩查询日以官方后续通知为准。</t>
-  </si>
-  <si>
-    <t>2026.08.13</t>
-  </si>
-  <si>
-    <t>JP-JLPT-2026-12</t>
-  </si>
-  <si>
-    <t>2026年12月场</t>
-  </si>
-  <si>
-    <t>https://www.jlpt.jp/sp/cn/index.html</t>
-  </si>
-  <si>
-    <t>考试日期已确认；截至2026-08-13，中国大陆报名及出分日期尚未发布。</t>
-  </si>
-  <si>
-    <t>KR-TOPIK-2026-04</t>
-  </si>
-  <si>
-    <t>第105届｜2026年4月中国大陆场</t>
-  </si>
-  <si>
-    <t>https://news.neea.cn/TOPIK/1/47EAF4B953C86421E0630632C80A9937.htm</t>
-  </si>
-  <si>
-    <t>TOPIK I、TOPIK II同日分时段考试。</t>
-  </si>
-  <si>
-    <t>KR-TOPIK-2026-10</t>
-  </si>
-  <si>
-    <t>第108届｜2026年10月中国大陆场</t>
-  </si>
-  <si>
-    <t>https://news.neea.cn/TOPIK/1/47EAF4B953C86421E0630632C80A9938.html</t>
-  </si>
-  <si>
-    <t>DE-TESTDAF-2026-03</t>
-  </si>
-  <si>
-    <t>2026年3月中国大陆场</t>
-  </si>
-  <si>
-    <t>https://news.neea.cn/TESTDAF/1/19A11C5BFAD24500B18387181CB00657.htm</t>
-  </si>
-  <si>
-    <t>纸笔考试；预计考后约6周出分。</t>
-  </si>
-  <si>
-    <t>DE-TESTDAF-2026-07</t>
-  </si>
-  <si>
-    <t>2026年7月中国大陆场</t>
-  </si>
-  <si>
-    <t>纸笔考试；具体出分日期以官方通知为准。</t>
-  </si>
-  <si>
-    <t>DE-TESTDAF-2026-11</t>
-  </si>
-  <si>
-    <t>2026年11月中国大陆场</t>
-  </si>
-  <si>
-    <t>考试日期按2026中国大陆年度安排录入；截至2026-08-13报名通知尚待NEEA发布。</t>
-  </si>
-  <si>
-    <t>DE-GOETHE-2026-08</t>
-  </si>
-  <si>
-    <t>2026年8月北京场（多级别）</t>
-  </si>
-  <si>
-    <t>https://www.goethe.de/ins/cn/de/spr/prf/anm.html</t>
-  </si>
-  <si>
-    <t>北京歌德学院</t>
-  </si>
-  <si>
-    <t>8月各级别日期不同：B2 8月7/28日、A2青少年8月13日、C1 8月14日、B1 8月19/20日；考试日期字段填最早日期。</t>
-  </si>
-  <si>
-    <t>JP-JLCT-2026-01</t>
-  </si>
-  <si>
-    <t>2026年1月场</t>
-  </si>
-  <si>
-    <t>JP-JLCT-2026-03</t>
-  </si>
-  <si>
-    <t>2026年3月场</t>
-  </si>
-  <si>
-    <t>JP-JLCT-2026-05</t>
-  </si>
-  <si>
-    <t>2026年5月场</t>
-  </si>
-  <si>
-    <t>JP-JLCT-2026-06</t>
-  </si>
-  <si>
-    <t>2026年6月场</t>
-  </si>
-  <si>
-    <t>JP-JLCT-2026-07</t>
-  </si>
-  <si>
-    <t>JP-JLCT-2026-08</t>
-  </si>
-  <si>
-    <t>2026年8月场</t>
-  </si>
-  <si>
-    <t>JP-JLCT-2026-09</t>
-  </si>
-  <si>
-    <t>2026年9月场</t>
-  </si>
-  <si>
-    <t>JP-JLCT-2026-10</t>
-  </si>
-  <si>
-    <t>2026年10月场</t>
-  </si>
-  <si>
-    <t>JP-JLCT-2026-11</t>
-  </si>
-  <si>
-    <t>2026年11月场</t>
-  </si>
-  <si>
-    <t>JP-JLCT-2026-12</t>
-  </si>
-  <si>
-    <t>FR-TCFTEF-2026-09</t>
-  </si>
-  <si>
-    <t>2026年9月考点场次</t>
-  </si>
-  <si>
-    <t>https://www.france-education-international.fr/test/tcf-tout-public</t>
-  </si>
-  <si>
-    <t>中国授权考点</t>
-  </si>
-  <si>
-    <t>SP-DELE-2026-02</t>
-  </si>
-  <si>
-    <t>2026年2月场</t>
-  </si>
-  <si>
-    <t>全球；中国考点以实际开放为准</t>
-  </si>
-  <si>
-    <t>不同地区/考点开放级别可能不同。</t>
-  </si>
-  <si>
-    <t>SP-DELE-2026-04</t>
-  </si>
-  <si>
-    <t>2026年4月场（仅西班牙）</t>
-  </si>
-  <si>
-    <t>SP-DELE-2026-05</t>
-  </si>
-  <si>
-    <t>5月22日为青少年场，5月23日为普通场；日期字段填首日。</t>
-  </si>
-  <si>
-    <t>SP-DELE-2026-10</t>
-  </si>
-  <si>
-    <t>10月16-17日按级别分场；日期字段填首日。</t>
-  </si>
-  <si>
-    <t>SP-DELE-2026-11</t>
-  </si>
-  <si>
-    <t>11月13-14日按级别分场；日期字段填首日。</t>
-  </si>
-  <si>
-    <t>IT-CILS-2026-02</t>
-  </si>
-  <si>
-    <t>2026年2月19日场</t>
-  </si>
-  <si>
-    <t>全球授权考点；中国考点以实际开放为准</t>
-  </si>
-  <si>
-    <t>不同级别并非每场均开放；请结合官方级别表及考点通知确认。</t>
-  </si>
-  <si>
-    <t>IT-CILS-2026-04</t>
-  </si>
-  <si>
-    <t>2026年4月14日场</t>
-  </si>
-  <si>
-    <t>IT-CILS-2026-06</t>
-  </si>
-  <si>
-    <t>2026年6月16日场</t>
-  </si>
-  <si>
-    <t>IT-CILS-2026-07</t>
-  </si>
-  <si>
-    <t>2026年7月22日场</t>
-  </si>
-  <si>
-    <t>IT-CILS-2026-10</t>
-  </si>
-  <si>
-    <t>2026年10月21日场</t>
-  </si>
-  <si>
-    <t>IT-CILS-2026-12</t>
-  </si>
-  <si>
-    <t>2026年12月3日场</t>
-  </si>
-  <si>
-    <t>DE-TESTDAF-2027-03</t>
-  </si>
-  <si>
-    <t>2027年3月中国大陆场</t>
-  </si>
-  <si>
-    <t>新增2027年3月中国大陆纸笔德福考试场次、报名时间及出分日期。</t>
-  </si>
-  <si>
-    <t>https://www.gast.de/portal/center-search/center-search/exams/china</t>
-  </si>
-  <si>
-    <t>考试编号C069；报名通过中国教育考试院德福报名网站进行。</t>
-  </si>
-  <si>
-    <t>DE-TESTDAF-2027-07</t>
-  </si>
-  <si>
-    <t>2027年7月中国大陆场</t>
-  </si>
-  <si>
-    <t>新增2027年7月中国大陆纸笔德福考试场次、报名时间及出分日期。</t>
-  </si>
-  <si>
-    <t>考试编号C070；报名通过中国教育考试院德福报名网站进行。</t>
-  </si>
-  <si>
-    <t>DE-TESTDAF-2027-11</t>
-  </si>
-  <si>
-    <t>2027年11月中国大陆场</t>
-  </si>
-  <si>
-    <t>新增2027年11月中国大陆纸笔德福考试场次、报名时间及出分日期。</t>
-  </si>
-  <si>
-    <t>考试编号C071；报名通过中国教育考试院德福报名网站进行。</t>
-  </si>
-  <si>
-    <t>内容ID</t>
-  </si>
-  <si>
-    <t>适用节点</t>
-  </si>
-  <si>
-    <t>起始天数</t>
-  </si>
-  <si>
-    <t>结束天数</t>
-  </si>
-  <si>
-    <t>内容类型</t>
-  </si>
-  <si>
-    <t>标题</t>
-  </si>
-  <si>
-    <t>知识点/谈资</t>
-  </si>
-  <si>
-    <t>邀约话术</t>
-  </si>
-  <si>
-    <t>适用人群</t>
-  </si>
-  <si>
-    <t>来源/备注</t>
-  </si>
-  <si>
-    <t>优先级</t>
-  </si>
-  <si>
-    <t>INV-DE-TD-001</t>
-  </si>
-  <si>
-    <t>德福</t>
-  </si>
-  <si>
-    <t>语法易错点</t>
-  </si>
-  <si>
-    <t>德福写作：weil 和 deshalb 别混用</t>
-  </si>
-  <si>
-    <t>weil 引导从句，变位动词放句末；deshalb 是副词，后面仍然是主句语序。写作时可用“原因句 + deshalb 结果句”增强逻辑，但不要写成 weil + 主句语序。</t>
-  </si>
-  <si>
-    <t>最近在准备德福吗？很多同学写作会把 weil 和 deshalb 的语序混在一起。我们整理了一页高频易错点，方便的话可以发你，也可以一起看看你现在最需要补哪一块。</t>
-  </si>
-  <si>
-    <t>德福备考、写作薄弱或准备冲刺的学员</t>
-  </si>
-  <si>
-    <t>示例内容，请维护人员结合课程教研资料核对后使用</t>
-  </si>
-  <si>
-    <t>INV-JP-JLPT-001</t>
-  </si>
-  <si>
-    <t>报名谈资</t>
-  </si>
-  <si>
-    <t>JLPT 报名后，先确定每天的有效学习量</t>
-  </si>
-  <si>
-    <t>报名完成只是起点。建议先用一次模考确认词汇、语法、阅读和听力的失分结构，再把每天学习任务拆成“输入、练习、复盘”三段。</t>
-  </si>
-  <si>
-    <t>JLPT 已经进入报名节点啦。你目前准备报哪个级别？如果还不确定，我可以发你一份级别判断和备考节奏表，帮你把接下来的时间安排清楚。</t>
-  </si>
-  <si>
-    <t>准备报名 JLPT、级别尚未确认的学员</t>
-  </si>
-  <si>
-    <t>示例内容</t>
-  </si>
-  <si>
-    <t>INV-KR-TOPIK-001</t>
-  </si>
-  <si>
-    <t>考试谈资</t>
-  </si>
-  <si>
-    <t>TOPIK 写作并不是词汇越难越好</t>
-  </si>
-  <si>
-    <t>TOPIK 写作更看重任务完成度、逻辑连接和表达准确性。先保证句子结构正确，再逐步加入中高级词汇，比堆砌生词更稳。</t>
-  </si>
-  <si>
-    <t>TOPIK 报名快截止了，你这次准备冲哪个等级？如果写作还没形成稳定框架，我可以把常见题型和备考重点发你参考。</t>
-  </si>
-  <si>
-    <t>TOPIK II 备考或写作薄弱学员</t>
-  </si>
-  <si>
-    <t>INV-FR-001</t>
-  </si>
-  <si>
-    <t>日常</t>
-  </si>
-  <si>
-    <t>知识点</t>
-  </si>
-  <si>
-    <t>法语听力先抓连接词，判断信息走向</t>
-  </si>
-  <si>
-    <t>听到 mais、pourtant、donc、en revanche 等连接词时，要特别注意前后观点的转折或结论，它们常常直接影响正确答案。</t>
-  </si>
-  <si>
-    <t>最近练法语听力时，有没有出现“单词都听到了，但答案还是选错”的情况？可以先从连接词和信息走向入手，我这里有一份听力抓重点的方法清单。</t>
-  </si>
-  <si>
-    <t>法语听力基础薄弱学员</t>
-  </si>
-  <si>
-    <t>规则ID</t>
-  </si>
-  <si>
-    <t>节点类型</t>
-  </si>
-  <si>
-    <t>营销阶段</t>
-  </si>
-  <si>
-    <t>雷达等级</t>
-  </si>
-  <si>
-    <t>本月是否重点</t>
-  </si>
-  <si>
-    <t>顾问建议动作</t>
-  </si>
-  <si>
-    <t>生成企微提醒</t>
-  </si>
-  <si>
-    <t>生成朋友圈</t>
-  </si>
-  <si>
-    <t>R01</t>
-  </si>
-  <si>
-    <t>强提醒期</t>
-  </si>
-  <si>
-    <t>🔴</t>
-  </si>
-  <si>
-    <t>盘点系统目标学员；提醒提前准备注册资料；朋友圈预告</t>
-  </si>
-  <si>
-    <t>R02</t>
-  </si>
-  <si>
-    <t>今日节点</t>
-  </si>
-  <si>
-    <t>🚨</t>
-  </si>
-  <si>
-    <t>当天提醒注册；触达重点意向客户；提醒在读学员</t>
-  </si>
-  <si>
-    <t>R03</t>
-  </si>
-  <si>
-    <t>重点跟进</t>
-  </si>
-  <si>
-    <t>🟡</t>
-  </si>
-  <si>
-    <t>筛选意向客户；学习规划切入；朋友圈预热</t>
-  </si>
-  <si>
-    <t>R04</t>
-  </si>
-  <si>
-    <t>强跟进期</t>
-  </si>
-  <si>
-    <t>重点客户私聊；群内提醒；朋友圈倒计时</t>
-  </si>
-  <si>
-    <t>R05</t>
-  </si>
-  <si>
-    <t>当天报名提醒；重点客户触达；确认报名准备</t>
-  </si>
-  <si>
-    <t>R06</t>
-  </si>
-  <si>
-    <t>截止倒计时</t>
-  </si>
-  <si>
-    <t>排查未报名学员；私聊提醒；朋友圈截止提醒</t>
-  </si>
-  <si>
-    <t>R07</t>
-  </si>
-  <si>
-    <t>最后报名提醒；逐一确认重点学员</t>
-  </si>
-  <si>
-    <t>R08</t>
-  </si>
-  <si>
-    <t>考前期</t>
-  </si>
-  <si>
-    <t>🔵</t>
-  </si>
-  <si>
-    <t>考前关怀；备考资料；铺垫考后规划</t>
-  </si>
-  <si>
-    <t>R09</t>
-  </si>
-  <si>
-    <t>考试日祝福；考后复盘预约；朋友圈考试日内容</t>
-  </si>
-  <si>
-    <t>R10</t>
-  </si>
-  <si>
-    <t>考后复盘</t>
-  </si>
-  <si>
-    <t>🟣</t>
-  </si>
-  <si>
-    <t>考后复盘；下一等级规划；续费/升阶沟通</t>
-  </si>
-  <si>
-    <t>R12</t>
   </si>
   <si>
     <t>出分提醒；成绩收集；晒分；下一阶段规划</t>
@@ -18322,7 +18325,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6359eedc-8c18-4575-897f-8bcc74696ae4}</x14:id>
+          <x14:id>{345e20d7-4d67-4c62-bb74-765b1e39c3ba}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -18358,7 +18361,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{6359eedc-8c18-4575-897f-8bcc74696ae4}">
+          <x14:cfRule type="dataBar" id="{345e20d7-4d67-4c62-bb74-765b1e39c3ba}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -18780,7 +18783,7 @@
         <v>282</v>
       </c>
       <c r="B12" s="22" t="s">
-        <v>102</v>
+        <v>283</v>
       </c>
       <c r="C12" s="22">
         <v>0</v>
@@ -18798,7 +18801,7 @@
         <v>23</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="I12" s="23" t="s">
         <v>23</v>
@@ -18812,7 +18815,7 @@
     </row>
     <row r="13" ht="38" customHeight="1" spans="1:11">
       <c r="A13" s="20" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B13" s="20" t="s">
         <v>103</v>
@@ -18824,22 +18827,22 @@
         <v>0</v>
       </c>
       <c r="E13" s="20" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F13" s="21" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="G13" s="21" t="s">
         <v>23</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="I13" s="21" t="s">
         <v>23</v>
       </c>
       <c r="J13" s="21" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="K13" s="21">
         <v>98</v>
@@ -22743,7 +22746,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8792fdc1-ee6b-4432-8b2e-1091746fec44}</x14:id>
+          <x14:id>{0836b5b2-f59b-4d50-8466-8295b3437a2a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22770,7 +22773,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{8792fdc1-ee6b-4432-8b2e-1091746fec44}">
+          <x14:cfRule type="dataBar" id="{0836b5b2-f59b-4d50-8466-8295b3437a2a}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -22801,7 +22804,7 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:6">
       <c r="A1" s="19" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B1" s="19" t="s">
         <v>204</v>
@@ -22810,10 +22813,10 @@
         <v>244</v>
       </c>
       <c r="D1" s="19" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E1" s="19" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F1" s="19" t="s">
         <v>11</v>
@@ -22821,19 +22824,19 @@
     </row>
     <row r="2" ht="100" customHeight="1" spans="1:6">
       <c r="A2" s="20" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B2" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C2" s="20" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F2" s="20" t="s">
         <v>23</v>
@@ -22841,19 +22844,19 @@
     </row>
     <row r="3" ht="100" customHeight="1" spans="1:6">
       <c r="A3" s="22" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B3" s="22" t="s">
         <v>103</v>
       </c>
       <c r="C3" s="22" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F3" s="22" t="s">
         <v>23</v>
@@ -24877,7 +24880,7 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:7">
       <c r="A1" s="19" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B1" s="19" t="s">
         <v>204</v>
@@ -24886,13 +24889,13 @@
         <v>244</v>
       </c>
       <c r="D1" s="19" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E1" s="19" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F1" s="19" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="G1" s="19" t="s">
         <v>11</v>
@@ -24900,7 +24903,7 @@
     </row>
     <row r="2" ht="50" customHeight="1" spans="1:7">
       <c r="A2" s="20" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B2" s="20" t="s">
         <v>99</v>
@@ -24909,10 +24912,10 @@
         <v>255</v>
       </c>
       <c r="D2" s="20" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F2" s="25"/>
       <c r="G2" s="20" t="s">
@@ -24921,7 +24924,7 @@
     </row>
     <row r="3" ht="50" customHeight="1" spans="1:7">
       <c r="A3" s="22" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B3" s="22" t="s">
         <v>99</v>
@@ -24930,10 +24933,10 @@
         <v>255</v>
       </c>
       <c r="D3" s="22" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F3" s="25"/>
       <c r="G3" s="22" t="s">
@@ -24942,7 +24945,7 @@
     </row>
     <row r="4" ht="50" customHeight="1" spans="1:7">
       <c r="A4" s="20" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B4" s="20" t="s">
         <v>99</v>
@@ -24951,10 +24954,10 @@
         <v>255</v>
       </c>
       <c r="D4" s="20" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F4" s="25"/>
       <c r="G4" s="20" t="s">
@@ -24963,19 +24966,19 @@
     </row>
     <row r="5" ht="50" customHeight="1" spans="1:7">
       <c r="A5" s="22" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B5" s="22" t="s">
-        <v>102</v>
+        <v>283</v>
       </c>
       <c r="C5" s="22" t="s">
         <v>255</v>
       </c>
       <c r="D5" s="22" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="F5" s="25"/>
       <c r="G5" s="22" t="s">
@@ -26993,16 +26996,16 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:4">
       <c r="A1" s="19" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B1" s="19" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C1" s="19" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D1" s="19" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="2" ht="38" customHeight="1" spans="1:4">
@@ -27016,7 +27019,7 @@
         <v>1</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="3" ht="38" customHeight="1" spans="1:4">
@@ -27030,7 +27033,7 @@
         <v>2</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="4" ht="38" customHeight="1" spans="1:4">
@@ -27044,7 +27047,7 @@
         <v>3</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="5" ht="38" customHeight="1" spans="1:4">
@@ -27058,7 +27061,7 @@
         <v>4</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="6" ht="38" customHeight="1" spans="1:4">
@@ -27072,7 +27075,7 @@
         <v>5</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="7" ht="38" customHeight="1" spans="1:4">
@@ -27080,13 +27083,13 @@
         <v>1</v>
       </c>
       <c r="B7" s="22" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C7" s="23">
         <v>6</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="8" ht="38" customHeight="1" spans="1:4">
@@ -27100,7 +27103,7 @@
         <v>7</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="9" ht="38" customHeight="1" spans="1:4">
@@ -27108,13 +27111,13 @@
         <v>1</v>
       </c>
       <c r="B9" s="22" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C9" s="23">
         <v>8</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="10" ht="38" customHeight="1" spans="1:4">
@@ -27128,7 +27131,7 @@
         <v>1</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="11" ht="38" customHeight="1" spans="1:4">
@@ -27142,7 +27145,7 @@
         <v>2</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="12" ht="38" customHeight="1" spans="1:4">
@@ -27156,7 +27159,7 @@
         <v>3</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="13" ht="38" customHeight="1" spans="1:4">
@@ -27170,7 +27173,7 @@
         <v>4</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="14" ht="38" customHeight="1" spans="1:4">
@@ -27178,13 +27181,13 @@
         <v>243</v>
       </c>
       <c r="B14" s="20" t="s">
-        <v>102</v>
+        <v>283</v>
       </c>
       <c r="C14" s="21">
         <v>5</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="15" ht="38" customHeight="1" spans="1:4">
@@ -27198,63 +27201,63 @@
         <v>6</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="16" ht="38" customHeight="1" spans="1:4">
       <c r="A16" s="20" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B16" s="20" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C16" s="21">
         <v>1</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="17" ht="38" customHeight="1" spans="1:4">
       <c r="A17" s="22" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B17" s="22" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C17" s="23">
         <v>2</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="18" ht="38" customHeight="1" spans="1:4">
       <c r="A18" s="20" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B18" s="20" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C18" s="21">
         <v>3</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="19" ht="38" customHeight="1" spans="1:4">
       <c r="A19" s="22" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B19" s="22" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C19" s="23">
         <v>4</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="20" ht="38" customHeight="1" spans="1:4">
@@ -27268,7 +27271,7 @@
         <v>1</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="21" ht="38" customHeight="1" spans="1:4">
@@ -27276,13 +27279,13 @@
         <v>104</v>
       </c>
       <c r="B21" s="22" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C21" s="23">
         <v>2</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="22" ht="38" customHeight="1" spans="1:4">
@@ -27290,13 +27293,13 @@
         <v>104</v>
       </c>
       <c r="B22" s="20" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C22" s="21">
         <v>3</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="23" ht="38" customHeight="1" spans="1:4">
@@ -27304,13 +27307,13 @@
         <v>104</v>
       </c>
       <c r="B23" s="22" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C23" s="23">
         <v>4</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="24" ht="38" customHeight="1" spans="1:4">
@@ -27318,116 +27321,116 @@
         <v>104</v>
       </c>
       <c r="B24" s="20" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C24" s="21">
         <v>5</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="25" ht="38" customHeight="1" spans="1:4">
       <c r="A25" s="22" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B25" s="22" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C25" s="23">
         <v>1</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="26" ht="38" customHeight="1" spans="1:4">
       <c r="A26" s="20" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B26" s="20" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C26" s="21">
         <v>2</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="27" ht="38" customHeight="1" spans="1:4">
       <c r="A27" s="22" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B27" s="22" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C27" s="23">
         <v>3</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="28" ht="38" customHeight="1" spans="1:4">
       <c r="A28" s="20" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B28" s="20" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C28" s="21">
         <v>4</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="29" ht="38" customHeight="1" spans="1:4">
       <c r="A29" s="22" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B29" s="22" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C29" s="23">
         <v>5</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="30" ht="38" customHeight="1" spans="1:4">
       <c r="A30" s="20" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B30" s="20" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C30" s="21">
         <v>6</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="31" ht="38" customHeight="1" spans="1:4">
       <c r="A31" s="22" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B31" s="22" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C31" s="23">
         <v>7</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="32" ht="38" customHeight="1" spans="1:4">
       <c r="A32" s="20" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B32" s="20" t="s">
         <v>23</v>
@@ -27436,21 +27439,21 @@
         <v>1</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="33" ht="38" customHeight="1" spans="1:4">
       <c r="A33" s="22" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B33" s="22" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C33" s="23">
         <v>2</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -28886,7 +28889,7 @@
   <sheetData>
     <row r="1" ht="42" customHeight="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -28896,95 +28899,95 @@
     </row>
     <row r="2" ht="28" customHeight="1" spans="1:6">
       <c r="A2" s="2" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="3" ht="42" customHeight="1" spans="1:6">
       <c r="A3" s="3" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="4" ht="42" customHeight="1" spans="1:6">
       <c r="A4" s="4" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="5" ht="42" customHeight="1" spans="1:6">
       <c r="A5" s="3" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="6" ht="42" customHeight="1" spans="1:6">
       <c r="A6" s="4" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="7" ht="42" customHeight="1" spans="1:6">
       <c r="A7" s="3" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="8" ht="42" customHeight="1" spans="1:6">
       <c r="A8" s="4" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="9" ht="42" customHeight="1" spans="1:6">
       <c r="A9" s="3" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1" spans="1:6">
       <c r="A11" s="5" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="5"/>
@@ -28994,49 +28997,49 @@
     </row>
     <row r="12" ht="46" customHeight="1" spans="1:6">
       <c r="A12" s="6" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="13" ht="46" customHeight="1" spans="1:6">
       <c r="A13" s="6" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="14" ht="46" customHeight="1" spans="1:6">
       <c r="A14" s="6" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1" spans="1:6">
       <c r="A16" s="5" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="5"/>
@@ -29046,21 +29049,21 @@
     </row>
     <row r="17" ht="28" customHeight="1" spans="1:6">
       <c r="A17" s="2" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="18" ht="42" customHeight="1" spans="1:6">
       <c r="A18" s="9" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C18" s="9" t="s">
         <v>12</v>
@@ -29068,13 +29071,13 @@
     </row>
     <row r="19" ht="42" customHeight="1" spans="1:6">
       <c r="A19" s="7" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="20" ht="42" customHeight="1" spans="1:6">
@@ -29082,10 +29085,10 @@
         <v>103</v>
       </c>
       <c r="B20" s="9" t="s">
+        <v>397</v>
+      </c>
+      <c r="C20" s="9" t="s">
         <v>396</v>
-      </c>
-      <c r="C20" s="9" t="s">
-        <v>395</v>
       </c>
     </row>
     <row r="21" ht="42" customHeight="1" spans="1:6">
@@ -29093,7 +29096,7 @@
         <v>104</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C21" s="7" t="s">
         <v>112</v>
@@ -29101,13 +29104,13 @@
     </row>
     <row r="22" ht="42" customHeight="1" spans="1:6">
       <c r="A22" s="9" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="23" ht="42" customHeight="1" spans="1:6">
@@ -29115,10 +29118,10 @@
         <v>106</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="24" ht="42" customHeight="1" spans="1:6">
@@ -29126,10 +29129,10 @@
         <v>109</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="25" ht="42" customHeight="1" spans="1:6">
@@ -29137,7 +29140,7 @@
         <v>11</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C25" s="7" t="s">
         <v>23</v>
@@ -29145,7 +29148,7 @@
     </row>
     <row r="27" ht="30" customHeight="1" spans="1:6">
       <c r="A27" s="5" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="5"/>
@@ -29155,7 +29158,7 @@
     </row>
     <row r="28" ht="40" customHeight="1" spans="1:6">
       <c r="A28" s="10" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B28" s="11"/>
       <c r="C28" s="11"/>
@@ -29173,7 +29176,7 @@
     </row>
     <row r="31" ht="34" customHeight="1" spans="1:6">
       <c r="A31" s="16" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B31" s="17"/>
       <c r="C31" s="17"/>

--- a/小语种考试营销雷达_数据模板_V2.xlsx
+++ b/小语种考试营销雷达_数据模板_V2.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12880" activeTab="1"/>
+    <workbookView windowWidth="28800" windowHeight="12880"/>
   </bookViews>
   <sheets>
     <sheet name="考试基础信息" sheetId="1" r:id="rId1"/>
@@ -18325,7 +18325,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{345e20d7-4d67-4c62-bb74-765b1e39c3ba}</x14:id>
+          <x14:id>{1034e50a-0ec0-42ad-8bfa-8f57289c3760}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -18361,7 +18361,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{345e20d7-4d67-4c62-bb74-765b1e39c3ba}">
+          <x14:cfRule type="dataBar" id="{1034e50a-0ec0-42ad-8bfa-8f57289c3760}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -22746,7 +22746,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0836b5b2-f59b-4d50-8466-8295b3437a2a}</x14:id>
+          <x14:id>{599a00b3-21d7-447f-832b-e38c9653b472}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22773,7 +22773,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{0836b5b2-f59b-4d50-8466-8295b3437a2a}">
+          <x14:cfRule type="dataBar" id="{599a00b3-21d7-447f-832b-e38c9653b472}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>

--- a/小语种考试营销雷达_数据模板_V2.xlsx
+++ b/小语种考试营销雷达_数据模板_V2.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12880"/>
+    <workbookView windowWidth="28800" windowHeight="12880" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="考试基础信息" sheetId="1" r:id="rId1"/>
@@ -8135,7 +8135,7 @@
         <v>11</v>
       </c>
       <c r="H8" s="37">
-        <v>45896</v>
+        <v>46261</v>
       </c>
       <c r="I8" s="37"/>
       <c r="J8" s="37">
@@ -18325,7 +18325,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{1034e50a-0ec0-42ad-8bfa-8f57289c3760}</x14:id>
+          <x14:id>{aafcbe9b-7f97-4d77-b204-e6e40b947c4f}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -18361,7 +18361,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{1034e50a-0ec0-42ad-8bfa-8f57289c3760}">
+          <x14:cfRule type="dataBar" id="{aafcbe9b-7f97-4d77-b204-e6e40b947c4f}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -22746,7 +22746,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{599a00b3-21d7-447f-832b-e38c9653b472}</x14:id>
+          <x14:id>{5e5e86a0-a167-4a6f-b5eb-0e5bea6a9926}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22773,7 +22773,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{599a00b3-21d7-447f-832b-e38c9653b472}">
+          <x14:cfRule type="dataBar" id="{5e5e86a0-a167-4a6f-b5eb-0e5bea6a9926}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>

--- a/小语种考试营销雷达_数据模板_V2.xlsx
+++ b/小语种考试营销雷达_数据模板_V2.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="871" uniqueCount="408">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="871" uniqueCount="407">
   <si>
     <t>考试iD</t>
   </si>
@@ -353,7 +353,7 @@
     <t>考试日期</t>
   </si>
   <si>
-    <t>预计出分</t>
+    <t>预计出分日期</t>
   </si>
   <si>
     <t>信息更新时间</t>
@@ -894,9 +894,6 @@
   </si>
   <si>
     <t>R12</t>
-  </si>
-  <si>
-    <t>预计出分日期</t>
   </si>
   <si>
     <t>出分提醒；成绩收集；晒分；下一阶段规划</t>
@@ -18325,7 +18322,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{aafcbe9b-7f97-4d77-b204-e6e40b947c4f}</x14:id>
+          <x14:id>{8724f6a5-ec31-4f5c-926f-081b460752ed}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -18361,7 +18358,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{aafcbe9b-7f97-4d77-b204-e6e40b947c4f}">
+          <x14:cfRule type="dataBar" id="{8724f6a5-ec31-4f5c-926f-081b460752ed}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -18783,7 +18780,7 @@
         <v>282</v>
       </c>
       <c r="B12" s="22" t="s">
-        <v>283</v>
+        <v>102</v>
       </c>
       <c r="C12" s="22">
         <v>0</v>
@@ -18801,7 +18798,7 @@
         <v>23</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="I12" s="23" t="s">
         <v>23</v>
@@ -18815,7 +18812,7 @@
     </row>
     <row r="13" ht="38" customHeight="1" spans="1:11">
       <c r="A13" s="20" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B13" s="20" t="s">
         <v>103</v>
@@ -18827,22 +18824,22 @@
         <v>0</v>
       </c>
       <c r="E13" s="20" t="s">
+        <v>285</v>
+      </c>
+      <c r="F13" s="21" t="s">
         <v>286</v>
-      </c>
-      <c r="F13" s="21" t="s">
-        <v>287</v>
       </c>
       <c r="G13" s="21" t="s">
         <v>23</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="I13" s="21" t="s">
         <v>23</v>
       </c>
       <c r="J13" s="21" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="K13" s="21">
         <v>98</v>
@@ -22746,7 +22743,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5e5e86a0-a167-4a6f-b5eb-0e5bea6a9926}</x14:id>
+          <x14:id>{65eb1a14-c6e3-4034-9104-bad86b920a98}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22773,7 +22770,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{5e5e86a0-a167-4a6f-b5eb-0e5bea6a9926}">
+          <x14:cfRule type="dataBar" id="{65eb1a14-c6e3-4034-9104-bad86b920a98}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -22804,7 +22801,7 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:6">
       <c r="A1" s="19" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B1" s="19" t="s">
         <v>204</v>
@@ -22813,10 +22810,10 @@
         <v>244</v>
       </c>
       <c r="D1" s="19" t="s">
+        <v>290</v>
+      </c>
+      <c r="E1" s="19" t="s">
         <v>291</v>
-      </c>
-      <c r="E1" s="19" t="s">
-        <v>292</v>
       </c>
       <c r="F1" s="19" t="s">
         <v>11</v>
@@ -22824,19 +22821,19 @@
     </row>
     <row r="2" ht="100" customHeight="1" spans="1:6">
       <c r="A2" s="20" t="s">
+        <v>292</v>
+      </c>
+      <c r="B2" s="20" t="s">
         <v>293</v>
       </c>
-      <c r="B2" s="20" t="s">
+      <c r="C2" s="20" t="s">
         <v>294</v>
       </c>
-      <c r="C2" s="20" t="s">
+      <c r="D2" s="3" t="s">
         <v>295</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="E2" s="3" t="s">
         <v>296</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>297</v>
       </c>
       <c r="F2" s="20" t="s">
         <v>23</v>
@@ -22844,19 +22841,19 @@
     </row>
     <row r="3" ht="100" customHeight="1" spans="1:6">
       <c r="A3" s="22" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B3" s="22" t="s">
         <v>103</v>
       </c>
       <c r="C3" s="22" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D3" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="E3" s="4" t="s">
         <v>299</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>300</v>
       </c>
       <c r="F3" s="22" t="s">
         <v>23</v>
@@ -24880,7 +24877,7 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:7">
       <c r="A1" s="19" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B1" s="19" t="s">
         <v>204</v>
@@ -24889,13 +24886,13 @@
         <v>244</v>
       </c>
       <c r="D1" s="19" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E1" s="19" t="s">
+        <v>290</v>
+      </c>
+      <c r="F1" s="19" t="s">
         <v>291</v>
-      </c>
-      <c r="F1" s="19" t="s">
-        <v>292</v>
       </c>
       <c r="G1" s="19" t="s">
         <v>11</v>
@@ -24903,7 +24900,7 @@
     </row>
     <row r="2" ht="50" customHeight="1" spans="1:7">
       <c r="A2" s="20" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B2" s="20" t="s">
         <v>99</v>
@@ -24912,10 +24909,10 @@
         <v>255</v>
       </c>
       <c r="D2" s="20" t="s">
+        <v>302</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>303</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>304</v>
       </c>
       <c r="F2" s="25"/>
       <c r="G2" s="20" t="s">
@@ -24924,7 +24921,7 @@
     </row>
     <row r="3" ht="50" customHeight="1" spans="1:7">
       <c r="A3" s="22" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B3" s="22" t="s">
         <v>99</v>
@@ -24933,10 +24930,10 @@
         <v>255</v>
       </c>
       <c r="D3" s="22" t="s">
+        <v>305</v>
+      </c>
+      <c r="E3" s="4" t="s">
         <v>306</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>307</v>
       </c>
       <c r="F3" s="25"/>
       <c r="G3" s="22" t="s">
@@ -24945,7 +24942,7 @@
     </row>
     <row r="4" ht="50" customHeight="1" spans="1:7">
       <c r="A4" s="20" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B4" s="20" t="s">
         <v>99</v>
@@ -24954,10 +24951,10 @@
         <v>255</v>
       </c>
       <c r="D4" s="20" t="s">
+        <v>308</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>309</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>310</v>
       </c>
       <c r="F4" s="25"/>
       <c r="G4" s="20" t="s">
@@ -24966,19 +24963,19 @@
     </row>
     <row r="5" ht="50" customHeight="1" spans="1:7">
       <c r="A5" s="22" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B5" s="22" t="s">
-        <v>283</v>
+        <v>102</v>
       </c>
       <c r="C5" s="22" t="s">
         <v>255</v>
       </c>
       <c r="D5" s="22" t="s">
+        <v>311</v>
+      </c>
+      <c r="E5" s="4" t="s">
         <v>312</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>313</v>
       </c>
       <c r="F5" s="25"/>
       <c r="G5" s="22" t="s">
@@ -26996,16 +26993,16 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:4">
       <c r="A1" s="19" t="s">
+        <v>313</v>
+      </c>
+      <c r="B1" s="19" t="s">
         <v>314</v>
       </c>
-      <c r="B1" s="19" t="s">
+      <c r="C1" s="19" t="s">
         <v>315</v>
       </c>
-      <c r="C1" s="19" t="s">
+      <c r="D1" s="19" t="s">
         <v>316</v>
-      </c>
-      <c r="D1" s="19" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="2" ht="38" customHeight="1" spans="1:4">
@@ -27019,7 +27016,7 @@
         <v>1</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="3" ht="38" customHeight="1" spans="1:4">
@@ -27033,7 +27030,7 @@
         <v>2</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="4" ht="38" customHeight="1" spans="1:4">
@@ -27047,7 +27044,7 @@
         <v>3</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="5" ht="38" customHeight="1" spans="1:4">
@@ -27061,7 +27058,7 @@
         <v>4</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="6" ht="38" customHeight="1" spans="1:4">
@@ -27075,7 +27072,7 @@
         <v>5</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="7" ht="38" customHeight="1" spans="1:4">
@@ -27083,13 +27080,13 @@
         <v>1</v>
       </c>
       <c r="B7" s="22" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C7" s="23">
         <v>6</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="8" ht="38" customHeight="1" spans="1:4">
@@ -27103,7 +27100,7 @@
         <v>7</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="9" ht="38" customHeight="1" spans="1:4">
@@ -27111,13 +27108,13 @@
         <v>1</v>
       </c>
       <c r="B9" s="22" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C9" s="23">
         <v>8</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="10" ht="38" customHeight="1" spans="1:4">
@@ -27131,7 +27128,7 @@
         <v>1</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="11" ht="38" customHeight="1" spans="1:4">
@@ -27145,7 +27142,7 @@
         <v>2</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="12" ht="38" customHeight="1" spans="1:4">
@@ -27159,7 +27156,7 @@
         <v>3</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="13" ht="38" customHeight="1" spans="1:4">
@@ -27173,7 +27170,7 @@
         <v>4</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="14" ht="38" customHeight="1" spans="1:4">
@@ -27181,13 +27178,13 @@
         <v>243</v>
       </c>
       <c r="B14" s="20" t="s">
-        <v>283</v>
+        <v>102</v>
       </c>
       <c r="C14" s="21">
         <v>5</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="15" ht="38" customHeight="1" spans="1:4">
@@ -27201,63 +27198,63 @@
         <v>6</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="16" ht="38" customHeight="1" spans="1:4">
       <c r="A16" s="20" t="s">
+        <v>321</v>
+      </c>
+      <c r="B16" s="20" t="s">
         <v>322</v>
-      </c>
-      <c r="B16" s="20" t="s">
-        <v>323</v>
       </c>
       <c r="C16" s="21">
         <v>1</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="17" ht="38" customHeight="1" spans="1:4">
       <c r="A17" s="22" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B17" s="22" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C17" s="23">
         <v>2</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="18" ht="38" customHeight="1" spans="1:4">
       <c r="A18" s="20" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B18" s="20" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C18" s="21">
         <v>3</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="19" ht="38" customHeight="1" spans="1:4">
       <c r="A19" s="22" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B19" s="22" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C19" s="23">
         <v>4</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="20" ht="38" customHeight="1" spans="1:4">
@@ -27271,7 +27268,7 @@
         <v>1</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="21" ht="38" customHeight="1" spans="1:4">
@@ -27279,13 +27276,13 @@
         <v>104</v>
       </c>
       <c r="B21" s="22" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C21" s="23">
         <v>2</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="22" ht="38" customHeight="1" spans="1:4">
@@ -27293,13 +27290,13 @@
         <v>104</v>
       </c>
       <c r="B22" s="20" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C22" s="21">
         <v>3</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="23" ht="38" customHeight="1" spans="1:4">
@@ -27307,13 +27304,13 @@
         <v>104</v>
       </c>
       <c r="B23" s="22" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C23" s="23">
         <v>4</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="24" ht="38" customHeight="1" spans="1:4">
@@ -27321,116 +27318,116 @@
         <v>104</v>
       </c>
       <c r="B24" s="20" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C24" s="21">
         <v>5</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="25" ht="38" customHeight="1" spans="1:4">
       <c r="A25" s="22" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B25" s="22" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C25" s="23">
         <v>1</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="26" ht="38" customHeight="1" spans="1:4">
       <c r="A26" s="20" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B26" s="20" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C26" s="21">
         <v>2</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="27" ht="38" customHeight="1" spans="1:4">
       <c r="A27" s="22" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B27" s="22" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C27" s="23">
         <v>3</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="28" ht="38" customHeight="1" spans="1:4">
       <c r="A28" s="20" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B28" s="20" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C28" s="21">
         <v>4</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="29" ht="38" customHeight="1" spans="1:4">
       <c r="A29" s="22" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B29" s="22" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C29" s="23">
         <v>5</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="30" ht="38" customHeight="1" spans="1:4">
       <c r="A30" s="20" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B30" s="20" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C30" s="21">
         <v>6</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="31" ht="38" customHeight="1" spans="1:4">
       <c r="A31" s="22" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B31" s="22" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C31" s="23">
         <v>7</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="32" ht="38" customHeight="1" spans="1:4">
       <c r="A32" s="20" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B32" s="20" t="s">
         <v>23</v>
@@ -27439,21 +27436,21 @@
         <v>1</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="33" ht="38" customHeight="1" spans="1:4">
       <c r="A33" s="22" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B33" s="22" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C33" s="23">
         <v>2</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -28889,7 +28886,7 @@
   <sheetData>
     <row r="1" ht="42" customHeight="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -28899,95 +28896,95 @@
     </row>
     <row r="2" ht="28" customHeight="1" spans="1:6">
       <c r="A2" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>351</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>352</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>353</v>
       </c>
     </row>
     <row r="3" ht="42" customHeight="1" spans="1:6">
       <c r="A3" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>354</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="C3" s="3" t="s">
         <v>355</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>356</v>
       </c>
     </row>
     <row r="4" ht="42" customHeight="1" spans="1:6">
       <c r="A4" s="4" t="s">
+        <v>356</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>357</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="C4" s="4" t="s">
         <v>358</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>359</v>
       </c>
     </row>
     <row r="5" ht="42" customHeight="1" spans="1:6">
       <c r="A5" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>360</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="C5" s="3" t="s">
         <v>361</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>362</v>
       </c>
     </row>
     <row r="6" ht="42" customHeight="1" spans="1:6">
       <c r="A6" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>363</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="C6" s="4" t="s">
         <v>364</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>365</v>
       </c>
     </row>
     <row r="7" ht="42" customHeight="1" spans="1:6">
       <c r="A7" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>366</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="C7" s="3" t="s">
         <v>367</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>368</v>
       </c>
     </row>
     <row r="8" ht="42" customHeight="1" spans="1:6">
       <c r="A8" s="4" t="s">
+        <v>368</v>
+      </c>
+      <c r="B8" s="4" t="s">
         <v>369</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="C8" s="4" t="s">
         <v>370</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>371</v>
       </c>
     </row>
     <row r="9" ht="42" customHeight="1" spans="1:6">
       <c r="A9" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>372</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="C9" s="3" t="s">
         <v>373</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>374</v>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1" spans="1:6">
       <c r="A11" s="5" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="5"/>
@@ -28997,49 +28994,49 @@
     </row>
     <row r="12" ht="46" customHeight="1" spans="1:6">
       <c r="A12" s="6" t="s">
+        <v>375</v>
+      </c>
+      <c r="B12" s="7" t="s">
         <v>376</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="C12" s="8" t="s">
         <v>377</v>
       </c>
-      <c r="C12" s="8" t="s">
+      <c r="D12" s="7" t="s">
         <v>378</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>379</v>
       </c>
     </row>
     <row r="13" ht="46" customHeight="1" spans="1:6">
       <c r="A13" s="6" t="s">
+        <v>379</v>
+      </c>
+      <c r="B13" s="7" t="s">
         <v>380</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="C13" s="8" t="s">
         <v>381</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="D13" s="7" t="s">
         <v>382</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>383</v>
       </c>
     </row>
     <row r="14" ht="46" customHeight="1" spans="1:6">
       <c r="A14" s="6" t="s">
+        <v>383</v>
+      </c>
+      <c r="B14" s="7" t="s">
         <v>384</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="C14" s="8" t="s">
         <v>385</v>
       </c>
-      <c r="C14" s="8" t="s">
+      <c r="D14" s="7" t="s">
         <v>386</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1" spans="1:6">
       <c r="A16" s="5" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="5"/>
@@ -29049,21 +29046,21 @@
     </row>
     <row r="17" ht="28" customHeight="1" spans="1:6">
       <c r="A17" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>389</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="C17" s="2" t="s">
         <v>390</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>391</v>
       </c>
     </row>
     <row r="18" ht="42" customHeight="1" spans="1:6">
       <c r="A18" s="9" t="s">
+        <v>391</v>
+      </c>
+      <c r="B18" s="9" t="s">
         <v>392</v>
-      </c>
-      <c r="B18" s="9" t="s">
-        <v>393</v>
       </c>
       <c r="C18" s="9" t="s">
         <v>12</v>
@@ -29071,13 +29068,13 @@
     </row>
     <row r="19" ht="42" customHeight="1" spans="1:6">
       <c r="A19" s="7" t="s">
+        <v>393</v>
+      </c>
+      <c r="B19" s="7" t="s">
         <v>394</v>
       </c>
-      <c r="B19" s="7" t="s">
+      <c r="C19" s="7" t="s">
         <v>395</v>
-      </c>
-      <c r="C19" s="7" t="s">
-        <v>396</v>
       </c>
     </row>
     <row r="20" ht="42" customHeight="1" spans="1:6">
@@ -29085,10 +29082,10 @@
         <v>103</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="21" ht="42" customHeight="1" spans="1:6">
@@ -29096,7 +29093,7 @@
         <v>104</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C21" s="7" t="s">
         <v>112</v>
@@ -29104,13 +29101,13 @@
     </row>
     <row r="22" ht="42" customHeight="1" spans="1:6">
       <c r="A22" s="9" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="23" ht="42" customHeight="1" spans="1:6">
@@ -29118,10 +29115,10 @@
         <v>106</v>
       </c>
       <c r="B23" s="7" t="s">
+        <v>399</v>
+      </c>
+      <c r="C23" s="7" t="s">
         <v>400</v>
-      </c>
-      <c r="C23" s="7" t="s">
-        <v>401</v>
       </c>
     </row>
     <row r="24" ht="42" customHeight="1" spans="1:6">
@@ -29129,10 +29126,10 @@
         <v>109</v>
       </c>
       <c r="B24" s="9" t="s">
+        <v>401</v>
+      </c>
+      <c r="C24" s="9" t="s">
         <v>402</v>
-      </c>
-      <c r="C24" s="9" t="s">
-        <v>403</v>
       </c>
     </row>
     <row r="25" ht="42" customHeight="1" spans="1:6">
@@ -29140,7 +29137,7 @@
         <v>11</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C25" s="7" t="s">
         <v>23</v>
@@ -29148,7 +29145,7 @@
     </row>
     <row r="27" ht="30" customHeight="1" spans="1:6">
       <c r="A27" s="5" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="5"/>
@@ -29158,7 +29155,7 @@
     </row>
     <row r="28" ht="40" customHeight="1" spans="1:6">
       <c r="A28" s="10" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B28" s="11"/>
       <c r="C28" s="11"/>
@@ -29176,7 +29173,7 @@
     </row>
     <row r="31" ht="34" customHeight="1" spans="1:6">
       <c r="A31" s="16" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B31" s="17"/>
       <c r="C31" s="17"/>
